--- a/Experiments/DBCV_Conclu.xlsx
+++ b/Experiments/DBCV_Conclu.xlsx
@@ -13,13 +13,15 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="254">
   <si>
     <t>Datapoints</t>
   </si>
@@ -363,9 +365,6 @@
     <t>181.386 secs</t>
   </si>
   <si>
-    <t>TEST DATASET</t>
-  </si>
-  <si>
     <t>641.189 secs</t>
   </si>
   <si>
@@ -616,6 +615,183 @@
   </si>
   <si>
     <t>54.398 secs</t>
+  </si>
+  <si>
+    <t>6.252 secs</t>
+  </si>
+  <si>
+    <t>303 clusters</t>
+  </si>
+  <si>
+    <t>0.202 secs</t>
+  </si>
+  <si>
+    <t>0.190</t>
+  </si>
+  <si>
+    <t>333.944 secs</t>
+  </si>
+  <si>
+    <t>99 outliers</t>
+  </si>
+  <si>
+    <t>-0.021</t>
+  </si>
+  <si>
+    <t>86.070 secs</t>
+  </si>
+  <si>
+    <t>6.575 secs</t>
+  </si>
+  <si>
+    <t>0.532 secs</t>
+  </si>
+  <si>
+    <t>-0.023</t>
+  </si>
+  <si>
+    <t>129.956 secs</t>
+  </si>
+  <si>
+    <t>4.989 secs</t>
+  </si>
+  <si>
+    <t>0.024 secs</t>
+  </si>
+  <si>
+    <t>9.226 secs</t>
+  </si>
+  <si>
+    <t>131.239 secs</t>
+  </si>
+  <si>
+    <t>TEST DATASET(512)</t>
+  </si>
+  <si>
+    <t>TEST DATASET(1024)</t>
+  </si>
+  <si>
+    <t>6.823 secs</t>
+  </si>
+  <si>
+    <t>0.053 secs</t>
+  </si>
+  <si>
+    <t>0.010 secs</t>
+  </si>
+  <si>
+    <t>131.956 secs</t>
+  </si>
+  <si>
+    <t>TEST DATASET(256)</t>
+  </si>
+  <si>
+    <t>5.901 secs</t>
+  </si>
+  <si>
+    <t>0.181 secs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.173 </t>
+  </si>
+  <si>
+    <t>329.048 secs</t>
+  </si>
+  <si>
+    <t>76.765 secs</t>
+  </si>
+  <si>
+    <t>0.471 secs</t>
+  </si>
+  <si>
+    <t>-0.078</t>
+  </si>
+  <si>
+    <t>136.173 secs</t>
+  </si>
+  <si>
+    <t>6.206 secs</t>
+  </si>
+  <si>
+    <t>6.106 secs</t>
+  </si>
+  <si>
+    <t>0.003</t>
+  </si>
+  <si>
+    <t>11.077 secs</t>
+  </si>
+  <si>
+    <t>133.593 secs</t>
+  </si>
+  <si>
+    <t>5.539 secs</t>
+  </si>
+  <si>
+    <t>0.031 secs</t>
+  </si>
+  <si>
+    <t>-0.020</t>
+  </si>
+  <si>
+    <t>132.193 secs</t>
+  </si>
+  <si>
+    <t>6.769 secs</t>
+  </si>
+  <si>
+    <t>0.189 secs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.165 </t>
+  </si>
+  <si>
+    <t>337.313 secs</t>
+  </si>
+  <si>
+    <t>314 clusters</t>
+  </si>
+  <si>
+    <t>120 outliers</t>
+  </si>
+  <si>
+    <t>-0.060</t>
+  </si>
+  <si>
+    <t>78.882 secs</t>
+  </si>
+  <si>
+    <t>4.872 secs</t>
+  </si>
+  <si>
+    <t>0.337 secs</t>
+  </si>
+  <si>
+    <t>-0.042</t>
+  </si>
+  <si>
+    <t>131.622 secs</t>
+  </si>
+  <si>
+    <t>5.831 secs</t>
+  </si>
+  <si>
+    <t>7.592 secs</t>
+  </si>
+  <si>
+    <t>130.678 secs</t>
+  </si>
+  <si>
+    <t>4.478 secs</t>
+  </si>
+  <si>
+    <t>0.033 secs</t>
+  </si>
+  <si>
+    <t>-0.061</t>
+  </si>
+  <si>
+    <t>128.358 secs</t>
   </si>
 </sst>
 </file>
@@ -686,7 +862,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
@@ -710,6 +886,8 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1015,7 +1193,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:N63"/>
+  <dimension ref="A1:N74"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.33203125" style="7" bestFit="1" customWidth="1"/>
@@ -1036,7 +1214,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G1" s="9" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -1391,1093 +1569,1961 @@
       <c r="N13" s="2"/>
     </row>
     <row r="14" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2"/>
+      <c r="A14" s="7">
+        <v>1000</v>
+      </c>
+      <c r="B14" s="7"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="7">
+        <v>2</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I14" s="7">
+        <v>314</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="15" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="3">
-        <v>2000</v>
-      </c>
-      <c r="B15" s="3">
-        <v>512</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D15" s="1"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="3">
+      <c r="B15" s="7"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="8"/>
+    </row>
+    <row r="16" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="7">
+        <v>1000</v>
+      </c>
+      <c r="B16" s="7"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="7">
         <v>2</v>
       </c>
-      <c r="G15" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="I15" s="3">
+      <c r="G16" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I16" s="7">
         <v>175</v>
       </c>
-      <c r="J15" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="M15" s="2"/>
-      <c r="N15" s="2"/>
-    </row>
-    <row r="16" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="3">
-        <v>2000</v>
-      </c>
-      <c r="B16" s="3">
-        <v>512</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D16" s="3">
-        <v>154</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F16" s="1"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="I16" s="3">
-        <v>175</v>
-      </c>
       <c r="J16" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="M16" s="2"/>
-      <c r="N16" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="K16" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>246</v>
+      </c>
     </row>
     <row r="17" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="3">
-        <v>2000</v>
-      </c>
-      <c r="B17" s="3">
-        <v>512</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="D17" s="3">
-        <v>154</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="F17" s="1"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="I17" s="7">
-        <v>175</v>
-      </c>
-      <c r="J17" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="K17" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="L17" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="M17" s="2"/>
-      <c r="N17" s="2" t="s">
-        <v>69</v>
-      </c>
+      <c r="B17" s="7"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="8"/>
+      <c r="K17" s="6"/>
     </row>
     <row r="18" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="3">
-        <v>2000</v>
-      </c>
-      <c r="B18" s="3">
-        <v>512</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D18" s="1"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="3">
+      <c r="A18" s="7">
+        <v>1000</v>
+      </c>
+      <c r="B18" s="7"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="7">
         <v>2</v>
       </c>
-      <c r="G18" s="2" t="s">
-        <v>72</v>
+      <c r="G18" s="8" t="s">
+        <v>247</v>
       </c>
       <c r="H18" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="I18" s="3">
+      <c r="I18" s="7">
         <v>175</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="M18" s="2"/>
-      <c r="N18" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="K18" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>249</v>
+      </c>
     </row>
     <row r="19" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="3">
-        <v>2000</v>
-      </c>
-      <c r="B19" s="3">
-        <v>512</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D19" s="3">
-        <v>154</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F19" s="1"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="8" t="s">
+      <c r="B19" s="7"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="8"/>
+      <c r="K19" s="6"/>
+    </row>
+    <row r="20" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="7">
+        <v>1000</v>
+      </c>
+      <c r="B20" s="7"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="7">
+        <v>2</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I20" s="7">
+        <v>175</v>
+      </c>
+      <c r="J20" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="K20" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="7"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="8"/>
+    </row>
+    <row r="22" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="H22" s="12"/>
+      <c r="I22" s="12"/>
+      <c r="J22" s="12"/>
+      <c r="K22" s="12"/>
+    </row>
+    <row r="23" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="K23" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="7">
+        <v>1000</v>
+      </c>
+      <c r="B24" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I19" s="3">
-        <v>363</v>
-      </c>
-      <c r="J19" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="L19" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="M19" s="2"/>
-      <c r="N19" s="2"/>
-    </row>
-    <row r="20" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="3">
-        <v>2000</v>
-      </c>
-      <c r="B20" s="3">
-        <v>512</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D20" s="1"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="3">
-        <v>2</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H20" s="8" t="s">
+      <c r="C24" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="G24" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="I20" s="3">
-        <v>605</v>
-      </c>
-      <c r="J20" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="M20" s="2"/>
-      <c r="N20" s="2"/>
-    </row>
-    <row r="21" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="3">
-        <v>2000</v>
-      </c>
-      <c r="B21" s="3">
-        <v>512</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D21" s="3">
-        <v>154</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="F21" s="1"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="I21" s="3">
-        <v>175</v>
-      </c>
-      <c r="J21" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="L21" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="M21" s="2"/>
-      <c r="N21" s="2"/>
-    </row>
-    <row r="22" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="3">
-        <v>2000</v>
-      </c>
-      <c r="B22" s="3">
-        <v>512</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D22" s="1"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="3">
-        <v>2</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H22" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="I22" s="3">
-        <v>175</v>
-      </c>
-      <c r="J22" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="L22" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="M22" s="2"/>
-      <c r="N22" s="2"/>
-    </row>
-    <row r="23" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="2"/>
-      <c r="K23" s="2"/>
-      <c r="L23" s="2"/>
-      <c r="M23" s="2"/>
-      <c r="N23" s="2"/>
-    </row>
-    <row r="24" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="2"/>
-      <c r="K24" s="2"/>
-      <c r="L24" s="2"/>
-      <c r="M24" s="2"/>
-      <c r="N24" s="2"/>
+      <c r="H24" s="8">
+        <v>120</v>
+      </c>
+      <c r="I24" s="7">
+        <v>38</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>242</v>
+      </c>
     </row>
     <row r="25" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="3">
-        <v>5000</v>
-      </c>
-      <c r="B25" s="3">
-        <v>512</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>96</v>
-      </c>
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="2"/>
       <c r="D25" s="1"/>
       <c r="E25" s="2"/>
-      <c r="F25" s="3">
-        <v>2</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="H25" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="I25" s="3">
-        <v>1586</v>
-      </c>
-      <c r="J25" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="K25" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="L25" s="8" t="s">
-        <v>118</v>
-      </c>
+      <c r="F25" s="1"/>
+      <c r="G25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
       <c r="M25" s="2"/>
       <c r="N25" s="2"/>
     </row>
     <row r="26" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="1">
-        <v>5000</v>
-      </c>
-      <c r="B26" s="1">
+      <c r="A26" s="3">
+        <v>2000</v>
+      </c>
+      <c r="B26" s="3">
         <v>512</v>
       </c>
-      <c r="C26" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="D26" s="1">
-        <v>154</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="F26" s="1"/>
-      <c r="G26" s="2"/>
+      <c r="C26" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D26" s="1"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="3">
+        <v>2</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="H26" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="I26" s="7">
-        <v>914</v>
+        <v>25</v>
+      </c>
+      <c r="I26" s="3">
+        <v>175</v>
       </c>
       <c r="J26" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="K26" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="L26" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="M26" s="8" t="s">
-        <v>69</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="M26" s="2"/>
       <c r="N26" s="2"/>
     </row>
     <row r="27" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="B27" s="3">
         <v>512</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="D27" s="1"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="3">
-        <v>2</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>100</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="D27" s="3">
+        <v>154</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F27" s="1"/>
+      <c r="G27" s="2"/>
       <c r="H27" s="8" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="I27" s="3">
         <v>175</v>
       </c>
       <c r="J27" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="K27" s="6" t="s">
-        <v>103</v>
+        <v>64</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>67</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>101</v>
+        <v>68</v>
       </c>
       <c r="M27" s="2"/>
       <c r="N27" s="2"/>
     </row>
     <row r="28" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="1">
-        <v>5000</v>
-      </c>
-      <c r="B28" s="1">
+      <c r="A28" s="3">
+        <v>2000</v>
+      </c>
+      <c r="B28" s="3">
         <v>512</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D28" s="1">
+        <v>135</v>
+      </c>
+      <c r="D28" s="3">
         <v>154</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="F28" s="1"/>
       <c r="G28" s="2"/>
-      <c r="H28" s="6" t="s">
-        <v>36</v>
+      <c r="H28" s="8" t="s">
+        <v>47</v>
       </c>
       <c r="I28" s="7">
         <v>175</v>
       </c>
       <c r="J28" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>107</v>
+        <v>134</v>
+      </c>
+      <c r="K28" s="6" t="s">
+        <v>138</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="M28" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="M28" s="2"/>
+      <c r="N28" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="N28" s="2"/>
     </row>
     <row r="29" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="1">
-        <v>5000</v>
-      </c>
-      <c r="B29" s="1">
+      <c r="A29" s="3">
+        <v>2000</v>
+      </c>
+      <c r="B29" s="3">
         <v>512</v>
       </c>
-      <c r="C29" s="8" t="s">
-        <v>109</v>
+      <c r="C29" s="2" t="s">
+        <v>71</v>
       </c>
       <c r="D29" s="1"/>
       <c r="E29" s="2"/>
-      <c r="F29" s="1">
+      <c r="F29" s="3">
         <v>2</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>110</v>
+        <v>72</v>
       </c>
       <c r="H29" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="I29" s="7">
+      <c r="I29" s="3">
         <v>175</v>
       </c>
       <c r="J29" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K29" s="6" t="s">
-        <v>113</v>
+        <v>70</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>73</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="M29" s="2"/>
       <c r="N29" s="2"/>
     </row>
     <row r="30" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="1">
-        <v>5000</v>
-      </c>
-      <c r="B30" s="1">
+      <c r="A30" s="3">
+        <v>2000</v>
+      </c>
+      <c r="B30" s="3">
         <v>512</v>
       </c>
-      <c r="C30" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="D30" s="1">
+      <c r="C30" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D30" s="3">
         <v>154</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="F30" s="1"/>
       <c r="G30" s="2"/>
       <c r="H30" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="I30" s="7">
-        <v>175</v>
+        <v>14</v>
+      </c>
+      <c r="I30" s="3">
+        <v>363</v>
       </c>
       <c r="J30" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="K30" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="L30" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="M30" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="N30" s="2" t="s">
-        <v>69</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="L30" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="M30" s="2"/>
+      <c r="N30" s="2"/>
     </row>
     <row r="31" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="1">
-        <v>5000</v>
-      </c>
-      <c r="B31" s="1">
+      <c r="A31" s="3">
+        <v>2000</v>
+      </c>
+      <c r="B31" s="3">
         <v>512</v>
       </c>
-      <c r="C31" s="8" t="s">
-        <v>128</v>
+      <c r="C31" s="2" t="s">
+        <v>81</v>
       </c>
       <c r="D31" s="1"/>
       <c r="E31" s="2"/>
-      <c r="F31" s="1">
+      <c r="F31" s="3">
         <v>2</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>129</v>
+        <v>82</v>
       </c>
       <c r="H31" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="I31" s="7">
-        <v>175</v>
+        <v>14</v>
+      </c>
+      <c r="I31" s="3">
+        <v>605</v>
       </c>
       <c r="J31" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="K31" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="L31" s="8" t="s">
-        <v>131</v>
+        <v>80</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>84</v>
       </c>
       <c r="M31" s="2"/>
       <c r="N31" s="2"/>
     </row>
     <row r="32" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="1">
-        <v>5000</v>
-      </c>
-      <c r="B32" s="1">
+      <c r="A32" s="3">
+        <v>2000</v>
+      </c>
+      <c r="B32" s="3">
         <v>512</v>
       </c>
-      <c r="C32" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="D32" s="1">
+      <c r="C32" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D32" s="3">
         <v>154</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>134</v>
+        <v>87</v>
       </c>
       <c r="F32" s="1"/>
       <c r="G32" s="2"/>
       <c r="H32" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="I32" s="7">
+        <v>36</v>
+      </c>
+      <c r="I32" s="3">
         <v>175</v>
       </c>
       <c r="J32" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="K32" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="L32" s="8" t="s">
-        <v>152</v>
+        <v>85</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="M32" s="2"/>
       <c r="N32" s="2"/>
     </row>
     <row r="33" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="1"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="1"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="1"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="1"/>
-      <c r="J33" s="2"/>
-      <c r="K33" s="2"/>
-      <c r="L33" s="2"/>
+      <c r="A33" s="3">
+        <v>2000</v>
+      </c>
+      <c r="B33" s="3">
+        <v>512</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D33" s="1"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="3">
+        <v>2</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H33" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I33" s="3">
+        <v>175</v>
+      </c>
+      <c r="J33" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="K33" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>94</v>
+      </c>
       <c r="M33" s="2"/>
       <c r="N33" s="2"/>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
-      <c r="B34" s="2"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="1"/>
-      <c r="J34" s="2"/>
+      <c r="B34" s="1"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="2"/>
       <c r="K34" s="2"/>
       <c r="L34" s="2"/>
       <c r="M34" s="2"/>
       <c r="N34" s="2"/>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
-      <c r="B35" s="2"/>
-      <c r="C35" s="1"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="1"/>
-      <c r="J35" s="2"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="2"/>
       <c r="K35" s="2"/>
       <c r="L35" s="2"/>
       <c r="M35" s="2"/>
       <c r="N35" s="2"/>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B36" s="2"/>
-      <c r="C36" s="1"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="2"/>
-      <c r="I36" s="1"/>
-      <c r="J36" s="2"/>
-      <c r="K36" s="2"/>
-      <c r="L36" s="2"/>
+    <row r="36" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="3">
+        <v>5000</v>
+      </c>
+      <c r="B36" s="3">
+        <v>512</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D36" s="1"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="3">
+        <v>2</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="H36" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I36" s="3">
+        <v>1586</v>
+      </c>
+      <c r="J36" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="K36" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="L36" s="8" t="s">
+        <v>117</v>
+      </c>
       <c r="M36" s="2"/>
       <c r="N36" s="2"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B37" s="11" t="s">
+    <row r="37" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
+        <v>5000</v>
+      </c>
+      <c r="B37" s="1">
+        <v>512</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="D37" s="1">
+        <v>154</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F37" s="1"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I37" s="7">
+        <v>914</v>
+      </c>
+      <c r="J37" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="K37" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="L37" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="M37" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="N37" s="2"/>
+    </row>
+    <row r="38" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="3">
+        <v>5000</v>
+      </c>
+      <c r="B38" s="3">
+        <v>512</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D38" s="1"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="3">
+        <v>2</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H38" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I38" s="3">
+        <v>175</v>
+      </c>
+      <c r="J38" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="K38" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="L38" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="M38" s="2"/>
+      <c r="N38" s="2"/>
+    </row>
+    <row r="39" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="1">
+        <v>5000</v>
+      </c>
+      <c r="B39" s="1">
+        <v>512</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D39" s="1">
+        <v>154</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F39" s="1"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I39" s="7">
+        <v>175</v>
+      </c>
+      <c r="J39" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="K39" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="L39" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="M39" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="N39" s="2"/>
+    </row>
+    <row r="40" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="1">
+        <v>5000</v>
+      </c>
+      <c r="B40" s="1">
+        <v>512</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D40" s="1"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="1">
+        <v>2</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H40" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="I40" s="7">
+        <v>175</v>
+      </c>
+      <c r="J40" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="K40" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="L40" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="M40" s="2"/>
+      <c r="N40" s="2"/>
+    </row>
+    <row r="41" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="1">
+        <v>5000</v>
+      </c>
+      <c r="B41" s="1">
+        <v>512</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D41" s="1">
+        <v>154</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F41" s="1"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="I41" s="7">
+        <v>175</v>
+      </c>
+      <c r="J41" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="K41" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="L41" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="M41" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="N41" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="1">
+        <v>5000</v>
+      </c>
+      <c r="B42" s="1">
+        <v>512</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="D42" s="1"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="1">
+        <v>2</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="H42" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I42" s="7">
+        <v>175</v>
+      </c>
+      <c r="J42" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="K42" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="L42" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="M42" s="2"/>
+      <c r="N42" s="2"/>
+    </row>
+    <row r="43" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="1">
+        <v>5000</v>
+      </c>
+      <c r="B43" s="1">
+        <v>512</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="D43" s="1">
+        <v>154</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F43" s="1"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I43" s="7">
+        <v>175</v>
+      </c>
+      <c r="J43" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="K43" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="L43" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="M43" s="2"/>
+      <c r="N43" s="2"/>
+    </row>
+    <row r="44" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="1"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="1"/>
+      <c r="J44" s="2"/>
+      <c r="K44" s="2"/>
+      <c r="L44" s="2"/>
+      <c r="M44" s="2"/>
+      <c r="N44" s="2"/>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A45" s="1"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="1"/>
+      <c r="J45" s="2"/>
+      <c r="K45" s="2"/>
+      <c r="L45" s="2"/>
+      <c r="M45" s="2"/>
+      <c r="N45" s="2"/>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A46" s="1"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="1"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="1"/>
+      <c r="J46" s="2"/>
+      <c r="K46" s="2"/>
+      <c r="L46" s="2"/>
+      <c r="M46" s="2"/>
+      <c r="N46" s="2"/>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B47" s="2"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="1"/>
+      <c r="J47" s="2"/>
+      <c r="K47" s="2"/>
+      <c r="L47" s="2"/>
+      <c r="M47" s="2"/>
+      <c r="N47" s="2"/>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B48" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="C48" s="11"/>
+      <c r="D48" s="11"/>
+      <c r="E48" s="11"/>
+      <c r="F48" s="11"/>
+      <c r="G48" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="H48" s="12"/>
+      <c r="I48" s="12"/>
+      <c r="J48" s="12"/>
+      <c r="K48" s="12"/>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B49" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="C37" s="11"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="11"/>
-      <c r="F37" s="11"/>
-      <c r="G37" s="12" t="s">
+      <c r="C49" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G49" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="H49" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="I49" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="J49" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="K49" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A50" s="7">
+        <v>1000</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C50" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="H37" s="12"/>
-      <c r="I37" s="12"/>
-      <c r="J37" s="12"/>
-      <c r="K37" s="12"/>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B38" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="D38" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="E38" s="7" t="s">
+      <c r="D50" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="G50" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H50" s="8">
+        <v>80</v>
+      </c>
+      <c r="I50" s="7">
+        <v>39</v>
+      </c>
+      <c r="J50" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="K50" s="7" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="G65" s="9" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A66" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B66" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D66" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E66" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F66" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G66" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="H66" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="I66" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J66" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="K66" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="F38" s="8" t="s">
+      <c r="L66" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G38" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="H38" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="I38" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="J38" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="K38" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="7">
+      <c r="M66" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="N66" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A67" s="7">
         <v>1000</v>
       </c>
-      <c r="B39" s="8" t="s">
+      <c r="B67" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C39" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D39" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="E39" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="F39" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="G39" s="7" t="s">
+      <c r="C67" s="7">
+        <v>165</v>
+      </c>
+      <c r="D67" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="E67" s="7">
+        <v>512</v>
+      </c>
+      <c r="F67" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="G67" s="7">
+        <v>154</v>
+      </c>
+      <c r="H67" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="K67" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="L67" s="8" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A68" s="7">
+        <v>1000</v>
+      </c>
+      <c r="B68" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="H39" s="8">
-        <v>80</v>
-      </c>
-      <c r="I39" s="7">
-        <v>39</v>
-      </c>
-      <c r="J39" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="K39" s="7" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="G54" s="9" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A55" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B55" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C55" s="7" t="s">
+      <c r="C68" s="7">
+        <v>323</v>
+      </c>
+      <c r="D68" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="E68" s="7">
+        <v>512</v>
+      </c>
+      <c r="F68" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="I68" s="7">
         <v>2</v>
       </c>
-      <c r="D55" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E55" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="F55" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="G55" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="H55" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="I55" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="J55" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="K55" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="L55" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="M55" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="N55" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A56" s="7">
+      <c r="J68" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="K68" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="L68" s="8" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A69" s="7">
         <v>1000</v>
       </c>
-      <c r="B56" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C56" s="7">
+      <c r="B69" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C69" s="7">
+        <v>175</v>
+      </c>
+      <c r="D69" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="E69" s="7">
+        <v>512</v>
+      </c>
+      <c r="F69" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="I69" s="7">
+        <v>2</v>
+      </c>
+      <c r="J69" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="K69" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="L69" s="8" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A70" s="7">
+        <v>1000</v>
+      </c>
+      <c r="B70" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C70" s="7">
+        <v>175</v>
+      </c>
+      <c r="D70" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="E70" s="7">
+        <v>512</v>
+      </c>
+      <c r="F70" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="G70" s="7">
+        <v>154</v>
+      </c>
+      <c r="H70" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="K70" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="D56" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="E56" s="7">
+      <c r="L70" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="N70" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A71" s="7">
+        <v>1000</v>
+      </c>
+      <c r="B71" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C71" s="7">
+        <v>175</v>
+      </c>
+      <c r="D71" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="E71" s="7">
         <v>512</v>
       </c>
-      <c r="F56" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="G56" s="7">
+      <c r="F71" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="I71" s="7">
+        <v>2</v>
+      </c>
+      <c r="J71" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="K71" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="L71" s="8" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A72" s="7">
+        <v>1000</v>
+      </c>
+      <c r="B72" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="C72" s="7">
+        <v>175</v>
+      </c>
+      <c r="D72" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="E72" s="7">
+        <v>512</v>
+      </c>
+      <c r="F72" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="G72" s="7">
         <v>154</v>
       </c>
-      <c r="H56" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="K56" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="L56" s="8" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A57" s="7">
+      <c r="H72" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="K72" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="L72" s="8" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A73" s="7">
         <v>1000</v>
       </c>
-      <c r="B57" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C57" s="7">
-        <v>323</v>
-      </c>
-      <c r="D57" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="E57" s="7">
+      <c r="B73" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C73" s="7">
+        <v>175</v>
+      </c>
+      <c r="D73" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="E73" s="7">
         <v>512</v>
       </c>
-      <c r="F57" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="I57" s="7">
+      <c r="F73" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="G73" s="7">
+        <v>154</v>
+      </c>
+      <c r="H73" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="K73" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="L73" s="8" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A74" s="7">
+        <v>1000</v>
+      </c>
+      <c r="B74" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C74" s="7">
+        <v>175</v>
+      </c>
+      <c r="D74" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="E74" s="7">
+        <v>512</v>
+      </c>
+      <c r="F74" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="I74" s="7">
         <v>2</v>
       </c>
-      <c r="J57" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="K57" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="L57" s="8" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A58" s="7">
-        <v>1000</v>
-      </c>
-      <c r="B58" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="C58" s="7">
-        <v>175</v>
-      </c>
-      <c r="D58" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="E58" s="7">
-        <v>512</v>
-      </c>
-      <c r="F58" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="I58" s="7">
-        <v>2</v>
-      </c>
-      <c r="J58" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="K58" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="L58" s="8" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A59" s="7">
-        <v>1000</v>
-      </c>
-      <c r="B59" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="C59" s="7">
-        <v>175</v>
-      </c>
-      <c r="D59" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="E59" s="7">
-        <v>512</v>
-      </c>
-      <c r="F59" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="G59" s="7">
-        <v>154</v>
-      </c>
-      <c r="H59" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="K59" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="L59" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="N59" s="8" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A60" s="7">
-        <v>1000</v>
-      </c>
-      <c r="B60" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C60" s="7">
-        <v>175</v>
-      </c>
-      <c r="D60" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="E60" s="7">
-        <v>512</v>
-      </c>
-      <c r="F60" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="I60" s="7">
-        <v>2</v>
-      </c>
-      <c r="J60" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="K60" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="L60" s="8" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A61" s="7">
-        <v>1000</v>
-      </c>
-      <c r="B61" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="C61" s="7">
-        <v>175</v>
-      </c>
-      <c r="D61" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="E61" s="7">
-        <v>512</v>
-      </c>
-      <c r="F61" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="G61" s="7">
-        <v>154</v>
-      </c>
-      <c r="H61" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="K61" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="L61" s="8" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A62" s="7">
-        <v>1000</v>
-      </c>
-      <c r="B62" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C62" s="7">
-        <v>175</v>
-      </c>
-      <c r="D62" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="E62" s="7">
-        <v>512</v>
-      </c>
-      <c r="F62" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="G62" s="7">
-        <v>154</v>
-      </c>
-      <c r="H62" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="K62" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="L62" s="8" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A63" s="7">
-        <v>1000</v>
-      </c>
-      <c r="B63" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C63" s="7">
-        <v>175</v>
-      </c>
-      <c r="D63" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="E63" s="7">
-        <v>512</v>
-      </c>
-      <c r="F63" s="8" t="s">
+      <c r="J74" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="I63" s="7">
-        <v>2</v>
-      </c>
-      <c r="J63" s="8" t="s">
+      <c r="K74" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="K63" s="10" t="s">
+      <c r="L74" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="L63" s="8" t="s">
-        <v>183</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="G37:K37"/>
+  <mergeCells count="4">
+    <mergeCell ref="B48:F48"/>
+    <mergeCell ref="G48:K48"/>
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="G22:K22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13" customWidth="1"/>
+    <col min="2" max="2" width="12.5546875" customWidth="1"/>
+    <col min="3" max="3" width="14.44140625" customWidth="1"/>
+    <col min="4" max="4" width="15.88671875" customWidth="1"/>
+    <col min="5" max="5" width="13.21875" customWidth="1"/>
+    <col min="6" max="6" width="18.21875" customWidth="1"/>
+    <col min="7" max="7" width="17.6640625" customWidth="1"/>
+    <col min="8" max="9" width="17.109375" customWidth="1"/>
+    <col min="10" max="10" width="16.21875" customWidth="1"/>
+    <col min="11" max="11" width="27.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="7"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="H1" s="8"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" s="7"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8"/>
+      <c r="N2" s="8"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" s="7"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>1000</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5" t="s">
+        <v>195</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5">
+        <v>303</v>
+      </c>
+      <c r="H5" t="s">
+        <v>197</v>
+      </c>
+      <c r="I5" t="s">
+        <v>198</v>
+      </c>
+      <c r="J5" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>1000</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7" t="s">
+        <v>203</v>
+      </c>
+      <c r="F7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7">
+        <v>175</v>
+      </c>
+      <c r="H7" t="s">
+        <v>204</v>
+      </c>
+      <c r="I7" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="J7" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>1000</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9" t="s">
+        <v>207</v>
+      </c>
+      <c r="F9" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9">
+        <v>175</v>
+      </c>
+      <c r="H9" t="s">
+        <v>209</v>
+      </c>
+      <c r="I9" t="s">
+        <v>208</v>
+      </c>
+      <c r="J9" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>1000</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+      <c r="E11" t="s">
+        <v>213</v>
+      </c>
+      <c r="F11" t="s">
+        <v>25</v>
+      </c>
+      <c r="G11">
+        <v>175</v>
+      </c>
+      <c r="H11" t="s">
+        <v>214</v>
+      </c>
+      <c r="I11" t="s">
+        <v>215</v>
+      </c>
+      <c r="J11" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A14" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B14" s="8"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A15" s="7"/>
+      <c r="B15" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="H15" s="12"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="12"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A16" s="7"/>
+      <c r="B16" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" s="7">
+        <v>1000</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H17" s="8">
+        <v>126</v>
+      </c>
+      <c r="I17" s="7">
+        <v>40</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>202</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="G15:K15"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:N15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.33203125" customWidth="1"/>
+    <col min="2" max="2" width="15.6640625" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" customWidth="1"/>
+    <col min="5" max="5" width="14.44140625" customWidth="1"/>
+    <col min="6" max="6" width="16.109375" customWidth="1"/>
+    <col min="7" max="8" width="17.109375" customWidth="1"/>
+    <col min="9" max="9" width="13.21875" customWidth="1"/>
+    <col min="10" max="10" width="15.88671875" customWidth="1"/>
+    <col min="11" max="11" width="27.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="7"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="H1" s="8"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" s="7"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8"/>
+      <c r="N2" s="8"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" s="7"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>1000</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5" t="s">
+        <v>218</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5">
+        <v>300</v>
+      </c>
+      <c r="H5" t="s">
+        <v>219</v>
+      </c>
+      <c r="I5" t="s">
+        <v>220</v>
+      </c>
+      <c r="J5" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>1000</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7" t="s">
+        <v>226</v>
+      </c>
+      <c r="F7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7">
+        <v>175</v>
+      </c>
+      <c r="H7" t="s">
+        <v>223</v>
+      </c>
+      <c r="I7" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="J7" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>1000</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9" t="s">
+        <v>227</v>
+      </c>
+      <c r="F9" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9">
+        <v>175</v>
+      </c>
+      <c r="H9" t="s">
+        <v>229</v>
+      </c>
+      <c r="I9" t="s">
+        <v>228</v>
+      </c>
+      <c r="J9" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>1000</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+      <c r="E11" t="s">
+        <v>231</v>
+      </c>
+      <c r="F11" t="s">
+        <v>25</v>
+      </c>
+      <c r="G11">
+        <v>175</v>
+      </c>
+      <c r="H11" t="s">
+        <v>232</v>
+      </c>
+      <c r="I11" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="J11" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A12" s="8"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A13" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="12"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A14" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A15" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="7">
+        <v>300</v>
+      </c>
+      <c r="C15" s="8">
+        <v>92</v>
+      </c>
+      <c r="D15" t="s">
+        <v>220</v>
+      </c>
+      <c r="E15" t="s">
+        <v>221</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" s="8">
+        <v>116</v>
+      </c>
+      <c r="H15" s="7">
+        <v>34</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>222</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="F13:J13"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Experiments/DBCV_Conclu.xlsx
+++ b/Experiments/DBCV_Conclu.xlsx
@@ -9,19 +9,25 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18192" windowHeight="8508"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18190" windowHeight="8510" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet5" sheetId="5" r:id="rId5"/>
+    <sheet name="Sheet6" sheetId="6" r:id="rId6"/>
+    <sheet name="Sheet7" sheetId="7" r:id="rId7"/>
+    <sheet name="Sheet8" sheetId="8" r:id="rId8"/>
+    <sheet name="Sheet9" sheetId="9" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="449">
   <si>
     <t>Datapoints</t>
   </si>
@@ -793,12 +799,597 @@
   <si>
     <t>128.358 secs</t>
   </si>
+  <si>
+    <t>TEST DATASET(128)</t>
+  </si>
+  <si>
+    <t>3.036 secs</t>
+  </si>
+  <si>
+    <t>0.121 secs</t>
+  </si>
+  <si>
+    <t>156.689 secs</t>
+  </si>
+  <si>
+    <t>5.255 secs</t>
+  </si>
+  <si>
+    <t>-0.037</t>
+  </si>
+  <si>
+    <t>177.251 secs</t>
+  </si>
+  <si>
+    <t>0.174</t>
+  </si>
+  <si>
+    <t>354.460 secs</t>
+  </si>
+  <si>
+    <t>-0.031</t>
+  </si>
+  <si>
+    <t>59.516 secs</t>
+  </si>
+  <si>
+    <t>3.295 secs</t>
+  </si>
+  <si>
+    <t>5.511 secs</t>
+  </si>
+  <si>
+    <t>0.024</t>
+  </si>
+  <si>
+    <t>116.696 secs</t>
+  </si>
+  <si>
+    <t>86.531 secs</t>
+  </si>
+  <si>
+    <t>0.057 secs</t>
+  </si>
+  <si>
+    <t>-0.033</t>
+  </si>
+  <si>
+    <t>94.799 secs</t>
+  </si>
+  <si>
+    <t>TEST DATASET(64)</t>
+  </si>
+  <si>
+    <t>0.111 secs</t>
+  </si>
+  <si>
+    <t>0.137</t>
+  </si>
+  <si>
+    <t>295.402 secs</t>
+  </si>
+  <si>
+    <t>-0.070</t>
+  </si>
+  <si>
+    <t>78.698 secs</t>
+  </si>
+  <si>
+    <t>3.059 secs</t>
+  </si>
+  <si>
+    <t>167.086 secs</t>
+  </si>
+  <si>
+    <t>3.143 secs</t>
+  </si>
+  <si>
+    <t>-0.068</t>
+  </si>
+  <si>
+    <t>145.711 secs</t>
+  </si>
+  <si>
+    <t>3.189 secs</t>
+  </si>
+  <si>
+    <t>8.760 secs</t>
+  </si>
+  <si>
+    <t>152.836 secs</t>
+  </si>
+  <si>
+    <t>3.914 secs</t>
+  </si>
+  <si>
+    <t>0.032 secs</t>
+  </si>
+  <si>
+    <t>-0.017</t>
+  </si>
+  <si>
+    <t>157.152 secs</t>
+  </si>
+  <si>
+    <t>TEST DATASET(32)</t>
+  </si>
+  <si>
+    <t>2.748 secs</t>
+  </si>
+  <si>
+    <t>0.112 secs</t>
+  </si>
+  <si>
+    <t>123.917 secs</t>
+  </si>
+  <si>
+    <t>1.434 secs</t>
+  </si>
+  <si>
+    <t>0.156</t>
+  </si>
+  <si>
+    <t>244.027 secs</t>
+  </si>
+  <si>
+    <t>107.670 secs</t>
+  </si>
+  <si>
+    <t>141.890 secs</t>
+  </si>
+  <si>
+    <t>TEST DATASET(16)</t>
+  </si>
+  <si>
+    <t>2.985 secs</t>
+  </si>
+  <si>
+    <t>6.190 secs</t>
+  </si>
+  <si>
+    <t>0.016</t>
+  </si>
+  <si>
+    <t>107.808 secs</t>
+  </si>
+  <si>
+    <t>55.501 secs</t>
+  </si>
+  <si>
+    <t>0.023</t>
+  </si>
+  <si>
+    <t>93.092 secs</t>
+  </si>
+  <si>
+    <t>2.673 secs</t>
+  </si>
+  <si>
+    <t>0.116 secs</t>
+  </si>
+  <si>
+    <t>0.182</t>
+  </si>
+  <si>
+    <t>262.840 secs</t>
+  </si>
+  <si>
+    <t>0.001</t>
+  </si>
+  <si>
+    <t>110.979 secs</t>
+  </si>
+  <si>
+    <t>147.240 secs</t>
+  </si>
+  <si>
+    <t>2.276 secs</t>
+  </si>
+  <si>
+    <t>147.403 secs</t>
+  </si>
+  <si>
+    <t>0.027</t>
+  </si>
+  <si>
+    <t>3.005 secs</t>
+  </si>
+  <si>
+    <t>6.064 secs</t>
+  </si>
+  <si>
+    <t>109.908 secs</t>
+  </si>
+  <si>
+    <t>76.469 secs</t>
+  </si>
+  <si>
+    <t>0.005</t>
+  </si>
+  <si>
+    <t>92.398 secs</t>
+  </si>
+  <si>
+    <t>TEST DATASET(8)</t>
+  </si>
+  <si>
+    <t>2.851 secs</t>
+  </si>
+  <si>
+    <t>0.113</t>
+  </si>
+  <si>
+    <t>164.529 secs</t>
+  </si>
+  <si>
+    <t>7.996 secs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135 </t>
+  </si>
+  <si>
+    <t>294.543 secs</t>
+  </si>
+  <si>
+    <t>81.233 secs</t>
+  </si>
+  <si>
+    <t>-0.028</t>
+  </si>
+  <si>
+    <t>146.129 secs</t>
+  </si>
+  <si>
+    <t>2.693 secs</t>
+  </si>
+  <si>
+    <t>3.949 secs</t>
+  </si>
+  <si>
+    <t>-0.026</t>
+  </si>
+  <si>
+    <t>115.756 secs</t>
+  </si>
+  <si>
+    <t>80.714 secs</t>
+  </si>
+  <si>
+    <t>93.977 secs</t>
+  </si>
+  <si>
+    <t>5.484 secs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.170 </t>
+  </si>
+  <si>
+    <t>203.930 secs</t>
+  </si>
+  <si>
+    <t>-0.105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">255.735 secs </t>
+  </si>
+  <si>
+    <t>-0.220</t>
+  </si>
+  <si>
+    <t>3.865 secs</t>
+  </si>
+  <si>
+    <t>-0.144</t>
+  </si>
+  <si>
+    <t>150.437 secs</t>
+  </si>
+  <si>
+    <t>-0.155</t>
+  </si>
+  <si>
+    <t>160.240 secs</t>
+  </si>
+  <si>
+    <t>0.138 secs</t>
+  </si>
+  <si>
+    <t>4.351 secs</t>
+  </si>
+  <si>
+    <t>-0.101</t>
+  </si>
+  <si>
+    <t>-0.193</t>
+  </si>
+  <si>
+    <t>70.254 secs</t>
+  </si>
+  <si>
+    <t>-0.148</t>
+  </si>
+  <si>
+    <t>246.380 secs</t>
+  </si>
+  <si>
+    <t>195.106 secs</t>
+  </si>
+  <si>
+    <t>4.856 secs</t>
+  </si>
+  <si>
+    <t>-0.176</t>
+  </si>
+  <si>
+    <t>167.438 secs</t>
+  </si>
+  <si>
+    <t>0.035 secs</t>
+  </si>
+  <si>
+    <t>-0.121</t>
+  </si>
+  <si>
+    <t>167.431 secs</t>
+  </si>
+  <si>
+    <t>0.151 secs</t>
+  </si>
+  <si>
+    <t>-0.120 secs</t>
+  </si>
+  <si>
+    <t>244.515 secs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.180 </t>
+  </si>
+  <si>
+    <t>63.904 secs</t>
+  </si>
+  <si>
+    <t>0.494 secs</t>
+  </si>
+  <si>
+    <t>-0.132</t>
+  </si>
+  <si>
+    <t>203.314 secs</t>
+  </si>
+  <si>
+    <t>5.119 secs</t>
+  </si>
+  <si>
+    <t>0.077 secs</t>
+  </si>
+  <si>
+    <t>-0.122</t>
+  </si>
+  <si>
+    <t>146.818 secs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.085 </t>
+  </si>
+  <si>
+    <t>155.761 secs</t>
+  </si>
+  <si>
+    <t>0.200 secs</t>
+  </si>
+  <si>
+    <t>3.364 secs</t>
+  </si>
+  <si>
+    <t>-0.095</t>
+  </si>
+  <si>
+    <t>199.349 secs</t>
+  </si>
+  <si>
+    <t>-0.073</t>
+  </si>
+  <si>
+    <t>228.455 secs</t>
+  </si>
+  <si>
+    <t>-0.178</t>
+  </si>
+  <si>
+    <t>64.090 secs</t>
+  </si>
+  <si>
+    <t>-0.118</t>
+  </si>
+  <si>
+    <t>161.340 secs</t>
+  </si>
+  <si>
+    <t>3.041 secs</t>
+  </si>
+  <si>
+    <t>0.088 secs</t>
+  </si>
+  <si>
+    <t>-0.080</t>
+  </si>
+  <si>
+    <t>163.633 secs</t>
+  </si>
+  <si>
+    <t>0.237 secs</t>
+  </si>
+  <si>
+    <t>0.304</t>
+  </si>
+  <si>
+    <t>131.231 secs</t>
+  </si>
+  <si>
+    <t>0.672 secs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.087 </t>
+  </si>
+  <si>
+    <t>97.613 secs</t>
+  </si>
+  <si>
+    <t>8.273 secs</t>
+  </si>
+  <si>
+    <t>-0.094</t>
+  </si>
+  <si>
+    <t>151.214 secs</t>
+  </si>
+  <si>
+    <t>0.067 secs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.074 </t>
+  </si>
+  <si>
+    <t>162.693 secs</t>
+  </si>
+  <si>
+    <t>TEST DATASET(4)</t>
+  </si>
+  <si>
+    <t>0.105 secs</t>
+  </si>
+  <si>
+    <t>-0.133</t>
+  </si>
+  <si>
+    <t>258.818 secs</t>
+  </si>
+  <si>
+    <t>-0.248</t>
+  </si>
+  <si>
+    <t>70.953 secs</t>
+  </si>
+  <si>
+    <t>0.874 secs</t>
+  </si>
+  <si>
+    <t>191.018 secs</t>
+  </si>
+  <si>
+    <t>16.396 secs</t>
+  </si>
+  <si>
+    <t>0.036 secs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.307 </t>
+  </si>
+  <si>
+    <t>178.445 secs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.197 </t>
+  </si>
+  <si>
+    <t>176.516 secs</t>
+  </si>
+  <si>
+    <t>TEST DATASET(2)</t>
+  </si>
+  <si>
+    <t>0.115 secs</t>
+  </si>
+  <si>
+    <t>0.036</t>
+  </si>
+  <si>
+    <t>340.224 secs</t>
+  </si>
+  <si>
+    <t>-0.141</t>
+  </si>
+  <si>
+    <t>71.157 secs</t>
+  </si>
+  <si>
+    <t>4.255 secs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.204 </t>
+  </si>
+  <si>
+    <t>199.742 secs</t>
+  </si>
+  <si>
+    <t>0.076 secs</t>
+  </si>
+  <si>
+    <t>-0.166</t>
+  </si>
+  <si>
+    <t>200.629 secs</t>
+  </si>
+  <si>
+    <t>296.005 secs</t>
+  </si>
+  <si>
+    <t>-0.450</t>
+  </si>
+  <si>
+    <t>97.039 secs</t>
+  </si>
+  <si>
+    <t>2.876 secs</t>
+  </si>
+  <si>
+    <t>0.117 secs</t>
+  </si>
+  <si>
+    <t>3.102 secs</t>
+  </si>
+  <si>
+    <t>0.555 secs</t>
+  </si>
+  <si>
+    <t>193.242 secs</t>
+  </si>
+  <si>
+    <t>0.087</t>
+  </si>
+  <si>
+    <t>319.429 secs</t>
+  </si>
+  <si>
+    <t>49.106 secs</t>
+  </si>
+  <si>
+    <t>2.517 secs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.116 </t>
+  </si>
+  <si>
+    <t>92.347 secs</t>
+  </si>
+  <si>
+    <t>2.432 secs</t>
+  </si>
+  <si>
+    <t>1.952 secs</t>
+  </si>
+  <si>
+    <t>-0.071</t>
+  </si>
+  <si>
+    <t>92.449 secs</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -834,13 +1425,26 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -862,7 +1466,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
@@ -880,14 +1484,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1194,32 +1801,32 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:N74"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.33203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.88671875" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.36328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.90625" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.88671875" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.88671875" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5546875" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.88671875" style="8" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5546875" style="7" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.6640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="29.88671875" style="8" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="80.88671875" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.90625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.90625" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.54296875" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.54296875" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.90625" style="8" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.54296875" style="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.54296875" style="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.6328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.08984375" style="8" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="29.90625" style="8" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="80.90625" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G1" s="9" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="4" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -1263,7 +1870,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>1000</v>
       </c>
@@ -1299,7 +1906,7 @@
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
     </row>
-    <row r="6" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>1000</v>
       </c>
@@ -1335,7 +1942,7 @@
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
     </row>
-    <row r="7" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>1000</v>
       </c>
@@ -1371,7 +1978,7 @@
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
     </row>
-    <row r="8" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>1000</v>
       </c>
@@ -1407,7 +2014,7 @@
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
     </row>
-    <row r="9" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>1000</v>
       </c>
@@ -1443,7 +2050,7 @@
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
     </row>
-    <row r="10" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>1000</v>
       </c>
@@ -1479,7 +2086,7 @@
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
     </row>
-    <row r="11" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>1000</v>
       </c>
@@ -1519,7 +2126,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>1000</v>
       </c>
@@ -1555,7 +2162,7 @@
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
     </row>
-    <row r="13" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="2"/>
@@ -1568,7 +2175,7 @@
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
     </row>
-    <row r="14" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="7">
         <v>1000</v>
       </c>
@@ -1598,7 +2205,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="7"/>
       <c r="C15" s="8"/>
       <c r="D15" s="7"/>
@@ -1606,7 +2213,7 @@
       <c r="F15" s="7"/>
       <c r="G15" s="8"/>
     </row>
-    <row r="16" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="7">
         <v>1000</v>
       </c>
@@ -1636,7 +2243,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="7"/>
       <c r="C17" s="8"/>
       <c r="D17" s="7"/>
@@ -1645,7 +2252,7 @@
       <c r="G17" s="8"/>
       <c r="K17" s="6"/>
     </row>
-    <row r="18" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="7">
         <v>1000</v>
       </c>
@@ -1675,7 +2282,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="7"/>
       <c r="C19" s="8"/>
       <c r="D19" s="7"/>
@@ -1684,7 +2291,7 @@
       <c r="G19" s="8"/>
       <c r="K19" s="6"/>
     </row>
-    <row r="20" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="7">
         <v>1000</v>
       </c>
@@ -1714,7 +2321,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="7"/>
       <c r="C21" s="8"/>
       <c r="D21" s="7"/>
@@ -1722,23 +2329,23 @@
       <c r="F21" s="7"/>
       <c r="G21" s="8"/>
     </row>
-    <row r="22" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="11" t="s">
+    <row r="22" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="13" t="s">
         <v>183</v>
       </c>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="12" t="s">
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="14" t="s">
         <v>187</v>
       </c>
-      <c r="H22" s="12"/>
-      <c r="I22" s="12"/>
-      <c r="J22" s="12"/>
-      <c r="K22" s="12"/>
-    </row>
-    <row r="23" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H22" s="14"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="14"/>
+      <c r="K22" s="14"/>
+    </row>
+    <row r="23" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="8" t="s">
         <v>184</v>
       </c>
@@ -1770,7 +2377,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="7">
         <v>1000</v>
       </c>
@@ -1805,7 +2412,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="2"/>
@@ -1818,7 +2425,7 @@
       <c r="M25" s="2"/>
       <c r="N25" s="2"/>
     </row>
-    <row r="26" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="3">
         <v>2000</v>
       </c>
@@ -1854,7 +2461,7 @@
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
     </row>
-    <row r="27" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="3">
         <v>2000</v>
       </c>
@@ -1890,7 +2497,7 @@
       <c r="M27" s="2"/>
       <c r="N27" s="2"/>
     </row>
-    <row r="28" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="3">
         <v>2000</v>
       </c>
@@ -1928,7 +2535,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="3">
         <v>2000</v>
       </c>
@@ -1964,7 +2571,7 @@
       <c r="M29" s="2"/>
       <c r="N29" s="2"/>
     </row>
-    <row r="30" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="3">
         <v>2000</v>
       </c>
@@ -2000,7 +2607,7 @@
       <c r="M30" s="2"/>
       <c r="N30" s="2"/>
     </row>
-    <row r="31" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="3">
         <v>2000</v>
       </c>
@@ -2036,7 +2643,7 @@
       <c r="M31" s="2"/>
       <c r="N31" s="2"/>
     </row>
-    <row r="32" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="3">
         <v>2000</v>
       </c>
@@ -2072,7 +2679,7 @@
       <c r="M32" s="2"/>
       <c r="N32" s="2"/>
     </row>
-    <row r="33" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="3">
         <v>2000</v>
       </c>
@@ -2108,7 +2715,7 @@
       <c r="M33" s="2"/>
       <c r="N33" s="2"/>
     </row>
-    <row r="34" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="2"/>
@@ -2121,7 +2728,7 @@
       <c r="M34" s="2"/>
       <c r="N34" s="2"/>
     </row>
-    <row r="35" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="2"/>
@@ -2134,7 +2741,7 @@
       <c r="M35" s="2"/>
       <c r="N35" s="2"/>
     </row>
-    <row r="36" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="3">
         <v>5000</v>
       </c>
@@ -2170,7 +2777,7 @@
       <c r="M36" s="2"/>
       <c r="N36" s="2"/>
     </row>
-    <row r="37" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <v>5000</v>
       </c>
@@ -2208,7 +2815,7 @@
       </c>
       <c r="N37" s="2"/>
     </row>
-    <row r="38" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="3">
         <v>5000</v>
       </c>
@@ -2244,7 +2851,7 @@
       <c r="M38" s="2"/>
       <c r="N38" s="2"/>
     </row>
-    <row r="39" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
         <v>5000</v>
       </c>
@@ -2282,7 +2889,7 @@
       </c>
       <c r="N39" s="2"/>
     </row>
-    <row r="40" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
         <v>5000</v>
       </c>
@@ -2318,7 +2925,7 @@
       <c r="M40" s="2"/>
       <c r="N40" s="2"/>
     </row>
-    <row r="41" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <v>5000</v>
       </c>
@@ -2358,7 +2965,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="42" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <v>5000</v>
       </c>
@@ -2394,7 +3001,7 @@
       <c r="M42" s="2"/>
       <c r="N42" s="2"/>
     </row>
-    <row r="43" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
         <v>5000</v>
       </c>
@@ -2430,7 +3037,7 @@
       <c r="M43" s="2"/>
       <c r="N43" s="2"/>
     </row>
-    <row r="44" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="1"/>
       <c r="B44" s="2"/>
       <c r="C44" s="1"/>
@@ -2446,7 +3053,7 @@
       <c r="M44" s="2"/>
       <c r="N44" s="2"/>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A45" s="1"/>
       <c r="B45" s="2"/>
       <c r="C45" s="1"/>
@@ -2462,7 +3069,7 @@
       <c r="M45" s="2"/>
       <c r="N45" s="2"/>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A46" s="1"/>
       <c r="B46" s="2"/>
       <c r="C46" s="1"/>
@@ -2478,7 +3085,7 @@
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>102</v>
       </c>
@@ -2496,23 +3103,23 @@
       <c r="M47" s="2"/>
       <c r="N47" s="2"/>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B48" s="11" t="s">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="B48" s="13" t="s">
         <v>183</v>
       </c>
-      <c r="C48" s="11"/>
-      <c r="D48" s="11"/>
-      <c r="E48" s="11"/>
-      <c r="F48" s="11"/>
-      <c r="G48" s="12" t="s">
+      <c r="C48" s="13"/>
+      <c r="D48" s="13"/>
+      <c r="E48" s="13"/>
+      <c r="F48" s="13"/>
+      <c r="G48" s="14" t="s">
         <v>187</v>
       </c>
-      <c r="H48" s="12"/>
-      <c r="I48" s="12"/>
-      <c r="J48" s="12"/>
-      <c r="K48" s="12"/>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="H48" s="14"/>
+      <c r="I48" s="14"/>
+      <c r="J48" s="14"/>
+      <c r="K48" s="14"/>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B49" s="8" t="s">
         <v>184</v>
       </c>
@@ -2544,7 +3151,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A50" s="7">
         <v>1000</v>
       </c>
@@ -2579,12 +3186,12 @@
         <v>194</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.35">
       <c r="G65" s="9" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A66" s="7" t="s">
         <v>0</v>
       </c>
@@ -2628,7 +3235,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A67" s="7">
         <v>1000</v>
       </c>
@@ -2660,7 +3267,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A68" s="7">
         <v>1000</v>
       </c>
@@ -2692,7 +3299,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A69" s="7">
         <v>1000</v>
       </c>
@@ -2724,7 +3331,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A70" s="7">
         <v>1000</v>
       </c>
@@ -2759,7 +3366,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A71" s="7">
         <v>1000</v>
       </c>
@@ -2791,7 +3398,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A72" s="7">
         <v>1000</v>
       </c>
@@ -2823,7 +3430,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A73" s="7">
         <v>1000</v>
       </c>
@@ -2855,7 +3462,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A74" s="7">
         <v>1000</v>
       </c>
@@ -2902,21 +3509,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
-    <col min="2" max="2" width="12.5546875" customWidth="1"/>
-    <col min="3" max="3" width="14.44140625" customWidth="1"/>
-    <col min="4" max="4" width="15.88671875" customWidth="1"/>
-    <col min="5" max="5" width="13.21875" customWidth="1"/>
-    <col min="6" max="6" width="18.21875" customWidth="1"/>
-    <col min="7" max="7" width="17.6640625" customWidth="1"/>
-    <col min="8" max="9" width="17.109375" customWidth="1"/>
-    <col min="10" max="10" width="16.21875" customWidth="1"/>
-    <col min="11" max="11" width="27.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.54296875" customWidth="1"/>
+    <col min="3" max="3" width="14.453125" customWidth="1"/>
+    <col min="4" max="4" width="15.90625" customWidth="1"/>
+    <col min="5" max="5" width="13.1796875" customWidth="1"/>
+    <col min="6" max="6" width="18.1796875" customWidth="1"/>
+    <col min="7" max="7" width="17.6328125" customWidth="1"/>
+    <col min="8" max="9" width="17.08984375" customWidth="1"/>
+    <col min="10" max="10" width="16.1796875" customWidth="1"/>
+    <col min="11" max="11" width="27.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="7"/>
       <c r="B1" s="8"/>
       <c r="C1" s="7"/>
@@ -2934,7 +3541,7 @@
       <c r="M1" s="8"/>
       <c r="N1" s="8"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="7"/>
@@ -2950,7 +3557,7 @@
       <c r="M2" s="8"/>
       <c r="N2" s="8"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="7"/>
       <c r="B3" s="8"/>
       <c r="C3" s="7"/>
@@ -2966,7 +3573,7 @@
       <c r="M3" s="8"/>
       <c r="N3" s="8"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
         <v>0</v>
       </c>
@@ -3004,7 +3611,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>1000</v>
       </c>
@@ -3030,7 +3637,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>1000</v>
       </c>
@@ -3049,14 +3656,14 @@
       <c r="H7" t="s">
         <v>204</v>
       </c>
-      <c r="I7" s="13" t="s">
+      <c r="I7" s="11" t="s">
         <v>205</v>
       </c>
       <c r="J7" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>1000</v>
       </c>
@@ -3082,7 +3689,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>1000</v>
       </c>
@@ -3108,7 +3715,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="7" t="s">
         <v>102</v>
       </c>
@@ -3123,24 +3730,24 @@
       <c r="J14" s="8"/>
       <c r="K14" s="8"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="7"/>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="13" t="s">
         <v>183</v>
       </c>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="12" t="s">
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="14" t="s">
         <v>187</v>
       </c>
-      <c r="H15" s="12"/>
-      <c r="I15" s="12"/>
-      <c r="J15" s="12"/>
-      <c r="K15" s="12"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="H15" s="14"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="14"/>
+      <c r="K15" s="14"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="7"/>
       <c r="B16" s="8" t="s">
         <v>184</v>
@@ -3173,7 +3780,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" s="7">
         <v>1000</v>
       </c>
@@ -3221,21 +3828,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" customWidth="1"/>
-    <col min="2" max="2" width="15.6640625" customWidth="1"/>
+    <col min="1" max="1" width="10.36328125" customWidth="1"/>
+    <col min="2" max="2" width="15.6328125" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" customWidth="1"/>
-    <col min="5" max="5" width="14.44140625" customWidth="1"/>
-    <col min="6" max="6" width="16.109375" customWidth="1"/>
-    <col min="7" max="8" width="17.109375" customWidth="1"/>
-    <col min="9" max="9" width="13.21875" customWidth="1"/>
-    <col min="10" max="10" width="15.88671875" customWidth="1"/>
-    <col min="11" max="11" width="27.44140625" customWidth="1"/>
+    <col min="4" max="4" width="11.54296875" customWidth="1"/>
+    <col min="5" max="5" width="14.453125" customWidth="1"/>
+    <col min="6" max="6" width="16.08984375" customWidth="1"/>
+    <col min="7" max="8" width="17.08984375" customWidth="1"/>
+    <col min="9" max="9" width="13.1796875" customWidth="1"/>
+    <col min="10" max="10" width="15.90625" customWidth="1"/>
+    <col min="11" max="11" width="27.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="7"/>
       <c r="B1" s="8"/>
       <c r="C1" s="7"/>
@@ -3253,7 +3860,7 @@
       <c r="M1" s="8"/>
       <c r="N1" s="8"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="7"/>
@@ -3269,7 +3876,7 @@
       <c r="M2" s="8"/>
       <c r="N2" s="8"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="7"/>
       <c r="B3" s="8"/>
       <c r="C3" s="7"/>
@@ -3285,7 +3892,7 @@
       <c r="M3" s="8"/>
       <c r="N3" s="8"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
         <v>0</v>
       </c>
@@ -3323,7 +3930,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>1000</v>
       </c>
@@ -3349,7 +3956,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>1000</v>
       </c>
@@ -3368,14 +3975,14 @@
       <c r="H7" t="s">
         <v>223</v>
       </c>
-      <c r="I7" s="13" t="s">
+      <c r="I7" s="11" t="s">
         <v>224</v>
       </c>
       <c r="J7" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>1000</v>
       </c>
@@ -3401,7 +4008,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>1000</v>
       </c>
@@ -3420,14 +4027,14 @@
       <c r="H11" t="s">
         <v>232</v>
       </c>
-      <c r="I11" s="14" t="s">
+      <c r="I11" s="12" t="s">
         <v>233</v>
       </c>
       <c r="J11" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="8"/>
       <c r="B12" s="7"/>
       <c r="C12" s="8"/>
@@ -3439,23 +4046,23 @@
       <c r="I12" s="8"/>
       <c r="J12" s="8"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="11" t="s">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A13" s="13" t="s">
         <v>183</v>
       </c>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="12" t="s">
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="14" t="s">
         <v>187</v>
       </c>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="12"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="14"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="8" t="s">
         <v>184</v>
       </c>
@@ -3487,7 +4094,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="8" t="s">
         <v>14</v>
       </c>
@@ -3526,4 +4133,2817 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:N26"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="13.453125" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="3" max="3" width="12.453125" customWidth="1"/>
+    <col min="4" max="4" width="12.81640625" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="6" max="6" width="15.6328125" customWidth="1"/>
+    <col min="7" max="7" width="15.08984375" customWidth="1"/>
+    <col min="8" max="8" width="17.36328125" customWidth="1"/>
+    <col min="9" max="9" width="16.81640625" customWidth="1"/>
+    <col min="10" max="10" width="15" customWidth="1"/>
+    <col min="11" max="11" width="29.26953125" customWidth="1"/>
+    <col min="12" max="12" width="79" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A1" s="7"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="H1" s="8"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A2" s="7"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8"/>
+      <c r="N2" s="8"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A3" s="7"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A4" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>1000</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5" t="s">
+        <v>255</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5">
+        <v>307</v>
+      </c>
+      <c r="H5" t="s">
+        <v>256</v>
+      </c>
+      <c r="I5" t="s">
+        <v>261</v>
+      </c>
+      <c r="J5" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>1000</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7" t="s">
+        <v>257</v>
+      </c>
+      <c r="F7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7">
+        <v>175</v>
+      </c>
+      <c r="H7" t="s">
+        <v>258</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="J7" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>1000</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9" t="s">
+        <v>265</v>
+      </c>
+      <c r="F9" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9">
+        <v>175</v>
+      </c>
+      <c r="H9" t="s">
+        <v>266</v>
+      </c>
+      <c r="I9" t="s">
+        <v>267</v>
+      </c>
+      <c r="J9" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>1000</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+      <c r="E11" t="s">
+        <v>269</v>
+      </c>
+      <c r="F11" t="s">
+        <v>25</v>
+      </c>
+      <c r="G11">
+        <v>175</v>
+      </c>
+      <c r="H11" t="s">
+        <v>270</v>
+      </c>
+      <c r="I11" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="J11" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A12" s="8"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A13" s="17">
+        <v>1000</v>
+      </c>
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" s="17">
+        <v>2</v>
+      </c>
+      <c r="H13" s="17" t="s">
+        <v>393</v>
+      </c>
+      <c r="I13" s="17" t="s">
+        <v>394</v>
+      </c>
+      <c r="J13" s="17" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>1000</v>
+      </c>
+      <c r="F15" t="s">
+        <v>36</v>
+      </c>
+      <c r="G15">
+        <v>175</v>
+      </c>
+      <c r="H15" t="s">
+        <v>396</v>
+      </c>
+      <c r="I15" s="11" t="s">
+        <v>397</v>
+      </c>
+      <c r="J15" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>1000</v>
+      </c>
+      <c r="F17" t="s">
+        <v>47</v>
+      </c>
+      <c r="G17">
+        <v>175</v>
+      </c>
+      <c r="H17" t="s">
+        <v>399</v>
+      </c>
+      <c r="I17" s="12" t="s">
+        <v>400</v>
+      </c>
+      <c r="J17" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>1000</v>
+      </c>
+      <c r="F19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G19">
+        <v>175</v>
+      </c>
+      <c r="H19" t="s">
+        <v>402</v>
+      </c>
+      <c r="I19" s="12" t="s">
+        <v>403</v>
+      </c>
+      <c r="J19" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A23" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="14"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A24" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A25" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" s="7">
+        <v>307</v>
+      </c>
+      <c r="C25" s="8">
+        <v>84</v>
+      </c>
+      <c r="D25" t="s">
+        <v>261</v>
+      </c>
+      <c r="E25" t="s">
+        <v>262</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G25" s="8">
+        <v>122</v>
+      </c>
+      <c r="H25" s="7">
+        <v>37</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="J25" s="7" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A26" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26">
+        <v>2</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26" t="s">
+        <v>394</v>
+      </c>
+      <c r="E26" t="s">
+        <v>395</v>
+      </c>
+      <c r="F26" s="8"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="F23:J23"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L31"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="15.1796875" customWidth="1"/>
+    <col min="2" max="2" width="13.90625" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="5" width="14.1796875" customWidth="1"/>
+    <col min="6" max="6" width="14.453125" customWidth="1"/>
+    <col min="7" max="7" width="13.6328125" customWidth="1"/>
+    <col min="8" max="8" width="14.26953125" customWidth="1"/>
+    <col min="9" max="9" width="13.453125" customWidth="1"/>
+    <col min="10" max="10" width="15.81640625" customWidth="1"/>
+    <col min="11" max="11" width="30.90625" customWidth="1"/>
+    <col min="12" max="12" width="75.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A1" s="7"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="H1" s="8"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" s="7"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" s="7"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>1000</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5" t="s">
+        <v>279</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5">
+        <v>291</v>
+      </c>
+      <c r="H5" t="s">
+        <v>274</v>
+      </c>
+      <c r="I5" t="s">
+        <v>275</v>
+      </c>
+      <c r="J5" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>1000</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7" t="s">
+        <v>280</v>
+      </c>
+      <c r="F7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7">
+        <v>175</v>
+      </c>
+      <c r="H7" t="s">
+        <v>281</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>282</v>
+      </c>
+      <c r="J7" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>1000</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9" t="s">
+        <v>284</v>
+      </c>
+      <c r="F9" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9">
+        <v>175</v>
+      </c>
+      <c r="H9" t="s">
+        <v>285</v>
+      </c>
+      <c r="I9" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="J9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>1000</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>287</v>
+      </c>
+      <c r="F11" t="s">
+        <v>25</v>
+      </c>
+      <c r="G11">
+        <v>175</v>
+      </c>
+      <c r="H11" t="s">
+        <v>288</v>
+      </c>
+      <c r="I11" s="12" t="s">
+        <v>289</v>
+      </c>
+      <c r="J11" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A12" s="8"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>1000</v>
+      </c>
+      <c r="F13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13">
+        <v>217</v>
+      </c>
+      <c r="H13" t="s">
+        <v>379</v>
+      </c>
+      <c r="I13" s="12" t="s">
+        <v>383</v>
+      </c>
+      <c r="J13" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>1000</v>
+      </c>
+      <c r="F15" t="s">
+        <v>36</v>
+      </c>
+      <c r="G15">
+        <v>175</v>
+      </c>
+      <c r="H15" t="s">
+        <v>380</v>
+      </c>
+      <c r="I15" s="11" t="s">
+        <v>381</v>
+      </c>
+      <c r="J15" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>1000</v>
+      </c>
+      <c r="F17" t="s">
+        <v>47</v>
+      </c>
+      <c r="G17">
+        <v>175</v>
+      </c>
+      <c r="H17" s="16" t="s">
+        <v>389</v>
+      </c>
+      <c r="I17" s="12" t="s">
+        <v>387</v>
+      </c>
+      <c r="J17" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>1000</v>
+      </c>
+      <c r="E19" s="15"/>
+      <c r="F19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G19">
+        <v>175</v>
+      </c>
+      <c r="H19" t="s">
+        <v>390</v>
+      </c>
+      <c r="I19" s="12" t="s">
+        <v>391</v>
+      </c>
+      <c r="J19" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A28" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="14"/>
+      <c r="J28" s="14"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A29" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="I29" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="J29" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A30" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B30" s="7">
+        <v>291</v>
+      </c>
+      <c r="C30" s="8">
+        <v>94</v>
+      </c>
+      <c r="D30" t="s">
+        <v>275</v>
+      </c>
+      <c r="E30" t="s">
+        <v>276</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G30" s="8">
+        <v>109</v>
+      </c>
+      <c r="H30" s="7">
+        <v>30</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="J30" s="7" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A31" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B31">
+        <v>217</v>
+      </c>
+      <c r="C31">
+        <v>266</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>383</v>
+      </c>
+      <c r="E31" t="s">
+        <v>384</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G31">
+        <v>122</v>
+      </c>
+      <c r="H31">
+        <v>77</v>
+      </c>
+      <c r="I31" s="12" t="s">
+        <v>385</v>
+      </c>
+      <c r="J31" t="s">
+        <v>386</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="F28:J28"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L28"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.90625" customWidth="1"/>
+    <col min="2" max="2" width="13.81640625" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="13.54296875" customWidth="1"/>
+    <col min="5" max="5" width="12.54296875" customWidth="1"/>
+    <col min="6" max="6" width="14.36328125" customWidth="1"/>
+    <col min="7" max="7" width="17.54296875" customWidth="1"/>
+    <col min="8" max="8" width="15.36328125" customWidth="1"/>
+    <col min="9" max="9" width="14.54296875" customWidth="1"/>
+    <col min="10" max="10" width="14.453125" customWidth="1"/>
+    <col min="11" max="11" width="31.08984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A1" s="7"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="H1" s="8"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" s="7"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" s="7"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>1000</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5" t="s">
+        <v>292</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5">
+        <v>276</v>
+      </c>
+      <c r="H5" t="s">
+        <v>293</v>
+      </c>
+      <c r="I5" t="s">
+        <v>296</v>
+      </c>
+      <c r="J5" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>1000</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7" t="s">
+        <v>294</v>
+      </c>
+      <c r="F7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7">
+        <v>175</v>
+      </c>
+      <c r="H7" t="s">
+        <v>295</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="J7" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>1000</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9" t="s">
+        <v>301</v>
+      </c>
+      <c r="F9" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9">
+        <v>175</v>
+      </c>
+      <c r="H9" t="s">
+        <v>302</v>
+      </c>
+      <c r="I9" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="J9" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>1000</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>305</v>
+      </c>
+      <c r="F11" t="s">
+        <v>25</v>
+      </c>
+      <c r="G11">
+        <v>175</v>
+      </c>
+      <c r="H11" t="s">
+        <v>232</v>
+      </c>
+      <c r="I11" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="J11" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A12" s="8"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>1000</v>
+      </c>
+      <c r="F13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13">
+        <v>228</v>
+      </c>
+      <c r="H13" t="s">
+        <v>365</v>
+      </c>
+      <c r="I13" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="J13" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>1000</v>
+      </c>
+      <c r="F15" t="s">
+        <v>36</v>
+      </c>
+      <c r="G15">
+        <v>175</v>
+      </c>
+      <c r="H15" t="s">
+        <v>370</v>
+      </c>
+      <c r="I15" s="11" t="s">
+        <v>371</v>
+      </c>
+      <c r="J15" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>1000</v>
+      </c>
+      <c r="F17" t="s">
+        <v>47</v>
+      </c>
+      <c r="G17">
+        <v>175</v>
+      </c>
+      <c r="H17" t="s">
+        <v>373</v>
+      </c>
+      <c r="I17" s="12" t="s">
+        <v>375</v>
+      </c>
+      <c r="J17" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>1000</v>
+      </c>
+      <c r="E19" s="15"/>
+      <c r="F19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G19">
+        <v>175</v>
+      </c>
+      <c r="H19" t="s">
+        <v>374</v>
+      </c>
+      <c r="I19" s="12" t="s">
+        <v>377</v>
+      </c>
+      <c r="J19" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A25" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="14"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A26" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="J26" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A27" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" s="7">
+        <v>276</v>
+      </c>
+      <c r="C27" s="8">
+        <v>75</v>
+      </c>
+      <c r="D27" t="s">
+        <v>296</v>
+      </c>
+      <c r="E27" t="s">
+        <v>297</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G27" s="8">
+        <v>121</v>
+      </c>
+      <c r="H27" s="7">
+        <v>42</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="J27" s="7" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28">
+        <v>228</v>
+      </c>
+      <c r="C28">
+        <v>285</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="E28" t="s">
+        <v>367</v>
+      </c>
+      <c r="F28" t="s">
+        <v>14</v>
+      </c>
+      <c r="G28">
+        <v>124</v>
+      </c>
+      <c r="H28">
+        <v>79</v>
+      </c>
+      <c r="I28" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="J28" t="s">
+        <v>369</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="F25:J25"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L28"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="14.90625" customWidth="1"/>
+    <col min="2" max="2" width="14.453125" customWidth="1"/>
+    <col min="3" max="3" width="13.453125" customWidth="1"/>
+    <col min="4" max="4" width="13.26953125" customWidth="1"/>
+    <col min="5" max="5" width="16.08984375" customWidth="1"/>
+    <col min="6" max="6" width="17.08984375" customWidth="1"/>
+    <col min="7" max="7" width="17.54296875" customWidth="1"/>
+    <col min="8" max="8" width="16.54296875" customWidth="1"/>
+    <col min="9" max="9" width="16.81640625" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="27.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A1" s="7"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="H1" s="8"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" s="7"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" s="7"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>1000</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5" t="s">
+        <v>308</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5">
+        <v>288</v>
+      </c>
+      <c r="H5" t="s">
+        <v>309</v>
+      </c>
+      <c r="I5" t="s">
+        <v>310</v>
+      </c>
+      <c r="J5" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>1000</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7" t="s">
+        <v>314</v>
+      </c>
+      <c r="F7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7">
+        <v>175</v>
+      </c>
+      <c r="H7" t="s">
+        <v>315</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="J7" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>1000</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9" t="s">
+        <v>318</v>
+      </c>
+      <c r="F9" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9">
+        <v>175</v>
+      </c>
+      <c r="H9" t="s">
+        <v>319</v>
+      </c>
+      <c r="I9" s="12" t="s">
+        <v>317</v>
+      </c>
+      <c r="J9" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>1000</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>321</v>
+      </c>
+      <c r="F11" t="s">
+        <v>25</v>
+      </c>
+      <c r="G11">
+        <v>175</v>
+      </c>
+      <c r="H11" t="s">
+        <v>232</v>
+      </c>
+      <c r="I11" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="J11" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A12" s="8"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>1000</v>
+      </c>
+      <c r="F13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13">
+        <v>240</v>
+      </c>
+      <c r="H13" t="s">
+        <v>351</v>
+      </c>
+      <c r="I13" s="12" t="s">
+        <v>353</v>
+      </c>
+      <c r="J13" s="16" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>1000</v>
+      </c>
+      <c r="F15" t="s">
+        <v>36</v>
+      </c>
+      <c r="G15">
+        <v>175</v>
+      </c>
+      <c r="H15" t="s">
+        <v>352</v>
+      </c>
+      <c r="I15" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="J15" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>1000</v>
+      </c>
+      <c r="F17" t="s">
+        <v>47</v>
+      </c>
+      <c r="G17">
+        <v>175</v>
+      </c>
+      <c r="H17" t="s">
+        <v>359</v>
+      </c>
+      <c r="I17" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="J17" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>1000</v>
+      </c>
+      <c r="E19" s="15"/>
+      <c r="F19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G19">
+        <v>175</v>
+      </c>
+      <c r="H19" t="s">
+        <v>362</v>
+      </c>
+      <c r="I19" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="J19" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A25" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="14"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A26" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="J26" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A27" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" s="7">
+        <v>288</v>
+      </c>
+      <c r="C27" s="8">
+        <v>83</v>
+      </c>
+      <c r="D27" t="s">
+        <v>310</v>
+      </c>
+      <c r="E27" t="s">
+        <v>311</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G27" s="8">
+        <v>118</v>
+      </c>
+      <c r="H27" s="7">
+        <v>37</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="J27" s="7" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A28" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28">
+        <v>240</v>
+      </c>
+      <c r="C28">
+        <v>252</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>353</v>
+      </c>
+      <c r="E28" s="16">
+        <v>246380</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G28" s="8">
+        <v>136</v>
+      </c>
+      <c r="H28" s="8">
+        <v>84</v>
+      </c>
+      <c r="I28" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="J28" t="s">
+        <v>355</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="F25:J25"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L33"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="2" width="14.08984375" customWidth="1"/>
+    <col min="3" max="3" width="13.36328125" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" customWidth="1"/>
+    <col min="5" max="5" width="12.7265625" customWidth="1"/>
+    <col min="6" max="6" width="17.36328125" customWidth="1"/>
+    <col min="7" max="7" width="14.6328125" customWidth="1"/>
+    <col min="8" max="8" width="14.54296875" customWidth="1"/>
+    <col min="9" max="9" width="14.08984375" customWidth="1"/>
+    <col min="10" max="10" width="16.08984375" customWidth="1"/>
+    <col min="11" max="11" width="43.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A1" s="7"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="H1" s="8"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" s="7"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" s="7"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>1000</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5" t="s">
+        <v>325</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5">
+        <v>289</v>
+      </c>
+      <c r="H5" t="s">
+        <v>326</v>
+      </c>
+      <c r="I5" t="s">
+        <v>329</v>
+      </c>
+      <c r="J5" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>1000</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7" t="s">
+        <v>327</v>
+      </c>
+      <c r="F7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7">
+        <v>175</v>
+      </c>
+      <c r="H7" t="s">
+        <v>328</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>332</v>
+      </c>
+      <c r="J7" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>1000</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9" t="s">
+        <v>334</v>
+      </c>
+      <c r="F9" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9">
+        <v>175</v>
+      </c>
+      <c r="H9" t="s">
+        <v>335</v>
+      </c>
+      <c r="I9" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="J9" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>1000</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>338</v>
+      </c>
+      <c r="F11" t="s">
+        <v>25</v>
+      </c>
+      <c r="G11">
+        <v>175</v>
+      </c>
+      <c r="H11" t="s">
+        <v>251</v>
+      </c>
+      <c r="I11" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="J11" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A12" s="8"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>1000</v>
+      </c>
+      <c r="F13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13">
+        <v>245</v>
+      </c>
+      <c r="H13" t="s">
+        <v>274</v>
+      </c>
+      <c r="I13" s="12" t="s">
+        <v>343</v>
+      </c>
+      <c r="J13" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>1000</v>
+      </c>
+      <c r="F15" t="s">
+        <v>36</v>
+      </c>
+      <c r="G15">
+        <v>175</v>
+      </c>
+      <c r="H15" t="s">
+        <v>340</v>
+      </c>
+      <c r="I15" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="J15" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>1000</v>
+      </c>
+      <c r="F17" t="s">
+        <v>47</v>
+      </c>
+      <c r="G17">
+        <v>175</v>
+      </c>
+      <c r="H17" t="s">
+        <v>346</v>
+      </c>
+      <c r="I17" s="12" t="s">
+        <v>347</v>
+      </c>
+      <c r="J17" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>1000</v>
+      </c>
+      <c r="F19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G19">
+        <v>175</v>
+      </c>
+      <c r="H19" t="s">
+        <v>178</v>
+      </c>
+      <c r="I19" s="12" t="s">
+        <v>349</v>
+      </c>
+      <c r="J19" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A30" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="14"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A31" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="I31" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="J31" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A32" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B32" s="7">
+        <v>289</v>
+      </c>
+      <c r="C32" s="8">
+        <v>97</v>
+      </c>
+      <c r="D32" t="s">
+        <v>329</v>
+      </c>
+      <c r="E32" t="s">
+        <v>330</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G32" s="8">
+        <v>117</v>
+      </c>
+      <c r="H32" s="7">
+        <v>35</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="J32" s="7" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>14</v>
+      </c>
+      <c r="B33">
+        <v>245</v>
+      </c>
+      <c r="C33">
+        <v>275</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>343</v>
+      </c>
+      <c r="E33" t="s">
+        <v>344</v>
+      </c>
+      <c r="F33" t="s">
+        <v>14</v>
+      </c>
+      <c r="G33">
+        <v>143</v>
+      </c>
+      <c r="H33">
+        <v>91</v>
+      </c>
+      <c r="I33" s="12" t="s">
+        <v>345</v>
+      </c>
+      <c r="J33" s="16">
+        <v>76609</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="F30:J30"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L58"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="15.453125" customWidth="1"/>
+    <col min="2" max="2" width="16.36328125" customWidth="1"/>
+    <col min="3" max="3" width="13.08984375" customWidth="1"/>
+    <col min="4" max="4" width="13.1796875" customWidth="1"/>
+    <col min="5" max="5" width="13.36328125" customWidth="1"/>
+    <col min="6" max="6" width="15.7265625" customWidth="1"/>
+    <col min="7" max="7" width="13.26953125" customWidth="1"/>
+    <col min="8" max="8" width="13.7265625" customWidth="1"/>
+    <col min="9" max="9" width="13.90625" customWidth="1"/>
+    <col min="10" max="10" width="13" customWidth="1"/>
+    <col min="11" max="11" width="29.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A1" s="7"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="9" t="s">
+        <v>405</v>
+      </c>
+      <c r="H1" s="8"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" s="7"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" s="7"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>1000</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5" t="s">
+        <v>434</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5">
+        <v>298</v>
+      </c>
+      <c r="H5" t="s">
+        <v>435</v>
+      </c>
+      <c r="I5" t="s">
+        <v>439</v>
+      </c>
+      <c r="J5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>1000</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7" t="s">
+        <v>436</v>
+      </c>
+      <c r="F7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7">
+        <v>175</v>
+      </c>
+      <c r="H7" t="s">
+        <v>437</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="J7" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>1000</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9" t="s">
+        <v>445</v>
+      </c>
+      <c r="F9" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9">
+        <v>175</v>
+      </c>
+      <c r="H9" t="s">
+        <v>446</v>
+      </c>
+      <c r="I9" s="12" t="s">
+        <v>447</v>
+      </c>
+      <c r="J9" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>1000</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>442</v>
+      </c>
+      <c r="F11" t="s">
+        <v>25</v>
+      </c>
+      <c r="G11">
+        <v>175</v>
+      </c>
+      <c r="H11" t="s">
+        <v>178</v>
+      </c>
+      <c r="I11" s="12" t="s">
+        <v>443</v>
+      </c>
+      <c r="J11" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A12" s="8"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>1000</v>
+      </c>
+      <c r="F13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13">
+        <v>253</v>
+      </c>
+      <c r="H13" t="s">
+        <v>406</v>
+      </c>
+      <c r="I13" s="12" t="s">
+        <v>407</v>
+      </c>
+      <c r="J13" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>1000</v>
+      </c>
+      <c r="F15" t="s">
+        <v>36</v>
+      </c>
+      <c r="G15">
+        <v>175</v>
+      </c>
+      <c r="H15" t="s">
+        <v>411</v>
+      </c>
+      <c r="I15" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="J15" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>1000</v>
+      </c>
+      <c r="F17" t="s">
+        <v>47</v>
+      </c>
+      <c r="G17">
+        <v>175</v>
+      </c>
+      <c r="H17" t="s">
+        <v>413</v>
+      </c>
+      <c r="I17" s="12" t="s">
+        <v>415</v>
+      </c>
+      <c r="J17" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>1000</v>
+      </c>
+      <c r="F19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G19">
+        <v>175</v>
+      </c>
+      <c r="H19" t="s">
+        <v>414</v>
+      </c>
+      <c r="I19" s="12" t="s">
+        <v>417</v>
+      </c>
+      <c r="J19" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A24" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A25" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A26" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" s="7">
+        <v>298</v>
+      </c>
+      <c r="C26" s="8">
+        <v>115</v>
+      </c>
+      <c r="D26" t="s">
+        <v>439</v>
+      </c>
+      <c r="E26" t="s">
+        <v>440</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G26" s="8">
+        <v>104</v>
+      </c>
+      <c r="H26" s="7">
+        <v>22</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="J26" s="7" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27">
+        <v>253</v>
+      </c>
+      <c r="C27">
+        <v>255</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>407</v>
+      </c>
+      <c r="E27" t="s">
+        <v>408</v>
+      </c>
+      <c r="F27" t="s">
+        <v>14</v>
+      </c>
+      <c r="G27">
+        <v>141</v>
+      </c>
+      <c r="H27">
+        <v>81</v>
+      </c>
+      <c r="I27" s="12" t="s">
+        <v>409</v>
+      </c>
+      <c r="J27" s="16" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A32" s="7"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="8"/>
+      <c r="G32" s="9" t="s">
+        <v>419</v>
+      </c>
+      <c r="H32" s="8"/>
+      <c r="I32" s="7"/>
+      <c r="J32" s="8"/>
+      <c r="K32" s="8"/>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A33" s="7"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="7"/>
+      <c r="H33" s="8"/>
+      <c r="I33" s="7"/>
+      <c r="J33" s="8"/>
+      <c r="K33" s="8"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A34" s="7"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="7"/>
+      <c r="H34" s="8"/>
+      <c r="I34" s="7"/>
+      <c r="J34" s="8"/>
+      <c r="K34" s="8"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A35" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="H35" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I35" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J35" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K35" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="L35" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>1000</v>
+      </c>
+      <c r="D36">
+        <v>2</v>
+      </c>
+      <c r="F36" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>1000</v>
+      </c>
+      <c r="D38">
+        <v>2</v>
+      </c>
+      <c r="F38" t="s">
+        <v>36</v>
+      </c>
+      <c r="G38">
+        <v>175</v>
+      </c>
+      <c r="I38" s="11"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>1000</v>
+      </c>
+      <c r="D40">
+        <v>2</v>
+      </c>
+      <c r="F40" t="s">
+        <v>47</v>
+      </c>
+      <c r="G40">
+        <v>175</v>
+      </c>
+      <c r="I40" s="12"/>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>1000</v>
+      </c>
+      <c r="D42">
+        <v>2</v>
+      </c>
+      <c r="E42" s="15"/>
+      <c r="F42" t="s">
+        <v>25</v>
+      </c>
+      <c r="G42">
+        <v>175</v>
+      </c>
+      <c r="I42" s="12"/>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A43" s="8"/>
+      <c r="B43" s="7"/>
+      <c r="C43" s="8"/>
+      <c r="D43" s="7"/>
+      <c r="E43" s="8"/>
+      <c r="F43" s="7"/>
+      <c r="G43" s="8"/>
+      <c r="H43" s="7"/>
+      <c r="I43" s="8"/>
+      <c r="J43" s="8"/>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>1000</v>
+      </c>
+      <c r="F44" t="s">
+        <v>14</v>
+      </c>
+      <c r="G44">
+        <v>303</v>
+      </c>
+      <c r="H44" t="s">
+        <v>420</v>
+      </c>
+      <c r="I44" s="12" t="s">
+        <v>421</v>
+      </c>
+      <c r="J44" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>1000</v>
+      </c>
+      <c r="F46" t="s">
+        <v>36</v>
+      </c>
+      <c r="G46">
+        <v>175</v>
+      </c>
+      <c r="H46" t="s">
+        <v>425</v>
+      </c>
+      <c r="I46" s="12" t="s">
+        <v>426</v>
+      </c>
+      <c r="J46" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>1000</v>
+      </c>
+      <c r="F48" t="s">
+        <v>47</v>
+      </c>
+      <c r="G48">
+        <v>175</v>
+      </c>
+      <c r="H48" t="s">
+        <v>431</v>
+      </c>
+      <c r="I48" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="J48" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <v>1000</v>
+      </c>
+      <c r="F50" t="s">
+        <v>25</v>
+      </c>
+      <c r="G50">
+        <v>175</v>
+      </c>
+      <c r="H50" t="s">
+        <v>428</v>
+      </c>
+      <c r="I50" s="12" t="s">
+        <v>429</v>
+      </c>
+      <c r="J50" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A55" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="B55" s="13"/>
+      <c r="C55" s="13"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="G55" s="14"/>
+      <c r="H55" s="14"/>
+      <c r="I55" s="14"/>
+      <c r="J55" s="14"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A56" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="G56" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="H56" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="I56" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="J56" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A57" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B57" s="7"/>
+      <c r="C57" s="8"/>
+      <c r="F57" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G57" s="8"/>
+      <c r="H57" s="7"/>
+      <c r="I57" s="6"/>
+      <c r="J57" s="7"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>14</v>
+      </c>
+      <c r="B58">
+        <v>303</v>
+      </c>
+      <c r="C58">
+        <v>137</v>
+      </c>
+      <c r="D58" s="12" t="s">
+        <v>421</v>
+      </c>
+      <c r="E58" t="s">
+        <v>422</v>
+      </c>
+      <c r="F58" t="s">
+        <v>14</v>
+      </c>
+      <c r="G58">
+        <v>143</v>
+      </c>
+      <c r="H58">
+        <v>64</v>
+      </c>
+      <c r="I58" s="12" t="s">
+        <v>423</v>
+      </c>
+      <c r="J58" s="16" t="s">
+        <v>424</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="F24:J24"/>
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="F55:J55"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Experiments/DBCV_Conclu.xlsx
+++ b/Experiments/DBCV_Conclu.xlsx
@@ -9,25 +9,26 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18190" windowHeight="8510" activeTab="8"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18192" windowHeight="8508" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
-    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
-    <sheet name="Sheet5" sheetId="5" r:id="rId5"/>
-    <sheet name="Sheet6" sheetId="6" r:id="rId6"/>
-    <sheet name="Sheet7" sheetId="7" r:id="rId7"/>
-    <sheet name="Sheet8" sheetId="8" r:id="rId8"/>
-    <sheet name="Sheet9" sheetId="9" r:id="rId9"/>
+    <sheet name="Sheet10" sheetId="10" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId5"/>
+    <sheet name="Sheet5" sheetId="5" r:id="rId6"/>
+    <sheet name="Sheet6" sheetId="6" r:id="rId7"/>
+    <sheet name="Sheet7" sheetId="7" r:id="rId8"/>
+    <sheet name="Sheet8" sheetId="8" r:id="rId9"/>
+    <sheet name="Sheet9" sheetId="9" r:id="rId10"/>
   </sheets>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1046" uniqueCount="501">
   <si>
     <t>Datapoints</t>
   </si>
@@ -1383,6 +1384,162 @@
   </si>
   <si>
     <t>92.449 secs</t>
+  </si>
+  <si>
+    <t>TEST DATASET(2048)</t>
+  </si>
+  <si>
+    <t>18.507 secs</t>
+  </si>
+  <si>
+    <t>3.594 secs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.189 </t>
+  </si>
+  <si>
+    <t>243.297 secs</t>
+  </si>
+  <si>
+    <t>(K=64)</t>
+  </si>
+  <si>
+    <t>(K=32)</t>
+  </si>
+  <si>
+    <t>16.595 secs</t>
+  </si>
+  <si>
+    <t>3.709 secs</t>
+  </si>
+  <si>
+    <t>0.222 secs</t>
+  </si>
+  <si>
+    <t>-0.040</t>
+  </si>
+  <si>
+    <t>102.518 secs</t>
+  </si>
+  <si>
+    <t>15.525 secs</t>
+  </si>
+  <si>
+    <t>3.368 secs</t>
+  </si>
+  <si>
+    <t>-0.013</t>
+  </si>
+  <si>
+    <t>109.668 secs</t>
+  </si>
+  <si>
+    <t>18.593 secs</t>
+  </si>
+  <si>
+    <t>0.020</t>
+  </si>
+  <si>
+    <t>3.918 secs</t>
+  </si>
+  <si>
+    <t>9.257 secs</t>
+  </si>
+  <si>
+    <t>101.925 secs</t>
+  </si>
+  <si>
+    <t>3.744 secs</t>
+  </si>
+  <si>
+    <t>0.197</t>
+  </si>
+  <si>
+    <t>0.123 secs</t>
+  </si>
+  <si>
+    <t>234.075 secs</t>
+  </si>
+  <si>
+    <t>56.809 secs</t>
+  </si>
+  <si>
+    <t>3.731 secs</t>
+  </si>
+  <si>
+    <t>0.176 secs</t>
+  </si>
+  <si>
+    <t>-0.029</t>
+  </si>
+  <si>
+    <t>101.171 secs</t>
+  </si>
+  <si>
+    <t>(K=16)</t>
+  </si>
+  <si>
+    <t>3.663 secs</t>
+  </si>
+  <si>
+    <t>-0.007</t>
+  </si>
+  <si>
+    <t>102.203 secs</t>
+  </si>
+  <si>
+    <t>3.349 secs</t>
+  </si>
+  <si>
+    <t>7.221 secs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.042 </t>
+  </si>
+  <si>
+    <t>100.748 secs</t>
+  </si>
+  <si>
+    <t>3.797 secs</t>
+  </si>
+  <si>
+    <t>244.248 secs</t>
+  </si>
+  <si>
+    <t>-0.030</t>
+  </si>
+  <si>
+    <t>57.618 secs</t>
+  </si>
+  <si>
+    <t>3.557 secs</t>
+  </si>
+  <si>
+    <t>0.257 secs</t>
+  </si>
+  <si>
+    <t>0.140 secs</t>
+  </si>
+  <si>
+    <t>-0.50</t>
+  </si>
+  <si>
+    <t>100.699 secs</t>
+  </si>
+  <si>
+    <t>104.203 secs</t>
+  </si>
+  <si>
+    <t>3.480 secs</t>
+  </si>
+  <si>
+    <t>6.331 secs</t>
+  </si>
+  <si>
+    <t>0.030</t>
+  </si>
+  <si>
+    <t>103.005 secs</t>
   </si>
 </sst>
 </file>
@@ -1466,7 +1623,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
@@ -1486,15 +1643,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1801,32 +1959,32 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:N74"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.36328125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.90625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.88671875" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.90625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.90625" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.54296875" style="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.54296875" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.90625" style="8" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.54296875" style="7" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.54296875" style="8" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.6328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.08984375" style="8" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="29.90625" style="8" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="80.90625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.88671875" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.88671875" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.88671875" style="8" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="29.88671875" style="8" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="80.88671875" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G1" s="9" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="4" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -1870,7 +2028,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>1000</v>
       </c>
@@ -1906,7 +2064,7 @@
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
     </row>
-    <row r="6" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>1000</v>
       </c>
@@ -1942,7 +2100,7 @@
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
     </row>
-    <row r="7" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>1000</v>
       </c>
@@ -1978,7 +2136,7 @@
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
     </row>
-    <row r="8" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>1000</v>
       </c>
@@ -2014,7 +2172,7 @@
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
     </row>
-    <row r="9" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>1000</v>
       </c>
@@ -2050,7 +2208,7 @@
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
     </row>
-    <row r="10" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>1000</v>
       </c>
@@ -2086,7 +2244,7 @@
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
     </row>
-    <row r="11" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>1000</v>
       </c>
@@ -2126,7 +2284,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>1000</v>
       </c>
@@ -2162,7 +2320,7 @@
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
     </row>
-    <row r="13" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="2"/>
@@ -2175,7 +2333,7 @@
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
     </row>
-    <row r="14" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7">
         <v>1000</v>
       </c>
@@ -2205,7 +2363,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="7"/>
       <c r="C15" s="8"/>
       <c r="D15" s="7"/>
@@ -2213,7 +2371,7 @@
       <c r="F15" s="7"/>
       <c r="G15" s="8"/>
     </row>
-    <row r="16" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7">
         <v>1000</v>
       </c>
@@ -2243,7 +2401,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="7"/>
       <c r="C17" s="8"/>
       <c r="D17" s="7"/>
@@ -2252,7 +2410,7 @@
       <c r="G17" s="8"/>
       <c r="K17" s="6"/>
     </row>
-    <row r="18" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="7">
         <v>1000</v>
       </c>
@@ -2282,7 +2440,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="7"/>
       <c r="C19" s="8"/>
       <c r="D19" s="7"/>
@@ -2291,7 +2449,7 @@
       <c r="G19" s="8"/>
       <c r="K19" s="6"/>
     </row>
-    <row r="20" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="7">
         <v>1000</v>
       </c>
@@ -2321,7 +2479,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="7"/>
       <c r="C21" s="8"/>
       <c r="D21" s="7"/>
@@ -2329,23 +2487,23 @@
       <c r="F21" s="7"/>
       <c r="G21" s="8"/>
     </row>
-    <row r="22" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="13" t="s">
+    <row r="22" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="14" t="s">
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="H22" s="14"/>
-      <c r="I22" s="14"/>
-      <c r="J22" s="14"/>
-      <c r="K22" s="14"/>
-    </row>
-    <row r="23" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H22" s="17"/>
+      <c r="I22" s="17"/>
+      <c r="J22" s="17"/>
+      <c r="K22" s="17"/>
+    </row>
+    <row r="23" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="8" t="s">
         <v>184</v>
       </c>
@@ -2377,7 +2535,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="7">
         <v>1000</v>
       </c>
@@ -2412,7 +2570,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="2"/>
@@ -2425,7 +2583,7 @@
       <c r="M25" s="2"/>
       <c r="N25" s="2"/>
     </row>
-    <row r="26" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>2000</v>
       </c>
@@ -2461,7 +2619,7 @@
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
     </row>
-    <row r="27" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <v>2000</v>
       </c>
@@ -2497,7 +2655,7 @@
       <c r="M27" s="2"/>
       <c r="N27" s="2"/>
     </row>
-    <row r="28" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <v>2000</v>
       </c>
@@ -2535,7 +2693,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <v>2000</v>
       </c>
@@ -2571,7 +2729,7 @@
       <c r="M29" s="2"/>
       <c r="N29" s="2"/>
     </row>
-    <row r="30" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <v>2000</v>
       </c>
@@ -2607,7 +2765,7 @@
       <c r="M30" s="2"/>
       <c r="N30" s="2"/>
     </row>
-    <row r="31" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>2000</v>
       </c>
@@ -2643,7 +2801,7 @@
       <c r="M31" s="2"/>
       <c r="N31" s="2"/>
     </row>
-    <row r="32" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <v>2000</v>
       </c>
@@ -2679,7 +2837,7 @@
       <c r="M32" s="2"/>
       <c r="N32" s="2"/>
     </row>
-    <row r="33" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <v>2000</v>
       </c>
@@ -2715,7 +2873,7 @@
       <c r="M33" s="2"/>
       <c r="N33" s="2"/>
     </row>
-    <row r="34" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="2"/>
@@ -2728,7 +2886,7 @@
       <c r="M34" s="2"/>
       <c r="N34" s="2"/>
     </row>
-    <row r="35" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="2"/>
@@ -2741,7 +2899,7 @@
       <c r="M35" s="2"/>
       <c r="N35" s="2"/>
     </row>
-    <row r="36" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
         <v>5000</v>
       </c>
@@ -2777,7 +2935,7 @@
       <c r="M36" s="2"/>
       <c r="N36" s="2"/>
     </row>
-    <row r="37" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>5000</v>
       </c>
@@ -2815,7 +2973,7 @@
       </c>
       <c r="N37" s="2"/>
     </row>
-    <row r="38" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
         <v>5000</v>
       </c>
@@ -2851,7 +3009,7 @@
       <c r="M38" s="2"/>
       <c r="N38" s="2"/>
     </row>
-    <row r="39" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>5000</v>
       </c>
@@ -2889,7 +3047,7 @@
       </c>
       <c r="N39" s="2"/>
     </row>
-    <row r="40" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>5000</v>
       </c>
@@ -2925,7 +3083,7 @@
       <c r="M40" s="2"/>
       <c r="N40" s="2"/>
     </row>
-    <row r="41" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>5000</v>
       </c>
@@ -2965,7 +3123,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="42" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>5000</v>
       </c>
@@ -3001,7 +3159,7 @@
       <c r="M42" s="2"/>
       <c r="N42" s="2"/>
     </row>
-    <row r="43" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>5000</v>
       </c>
@@ -3037,7 +3195,7 @@
       <c r="M43" s="2"/>
       <c r="N43" s="2"/>
     </row>
-    <row r="44" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="2"/>
       <c r="C44" s="1"/>
@@ -3053,7 +3211,7 @@
       <c r="M44" s="2"/>
       <c r="N44" s="2"/>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="B45" s="2"/>
       <c r="C45" s="1"/>
@@ -3069,7 +3227,7 @@
       <c r="M45" s="2"/>
       <c r="N45" s="2"/>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
       <c r="B46" s="2"/>
       <c r="C46" s="1"/>
@@ -3085,7 +3243,7 @@
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>102</v>
       </c>
@@ -3103,23 +3261,23 @@
       <c r="M47" s="2"/>
       <c r="N47" s="2"/>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="B48" s="13" t="s">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B48" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="C48" s="13"/>
-      <c r="D48" s="13"/>
-      <c r="E48" s="13"/>
-      <c r="F48" s="13"/>
-      <c r="G48" s="14" t="s">
+      <c r="C48" s="16"/>
+      <c r="D48" s="16"/>
+      <c r="E48" s="16"/>
+      <c r="F48" s="16"/>
+      <c r="G48" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="H48" s="14"/>
-      <c r="I48" s="14"/>
-      <c r="J48" s="14"/>
-      <c r="K48" s="14"/>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="H48" s="17"/>
+      <c r="I48" s="17"/>
+      <c r="J48" s="17"/>
+      <c r="K48" s="17"/>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B49" s="8" t="s">
         <v>184</v>
       </c>
@@ -3151,7 +3309,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" s="7">
         <v>1000</v>
       </c>
@@ -3186,12 +3344,12 @@
         <v>194</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="G65" s="9" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" s="7" t="s">
         <v>0</v>
       </c>
@@ -3235,7 +3393,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" s="7">
         <v>1000</v>
       </c>
@@ -3267,7 +3425,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" s="7">
         <v>1000</v>
       </c>
@@ -3299,7 +3457,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" s="7">
         <v>1000</v>
       </c>
@@ -3331,7 +3489,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" s="7">
         <v>1000</v>
       </c>
@@ -3366,7 +3524,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" s="7">
         <v>1000</v>
       </c>
@@ -3398,7 +3556,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" s="7">
         <v>1000</v>
       </c>
@@ -3430,7 +3588,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" s="7">
         <v>1000</v>
       </c>
@@ -3462,7 +3620,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" s="7">
         <v>1000</v>
       </c>
@@ -3506,24 +3664,1250 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L58"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.44140625" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" customWidth="1"/>
+    <col min="3" max="3" width="13.109375" customWidth="1"/>
+    <col min="4" max="4" width="13.21875" customWidth="1"/>
+    <col min="5" max="5" width="13.33203125" customWidth="1"/>
+    <col min="6" max="6" width="15.77734375" customWidth="1"/>
+    <col min="7" max="7" width="13.21875" customWidth="1"/>
+    <col min="8" max="8" width="13.77734375" customWidth="1"/>
+    <col min="9" max="9" width="13.88671875" customWidth="1"/>
+    <col min="10" max="10" width="13" customWidth="1"/>
+    <col min="11" max="11" width="29.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1" s="7"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="9" t="s">
+        <v>405</v>
+      </c>
+      <c r="H1" s="8"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="7"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="7"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>1000</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5" t="s">
+        <v>434</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5">
+        <v>298</v>
+      </c>
+      <c r="H5" t="s">
+        <v>435</v>
+      </c>
+      <c r="I5" t="s">
+        <v>439</v>
+      </c>
+      <c r="J5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>1000</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7" t="s">
+        <v>436</v>
+      </c>
+      <c r="F7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7">
+        <v>175</v>
+      </c>
+      <c r="H7" t="s">
+        <v>437</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="J7" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>1000</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9" t="s">
+        <v>445</v>
+      </c>
+      <c r="F9" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9">
+        <v>175</v>
+      </c>
+      <c r="H9" t="s">
+        <v>446</v>
+      </c>
+      <c r="I9" s="12" t="s">
+        <v>447</v>
+      </c>
+      <c r="J9" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>1000</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>442</v>
+      </c>
+      <c r="F11" t="s">
+        <v>25</v>
+      </c>
+      <c r="G11">
+        <v>175</v>
+      </c>
+      <c r="H11" t="s">
+        <v>178</v>
+      </c>
+      <c r="I11" s="12" t="s">
+        <v>443</v>
+      </c>
+      <c r="J11" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" s="8"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>1000</v>
+      </c>
+      <c r="F13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13">
+        <v>253</v>
+      </c>
+      <c r="H13" t="s">
+        <v>406</v>
+      </c>
+      <c r="I13" s="12" t="s">
+        <v>407</v>
+      </c>
+      <c r="J13" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>1000</v>
+      </c>
+      <c r="F15" t="s">
+        <v>36</v>
+      </c>
+      <c r="G15">
+        <v>175</v>
+      </c>
+      <c r="H15" t="s">
+        <v>411</v>
+      </c>
+      <c r="I15" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="J15" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>1000</v>
+      </c>
+      <c r="F17" t="s">
+        <v>47</v>
+      </c>
+      <c r="G17">
+        <v>175</v>
+      </c>
+      <c r="H17" t="s">
+        <v>413</v>
+      </c>
+      <c r="I17" s="12" t="s">
+        <v>415</v>
+      </c>
+      <c r="J17" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>1000</v>
+      </c>
+      <c r="F19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G19">
+        <v>175</v>
+      </c>
+      <c r="H19" t="s">
+        <v>414</v>
+      </c>
+      <c r="I19" s="12" t="s">
+        <v>417</v>
+      </c>
+      <c r="J19" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="B24" s="16"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="17" t="s">
+        <v>187</v>
+      </c>
+      <c r="G24" s="17"/>
+      <c r="H24" s="17"/>
+      <c r="I24" s="17"/>
+      <c r="J24" s="17"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" s="7">
+        <v>298</v>
+      </c>
+      <c r="C26" s="8">
+        <v>115</v>
+      </c>
+      <c r="D26" t="s">
+        <v>439</v>
+      </c>
+      <c r="E26" t="s">
+        <v>440</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G26" s="8">
+        <v>104</v>
+      </c>
+      <c r="H26" s="7">
+        <v>22</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="J26" s="7" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27">
+        <v>253</v>
+      </c>
+      <c r="C27">
+        <v>255</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>407</v>
+      </c>
+      <c r="E27" t="s">
+        <v>408</v>
+      </c>
+      <c r="F27" t="s">
+        <v>14</v>
+      </c>
+      <c r="G27">
+        <v>141</v>
+      </c>
+      <c r="H27">
+        <v>81</v>
+      </c>
+      <c r="I27" s="12" t="s">
+        <v>409</v>
+      </c>
+      <c r="J27" s="14" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A32" s="7"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="8"/>
+      <c r="G32" s="9" t="s">
+        <v>419</v>
+      </c>
+      <c r="H32" s="8"/>
+      <c r="I32" s="7"/>
+      <c r="J32" s="8"/>
+      <c r="K32" s="8"/>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A33" s="7"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="7"/>
+      <c r="H33" s="8"/>
+      <c r="I33" s="7"/>
+      <c r="J33" s="8"/>
+      <c r="K33" s="8"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A34" s="7"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="7"/>
+      <c r="H34" s="8"/>
+      <c r="I34" s="7"/>
+      <c r="J34" s="8"/>
+      <c r="K34" s="8"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A35" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="H35" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I35" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J35" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K35" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="L35" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>1000</v>
+      </c>
+      <c r="D36">
+        <v>2</v>
+      </c>
+      <c r="F36" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>1000</v>
+      </c>
+      <c r="D38">
+        <v>2</v>
+      </c>
+      <c r="F38" t="s">
+        <v>36</v>
+      </c>
+      <c r="G38">
+        <v>175</v>
+      </c>
+      <c r="I38" s="11"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>1000</v>
+      </c>
+      <c r="D40">
+        <v>2</v>
+      </c>
+      <c r="F40" t="s">
+        <v>47</v>
+      </c>
+      <c r="G40">
+        <v>175</v>
+      </c>
+      <c r="I40" s="12"/>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>1000</v>
+      </c>
+      <c r="D42">
+        <v>2</v>
+      </c>
+      <c r="E42" s="13"/>
+      <c r="F42" t="s">
+        <v>25</v>
+      </c>
+      <c r="G42">
+        <v>175</v>
+      </c>
+      <c r="I42" s="12"/>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A43" s="8"/>
+      <c r="B43" s="7"/>
+      <c r="C43" s="8"/>
+      <c r="D43" s="7"/>
+      <c r="E43" s="8"/>
+      <c r="F43" s="7"/>
+      <c r="G43" s="8"/>
+      <c r="H43" s="7"/>
+      <c r="I43" s="8"/>
+      <c r="J43" s="8"/>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>1000</v>
+      </c>
+      <c r="F44" t="s">
+        <v>14</v>
+      </c>
+      <c r="G44">
+        <v>303</v>
+      </c>
+      <c r="H44" t="s">
+        <v>420</v>
+      </c>
+      <c r="I44" s="12" t="s">
+        <v>421</v>
+      </c>
+      <c r="J44" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>1000</v>
+      </c>
+      <c r="F46" t="s">
+        <v>36</v>
+      </c>
+      <c r="G46">
+        <v>175</v>
+      </c>
+      <c r="H46" t="s">
+        <v>425</v>
+      </c>
+      <c r="I46" s="12" t="s">
+        <v>426</v>
+      </c>
+      <c r="J46" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>1000</v>
+      </c>
+      <c r="F48" t="s">
+        <v>47</v>
+      </c>
+      <c r="G48">
+        <v>175</v>
+      </c>
+      <c r="H48" t="s">
+        <v>431</v>
+      </c>
+      <c r="I48" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="J48" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>1000</v>
+      </c>
+      <c r="F50" t="s">
+        <v>25</v>
+      </c>
+      <c r="G50">
+        <v>175</v>
+      </c>
+      <c r="H50" t="s">
+        <v>428</v>
+      </c>
+      <c r="I50" s="12" t="s">
+        <v>429</v>
+      </c>
+      <c r="J50" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A55" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="B55" s="16"/>
+      <c r="C55" s="16"/>
+      <c r="D55" s="16"/>
+      <c r="E55" s="16"/>
+      <c r="F55" s="17" t="s">
+        <v>187</v>
+      </c>
+      <c r="G55" s="17"/>
+      <c r="H55" s="17"/>
+      <c r="I55" s="17"/>
+      <c r="J55" s="17"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A56" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="G56" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="H56" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="I56" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="J56" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A57" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B57" s="7"/>
+      <c r="C57" s="8"/>
+      <c r="F57" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G57" s="8"/>
+      <c r="H57" s="7"/>
+      <c r="I57" s="6"/>
+      <c r="J57" s="7"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>14</v>
+      </c>
+      <c r="B58">
+        <v>303</v>
+      </c>
+      <c r="C58">
+        <v>137</v>
+      </c>
+      <c r="D58" s="12" t="s">
+        <v>421</v>
+      </c>
+      <c r="E58" t="s">
+        <v>422</v>
+      </c>
+      <c r="F58" t="s">
+        <v>14</v>
+      </c>
+      <c r="G58">
+        <v>143</v>
+      </c>
+      <c r="H58">
+        <v>64</v>
+      </c>
+      <c r="I58" s="12" t="s">
+        <v>423</v>
+      </c>
+      <c r="J58" s="14" t="s">
+        <v>424</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="F24:J24"/>
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="F55:J55"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N17"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:N21"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="12.88671875" customWidth="1"/>
+    <col min="3" max="3" width="12.77734375" customWidth="1"/>
+    <col min="4" max="4" width="13.5546875" customWidth="1"/>
+    <col min="5" max="5" width="11.88671875" customWidth="1"/>
+    <col min="6" max="6" width="9.6640625" customWidth="1"/>
+    <col min="7" max="7" width="11.33203125" customWidth="1"/>
+    <col min="8" max="8" width="16.77734375" customWidth="1"/>
+    <col min="9" max="9" width="14.109375" customWidth="1"/>
+    <col min="10" max="10" width="15.21875" customWidth="1"/>
+    <col min="11" max="11" width="13.88671875" customWidth="1"/>
+    <col min="12" max="12" width="12.88671875" customWidth="1"/>
+    <col min="13" max="13" width="27.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="7"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="9" t="s">
+        <v>449</v>
+      </c>
+      <c r="H1" s="8"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" s="7"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" s="7"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="N4" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
+        <v>1000</v>
+      </c>
+      <c r="B5" s="3">
+        <v>512</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>450</v>
+      </c>
+      <c r="D5" s="7"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="3">
+        <v>2</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>451</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5" s="3">
+        <v>289</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>452</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>453</v>
+      </c>
+      <c r="M5" s="8"/>
+      <c r="N5" s="8"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="8"/>
+      <c r="N6" s="8"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
+        <v>1000</v>
+      </c>
+      <c r="B7" s="3">
+        <v>512</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>461</v>
+      </c>
+      <c r="D7" s="7"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="3">
+        <v>2</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>462</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7" s="3">
+        <v>175</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>463</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>464</v>
+      </c>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N8" s="8"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
+        <v>1000</v>
+      </c>
+      <c r="B9" s="3">
+        <v>512</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>456</v>
+      </c>
+      <c r="D9" s="7"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="3">
+        <v>2</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>457</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I9" s="3">
+        <v>175</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>458</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
+        <v>1000</v>
+      </c>
+      <c r="B11" s="3">
+        <v>512</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>465</v>
+      </c>
+      <c r="D11" s="7"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="3">
+        <v>2</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>467</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="I11" s="3">
+        <v>175</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>468</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>466</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>469</v>
+      </c>
+      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N12" s="8"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="8"/>
+      <c r="N13" s="8"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="8"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="8"/>
+      <c r="N15" s="8"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A16" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B16" s="8"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="8"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A17" s="7"/>
+      <c r="B17" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="17" t="s">
+        <v>187</v>
+      </c>
+      <c r="H17" s="17"/>
+      <c r="I17" s="17"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="17"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="8"/>
+      <c r="N17" s="8"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A18" s="7"/>
+      <c r="B18" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="K18" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="L18" s="8"/>
+      <c r="M18" s="8"/>
+      <c r="N18" s="8"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A19" s="7">
+        <v>1000</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="7">
+        <v>289</v>
+      </c>
+      <c r="D19" s="8">
+        <v>105</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>452</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>453</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H19" s="8">
+        <v>127</v>
+      </c>
+      <c r="I19" s="7">
+        <v>53</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="K19" s="7">
+        <v>65340</v>
+      </c>
+      <c r="L19" s="8"/>
+      <c r="M19" s="8"/>
+      <c r="N19" s="8"/>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="6"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="8"/>
+      <c r="N20" s="8"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="8"/>
+      <c r="N21" s="8"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="G17:K17"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:N54"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
-    <col min="2" max="2" width="12.54296875" customWidth="1"/>
-    <col min="3" max="3" width="14.453125" customWidth="1"/>
-    <col min="4" max="4" width="15.90625" customWidth="1"/>
-    <col min="5" max="5" width="13.1796875" customWidth="1"/>
-    <col min="6" max="6" width="18.1796875" customWidth="1"/>
-    <col min="7" max="7" width="17.6328125" customWidth="1"/>
-    <col min="8" max="9" width="17.08984375" customWidth="1"/>
-    <col min="10" max="10" width="16.1796875" customWidth="1"/>
-    <col min="11" max="11" width="27.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5546875" customWidth="1"/>
+    <col min="3" max="3" width="14.44140625" customWidth="1"/>
+    <col min="4" max="4" width="15.88671875" customWidth="1"/>
+    <col min="5" max="5" width="13.21875" customWidth="1"/>
+    <col min="6" max="6" width="18.21875" customWidth="1"/>
+    <col min="7" max="7" width="17.6640625" customWidth="1"/>
+    <col min="8" max="9" width="17.109375" customWidth="1"/>
+    <col min="10" max="10" width="16.21875" customWidth="1"/>
+    <col min="11" max="11" width="27.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="7"/>
       <c r="B1" s="8"/>
       <c r="C1" s="7"/>
@@ -3533,7 +4917,9 @@
       <c r="G1" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="H1" s="8"/>
+      <c r="H1" s="18" t="s">
+        <v>454</v>
+      </c>
       <c r="I1" s="7"/>
       <c r="J1" s="8"/>
       <c r="K1" s="8"/>
@@ -3541,7 +4927,7 @@
       <c r="M1" s="8"/>
       <c r="N1" s="8"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="7"/>
@@ -3557,7 +4943,7 @@
       <c r="M2" s="8"/>
       <c r="N2" s="8"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="7"/>
       <c r="B3" s="8"/>
       <c r="C3" s="7"/>
@@ -3573,7 +4959,7 @@
       <c r="M3" s="8"/>
       <c r="N3" s="8"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>0</v>
       </c>
@@ -3611,7 +4997,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1000</v>
       </c>
@@ -3637,7 +5023,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1000</v>
       </c>
@@ -3663,7 +5049,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1000</v>
       </c>
@@ -3689,7 +5075,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1000</v>
       </c>
@@ -3715,7 +5101,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
         <v>102</v>
       </c>
@@ -3730,24 +5116,24 @@
       <c r="J14" s="8"/>
       <c r="K14" s="8"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="7"/>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="14" t="s">
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="H15" s="14"/>
-      <c r="I15" s="14"/>
-      <c r="J15" s="14"/>
-      <c r="K15" s="14"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="H15" s="17"/>
+      <c r="I15" s="17"/>
+      <c r="J15" s="17"/>
+      <c r="K15" s="17"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="7"/>
       <c r="B16" s="8" t="s">
         <v>184</v>
@@ -3780,7 +5166,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="7">
         <v>1000</v>
       </c>
@@ -3815,34 +5201,538 @@
         <v>202</v>
       </c>
     </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="G20" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="H20" s="18" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K22" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>1000</v>
+      </c>
+      <c r="D23">
+        <v>2</v>
+      </c>
+      <c r="E23" t="s">
+        <v>470</v>
+      </c>
+      <c r="F23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G23">
+        <v>283</v>
+      </c>
+      <c r="H23" t="s">
+        <v>472</v>
+      </c>
+      <c r="I23" t="s">
+        <v>471</v>
+      </c>
+      <c r="J23" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>1000</v>
+      </c>
+      <c r="D25">
+        <v>2</v>
+      </c>
+      <c r="E25" t="s">
+        <v>475</v>
+      </c>
+      <c r="F25" t="s">
+        <v>36</v>
+      </c>
+      <c r="G25">
+        <v>175</v>
+      </c>
+      <c r="H25" t="s">
+        <v>476</v>
+      </c>
+      <c r="I25" s="11" t="s">
+        <v>477</v>
+      </c>
+      <c r="J25" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>1000</v>
+      </c>
+      <c r="D27">
+        <v>2</v>
+      </c>
+      <c r="E27" t="s">
+        <v>483</v>
+      </c>
+      <c r="F27" t="s">
+        <v>47</v>
+      </c>
+      <c r="G27">
+        <v>175</v>
+      </c>
+      <c r="H27" t="s">
+        <v>484</v>
+      </c>
+      <c r="I27" t="s">
+        <v>485</v>
+      </c>
+      <c r="J27" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>1000</v>
+      </c>
+      <c r="D29">
+        <v>2</v>
+      </c>
+      <c r="E29" t="s">
+        <v>480</v>
+      </c>
+      <c r="F29" t="s">
+        <v>25</v>
+      </c>
+      <c r="G29">
+        <v>175</v>
+      </c>
+      <c r="H29" t="s">
+        <v>232</v>
+      </c>
+      <c r="I29" s="12" t="s">
+        <v>481</v>
+      </c>
+      <c r="J29" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A32" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B32" s="8"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="8"/>
+      <c r="G32" s="7"/>
+      <c r="H32" s="8"/>
+      <c r="I32" s="7"/>
+      <c r="J32" s="8"/>
+      <c r="K32" s="8"/>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A33" s="7"/>
+      <c r="B33" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="C33" s="16"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="17" t="s">
+        <v>187</v>
+      </c>
+      <c r="H33" s="17"/>
+      <c r="I33" s="17"/>
+      <c r="J33" s="17"/>
+      <c r="K33" s="17"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A34" s="7"/>
+      <c r="B34" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="H34" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="I34" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="J34" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="K34" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A35" s="7">
+        <v>1000</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" s="7">
+        <v>283</v>
+      </c>
+      <c r="D35" s="8">
+        <v>102</v>
+      </c>
+      <c r="E35" t="s">
+        <v>471</v>
+      </c>
+      <c r="F35" t="s">
+        <v>473</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H35" s="8">
+        <v>114</v>
+      </c>
+      <c r="I35" s="7">
+        <v>43</v>
+      </c>
+      <c r="J35" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="K35" s="7" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="G39" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="H39" s="18" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A41" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="G41" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="H41" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I41" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J41" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K41" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="L41" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>1000</v>
+      </c>
+      <c r="D42">
+        <v>2</v>
+      </c>
+      <c r="E42" t="s">
+        <v>487</v>
+      </c>
+      <c r="F42" t="s">
+        <v>14</v>
+      </c>
+      <c r="G42">
+        <v>291</v>
+      </c>
+      <c r="H42" t="s">
+        <v>493</v>
+      </c>
+      <c r="I42" t="s">
+        <v>310</v>
+      </c>
+      <c r="J42" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>1000</v>
+      </c>
+      <c r="D44">
+        <v>2</v>
+      </c>
+      <c r="E44" t="s">
+        <v>491</v>
+      </c>
+      <c r="F44" t="s">
+        <v>36</v>
+      </c>
+      <c r="G44">
+        <v>175</v>
+      </c>
+      <c r="H44" t="s">
+        <v>492</v>
+      </c>
+      <c r="I44" s="11" t="s">
+        <v>494</v>
+      </c>
+      <c r="J44" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>1000</v>
+      </c>
+      <c r="D46">
+        <v>2</v>
+      </c>
+      <c r="E46" t="s">
+        <v>497</v>
+      </c>
+      <c r="F46" t="s">
+        <v>47</v>
+      </c>
+      <c r="G46">
+        <v>175</v>
+      </c>
+      <c r="H46" t="s">
+        <v>498</v>
+      </c>
+      <c r="I46" t="s">
+        <v>499</v>
+      </c>
+      <c r="J46" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>1000</v>
+      </c>
+      <c r="D48">
+        <v>2</v>
+      </c>
+      <c r="E48" t="s">
+        <v>475</v>
+      </c>
+      <c r="F48" t="s">
+        <v>25</v>
+      </c>
+      <c r="G48">
+        <v>175</v>
+      </c>
+      <c r="H48" t="s">
+        <v>251</v>
+      </c>
+      <c r="I48" s="12" t="s">
+        <v>481</v>
+      </c>
+      <c r="J48" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A51" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B51" s="8"/>
+      <c r="C51" s="7"/>
+      <c r="D51" s="8"/>
+      <c r="E51" s="7"/>
+      <c r="F51" s="8"/>
+      <c r="G51" s="7"/>
+      <c r="H51" s="8"/>
+      <c r="I51" s="7"/>
+      <c r="J51" s="8"/>
+      <c r="K51" s="8"/>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A52" s="7"/>
+      <c r="B52" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="C52" s="16"/>
+      <c r="D52" s="16"/>
+      <c r="E52" s="16"/>
+      <c r="F52" s="16"/>
+      <c r="G52" s="17" t="s">
+        <v>187</v>
+      </c>
+      <c r="H52" s="17"/>
+      <c r="I52" s="17"/>
+      <c r="J52" s="17"/>
+      <c r="K52" s="17"/>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A53" s="7"/>
+      <c r="B53" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F53" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G53" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="H53" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="I53" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="J53" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="K53" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A54" s="7">
+        <v>1000</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C54" s="7">
+        <v>291</v>
+      </c>
+      <c r="D54" s="8">
+        <v>110</v>
+      </c>
+      <c r="E54" t="s">
+        <v>310</v>
+      </c>
+      <c r="F54" t="s">
+        <v>488</v>
+      </c>
+      <c r="G54" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H54" s="8">
+        <v>117</v>
+      </c>
+      <c r="I54" s="7">
+        <v>38</v>
+      </c>
+      <c r="J54" s="6" t="s">
+        <v>489</v>
+      </c>
+      <c r="K54" s="7" t="s">
+        <v>490</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="6">
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="G15:K15"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="G33:K33"/>
+    <mergeCell ref="B52:F52"/>
+    <mergeCell ref="G52:K52"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.36328125" customWidth="1"/>
-    <col min="2" max="2" width="15.6328125" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" customWidth="1"/>
+    <col min="2" max="2" width="15.6640625" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="11.54296875" customWidth="1"/>
-    <col min="5" max="5" width="14.453125" customWidth="1"/>
-    <col min="6" max="6" width="16.08984375" customWidth="1"/>
-    <col min="7" max="8" width="17.08984375" customWidth="1"/>
-    <col min="9" max="9" width="13.1796875" customWidth="1"/>
-    <col min="10" max="10" width="15.90625" customWidth="1"/>
-    <col min="11" max="11" width="27.453125" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" customWidth="1"/>
+    <col min="5" max="5" width="14.44140625" customWidth="1"/>
+    <col min="6" max="6" width="16.109375" customWidth="1"/>
+    <col min="7" max="8" width="17.109375" customWidth="1"/>
+    <col min="9" max="9" width="13.21875" customWidth="1"/>
+    <col min="10" max="10" width="15.88671875" customWidth="1"/>
+    <col min="11" max="11" width="27.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="7"/>
       <c r="B1" s="8"/>
       <c r="C1" s="7"/>
@@ -3860,7 +5750,7 @@
       <c r="M1" s="8"/>
       <c r="N1" s="8"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="7"/>
@@ -3876,7 +5766,7 @@
       <c r="M2" s="8"/>
       <c r="N2" s="8"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="7"/>
       <c r="B3" s="8"/>
       <c r="C3" s="7"/>
@@ -3892,7 +5782,7 @@
       <c r="M3" s="8"/>
       <c r="N3" s="8"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>0</v>
       </c>
@@ -3930,7 +5820,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1000</v>
       </c>
@@ -3956,7 +5846,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1000</v>
       </c>
@@ -3982,7 +5872,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1000</v>
       </c>
@@ -4008,7 +5898,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1000</v>
       </c>
@@ -4034,7 +5924,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="8"/>
       <c r="B12" s="7"/>
       <c r="C12" s="8"/>
@@ -4046,23 +5936,23 @@
       <c r="I12" s="8"/>
       <c r="J12" s="8"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A13" s="13" t="s">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A13" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="14" t="s">
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="14"/>
-      <c r="J13" s="14"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="G13" s="17"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="17"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
         <v>184</v>
       </c>
@@ -4094,7 +5984,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
         <v>14</v>
       </c>
@@ -4135,26 +6025,26 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N26"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.453125" customWidth="1"/>
+    <col min="1" max="1" width="13.44140625" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="12.453125" customWidth="1"/>
-    <col min="4" max="4" width="12.81640625" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" customWidth="1"/>
+    <col min="4" max="4" width="12.77734375" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="6" max="6" width="15.6328125" customWidth="1"/>
-    <col min="7" max="7" width="15.08984375" customWidth="1"/>
-    <col min="8" max="8" width="17.36328125" customWidth="1"/>
-    <col min="9" max="9" width="16.81640625" customWidth="1"/>
+    <col min="6" max="6" width="15.6640625" customWidth="1"/>
+    <col min="7" max="7" width="15.109375" customWidth="1"/>
+    <col min="8" max="8" width="17.33203125" customWidth="1"/>
+    <col min="9" max="9" width="16.77734375" customWidth="1"/>
     <col min="10" max="10" width="15" customWidth="1"/>
-    <col min="11" max="11" width="29.26953125" customWidth="1"/>
+    <col min="11" max="11" width="29.21875" customWidth="1"/>
     <col min="12" max="12" width="79" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="7"/>
       <c r="B1" s="8"/>
       <c r="C1" s="7"/>
@@ -4172,7 +6062,7 @@
       <c r="M1" s="8"/>
       <c r="N1" s="8"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="7"/>
@@ -4188,7 +6078,7 @@
       <c r="M2" s="8"/>
       <c r="N2" s="8"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="7"/>
       <c r="B3" s="8"/>
       <c r="C3" s="7"/>
@@ -4204,7 +6094,7 @@
       <c r="M3" s="8"/>
       <c r="N3" s="8"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>0</v>
       </c>
@@ -4242,7 +6132,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1000</v>
       </c>
@@ -4268,7 +6158,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1000</v>
       </c>
@@ -4294,7 +6184,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1000</v>
       </c>
@@ -4320,7 +6210,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1000</v>
       </c>
@@ -4346,7 +6236,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="8"/>
       <c r="B12" s="7"/>
       <c r="C12" s="8"/>
@@ -4358,31 +6248,31 @@
       <c r="I12" s="8"/>
       <c r="J12" s="8"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A13" s="17">
-        <v>1000</v>
-      </c>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17" t="s">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A13" s="15">
+        <v>1000</v>
+      </c>
+      <c r="B13" s="15"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="G13" s="17">
-        <v>2</v>
-      </c>
-      <c r="H13" s="17" t="s">
+      <c r="G13" s="15">
+        <v>2</v>
+      </c>
+      <c r="H13" s="15" t="s">
         <v>393</v>
       </c>
-      <c r="I13" s="17" t="s">
+      <c r="I13" s="15" t="s">
         <v>394</v>
       </c>
-      <c r="J13" s="17" t="s">
+      <c r="J13" s="15" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>1000</v>
       </c>
@@ -4402,7 +6292,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>1000</v>
       </c>
@@ -4422,7 +6312,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>1000</v>
       </c>
@@ -4442,23 +6332,23 @@
         <v>404</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A23" s="13" t="s">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A23" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="14" t="s">
+      <c r="B23" s="16"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="14"/>
-      <c r="J23" s="14"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="G23" s="17"/>
+      <c r="H23" s="17"/>
+      <c r="I23" s="17"/>
+      <c r="J23" s="17"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
         <v>184</v>
       </c>
@@ -4490,7 +6380,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
         <v>14</v>
       </c>
@@ -4522,7 +6412,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
         <v>14</v>
       </c>
@@ -4550,25 +6440,25 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L31"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.1796875" customWidth="1"/>
-    <col min="2" max="2" width="13.90625" customWidth="1"/>
+    <col min="1" max="1" width="15.21875" customWidth="1"/>
+    <col min="2" max="2" width="13.88671875" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="5" width="14.1796875" customWidth="1"/>
-    <col min="6" max="6" width="14.453125" customWidth="1"/>
-    <col min="7" max="7" width="13.6328125" customWidth="1"/>
-    <col min="8" max="8" width="14.26953125" customWidth="1"/>
-    <col min="9" max="9" width="13.453125" customWidth="1"/>
-    <col min="10" max="10" width="15.81640625" customWidth="1"/>
-    <col min="11" max="11" width="30.90625" customWidth="1"/>
-    <col min="12" max="12" width="75.54296875" customWidth="1"/>
+    <col min="4" max="5" width="14.21875" customWidth="1"/>
+    <col min="6" max="6" width="14.44140625" customWidth="1"/>
+    <col min="7" max="7" width="13.6640625" customWidth="1"/>
+    <col min="8" max="8" width="14.21875" customWidth="1"/>
+    <col min="9" max="9" width="13.44140625" customWidth="1"/>
+    <col min="10" max="10" width="15.77734375" customWidth="1"/>
+    <col min="11" max="11" width="30.88671875" customWidth="1"/>
+    <col min="12" max="12" width="75.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="7"/>
       <c r="B1" s="8"/>
       <c r="C1" s="7"/>
@@ -4583,7 +6473,7 @@
       <c r="J1" s="8"/>
       <c r="K1" s="8"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="7"/>
@@ -4596,7 +6486,7 @@
       <c r="J2" s="8"/>
       <c r="K2" s="8"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="7"/>
       <c r="B3" s="8"/>
       <c r="C3" s="7"/>
@@ -4609,7 +6499,7 @@
       <c r="J3" s="8"/>
       <c r="K3" s="8"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>0</v>
       </c>
@@ -4647,7 +6537,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1000</v>
       </c>
@@ -4673,7 +6563,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1000</v>
       </c>
@@ -4699,7 +6589,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1000</v>
       </c>
@@ -4725,14 +6615,14 @@
         <v>286</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1000</v>
       </c>
       <c r="D11">
         <v>2</v>
       </c>
-      <c r="E11" s="15" t="s">
+      <c r="E11" s="13" t="s">
         <v>287</v>
       </c>
       <c r="F11" t="s">
@@ -4751,7 +6641,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="8"/>
       <c r="B12" s="7"/>
       <c r="C12" s="8"/>
@@ -4763,7 +6653,7 @@
       <c r="I12" s="8"/>
       <c r="J12" s="8"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>1000</v>
       </c>
@@ -4783,7 +6673,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>1000</v>
       </c>
@@ -4803,7 +6693,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>1000</v>
       </c>
@@ -4813,7 +6703,7 @@
       <c r="G17">
         <v>175</v>
       </c>
-      <c r="H17" s="16" t="s">
+      <c r="H17" s="14" t="s">
         <v>389</v>
       </c>
       <c r="I17" s="12" t="s">
@@ -4823,11 +6713,11 @@
         <v>388</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>1000</v>
       </c>
-      <c r="E19" s="15"/>
+      <c r="E19" s="13"/>
       <c r="F19" t="s">
         <v>25</v>
       </c>
@@ -4844,23 +6734,23 @@
         <v>392</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A28" s="13" t="s">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A28" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="14" t="s">
+      <c r="B28" s="16"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="14"/>
-      <c r="J28" s="14"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="G28" s="17"/>
+      <c r="H28" s="17"/>
+      <c r="I28" s="17"/>
+      <c r="J28" s="17"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="8" t="s">
         <v>184</v>
       </c>
@@ -4892,7 +6782,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
         <v>14</v>
       </c>
@@ -4924,7 +6814,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="8" t="s">
         <v>14</v>
       </c>
@@ -4966,25 +6856,25 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L28"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.90625" customWidth="1"/>
-    <col min="2" max="2" width="13.81640625" customWidth="1"/>
+    <col min="1" max="1" width="12.88671875" customWidth="1"/>
+    <col min="2" max="2" width="13.77734375" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="13.54296875" customWidth="1"/>
-    <col min="5" max="5" width="12.54296875" customWidth="1"/>
-    <col min="6" max="6" width="14.36328125" customWidth="1"/>
-    <col min="7" max="7" width="17.54296875" customWidth="1"/>
-    <col min="8" max="8" width="15.36328125" customWidth="1"/>
-    <col min="9" max="9" width="14.54296875" customWidth="1"/>
-    <col min="10" max="10" width="14.453125" customWidth="1"/>
-    <col min="11" max="11" width="31.08984375" customWidth="1"/>
+    <col min="4" max="4" width="13.5546875" customWidth="1"/>
+    <col min="5" max="5" width="12.5546875" customWidth="1"/>
+    <col min="6" max="6" width="14.33203125" customWidth="1"/>
+    <col min="7" max="7" width="17.5546875" customWidth="1"/>
+    <col min="8" max="8" width="15.33203125" customWidth="1"/>
+    <col min="9" max="9" width="14.5546875" customWidth="1"/>
+    <col min="10" max="10" width="14.44140625" customWidth="1"/>
+    <col min="11" max="11" width="31.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="7"/>
       <c r="B1" s="8"/>
       <c r="C1" s="7"/>
@@ -4999,7 +6889,7 @@
       <c r="J1" s="8"/>
       <c r="K1" s="8"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="7"/>
@@ -5012,7 +6902,7 @@
       <c r="J2" s="8"/>
       <c r="K2" s="8"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="7"/>
       <c r="B3" s="8"/>
       <c r="C3" s="7"/>
@@ -5025,7 +6915,7 @@
       <c r="J3" s="8"/>
       <c r="K3" s="8"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>0</v>
       </c>
@@ -5063,7 +6953,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1000</v>
       </c>
@@ -5089,7 +6979,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1000</v>
       </c>
@@ -5115,7 +7005,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1000</v>
       </c>
@@ -5141,14 +7031,14 @@
         <v>304</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1000</v>
       </c>
       <c r="D11">
         <v>2</v>
       </c>
-      <c r="E11" s="15" t="s">
+      <c r="E11" s="13" t="s">
         <v>305</v>
       </c>
       <c r="F11" t="s">
@@ -5167,7 +7057,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="8"/>
       <c r="B12" s="7"/>
       <c r="C12" s="8"/>
@@ -5179,7 +7069,7 @@
       <c r="I12" s="8"/>
       <c r="J12" s="8"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>1000</v>
       </c>
@@ -5199,7 +7089,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>1000</v>
       </c>
@@ -5219,7 +7109,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>1000</v>
       </c>
@@ -5239,11 +7129,11 @@
         <v>376</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>1000</v>
       </c>
-      <c r="E19" s="15"/>
+      <c r="E19" s="13"/>
       <c r="F19" t="s">
         <v>25</v>
       </c>
@@ -5260,23 +7150,23 @@
         <v>378</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A25" s="13" t="s">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A25" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="B25" s="13"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="14" t="s">
+      <c r="B25" s="16"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="14"/>
-      <c r="J25" s="14"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="G25" s="17"/>
+      <c r="H25" s="17"/>
+      <c r="I25" s="17"/>
+      <c r="J25" s="17"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
         <v>184</v>
       </c>
@@ -5308,7 +7198,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="8" t="s">
         <v>14</v>
       </c>
@@ -5340,7 +7230,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>14</v>
       </c>
@@ -5381,25 +7271,25 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L28"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.90625" customWidth="1"/>
-    <col min="2" max="2" width="14.453125" customWidth="1"/>
-    <col min="3" max="3" width="13.453125" customWidth="1"/>
-    <col min="4" max="4" width="13.26953125" customWidth="1"/>
-    <col min="5" max="5" width="16.08984375" customWidth="1"/>
-    <col min="6" max="6" width="17.08984375" customWidth="1"/>
-    <col min="7" max="7" width="17.54296875" customWidth="1"/>
-    <col min="8" max="8" width="16.54296875" customWidth="1"/>
-    <col min="9" max="9" width="16.81640625" customWidth="1"/>
+    <col min="1" max="1" width="14.88671875" customWidth="1"/>
+    <col min="2" max="2" width="14.44140625" customWidth="1"/>
+    <col min="3" max="3" width="13.44140625" customWidth="1"/>
+    <col min="4" max="4" width="13.21875" customWidth="1"/>
+    <col min="5" max="5" width="16.109375" customWidth="1"/>
+    <col min="6" max="6" width="17.109375" customWidth="1"/>
+    <col min="7" max="7" width="17.5546875" customWidth="1"/>
+    <col min="8" max="8" width="16.5546875" customWidth="1"/>
+    <col min="9" max="9" width="16.77734375" customWidth="1"/>
     <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="27.6328125" customWidth="1"/>
+    <col min="11" max="11" width="27.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="7"/>
       <c r="B1" s="8"/>
       <c r="C1" s="7"/>
@@ -5414,7 +7304,7 @@
       <c r="J1" s="8"/>
       <c r="K1" s="8"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="7"/>
@@ -5427,7 +7317,7 @@
       <c r="J2" s="8"/>
       <c r="K2" s="8"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="7"/>
       <c r="B3" s="8"/>
       <c r="C3" s="7"/>
@@ -5440,7 +7330,7 @@
       <c r="J3" s="8"/>
       <c r="K3" s="8"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>0</v>
       </c>
@@ -5478,7 +7368,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1000</v>
       </c>
@@ -5504,7 +7394,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1000</v>
       </c>
@@ -5530,7 +7420,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1000</v>
       </c>
@@ -5556,14 +7446,14 @@
         <v>320</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1000</v>
       </c>
       <c r="D11">
         <v>2</v>
       </c>
-      <c r="E11" s="15" t="s">
+      <c r="E11" s="13" t="s">
         <v>321</v>
       </c>
       <c r="F11" t="s">
@@ -5582,7 +7472,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="8"/>
       <c r="B12" s="7"/>
       <c r="C12" s="8"/>
@@ -5594,7 +7484,7 @@
       <c r="I12" s="8"/>
       <c r="J12" s="8"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>1000</v>
       </c>
@@ -5610,11 +7500,11 @@
       <c r="I13" s="12" t="s">
         <v>353</v>
       </c>
-      <c r="J13" s="16" t="s">
+      <c r="J13" s="14" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>1000</v>
       </c>
@@ -5634,7 +7524,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>1000</v>
       </c>
@@ -5654,11 +7544,11 @@
         <v>361</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>1000</v>
       </c>
-      <c r="E19" s="15"/>
+      <c r="E19" s="13"/>
       <c r="F19" t="s">
         <v>25</v>
       </c>
@@ -5675,23 +7565,23 @@
         <v>364</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A25" s="13" t="s">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A25" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="B25" s="13"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="14" t="s">
+      <c r="B25" s="16"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="14"/>
-      <c r="J25" s="14"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="G25" s="17"/>
+      <c r="H25" s="17"/>
+      <c r="I25" s="17"/>
+      <c r="J25" s="17"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
         <v>184</v>
       </c>
@@ -5723,7 +7613,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="8" t="s">
         <v>14</v>
       </c>
@@ -5755,7 +7645,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
         <v>14</v>
       </c>
@@ -5768,7 +7658,7 @@
       <c r="D28" s="12" t="s">
         <v>353</v>
       </c>
-      <c r="E28" s="16">
+      <c r="E28" s="14">
         <v>246380</v>
       </c>
       <c r="F28" s="8" t="s">
@@ -5796,24 +7686,24 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L33"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="14.08984375" customWidth="1"/>
-    <col min="3" max="3" width="13.36328125" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" customWidth="1"/>
-    <col min="5" max="5" width="12.7265625" customWidth="1"/>
-    <col min="6" max="6" width="17.36328125" customWidth="1"/>
-    <col min="7" max="7" width="14.6328125" customWidth="1"/>
-    <col min="8" max="8" width="14.54296875" customWidth="1"/>
-    <col min="9" max="9" width="14.08984375" customWidth="1"/>
-    <col min="10" max="10" width="16.08984375" customWidth="1"/>
-    <col min="11" max="11" width="43.1796875" customWidth="1"/>
+    <col min="1" max="2" width="14.109375" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" customWidth="1"/>
+    <col min="5" max="5" width="12.77734375" customWidth="1"/>
+    <col min="6" max="6" width="17.33203125" customWidth="1"/>
+    <col min="7" max="7" width="14.6640625" customWidth="1"/>
+    <col min="8" max="8" width="14.5546875" customWidth="1"/>
+    <col min="9" max="9" width="14.109375" customWidth="1"/>
+    <col min="10" max="10" width="16.109375" customWidth="1"/>
+    <col min="11" max="11" width="43.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="7"/>
       <c r="B1" s="8"/>
       <c r="C1" s="7"/>
@@ -5828,7 +7718,7 @@
       <c r="J1" s="8"/>
       <c r="K1" s="8"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="7"/>
@@ -5841,7 +7731,7 @@
       <c r="J2" s="8"/>
       <c r="K2" s="8"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="7"/>
       <c r="B3" s="8"/>
       <c r="C3" s="7"/>
@@ -5854,7 +7744,7 @@
       <c r="J3" s="8"/>
       <c r="K3" s="8"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>0</v>
       </c>
@@ -5892,7 +7782,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1000</v>
       </c>
@@ -5918,7 +7808,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1000</v>
       </c>
@@ -5944,7 +7834,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1000</v>
       </c>
@@ -5970,14 +7860,14 @@
         <v>337</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1000</v>
       </c>
       <c r="D11">
         <v>2</v>
       </c>
-      <c r="E11" s="15" t="s">
+      <c r="E11" s="13" t="s">
         <v>338</v>
       </c>
       <c r="F11" t="s">
@@ -5996,7 +7886,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="8"/>
       <c r="B12" s="7"/>
       <c r="C12" s="8"/>
@@ -6008,7 +7898,7 @@
       <c r="I12" s="8"/>
       <c r="J12" s="8"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>1000</v>
       </c>
@@ -6028,7 +7918,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>1000</v>
       </c>
@@ -6048,7 +7938,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>1000</v>
       </c>
@@ -6068,7 +7958,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>1000</v>
       </c>
@@ -6088,23 +7978,23 @@
         <v>350</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A30" s="13" t="s">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A30" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="14" t="s">
+      <c r="B30" s="16"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="14"/>
-      <c r="J30" s="14"/>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="G30" s="17"/>
+      <c r="H30" s="17"/>
+      <c r="I30" s="17"/>
+      <c r="J30" s="17"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="8" t="s">
         <v>184</v>
       </c>
@@ -6136,7 +8026,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="8" t="s">
         <v>14</v>
       </c>
@@ -6168,7 +8058,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>14</v>
       </c>
@@ -6196,7 +8086,7 @@
       <c r="I33" s="12" t="s">
         <v>345</v>
       </c>
-      <c r="J33" s="16">
+      <c r="J33" s="14">
         <v>76609</v>
       </c>
     </row>
@@ -6208,742 +8098,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L58"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="15.453125" customWidth="1"/>
-    <col min="2" max="2" width="16.36328125" customWidth="1"/>
-    <col min="3" max="3" width="13.08984375" customWidth="1"/>
-    <col min="4" max="4" width="13.1796875" customWidth="1"/>
-    <col min="5" max="5" width="13.36328125" customWidth="1"/>
-    <col min="6" max="6" width="15.7265625" customWidth="1"/>
-    <col min="7" max="7" width="13.26953125" customWidth="1"/>
-    <col min="8" max="8" width="13.7265625" customWidth="1"/>
-    <col min="9" max="9" width="13.90625" customWidth="1"/>
-    <col min="10" max="10" width="13" customWidth="1"/>
-    <col min="11" max="11" width="29.7265625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A1" s="7"/>
-      <c r="B1" s="8"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="9" t="s">
-        <v>405</v>
-      </c>
-      <c r="H1" s="8"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" s="7"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3" s="7"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A4" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="J4" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="K4" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="L4" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A5">
-        <v>1000</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5" t="s">
-        <v>434</v>
-      </c>
-      <c r="F5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5">
-        <v>298</v>
-      </c>
-      <c r="H5" t="s">
-        <v>435</v>
-      </c>
-      <c r="I5" t="s">
-        <v>439</v>
-      </c>
-      <c r="J5" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A7">
-        <v>1000</v>
-      </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-      <c r="E7" t="s">
-        <v>436</v>
-      </c>
-      <c r="F7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G7">
-        <v>175</v>
-      </c>
-      <c r="H7" t="s">
-        <v>437</v>
-      </c>
-      <c r="I7" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="J7" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A9">
-        <v>1000</v>
-      </c>
-      <c r="D9">
-        <v>2</v>
-      </c>
-      <c r="E9" t="s">
-        <v>445</v>
-      </c>
-      <c r="F9" t="s">
-        <v>47</v>
-      </c>
-      <c r="G9">
-        <v>175</v>
-      </c>
-      <c r="H9" t="s">
-        <v>446</v>
-      </c>
-      <c r="I9" s="12" t="s">
-        <v>447</v>
-      </c>
-      <c r="J9" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A11">
-        <v>1000</v>
-      </c>
-      <c r="D11">
-        <v>2</v>
-      </c>
-      <c r="E11" s="15" t="s">
-        <v>442</v>
-      </c>
-      <c r="F11" t="s">
-        <v>25</v>
-      </c>
-      <c r="G11">
-        <v>175</v>
-      </c>
-      <c r="H11" t="s">
-        <v>178</v>
-      </c>
-      <c r="I11" s="12" t="s">
-        <v>443</v>
-      </c>
-      <c r="J11" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A12" s="8"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A13">
-        <v>1000</v>
-      </c>
-      <c r="F13" t="s">
-        <v>14</v>
-      </c>
-      <c r="G13">
-        <v>253</v>
-      </c>
-      <c r="H13" t="s">
-        <v>406</v>
-      </c>
-      <c r="I13" s="12" t="s">
-        <v>407</v>
-      </c>
-      <c r="J13" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A15">
-        <v>1000</v>
-      </c>
-      <c r="F15" t="s">
-        <v>36</v>
-      </c>
-      <c r="G15">
-        <v>175</v>
-      </c>
-      <c r="H15" t="s">
-        <v>411</v>
-      </c>
-      <c r="I15" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="J15" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A17">
-        <v>1000</v>
-      </c>
-      <c r="F17" t="s">
-        <v>47</v>
-      </c>
-      <c r="G17">
-        <v>175</v>
-      </c>
-      <c r="H17" t="s">
-        <v>413</v>
-      </c>
-      <c r="I17" s="12" t="s">
-        <v>415</v>
-      </c>
-      <c r="J17" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A19">
-        <v>1000</v>
-      </c>
-      <c r="F19" t="s">
-        <v>25</v>
-      </c>
-      <c r="G19">
-        <v>175</v>
-      </c>
-      <c r="H19" t="s">
-        <v>414</v>
-      </c>
-      <c r="I19" s="12" t="s">
-        <v>417</v>
-      </c>
-      <c r="J19" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A24" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="14"/>
-      <c r="J24" s="14"/>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A25" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="H25" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="I25" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="J25" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A26" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B26" s="7">
-        <v>298</v>
-      </c>
-      <c r="C26" s="8">
-        <v>115</v>
-      </c>
-      <c r="D26" t="s">
-        <v>439</v>
-      </c>
-      <c r="E26" t="s">
-        <v>440</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G26" s="8">
-        <v>104</v>
-      </c>
-      <c r="H26" s="7">
-        <v>22</v>
-      </c>
-      <c r="I26" s="6" t="s">
-        <v>343</v>
-      </c>
-      <c r="J26" s="7" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>14</v>
-      </c>
-      <c r="B27">
-        <v>253</v>
-      </c>
-      <c r="C27">
-        <v>255</v>
-      </c>
-      <c r="D27" s="12" t="s">
-        <v>407</v>
-      </c>
-      <c r="E27" t="s">
-        <v>408</v>
-      </c>
-      <c r="F27" t="s">
-        <v>14</v>
-      </c>
-      <c r="G27">
-        <v>141</v>
-      </c>
-      <c r="H27">
-        <v>81</v>
-      </c>
-      <c r="I27" s="12" t="s">
-        <v>409</v>
-      </c>
-      <c r="J27" s="16" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A32" s="7"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="9" t="s">
-        <v>419</v>
-      </c>
-      <c r="H32" s="8"/>
-      <c r="I32" s="7"/>
-      <c r="J32" s="8"/>
-      <c r="K32" s="8"/>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A33" s="7"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="8"/>
-      <c r="G33" s="7"/>
-      <c r="H33" s="8"/>
-      <c r="I33" s="7"/>
-      <c r="J33" s="8"/>
-      <c r="K33" s="8"/>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A34" s="7"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="7"/>
-      <c r="H34" s="8"/>
-      <c r="I34" s="7"/>
-      <c r="J34" s="8"/>
-      <c r="K34" s="8"/>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A35" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F35" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="G35" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="H35" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="I35" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="J35" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="K35" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="L35" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A36">
-        <v>1000</v>
-      </c>
-      <c r="D36">
-        <v>2</v>
-      </c>
-      <c r="F36" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A38">
-        <v>1000</v>
-      </c>
-      <c r="D38">
-        <v>2</v>
-      </c>
-      <c r="F38" t="s">
-        <v>36</v>
-      </c>
-      <c r="G38">
-        <v>175</v>
-      </c>
-      <c r="I38" s="11"/>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A40">
-        <v>1000</v>
-      </c>
-      <c r="D40">
-        <v>2</v>
-      </c>
-      <c r="F40" t="s">
-        <v>47</v>
-      </c>
-      <c r="G40">
-        <v>175</v>
-      </c>
-      <c r="I40" s="12"/>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A42">
-        <v>1000</v>
-      </c>
-      <c r="D42">
-        <v>2</v>
-      </c>
-      <c r="E42" s="15"/>
-      <c r="F42" t="s">
-        <v>25</v>
-      </c>
-      <c r="G42">
-        <v>175</v>
-      </c>
-      <c r="I42" s="12"/>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A43" s="8"/>
-      <c r="B43" s="7"/>
-      <c r="C43" s="8"/>
-      <c r="D43" s="7"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="7"/>
-      <c r="G43" s="8"/>
-      <c r="H43" s="7"/>
-      <c r="I43" s="8"/>
-      <c r="J43" s="8"/>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A44">
-        <v>1000</v>
-      </c>
-      <c r="F44" t="s">
-        <v>14</v>
-      </c>
-      <c r="G44">
-        <v>303</v>
-      </c>
-      <c r="H44" t="s">
-        <v>420</v>
-      </c>
-      <c r="I44" s="12" t="s">
-        <v>421</v>
-      </c>
-      <c r="J44" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A46">
-        <v>1000</v>
-      </c>
-      <c r="F46" t="s">
-        <v>36</v>
-      </c>
-      <c r="G46">
-        <v>175</v>
-      </c>
-      <c r="H46" t="s">
-        <v>425</v>
-      </c>
-      <c r="I46" s="12" t="s">
-        <v>426</v>
-      </c>
-      <c r="J46" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A48">
-        <v>1000</v>
-      </c>
-      <c r="F48" t="s">
-        <v>47</v>
-      </c>
-      <c r="G48">
-        <v>175</v>
-      </c>
-      <c r="H48" t="s">
-        <v>431</v>
-      </c>
-      <c r="I48" s="12" t="s">
-        <v>432</v>
-      </c>
-      <c r="J48" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A50">
-        <v>1000</v>
-      </c>
-      <c r="F50" t="s">
-        <v>25</v>
-      </c>
-      <c r="G50">
-        <v>175</v>
-      </c>
-      <c r="H50" t="s">
-        <v>428</v>
-      </c>
-      <c r="I50" s="12" t="s">
-        <v>429</v>
-      </c>
-      <c r="J50" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A55" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="B55" s="13"/>
-      <c r="C55" s="13"/>
-      <c r="D55" s="13"/>
-      <c r="E55" s="13"/>
-      <c r="F55" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="G55" s="14"/>
-      <c r="H55" s="14"/>
-      <c r="I55" s="14"/>
-      <c r="J55" s="14"/>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A56" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="B56" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="C56" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="D56" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E56" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F56" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="G56" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="H56" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="I56" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="J56" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A57" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B57" s="7"/>
-      <c r="C57" s="8"/>
-      <c r="F57" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G57" s="8"/>
-      <c r="H57" s="7"/>
-      <c r="I57" s="6"/>
-      <c r="J57" s="7"/>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A58" t="s">
-        <v>14</v>
-      </c>
-      <c r="B58">
-        <v>303</v>
-      </c>
-      <c r="C58">
-        <v>137</v>
-      </c>
-      <c r="D58" s="12" t="s">
-        <v>421</v>
-      </c>
-      <c r="E58" t="s">
-        <v>422</v>
-      </c>
-      <c r="F58" t="s">
-        <v>14</v>
-      </c>
-      <c r="G58">
-        <v>143</v>
-      </c>
-      <c r="H58">
-        <v>64</v>
-      </c>
-      <c r="I58" s="12" t="s">
-        <v>423</v>
-      </c>
-      <c r="J58" s="16" t="s">
-        <v>424</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="F24:J24"/>
-    <mergeCell ref="A55:E55"/>
-    <mergeCell ref="F55:J55"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Experiments/DBCV_Conclu.xlsx
+++ b/Experiments/DBCV_Conclu.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18192" windowHeight="8508" activeTab="2"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18190" windowHeight="8510" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1046" uniqueCount="501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1258" uniqueCount="567">
   <si>
     <t>Datapoints</t>
   </si>
@@ -1540,6 +1540,204 @@
   </si>
   <si>
     <t>103.005 secs</t>
+  </si>
+  <si>
+    <t>(K=8)</t>
+  </si>
+  <si>
+    <t>3.018 secs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.139 </t>
+  </si>
+  <si>
+    <t>235.023 secs</t>
+  </si>
+  <si>
+    <t>-0.050</t>
+  </si>
+  <si>
+    <t>53.891 secs</t>
+  </si>
+  <si>
+    <t>(K=4)</t>
+  </si>
+  <si>
+    <t>(K=2)</t>
+  </si>
+  <si>
+    <t>3.091 secs</t>
+  </si>
+  <si>
+    <t>0.191 secs</t>
+  </si>
+  <si>
+    <t>-0.092</t>
+  </si>
+  <si>
+    <t>98.415 secs</t>
+  </si>
+  <si>
+    <t>3.101 secs</t>
+  </si>
+  <si>
+    <t>6.810 secs</t>
+  </si>
+  <si>
+    <t>-0.027</t>
+  </si>
+  <si>
+    <t>96.898 secs</t>
+  </si>
+  <si>
+    <t>3.177 secs</t>
+  </si>
+  <si>
+    <t>0.038 secs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.490 secs </t>
+  </si>
+  <si>
+    <t>0.122 secs</t>
+  </si>
+  <si>
+    <t>0.163</t>
+  </si>
+  <si>
+    <t>269.228 secs</t>
+  </si>
+  <si>
+    <t>-0.041</t>
+  </si>
+  <si>
+    <t>102.655 secs</t>
+  </si>
+  <si>
+    <t>121.577 secs</t>
+  </si>
+  <si>
+    <t>0.308 secs</t>
+  </si>
+  <si>
+    <t>-0.045</t>
+  </si>
+  <si>
+    <t>139.550 secs</t>
+  </si>
+  <si>
+    <t>3.751 secs</t>
+  </si>
+  <si>
+    <t>-0.004</t>
+  </si>
+  <si>
+    <t>11.623 secs</t>
+  </si>
+  <si>
+    <t>167.611 secs</t>
+  </si>
+  <si>
+    <t>5.013 secs</t>
+  </si>
+  <si>
+    <t>-0.005</t>
+  </si>
+  <si>
+    <t>169.509 secs</t>
+  </si>
+  <si>
+    <t>4.469 secs</t>
+  </si>
+  <si>
+    <t>0.126 secs</t>
+  </si>
+  <si>
+    <t>0.085</t>
+  </si>
+  <si>
+    <t>320.217 secs</t>
+  </si>
+  <si>
+    <t>-0.135</t>
+  </si>
+  <si>
+    <t>70.796 secs</t>
+  </si>
+  <si>
+    <t>172.364 secs</t>
+  </si>
+  <si>
+    <t>5.662 secs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.118 </t>
+  </si>
+  <si>
+    <t>155.136 secs</t>
+  </si>
+  <si>
+    <t>-0.089</t>
+  </si>
+  <si>
+    <t>115. 978 secs</t>
+  </si>
+  <si>
+    <t>73.029 secs</t>
+  </si>
+  <si>
+    <t>-0.100</t>
+  </si>
+  <si>
+    <t>98.683 secs</t>
+  </si>
+  <si>
+    <t>3.259 secs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.186 </t>
+  </si>
+  <si>
+    <t>332.309 secs</t>
+  </si>
+  <si>
+    <t>(K=128)</t>
+  </si>
+  <si>
+    <t>-0.024</t>
+  </si>
+  <si>
+    <t>50.194 secs</t>
+  </si>
+  <si>
+    <t>4.356 secs</t>
+  </si>
+  <si>
+    <t>0.172 secs</t>
+  </si>
+  <si>
+    <t>-0.049</t>
+  </si>
+  <si>
+    <t>205.339 secs</t>
+  </si>
+  <si>
+    <t>3.344 secs</t>
+  </si>
+  <si>
+    <t>11.716 secs</t>
+  </si>
+  <si>
+    <t>166.501 secs</t>
+  </si>
+  <si>
+    <t>5.815 secs</t>
+  </si>
+  <si>
+    <t>0.049 secs</t>
+  </si>
+  <si>
+    <t>170.280 secs</t>
   </si>
 </sst>
 </file>
@@ -1646,13 +1844,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1959,32 +2157,32 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:N74"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.33203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.88671875" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.36328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.90625" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.88671875" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.88671875" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5546875" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.88671875" style="8" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5546875" style="7" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.6640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="29.88671875" style="8" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="80.88671875" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.90625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.90625" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.54296875" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.54296875" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.90625" style="8" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.54296875" style="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.54296875" style="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.6328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.08984375" style="8" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="29.90625" style="8" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="80.90625" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G1" s="9" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="4" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -2028,7 +2226,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>1000</v>
       </c>
@@ -2064,7 +2262,7 @@
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
     </row>
-    <row r="6" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>1000</v>
       </c>
@@ -2100,7 +2298,7 @@
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
     </row>
-    <row r="7" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>1000</v>
       </c>
@@ -2136,7 +2334,7 @@
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
     </row>
-    <row r="8" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>1000</v>
       </c>
@@ -2172,7 +2370,7 @@
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
     </row>
-    <row r="9" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>1000</v>
       </c>
@@ -2208,7 +2406,7 @@
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
     </row>
-    <row r="10" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>1000</v>
       </c>
@@ -2244,7 +2442,7 @@
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
     </row>
-    <row r="11" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>1000</v>
       </c>
@@ -2284,7 +2482,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>1000</v>
       </c>
@@ -2320,7 +2518,7 @@
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
     </row>
-    <row r="13" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="2"/>
@@ -2333,7 +2531,7 @@
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
     </row>
-    <row r="14" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="7">
         <v>1000</v>
       </c>
@@ -2363,7 +2561,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="7"/>
       <c r="C15" s="8"/>
       <c r="D15" s="7"/>
@@ -2371,7 +2569,7 @@
       <c r="F15" s="7"/>
       <c r="G15" s="8"/>
     </row>
-    <row r="16" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="7">
         <v>1000</v>
       </c>
@@ -2401,7 +2599,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="7"/>
       <c r="C17" s="8"/>
       <c r="D17" s="7"/>
@@ -2410,7 +2608,7 @@
       <c r="G17" s="8"/>
       <c r="K17" s="6"/>
     </row>
-    <row r="18" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="7">
         <v>1000</v>
       </c>
@@ -2440,7 +2638,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="7"/>
       <c r="C19" s="8"/>
       <c r="D19" s="7"/>
@@ -2449,7 +2647,7 @@
       <c r="G19" s="8"/>
       <c r="K19" s="6"/>
     </row>
-    <row r="20" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="7">
         <v>1000</v>
       </c>
@@ -2479,7 +2677,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="7"/>
       <c r="C21" s="8"/>
       <c r="D21" s="7"/>
@@ -2487,23 +2685,23 @@
       <c r="F21" s="7"/>
       <c r="G21" s="8"/>
     </row>
-    <row r="22" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="16" t="s">
+    <row r="22" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="17" t="s">
         <v>183</v>
       </c>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="17" t="s">
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="18" t="s">
         <v>187</v>
       </c>
-      <c r="H22" s="17"/>
-      <c r="I22" s="17"/>
-      <c r="J22" s="17"/>
-      <c r="K22" s="17"/>
-    </row>
-    <row r="23" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H22" s="18"/>
+      <c r="I22" s="18"/>
+      <c r="J22" s="18"/>
+      <c r="K22" s="18"/>
+    </row>
+    <row r="23" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="8" t="s">
         <v>184</v>
       </c>
@@ -2535,7 +2733,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="7">
         <v>1000</v>
       </c>
@@ -2570,7 +2768,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="2"/>
@@ -2583,7 +2781,7 @@
       <c r="M25" s="2"/>
       <c r="N25" s="2"/>
     </row>
-    <row r="26" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="3">
         <v>2000</v>
       </c>
@@ -2619,7 +2817,7 @@
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
     </row>
-    <row r="27" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="3">
         <v>2000</v>
       </c>
@@ -2655,7 +2853,7 @@
       <c r="M27" s="2"/>
       <c r="N27" s="2"/>
     </row>
-    <row r="28" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="3">
         <v>2000</v>
       </c>
@@ -2693,7 +2891,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="3">
         <v>2000</v>
       </c>
@@ -2729,7 +2927,7 @@
       <c r="M29" s="2"/>
       <c r="N29" s="2"/>
     </row>
-    <row r="30" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="3">
         <v>2000</v>
       </c>
@@ -2765,7 +2963,7 @@
       <c r="M30" s="2"/>
       <c r="N30" s="2"/>
     </row>
-    <row r="31" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="3">
         <v>2000</v>
       </c>
@@ -2801,7 +2999,7 @@
       <c r="M31" s="2"/>
       <c r="N31" s="2"/>
     </row>
-    <row r="32" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="3">
         <v>2000</v>
       </c>
@@ -2837,7 +3035,7 @@
       <c r="M32" s="2"/>
       <c r="N32" s="2"/>
     </row>
-    <row r="33" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="3">
         <v>2000</v>
       </c>
@@ -2873,7 +3071,7 @@
       <c r="M33" s="2"/>
       <c r="N33" s="2"/>
     </row>
-    <row r="34" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="2"/>
@@ -2886,7 +3084,7 @@
       <c r="M34" s="2"/>
       <c r="N34" s="2"/>
     </row>
-    <row r="35" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="2"/>
@@ -2899,7 +3097,7 @@
       <c r="M35" s="2"/>
       <c r="N35" s="2"/>
     </row>
-    <row r="36" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="3">
         <v>5000</v>
       </c>
@@ -2935,7 +3133,7 @@
       <c r="M36" s="2"/>
       <c r="N36" s="2"/>
     </row>
-    <row r="37" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <v>5000</v>
       </c>
@@ -2973,7 +3171,7 @@
       </c>
       <c r="N37" s="2"/>
     </row>
-    <row r="38" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="3">
         <v>5000</v>
       </c>
@@ -3009,7 +3207,7 @@
       <c r="M38" s="2"/>
       <c r="N38" s="2"/>
     </row>
-    <row r="39" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
         <v>5000</v>
       </c>
@@ -3047,7 +3245,7 @@
       </c>
       <c r="N39" s="2"/>
     </row>
-    <row r="40" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
         <v>5000</v>
       </c>
@@ -3083,7 +3281,7 @@
       <c r="M40" s="2"/>
       <c r="N40" s="2"/>
     </row>
-    <row r="41" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <v>5000</v>
       </c>
@@ -3123,7 +3321,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="42" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <v>5000</v>
       </c>
@@ -3159,7 +3357,7 @@
       <c r="M42" s="2"/>
       <c r="N42" s="2"/>
     </row>
-    <row r="43" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
         <v>5000</v>
       </c>
@@ -3195,7 +3393,7 @@
       <c r="M43" s="2"/>
       <c r="N43" s="2"/>
     </row>
-    <row r="44" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="1"/>
       <c r="B44" s="2"/>
       <c r="C44" s="1"/>
@@ -3211,7 +3409,7 @@
       <c r="M44" s="2"/>
       <c r="N44" s="2"/>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A45" s="1"/>
       <c r="B45" s="2"/>
       <c r="C45" s="1"/>
@@ -3227,7 +3425,7 @@
       <c r="M45" s="2"/>
       <c r="N45" s="2"/>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A46" s="1"/>
       <c r="B46" s="2"/>
       <c r="C46" s="1"/>
@@ -3243,7 +3441,7 @@
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>102</v>
       </c>
@@ -3261,23 +3459,23 @@
       <c r="M47" s="2"/>
       <c r="N47" s="2"/>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B48" s="16" t="s">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="B48" s="17" t="s">
         <v>183</v>
       </c>
-      <c r="C48" s="16"/>
-      <c r="D48" s="16"/>
-      <c r="E48" s="16"/>
-      <c r="F48" s="16"/>
-      <c r="G48" s="17" t="s">
+      <c r="C48" s="17"/>
+      <c r="D48" s="17"/>
+      <c r="E48" s="17"/>
+      <c r="F48" s="17"/>
+      <c r="G48" s="18" t="s">
         <v>187</v>
       </c>
-      <c r="H48" s="17"/>
-      <c r="I48" s="17"/>
-      <c r="J48" s="17"/>
-      <c r="K48" s="17"/>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="H48" s="18"/>
+      <c r="I48" s="18"/>
+      <c r="J48" s="18"/>
+      <c r="K48" s="18"/>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B49" s="8" t="s">
         <v>184</v>
       </c>
@@ -3309,7 +3507,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A50" s="7">
         <v>1000</v>
       </c>
@@ -3344,12 +3542,12 @@
         <v>194</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.35">
       <c r="G65" s="9" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A66" s="7" t="s">
         <v>0</v>
       </c>
@@ -3393,7 +3591,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A67" s="7">
         <v>1000</v>
       </c>
@@ -3425,7 +3623,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A68" s="7">
         <v>1000</v>
       </c>
@@ -3457,7 +3655,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A69" s="7">
         <v>1000</v>
       </c>
@@ -3489,7 +3687,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A70" s="7">
         <v>1000</v>
       </c>
@@ -3524,7 +3722,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A71" s="7">
         <v>1000</v>
       </c>
@@ -3556,7 +3754,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A72" s="7">
         <v>1000</v>
       </c>
@@ -3588,7 +3786,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A73" s="7">
         <v>1000</v>
       </c>
@@ -3620,7 +3818,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A74" s="7">
         <v>1000</v>
       </c>
@@ -3667,22 +3865,22 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L58"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.44140625" customWidth="1"/>
-    <col min="2" max="2" width="16.33203125" customWidth="1"/>
-    <col min="3" max="3" width="13.109375" customWidth="1"/>
-    <col min="4" max="4" width="13.21875" customWidth="1"/>
-    <col min="5" max="5" width="13.33203125" customWidth="1"/>
-    <col min="6" max="6" width="15.77734375" customWidth="1"/>
-    <col min="7" max="7" width="13.21875" customWidth="1"/>
-    <col min="8" max="8" width="13.77734375" customWidth="1"/>
-    <col min="9" max="9" width="13.88671875" customWidth="1"/>
+    <col min="1" max="1" width="15.453125" customWidth="1"/>
+    <col min="2" max="2" width="16.36328125" customWidth="1"/>
+    <col min="3" max="3" width="13.08984375" customWidth="1"/>
+    <col min="4" max="4" width="13.1796875" customWidth="1"/>
+    <col min="5" max="5" width="13.36328125" customWidth="1"/>
+    <col min="6" max="6" width="15.81640625" customWidth="1"/>
+    <col min="7" max="7" width="13.1796875" customWidth="1"/>
+    <col min="8" max="8" width="13.81640625" customWidth="1"/>
+    <col min="9" max="9" width="13.90625" customWidth="1"/>
     <col min="10" max="10" width="13" customWidth="1"/>
-    <col min="11" max="11" width="29.77734375" customWidth="1"/>
+    <col min="11" max="11" width="29.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="7"/>
       <c r="B1" s="8"/>
       <c r="C1" s="7"/>
@@ -3697,7 +3895,7 @@
       <c r="J1" s="8"/>
       <c r="K1" s="8"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="7"/>
@@ -3710,7 +3908,7 @@
       <c r="J2" s="8"/>
       <c r="K2" s="8"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="7"/>
       <c r="B3" s="8"/>
       <c r="C3" s="7"/>
@@ -3723,7 +3921,7 @@
       <c r="J3" s="8"/>
       <c r="K3" s="8"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
         <v>0</v>
       </c>
@@ -3761,7 +3959,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>1000</v>
       </c>
@@ -3787,7 +3985,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>1000</v>
       </c>
@@ -3813,7 +4011,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>1000</v>
       </c>
@@ -3839,7 +4037,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>1000</v>
       </c>
@@ -3865,7 +4063,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="8"/>
       <c r="B12" s="7"/>
       <c r="C12" s="8"/>
@@ -3877,7 +4075,7 @@
       <c r="I12" s="8"/>
       <c r="J12" s="8"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>1000</v>
       </c>
@@ -3897,7 +4095,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>1000</v>
       </c>
@@ -3917,7 +4115,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>1000</v>
       </c>
@@ -3937,7 +4135,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>1000</v>
       </c>
@@ -3957,23 +4155,23 @@
         <v>418</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" s="16" t="s">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A24" s="17" t="s">
         <v>183</v>
       </c>
-      <c r="B24" s="16"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="17" t="s">
+      <c r="B24" s="17"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="18" t="s">
         <v>187</v>
       </c>
-      <c r="G24" s="17"/>
-      <c r="H24" s="17"/>
-      <c r="I24" s="17"/>
-      <c r="J24" s="17"/>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="18"/>
+      <c r="J24" s="18"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" s="8" t="s">
         <v>184</v>
       </c>
@@ -4005,7 +4203,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26" s="8" t="s">
         <v>14</v>
       </c>
@@ -4037,7 +4235,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>14</v>
       </c>
@@ -4069,7 +4267,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A32" s="7"/>
       <c r="B32" s="8"/>
       <c r="C32" s="7"/>
@@ -4084,7 +4282,7 @@
       <c r="J32" s="8"/>
       <c r="K32" s="8"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A33" s="7"/>
       <c r="B33" s="8"/>
       <c r="C33" s="7"/>
@@ -4097,7 +4295,7 @@
       <c r="J33" s="8"/>
       <c r="K33" s="8"/>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34" s="7"/>
       <c r="B34" s="8"/>
       <c r="C34" s="7"/>
@@ -4110,7 +4308,7 @@
       <c r="J34" s="8"/>
       <c r="K34" s="8"/>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A35" s="7" t="s">
         <v>0</v>
       </c>
@@ -4148,7 +4346,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>1000</v>
       </c>
@@ -4159,7 +4357,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>1000</v>
       </c>
@@ -4174,7 +4372,7 @@
       </c>
       <c r="I38" s="11"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>1000</v>
       </c>
@@ -4189,7 +4387,7 @@
       </c>
       <c r="I40" s="12"/>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>1000</v>
       </c>
@@ -4205,7 +4403,7 @@
       </c>
       <c r="I42" s="12"/>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A43" s="8"/>
       <c r="B43" s="7"/>
       <c r="C43" s="8"/>
@@ -4217,7 +4415,7 @@
       <c r="I43" s="8"/>
       <c r="J43" s="8"/>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>1000</v>
       </c>
@@ -4237,7 +4435,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>1000</v>
       </c>
@@ -4257,7 +4455,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>1000</v>
       </c>
@@ -4277,7 +4475,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>1000</v>
       </c>
@@ -4297,23 +4495,23 @@
         <v>430</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A55" s="16" t="s">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A55" s="17" t="s">
         <v>183</v>
       </c>
-      <c r="B55" s="16"/>
-      <c r="C55" s="16"/>
-      <c r="D55" s="16"/>
-      <c r="E55" s="16"/>
-      <c r="F55" s="17" t="s">
+      <c r="B55" s="17"/>
+      <c r="C55" s="17"/>
+      <c r="D55" s="17"/>
+      <c r="E55" s="17"/>
+      <c r="F55" s="18" t="s">
         <v>187</v>
       </c>
-      <c r="G55" s="17"/>
-      <c r="H55" s="17"/>
-      <c r="I55" s="17"/>
-      <c r="J55" s="17"/>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G55" s="18"/>
+      <c r="H55" s="18"/>
+      <c r="I55" s="18"/>
+      <c r="J55" s="18"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A56" s="8" t="s">
         <v>184</v>
       </c>
@@ -4345,7 +4543,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A57" s="8" t="s">
         <v>14</v>
       </c>
@@ -4359,7 +4557,7 @@
       <c r="I57" s="6"/>
       <c r="J57" s="7"/>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>14</v>
       </c>
@@ -4405,24 +4603,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="2" max="2" width="12.88671875" customWidth="1"/>
-    <col min="3" max="3" width="12.77734375" customWidth="1"/>
-    <col min="4" max="4" width="13.5546875" customWidth="1"/>
-    <col min="5" max="5" width="11.88671875" customWidth="1"/>
-    <col min="6" max="6" width="9.6640625" customWidth="1"/>
-    <col min="7" max="7" width="11.33203125" customWidth="1"/>
-    <col min="8" max="8" width="16.77734375" customWidth="1"/>
-    <col min="9" max="9" width="14.109375" customWidth="1"/>
-    <col min="10" max="10" width="15.21875" customWidth="1"/>
-    <col min="11" max="11" width="13.88671875" customWidth="1"/>
-    <col min="12" max="12" width="12.88671875" customWidth="1"/>
-    <col min="13" max="13" width="27.88671875" customWidth="1"/>
+    <col min="2" max="2" width="12.90625" customWidth="1"/>
+    <col min="3" max="3" width="12.81640625" customWidth="1"/>
+    <col min="4" max="4" width="13.54296875" customWidth="1"/>
+    <col min="5" max="5" width="11.90625" customWidth="1"/>
+    <col min="6" max="6" width="9.6328125" customWidth="1"/>
+    <col min="7" max="7" width="11.36328125" customWidth="1"/>
+    <col min="8" max="8" width="16.81640625" customWidth="1"/>
+    <col min="9" max="9" width="14.08984375" customWidth="1"/>
+    <col min="10" max="10" width="15.1796875" customWidth="1"/>
+    <col min="11" max="11" width="13.90625" customWidth="1"/>
+    <col min="12" max="12" width="12.90625" customWidth="1"/>
+    <col min="13" max="13" width="27.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="7"/>
       <c r="B1" s="8"/>
       <c r="C1" s="7"/>
@@ -4437,7 +4635,7 @@
       <c r="J1" s="8"/>
       <c r="K1" s="8"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="7"/>
@@ -4450,7 +4648,7 @@
       <c r="J2" s="8"/>
       <c r="K2" s="8"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="7"/>
       <c r="B3" s="8"/>
       <c r="C3" s="7"/>
@@ -4463,7 +4661,7 @@
       <c r="J3" s="8"/>
       <c r="K3" s="8"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
         <v>0</v>
       </c>
@@ -4507,7 +4705,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>1000</v>
       </c>
@@ -4543,7 +4741,7 @@
       <c r="M5" s="8"/>
       <c r="N5" s="8"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="8"/>
@@ -4559,7 +4757,7 @@
       <c r="M6" s="8"/>
       <c r="N6" s="8"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>1000</v>
       </c>
@@ -4595,10 +4793,10 @@
       <c r="M7" s="8"/>
       <c r="N7" s="8"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="N8" s="8"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>1000</v>
       </c>
@@ -4634,7 +4832,7 @@
       <c r="M9" s="8"/>
       <c r="N9" s="8"/>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="8"/>
@@ -4650,7 +4848,7 @@
       <c r="M10" s="8"/>
       <c r="N10" s="8"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>1000</v>
       </c>
@@ -4686,10 +4884,10 @@
       <c r="M11" s="8"/>
       <c r="N11" s="8"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="N12" s="8"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="7"/>
       <c r="B13" s="7"/>
       <c r="C13" s="8"/>
@@ -4705,7 +4903,7 @@
       <c r="M13" s="8"/>
       <c r="N13" s="8"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
       <c r="C14" s="8"/>
@@ -4721,7 +4919,7 @@
       <c r="M14" s="8"/>
       <c r="N14" s="8"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="7"/>
       <c r="B15" s="7"/>
       <c r="C15" s="8"/>
@@ -4737,7 +4935,7 @@
       <c r="M15" s="8"/>
       <c r="N15" s="8"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="7" t="s">
         <v>102</v>
       </c>
@@ -4755,27 +4953,27 @@
       <c r="M16" s="8"/>
       <c r="N16" s="8"/>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" s="7"/>
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="17" t="s">
         <v>183</v>
       </c>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="17" t="s">
+      <c r="C17" s="17"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="18" t="s">
         <v>187</v>
       </c>
-      <c r="H17" s="17"/>
-      <c r="I17" s="17"/>
-      <c r="J17" s="17"/>
-      <c r="K17" s="17"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="18"/>
+      <c r="J17" s="18"/>
+      <c r="K17" s="18"/>
       <c r="L17" s="8"/>
       <c r="M17" s="8"/>
       <c r="N17" s="8"/>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" s="7"/>
       <c r="B18" s="8" t="s">
         <v>184</v>
@@ -4811,7 +5009,7 @@
       <c r="M18" s="8"/>
       <c r="N18" s="8"/>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" s="7">
         <v>1000</v>
       </c>
@@ -4849,7 +5047,7 @@
       <c r="M19" s="8"/>
       <c r="N19" s="8"/>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="8"/>
@@ -4865,7 +5063,7 @@
       <c r="M20" s="8"/>
       <c r="N20" s="8"/>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
       <c r="C21" s="8"/>
@@ -4892,22 +5090,22 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N54"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:N126"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
-    <col min="2" max="2" width="12.5546875" customWidth="1"/>
-    <col min="3" max="3" width="14.44140625" customWidth="1"/>
-    <col min="4" max="4" width="15.88671875" customWidth="1"/>
-    <col min="5" max="5" width="13.21875" customWidth="1"/>
-    <col min="6" max="6" width="18.21875" customWidth="1"/>
-    <col min="7" max="7" width="17.6640625" customWidth="1"/>
-    <col min="8" max="9" width="17.109375" customWidth="1"/>
-    <col min="10" max="10" width="16.21875" customWidth="1"/>
-    <col min="11" max="11" width="27.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.54296875" customWidth="1"/>
+    <col min="3" max="3" width="14.453125" customWidth="1"/>
+    <col min="4" max="4" width="15.90625" customWidth="1"/>
+    <col min="5" max="5" width="13.1796875" customWidth="1"/>
+    <col min="6" max="6" width="18.1796875" customWidth="1"/>
+    <col min="7" max="7" width="17.6328125" customWidth="1"/>
+    <col min="8" max="9" width="17.08984375" customWidth="1"/>
+    <col min="10" max="10" width="16.1796875" customWidth="1"/>
+    <col min="11" max="11" width="27.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="7"/>
       <c r="B1" s="8"/>
       <c r="C1" s="7"/>
@@ -4917,7 +5115,7 @@
       <c r="G1" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="H1" s="18" t="s">
+      <c r="H1" s="16" t="s">
         <v>454</v>
       </c>
       <c r="I1" s="7"/>
@@ -4927,7 +5125,7 @@
       <c r="M1" s="8"/>
       <c r="N1" s="8"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="7"/>
@@ -4943,7 +5141,7 @@
       <c r="M2" s="8"/>
       <c r="N2" s="8"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="7"/>
       <c r="B3" s="8"/>
       <c r="C3" s="7"/>
@@ -4959,7 +5157,7 @@
       <c r="M3" s="8"/>
       <c r="N3" s="8"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
         <v>0</v>
       </c>
@@ -4997,7 +5195,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>1000</v>
       </c>
@@ -5023,7 +5221,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>1000</v>
       </c>
@@ -5049,7 +5247,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>1000</v>
       </c>
@@ -5075,7 +5273,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>1000</v>
       </c>
@@ -5101,7 +5299,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="7" t="s">
         <v>102</v>
       </c>
@@ -5116,24 +5314,24 @@
       <c r="J14" s="8"/>
       <c r="K14" s="8"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="7"/>
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="17" t="s">
         <v>183</v>
       </c>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="17" t="s">
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="18" t="s">
         <v>187</v>
       </c>
-      <c r="H15" s="17"/>
-      <c r="I15" s="17"/>
-      <c r="J15" s="17"/>
-      <c r="K15" s="17"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="H15" s="18"/>
+      <c r="I15" s="18"/>
+      <c r="J15" s="18"/>
+      <c r="K15" s="18"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="7"/>
       <c r="B16" s="8" t="s">
         <v>184</v>
@@ -5166,7 +5364,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" s="7">
         <v>1000</v>
       </c>
@@ -5201,15 +5399,15 @@
         <v>202</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="G20" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="H20" s="18" t="s">
+      <c r="H20" s="16" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A22" s="7" t="s">
         <v>0</v>
       </c>
@@ -5247,7 +5445,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>1000</v>
       </c>
@@ -5273,7 +5471,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>1000</v>
       </c>
@@ -5299,7 +5497,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>1000</v>
       </c>
@@ -5325,7 +5523,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>1000</v>
       </c>
@@ -5351,7 +5549,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A32" s="7" t="s">
         <v>102</v>
       </c>
@@ -5366,24 +5564,24 @@
       <c r="J32" s="8"/>
       <c r="K32" s="8"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A33" s="7"/>
-      <c r="B33" s="16" t="s">
+      <c r="B33" s="17" t="s">
         <v>183</v>
       </c>
-      <c r="C33" s="16"/>
-      <c r="D33" s="16"/>
-      <c r="E33" s="16"/>
-      <c r="F33" s="16"/>
-      <c r="G33" s="17" t="s">
+      <c r="C33" s="17"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="18" t="s">
         <v>187</v>
       </c>
-      <c r="H33" s="17"/>
-      <c r="I33" s="17"/>
-      <c r="J33" s="17"/>
-      <c r="K33" s="17"/>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H33" s="18"/>
+      <c r="I33" s="18"/>
+      <c r="J33" s="18"/>
+      <c r="K33" s="18"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34" s="7"/>
       <c r="B34" s="8" t="s">
         <v>184</v>
@@ -5416,7 +5614,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A35" s="7">
         <v>1000</v>
       </c>
@@ -5451,15 +5649,15 @@
         <v>474</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="G39" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="H39" s="18" t="s">
+      <c r="H39" s="16" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A41" s="7" t="s">
         <v>0</v>
       </c>
@@ -5497,7 +5695,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>1000</v>
       </c>
@@ -5523,7 +5721,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>1000</v>
       </c>
@@ -5549,7 +5747,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>1000</v>
       </c>
@@ -5575,7 +5773,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>1000</v>
       </c>
@@ -5601,7 +5799,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A51" s="7" t="s">
         <v>102</v>
       </c>
@@ -5616,24 +5814,24 @@
       <c r="J51" s="8"/>
       <c r="K51" s="8"/>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A52" s="7"/>
-      <c r="B52" s="16" t="s">
+      <c r="B52" s="17" t="s">
         <v>183</v>
       </c>
-      <c r="C52" s="16"/>
-      <c r="D52" s="16"/>
-      <c r="E52" s="16"/>
-      <c r="F52" s="16"/>
-      <c r="G52" s="17" t="s">
+      <c r="C52" s="17"/>
+      <c r="D52" s="17"/>
+      <c r="E52" s="17"/>
+      <c r="F52" s="17"/>
+      <c r="G52" s="18" t="s">
         <v>187</v>
       </c>
-      <c r="H52" s="17"/>
-      <c r="I52" s="17"/>
-      <c r="J52" s="17"/>
-      <c r="K52" s="17"/>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="H52" s="18"/>
+      <c r="I52" s="18"/>
+      <c r="J52" s="18"/>
+      <c r="K52" s="18"/>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A53" s="7"/>
       <c r="B53" s="8" t="s">
         <v>184</v>
@@ -5666,7 +5864,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A54" s="7">
         <v>1000</v>
       </c>
@@ -5701,14 +5899,1022 @@
         <v>490</v>
       </c>
     </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="G57" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="H57" s="16" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A59" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C59" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F59" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="G59" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="H59" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I59" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J59" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K59" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="L59" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A60">
+        <v>1000</v>
+      </c>
+      <c r="D60">
+        <v>2</v>
+      </c>
+      <c r="E60" t="s">
+        <v>502</v>
+      </c>
+      <c r="F60" t="s">
+        <v>14</v>
+      </c>
+      <c r="G60">
+        <v>291</v>
+      </c>
+      <c r="H60" t="s">
+        <v>493</v>
+      </c>
+      <c r="I60" t="s">
+        <v>503</v>
+      </c>
+      <c r="J60" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A62">
+        <v>1000</v>
+      </c>
+      <c r="D62">
+        <v>2</v>
+      </c>
+      <c r="E62" t="s">
+        <v>509</v>
+      </c>
+      <c r="F62" t="s">
+        <v>36</v>
+      </c>
+      <c r="G62">
+        <v>175</v>
+      </c>
+      <c r="H62" t="s">
+        <v>510</v>
+      </c>
+      <c r="I62" s="11" t="s">
+        <v>511</v>
+      </c>
+      <c r="J62" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A64">
+        <v>1000</v>
+      </c>
+      <c r="D64">
+        <v>2</v>
+      </c>
+      <c r="E64" t="s">
+        <v>513</v>
+      </c>
+      <c r="F64" t="s">
+        <v>47</v>
+      </c>
+      <c r="G64">
+        <v>175</v>
+      </c>
+      <c r="H64" t="s">
+        <v>514</v>
+      </c>
+      <c r="I64" s="12" t="s">
+        <v>515</v>
+      </c>
+      <c r="J64" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A66">
+        <v>1000</v>
+      </c>
+      <c r="D66">
+        <v>2</v>
+      </c>
+      <c r="E66" t="s">
+        <v>517</v>
+      </c>
+      <c r="F66" t="s">
+        <v>25</v>
+      </c>
+      <c r="G66">
+        <v>175</v>
+      </c>
+      <c r="H66" t="s">
+        <v>518</v>
+      </c>
+      <c r="I66" s="12" t="s">
+        <v>489</v>
+      </c>
+      <c r="J66" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A69" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B69" s="8"/>
+      <c r="C69" s="7"/>
+      <c r="D69" s="8"/>
+      <c r="E69" s="7"/>
+      <c r="F69" s="8"/>
+      <c r="G69" s="7"/>
+      <c r="H69" s="8"/>
+      <c r="I69" s="7"/>
+      <c r="J69" s="8"/>
+      <c r="K69" s="8"/>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A70" s="7"/>
+      <c r="B70" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="C70" s="17"/>
+      <c r="D70" s="17"/>
+      <c r="E70" s="17"/>
+      <c r="F70" s="17"/>
+      <c r="G70" s="18" t="s">
+        <v>187</v>
+      </c>
+      <c r="H70" s="18"/>
+      <c r="I70" s="18"/>
+      <c r="J70" s="18"/>
+      <c r="K70" s="18"/>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A71" s="7"/>
+      <c r="B71" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="D71" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="E71" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F71" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G71" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="H71" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="I71" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="J71" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="K71" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A72" s="7">
+        <v>1000</v>
+      </c>
+      <c r="B72" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C72" s="7">
+        <v>291</v>
+      </c>
+      <c r="D72" s="8">
+        <v>94</v>
+      </c>
+      <c r="E72" t="s">
+        <v>503</v>
+      </c>
+      <c r="F72" t="s">
+        <v>504</v>
+      </c>
+      <c r="G72" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H72" s="8">
+        <v>113</v>
+      </c>
+      <c r="I72" s="7">
+        <v>39</v>
+      </c>
+      <c r="J72" s="6" t="s">
+        <v>505</v>
+      </c>
+      <c r="K72" s="7" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="G75" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="H75" s="16" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A77" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D77" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E77" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F77" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="G77" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="H77" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I77" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J77" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K77" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="L77" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A78">
+        <v>1000</v>
+      </c>
+      <c r="D78">
+        <v>2</v>
+      </c>
+      <c r="E78" t="s">
+        <v>265</v>
+      </c>
+      <c r="F78" t="s">
+        <v>14</v>
+      </c>
+      <c r="G78">
+        <v>296</v>
+      </c>
+      <c r="H78" t="s">
+        <v>520</v>
+      </c>
+      <c r="I78" t="s">
+        <v>521</v>
+      </c>
+      <c r="J78" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A80">
+        <v>1000</v>
+      </c>
+      <c r="D80">
+        <v>2</v>
+      </c>
+      <c r="E80" t="s">
+        <v>525</v>
+      </c>
+      <c r="F80" t="s">
+        <v>36</v>
+      </c>
+      <c r="G80">
+        <v>175</v>
+      </c>
+      <c r="H80" t="s">
+        <v>526</v>
+      </c>
+      <c r="I80" s="11" t="s">
+        <v>527</v>
+      </c>
+      <c r="J80" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A82">
+        <v>1000</v>
+      </c>
+      <c r="D82">
+        <v>2</v>
+      </c>
+      <c r="E82" t="s">
+        <v>529</v>
+      </c>
+      <c r="F82" t="s">
+        <v>47</v>
+      </c>
+      <c r="G82">
+        <v>175</v>
+      </c>
+      <c r="H82" t="s">
+        <v>531</v>
+      </c>
+      <c r="I82" s="12" t="s">
+        <v>530</v>
+      </c>
+      <c r="J82" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A84">
+        <v>1000</v>
+      </c>
+      <c r="D84">
+        <v>2</v>
+      </c>
+      <c r="E84" t="s">
+        <v>533</v>
+      </c>
+      <c r="F84" t="s">
+        <v>25</v>
+      </c>
+      <c r="G84">
+        <v>175</v>
+      </c>
+      <c r="H84" t="s">
+        <v>288</v>
+      </c>
+      <c r="I84" s="12" t="s">
+        <v>534</v>
+      </c>
+      <c r="J84" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A87" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B87" s="8"/>
+      <c r="C87" s="7"/>
+      <c r="D87" s="8"/>
+      <c r="E87" s="7"/>
+      <c r="F87" s="8"/>
+      <c r="G87" s="7"/>
+      <c r="H87" s="8"/>
+      <c r="I87" s="7"/>
+      <c r="J87" s="8"/>
+      <c r="K87" s="8"/>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A88" s="7"/>
+      <c r="B88" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="C88" s="17"/>
+      <c r="D88" s="17"/>
+      <c r="E88" s="17"/>
+      <c r="F88" s="17"/>
+      <c r="G88" s="18" t="s">
+        <v>187</v>
+      </c>
+      <c r="H88" s="18"/>
+      <c r="I88" s="18"/>
+      <c r="J88" s="18"/>
+      <c r="K88" s="18"/>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A89" s="7"/>
+      <c r="B89" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="D89" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="E89" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F89" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G89" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="H89" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="I89" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="J89" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="K89" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A90" s="7">
+        <v>1000</v>
+      </c>
+      <c r="B90" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C90" s="7">
+        <v>296</v>
+      </c>
+      <c r="D90" s="8">
+        <v>94</v>
+      </c>
+      <c r="E90" t="s">
+        <v>521</v>
+      </c>
+      <c r="F90" t="s">
+        <v>522</v>
+      </c>
+      <c r="G90" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H90" s="8">
+        <v>118</v>
+      </c>
+      <c r="I90" s="7">
+        <v>45</v>
+      </c>
+      <c r="J90" s="6" t="s">
+        <v>523</v>
+      </c>
+      <c r="K90" s="7" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="G93" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="H93" s="16" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A95" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B95" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C95" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D95" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E95" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F95" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="G95" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="H95" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I95" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J95" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K95" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="L95" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A96">
+        <v>1000</v>
+      </c>
+      <c r="D96">
+        <v>2</v>
+      </c>
+      <c r="E96" t="s">
+        <v>536</v>
+      </c>
+      <c r="F96" t="s">
+        <v>14</v>
+      </c>
+      <c r="G96">
+        <v>289</v>
+      </c>
+      <c r="H96" t="s">
+        <v>537</v>
+      </c>
+      <c r="I96" t="s">
+        <v>538</v>
+      </c>
+      <c r="J96" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A98">
+        <v>1000</v>
+      </c>
+      <c r="D98">
+        <v>2</v>
+      </c>
+      <c r="E98" t="s">
+        <v>542</v>
+      </c>
+      <c r="F98" t="s">
+        <v>36</v>
+      </c>
+      <c r="G98">
+        <v>175</v>
+      </c>
+      <c r="H98" t="s">
+        <v>543</v>
+      </c>
+      <c r="I98" s="11" t="s">
+        <v>544</v>
+      </c>
+      <c r="J98" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A100">
+        <v>1000</v>
+      </c>
+      <c r="D100">
+        <v>2</v>
+      </c>
+      <c r="E100" t="s">
+        <v>483</v>
+      </c>
+      <c r="F100" t="s">
+        <v>47</v>
+      </c>
+      <c r="G100">
+        <v>175</v>
+      </c>
+      <c r="H100" t="s">
+        <v>543</v>
+      </c>
+      <c r="I100" s="12" t="s">
+        <v>546</v>
+      </c>
+      <c r="J100" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A102">
+        <v>1000</v>
+      </c>
+      <c r="D102">
+        <v>2</v>
+      </c>
+      <c r="E102" s="13" t="s">
+        <v>548</v>
+      </c>
+      <c r="F102" t="s">
+        <v>25</v>
+      </c>
+      <c r="G102">
+        <v>175</v>
+      </c>
+      <c r="H102" t="s">
+        <v>518</v>
+      </c>
+      <c r="I102" s="12" t="s">
+        <v>549</v>
+      </c>
+      <c r="J102" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A105" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B105" s="8"/>
+      <c r="C105" s="7"/>
+      <c r="D105" s="8"/>
+      <c r="E105" s="7"/>
+      <c r="F105" s="8"/>
+      <c r="G105" s="7"/>
+      <c r="H105" s="8"/>
+      <c r="I105" s="7"/>
+      <c r="J105" s="8"/>
+      <c r="K105" s="8"/>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A106" s="7"/>
+      <c r="B106" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="C106" s="17"/>
+      <c r="D106" s="17"/>
+      <c r="E106" s="17"/>
+      <c r="F106" s="17"/>
+      <c r="G106" s="18" t="s">
+        <v>187</v>
+      </c>
+      <c r="H106" s="18"/>
+      <c r="I106" s="18"/>
+      <c r="J106" s="18"/>
+      <c r="K106" s="18"/>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A107" s="7"/>
+      <c r="B107" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="C107" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="D107" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="E107" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F107" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G107" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="H107" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="I107" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="J107" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="K107" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A108" s="7">
+        <v>1000</v>
+      </c>
+      <c r="B108" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C108" s="7">
+        <v>289</v>
+      </c>
+      <c r="D108" s="8">
+        <v>113</v>
+      </c>
+      <c r="E108" t="s">
+        <v>538</v>
+      </c>
+      <c r="F108" t="s">
+        <v>539</v>
+      </c>
+      <c r="G108" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H108" s="8">
+        <v>113</v>
+      </c>
+      <c r="I108" s="7">
+        <v>29</v>
+      </c>
+      <c r="J108" s="6" t="s">
+        <v>540</v>
+      </c>
+      <c r="K108" s="7" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="G111" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="H111" s="16" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A113" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B113" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C113" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D113" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E113" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F113" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="G113" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="H113" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I113" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J113" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K113" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="L113" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A114">
+        <v>1000</v>
+      </c>
+      <c r="D114">
+        <v>2</v>
+      </c>
+      <c r="E114" t="s">
+        <v>551</v>
+      </c>
+      <c r="F114" t="s">
+        <v>14</v>
+      </c>
+      <c r="G114">
+        <v>301</v>
+      </c>
+      <c r="H114" t="s">
+        <v>420</v>
+      </c>
+      <c r="I114" t="s">
+        <v>552</v>
+      </c>
+      <c r="J114" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A116">
+        <v>1000</v>
+      </c>
+      <c r="D116">
+        <v>2</v>
+      </c>
+      <c r="E116" t="s">
+        <v>557</v>
+      </c>
+      <c r="F116" t="s">
+        <v>36</v>
+      </c>
+      <c r="G116">
+        <v>175</v>
+      </c>
+      <c r="H116" t="s">
+        <v>558</v>
+      </c>
+      <c r="I116" s="11" t="s">
+        <v>559</v>
+      </c>
+      <c r="J116" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A118">
+        <v>1000</v>
+      </c>
+      <c r="D118">
+        <v>2</v>
+      </c>
+      <c r="E118" t="s">
+        <v>561</v>
+      </c>
+      <c r="F118" t="s">
+        <v>47</v>
+      </c>
+      <c r="G118">
+        <v>175</v>
+      </c>
+      <c r="H118" t="s">
+        <v>562</v>
+      </c>
+      <c r="I118" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="J118" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A120">
+        <v>1000</v>
+      </c>
+      <c r="D120">
+        <v>2</v>
+      </c>
+      <c r="E120" s="13" t="s">
+        <v>564</v>
+      </c>
+      <c r="F120" t="s">
+        <v>25</v>
+      </c>
+      <c r="G120">
+        <v>175</v>
+      </c>
+      <c r="H120" t="s">
+        <v>565</v>
+      </c>
+      <c r="I120" s="12" t="s">
+        <v>523</v>
+      </c>
+      <c r="J120" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A123" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B123" s="8"/>
+      <c r="C123" s="7"/>
+      <c r="D123" s="8"/>
+      <c r="E123" s="7"/>
+      <c r="F123" s="8"/>
+      <c r="G123" s="7"/>
+      <c r="H123" s="8"/>
+      <c r="I123" s="7"/>
+      <c r="J123" s="8"/>
+      <c r="K123" s="8"/>
+    </row>
+    <row r="124" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A124" s="7"/>
+      <c r="B124" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="C124" s="17"/>
+      <c r="D124" s="17"/>
+      <c r="E124" s="17"/>
+      <c r="F124" s="17"/>
+      <c r="G124" s="18" t="s">
+        <v>187</v>
+      </c>
+      <c r="H124" s="18"/>
+      <c r="I124" s="18"/>
+      <c r="J124" s="18"/>
+      <c r="K124" s="18"/>
+    </row>
+    <row r="125" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A125" s="7"/>
+      <c r="B125" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="C125" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="D125" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="E125" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F125" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G125" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="H125" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="I125" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="J125" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="K125" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A126" s="7">
+        <v>1000</v>
+      </c>
+      <c r="B126" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C126" s="7">
+        <v>301</v>
+      </c>
+      <c r="D126" s="8">
+        <v>83</v>
+      </c>
+      <c r="E126" t="s">
+        <v>552</v>
+      </c>
+      <c r="F126" t="s">
+        <v>553</v>
+      </c>
+      <c r="G126" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H126" s="8">
+        <v>107</v>
+      </c>
+      <c r="I126" s="7">
+        <v>26</v>
+      </c>
+      <c r="J126" s="6" t="s">
+        <v>555</v>
+      </c>
+      <c r="K126" s="7" t="s">
+        <v>556</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="14">
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="G124:K124"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="G15:K15"/>
     <mergeCell ref="B33:F33"/>
     <mergeCell ref="G33:K33"/>
     <mergeCell ref="B52:F52"/>
     <mergeCell ref="G52:K52"/>
+    <mergeCell ref="B70:F70"/>
+    <mergeCell ref="G70:K70"/>
+    <mergeCell ref="B88:F88"/>
+    <mergeCell ref="G88:K88"/>
+    <mergeCell ref="B106:F106"/>
+    <mergeCell ref="G106:K106"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -5718,21 +6924,21 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" customWidth="1"/>
-    <col min="2" max="2" width="15.6640625" customWidth="1"/>
+    <col min="1" max="1" width="10.36328125" customWidth="1"/>
+    <col min="2" max="2" width="15.6328125" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" customWidth="1"/>
-    <col min="5" max="5" width="14.44140625" customWidth="1"/>
-    <col min="6" max="6" width="16.109375" customWidth="1"/>
-    <col min="7" max="8" width="17.109375" customWidth="1"/>
-    <col min="9" max="9" width="13.21875" customWidth="1"/>
-    <col min="10" max="10" width="15.88671875" customWidth="1"/>
-    <col min="11" max="11" width="27.44140625" customWidth="1"/>
+    <col min="4" max="4" width="11.54296875" customWidth="1"/>
+    <col min="5" max="5" width="14.453125" customWidth="1"/>
+    <col min="6" max="6" width="16.08984375" customWidth="1"/>
+    <col min="7" max="8" width="17.08984375" customWidth="1"/>
+    <col min="9" max="9" width="13.1796875" customWidth="1"/>
+    <col min="10" max="10" width="15.90625" customWidth="1"/>
+    <col min="11" max="11" width="27.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="7"/>
       <c r="B1" s="8"/>
       <c r="C1" s="7"/>
@@ -5750,7 +6956,7 @@
       <c r="M1" s="8"/>
       <c r="N1" s="8"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="7"/>
@@ -5766,7 +6972,7 @@
       <c r="M2" s="8"/>
       <c r="N2" s="8"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="7"/>
       <c r="B3" s="8"/>
       <c r="C3" s="7"/>
@@ -5782,7 +6988,7 @@
       <c r="M3" s="8"/>
       <c r="N3" s="8"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
         <v>0</v>
       </c>
@@ -5820,7 +7026,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>1000</v>
       </c>
@@ -5846,7 +7052,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>1000</v>
       </c>
@@ -5872,7 +7078,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>1000</v>
       </c>
@@ -5898,7 +7104,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>1000</v>
       </c>
@@ -5924,7 +7130,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="8"/>
       <c r="B12" s="7"/>
       <c r="C12" s="8"/>
@@ -5936,23 +7142,23 @@
       <c r="I12" s="8"/>
       <c r="J12" s="8"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="16" t="s">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A13" s="17" t="s">
         <v>183</v>
       </c>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="17" t="s">
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="18" t="s">
         <v>187</v>
       </c>
-      <c r="G13" s="17"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="17"/>
-      <c r="J13" s="17"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="G13" s="18"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="18"/>
+      <c r="J13" s="18"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="8" t="s">
         <v>184</v>
       </c>
@@ -5984,7 +7190,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="8" t="s">
         <v>14</v>
       </c>
@@ -6028,23 +7234,23 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N26"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.44140625" customWidth="1"/>
+    <col min="1" max="1" width="13.453125" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" customWidth="1"/>
-    <col min="4" max="4" width="12.77734375" customWidth="1"/>
+    <col min="3" max="3" width="12.453125" customWidth="1"/>
+    <col min="4" max="4" width="12.81640625" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="6" max="6" width="15.6640625" customWidth="1"/>
-    <col min="7" max="7" width="15.109375" customWidth="1"/>
-    <col min="8" max="8" width="17.33203125" customWidth="1"/>
-    <col min="9" max="9" width="16.77734375" customWidth="1"/>
+    <col min="6" max="6" width="15.6328125" customWidth="1"/>
+    <col min="7" max="7" width="15.08984375" customWidth="1"/>
+    <col min="8" max="8" width="17.36328125" customWidth="1"/>
+    <col min="9" max="9" width="16.81640625" customWidth="1"/>
     <col min="10" max="10" width="15" customWidth="1"/>
-    <col min="11" max="11" width="29.21875" customWidth="1"/>
+    <col min="11" max="11" width="29.1796875" customWidth="1"/>
     <col min="12" max="12" width="79" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="7"/>
       <c r="B1" s="8"/>
       <c r="C1" s="7"/>
@@ -6062,7 +7268,7 @@
       <c r="M1" s="8"/>
       <c r="N1" s="8"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="7"/>
@@ -6078,7 +7284,7 @@
       <c r="M2" s="8"/>
       <c r="N2" s="8"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="7"/>
       <c r="B3" s="8"/>
       <c r="C3" s="7"/>
@@ -6094,7 +7300,7 @@
       <c r="M3" s="8"/>
       <c r="N3" s="8"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
         <v>0</v>
       </c>
@@ -6132,7 +7338,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>1000</v>
       </c>
@@ -6158,7 +7364,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>1000</v>
       </c>
@@ -6184,7 +7390,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>1000</v>
       </c>
@@ -6210,7 +7416,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>1000</v>
       </c>
@@ -6236,7 +7442,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="8"/>
       <c r="B12" s="7"/>
       <c r="C12" s="8"/>
@@ -6248,7 +7454,7 @@
       <c r="I12" s="8"/>
       <c r="J12" s="8"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="15">
         <v>1000</v>
       </c>
@@ -6272,7 +7478,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>1000</v>
       </c>
@@ -6292,7 +7498,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>1000</v>
       </c>
@@ -6312,7 +7518,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>1000</v>
       </c>
@@ -6332,23 +7538,23 @@
         <v>404</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A23" s="16" t="s">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A23" s="17" t="s">
         <v>183</v>
       </c>
-      <c r="B23" s="16"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="17" t="s">
+      <c r="B23" s="17"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="18" t="s">
         <v>187</v>
       </c>
-      <c r="G23" s="17"/>
-      <c r="H23" s="17"/>
-      <c r="I23" s="17"/>
-      <c r="J23" s="17"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G23" s="18"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="18"/>
+      <c r="J23" s="18"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" s="8" t="s">
         <v>184</v>
       </c>
@@ -6380,7 +7586,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" s="8" t="s">
         <v>14</v>
       </c>
@@ -6412,7 +7618,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" s="8" t="s">
         <v>14</v>
       </c>
@@ -6443,22 +7649,22 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L31"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.21875" customWidth="1"/>
-    <col min="2" max="2" width="13.88671875" customWidth="1"/>
+    <col min="1" max="1" width="15.1796875" customWidth="1"/>
+    <col min="2" max="2" width="13.90625" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="5" width="14.21875" customWidth="1"/>
-    <col min="6" max="6" width="14.44140625" customWidth="1"/>
-    <col min="7" max="7" width="13.6640625" customWidth="1"/>
-    <col min="8" max="8" width="14.21875" customWidth="1"/>
-    <col min="9" max="9" width="13.44140625" customWidth="1"/>
-    <col min="10" max="10" width="15.77734375" customWidth="1"/>
-    <col min="11" max="11" width="30.88671875" customWidth="1"/>
-    <col min="12" max="12" width="75.5546875" customWidth="1"/>
+    <col min="4" max="5" width="14.1796875" customWidth="1"/>
+    <col min="6" max="6" width="14.453125" customWidth="1"/>
+    <col min="7" max="7" width="13.6328125" customWidth="1"/>
+    <col min="8" max="8" width="14.1796875" customWidth="1"/>
+    <col min="9" max="9" width="13.453125" customWidth="1"/>
+    <col min="10" max="10" width="15.81640625" customWidth="1"/>
+    <col min="11" max="11" width="30.90625" customWidth="1"/>
+    <col min="12" max="12" width="75.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="7"/>
       <c r="B1" s="8"/>
       <c r="C1" s="7"/>
@@ -6473,7 +7679,7 @@
       <c r="J1" s="8"/>
       <c r="K1" s="8"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="7"/>
@@ -6486,7 +7692,7 @@
       <c r="J2" s="8"/>
       <c r="K2" s="8"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="7"/>
       <c r="B3" s="8"/>
       <c r="C3" s="7"/>
@@ -6499,7 +7705,7 @@
       <c r="J3" s="8"/>
       <c r="K3" s="8"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
         <v>0</v>
       </c>
@@ -6537,7 +7743,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>1000</v>
       </c>
@@ -6563,7 +7769,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>1000</v>
       </c>
@@ -6589,7 +7795,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>1000</v>
       </c>
@@ -6615,7 +7821,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>1000</v>
       </c>
@@ -6641,7 +7847,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="8"/>
       <c r="B12" s="7"/>
       <c r="C12" s="8"/>
@@ -6653,7 +7859,7 @@
       <c r="I12" s="8"/>
       <c r="J12" s="8"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>1000</v>
       </c>
@@ -6673,7 +7879,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>1000</v>
       </c>
@@ -6693,7 +7899,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>1000</v>
       </c>
@@ -6713,7 +7919,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>1000</v>
       </c>
@@ -6734,23 +7940,23 @@
         <v>392</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A28" s="16" t="s">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A28" s="17" t="s">
         <v>183</v>
       </c>
-      <c r="B28" s="16"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="17" t="s">
+      <c r="B28" s="17"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="18" t="s">
         <v>187</v>
       </c>
-      <c r="G28" s="17"/>
-      <c r="H28" s="17"/>
-      <c r="I28" s="17"/>
-      <c r="J28" s="17"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G28" s="18"/>
+      <c r="H28" s="18"/>
+      <c r="I28" s="18"/>
+      <c r="J28" s="18"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" s="8" t="s">
         <v>184</v>
       </c>
@@ -6782,7 +7988,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" s="8" t="s">
         <v>14</v>
       </c>
@@ -6814,7 +8020,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" s="8" t="s">
         <v>14</v>
       </c>
@@ -6859,22 +8065,22 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.88671875" customWidth="1"/>
-    <col min="2" max="2" width="13.77734375" customWidth="1"/>
+    <col min="1" max="1" width="12.90625" customWidth="1"/>
+    <col min="2" max="2" width="13.81640625" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="13.5546875" customWidth="1"/>
-    <col min="5" max="5" width="12.5546875" customWidth="1"/>
-    <col min="6" max="6" width="14.33203125" customWidth="1"/>
-    <col min="7" max="7" width="17.5546875" customWidth="1"/>
-    <col min="8" max="8" width="15.33203125" customWidth="1"/>
-    <col min="9" max="9" width="14.5546875" customWidth="1"/>
-    <col min="10" max="10" width="14.44140625" customWidth="1"/>
-    <col min="11" max="11" width="31.109375" customWidth="1"/>
+    <col min="4" max="4" width="13.54296875" customWidth="1"/>
+    <col min="5" max="5" width="12.54296875" customWidth="1"/>
+    <col min="6" max="6" width="14.36328125" customWidth="1"/>
+    <col min="7" max="7" width="17.54296875" customWidth="1"/>
+    <col min="8" max="8" width="15.36328125" customWidth="1"/>
+    <col min="9" max="9" width="14.54296875" customWidth="1"/>
+    <col min="10" max="10" width="14.453125" customWidth="1"/>
+    <col min="11" max="11" width="31.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="7"/>
       <c r="B1" s="8"/>
       <c r="C1" s="7"/>
@@ -6889,7 +8095,7 @@
       <c r="J1" s="8"/>
       <c r="K1" s="8"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="7"/>
@@ -6902,7 +8108,7 @@
       <c r="J2" s="8"/>
       <c r="K2" s="8"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="7"/>
       <c r="B3" s="8"/>
       <c r="C3" s="7"/>
@@ -6915,7 +8121,7 @@
       <c r="J3" s="8"/>
       <c r="K3" s="8"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
         <v>0</v>
       </c>
@@ -6953,7 +8159,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>1000</v>
       </c>
@@ -6979,7 +8185,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>1000</v>
       </c>
@@ -7005,7 +8211,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>1000</v>
       </c>
@@ -7031,7 +8237,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>1000</v>
       </c>
@@ -7057,7 +8263,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="8"/>
       <c r="B12" s="7"/>
       <c r="C12" s="8"/>
@@ -7069,7 +8275,7 @@
       <c r="I12" s="8"/>
       <c r="J12" s="8"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>1000</v>
       </c>
@@ -7089,7 +8295,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>1000</v>
       </c>
@@ -7109,7 +8315,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>1000</v>
       </c>
@@ -7129,7 +8335,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>1000</v>
       </c>
@@ -7150,23 +8356,23 @@
         <v>378</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A25" s="16" t="s">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A25" s="17" t="s">
         <v>183</v>
       </c>
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="17" t="s">
+      <c r="B25" s="17"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="18" t="s">
         <v>187</v>
       </c>
-      <c r="G25" s="17"/>
-      <c r="H25" s="17"/>
-      <c r="I25" s="17"/>
-      <c r="J25" s="17"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G25" s="18"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="18"/>
+      <c r="J25" s="18"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" s="8" t="s">
         <v>184</v>
       </c>
@@ -7198,7 +8404,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" s="8" t="s">
         <v>14</v>
       </c>
@@ -7230,7 +8436,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>14</v>
       </c>
@@ -7274,22 +8480,22 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.88671875" customWidth="1"/>
-    <col min="2" max="2" width="14.44140625" customWidth="1"/>
-    <col min="3" max="3" width="13.44140625" customWidth="1"/>
-    <col min="4" max="4" width="13.21875" customWidth="1"/>
-    <col min="5" max="5" width="16.109375" customWidth="1"/>
-    <col min="6" max="6" width="17.109375" customWidth="1"/>
-    <col min="7" max="7" width="17.5546875" customWidth="1"/>
-    <col min="8" max="8" width="16.5546875" customWidth="1"/>
-    <col min="9" max="9" width="16.77734375" customWidth="1"/>
+    <col min="1" max="1" width="14.90625" customWidth="1"/>
+    <col min="2" max="2" width="14.453125" customWidth="1"/>
+    <col min="3" max="3" width="13.453125" customWidth="1"/>
+    <col min="4" max="4" width="13.1796875" customWidth="1"/>
+    <col min="5" max="5" width="16.08984375" customWidth="1"/>
+    <col min="6" max="6" width="17.08984375" customWidth="1"/>
+    <col min="7" max="7" width="17.54296875" customWidth="1"/>
+    <col min="8" max="8" width="16.54296875" customWidth="1"/>
+    <col min="9" max="9" width="16.81640625" customWidth="1"/>
     <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="27.6640625" customWidth="1"/>
+    <col min="11" max="11" width="27.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="7"/>
       <c r="B1" s="8"/>
       <c r="C1" s="7"/>
@@ -7304,7 +8510,7 @@
       <c r="J1" s="8"/>
       <c r="K1" s="8"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="7"/>
@@ -7317,7 +8523,7 @@
       <c r="J2" s="8"/>
       <c r="K2" s="8"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="7"/>
       <c r="B3" s="8"/>
       <c r="C3" s="7"/>
@@ -7330,7 +8536,7 @@
       <c r="J3" s="8"/>
       <c r="K3" s="8"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
         <v>0</v>
       </c>
@@ -7368,7 +8574,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>1000</v>
       </c>
@@ -7394,7 +8600,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>1000</v>
       </c>
@@ -7420,7 +8626,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>1000</v>
       </c>
@@ -7446,7 +8652,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>1000</v>
       </c>
@@ -7472,7 +8678,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="8"/>
       <c r="B12" s="7"/>
       <c r="C12" s="8"/>
@@ -7484,7 +8690,7 @@
       <c r="I12" s="8"/>
       <c r="J12" s="8"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>1000</v>
       </c>
@@ -7504,7 +8710,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>1000</v>
       </c>
@@ -7524,7 +8730,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>1000</v>
       </c>
@@ -7544,7 +8750,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>1000</v>
       </c>
@@ -7565,23 +8771,23 @@
         <v>364</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A25" s="16" t="s">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A25" s="17" t="s">
         <v>183</v>
       </c>
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="17" t="s">
+      <c r="B25" s="17"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="18" t="s">
         <v>187</v>
       </c>
-      <c r="G25" s="17"/>
-      <c r="H25" s="17"/>
-      <c r="I25" s="17"/>
-      <c r="J25" s="17"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G25" s="18"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="18"/>
+      <c r="J25" s="18"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" s="8" t="s">
         <v>184</v>
       </c>
@@ -7613,7 +8819,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" s="8" t="s">
         <v>14</v>
       </c>
@@ -7645,7 +8851,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" s="8" t="s">
         <v>14</v>
       </c>
@@ -7689,21 +8895,21 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="14.109375" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" customWidth="1"/>
-    <col min="5" max="5" width="12.77734375" customWidth="1"/>
-    <col min="6" max="6" width="17.33203125" customWidth="1"/>
-    <col min="7" max="7" width="14.6640625" customWidth="1"/>
-    <col min="8" max="8" width="14.5546875" customWidth="1"/>
-    <col min="9" max="9" width="14.109375" customWidth="1"/>
-    <col min="10" max="10" width="16.109375" customWidth="1"/>
-    <col min="11" max="11" width="43.21875" customWidth="1"/>
+    <col min="1" max="2" width="14.08984375" customWidth="1"/>
+    <col min="3" max="3" width="13.36328125" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" customWidth="1"/>
+    <col min="5" max="5" width="12.81640625" customWidth="1"/>
+    <col min="6" max="6" width="17.36328125" customWidth="1"/>
+    <col min="7" max="7" width="14.6328125" customWidth="1"/>
+    <col min="8" max="8" width="14.54296875" customWidth="1"/>
+    <col min="9" max="9" width="14.08984375" customWidth="1"/>
+    <col min="10" max="10" width="16.08984375" customWidth="1"/>
+    <col min="11" max="11" width="43.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="7"/>
       <c r="B1" s="8"/>
       <c r="C1" s="7"/>
@@ -7718,7 +8924,7 @@
       <c r="J1" s="8"/>
       <c r="K1" s="8"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="7"/>
@@ -7731,7 +8937,7 @@
       <c r="J2" s="8"/>
       <c r="K2" s="8"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="7"/>
       <c r="B3" s="8"/>
       <c r="C3" s="7"/>
@@ -7744,7 +8950,7 @@
       <c r="J3" s="8"/>
       <c r="K3" s="8"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
         <v>0</v>
       </c>
@@ -7782,7 +8988,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>1000</v>
       </c>
@@ -7808,7 +9014,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>1000</v>
       </c>
@@ -7834,7 +9040,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>1000</v>
       </c>
@@ -7860,7 +9066,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>1000</v>
       </c>
@@ -7886,7 +9092,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="8"/>
       <c r="B12" s="7"/>
       <c r="C12" s="8"/>
@@ -7898,7 +9104,7 @@
       <c r="I12" s="8"/>
       <c r="J12" s="8"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>1000</v>
       </c>
@@ -7918,7 +9124,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>1000</v>
       </c>
@@ -7938,7 +9144,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>1000</v>
       </c>
@@ -7958,7 +9164,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>1000</v>
       </c>
@@ -7978,23 +9184,23 @@
         <v>350</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A30" s="16" t="s">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A30" s="17" t="s">
         <v>183</v>
       </c>
-      <c r="B30" s="16"/>
-      <c r="C30" s="16"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="17" t="s">
+      <c r="B30" s="17"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="18" t="s">
         <v>187</v>
       </c>
-      <c r="G30" s="17"/>
-      <c r="H30" s="17"/>
-      <c r="I30" s="17"/>
-      <c r="J30" s="17"/>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G30" s="18"/>
+      <c r="H30" s="18"/>
+      <c r="I30" s="18"/>
+      <c r="J30" s="18"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" s="8" t="s">
         <v>184</v>
       </c>
@@ -8026,7 +9232,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" s="8" t="s">
         <v>14</v>
       </c>
@@ -8058,7 +9264,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>14</v>
       </c>

--- a/Experiments/DBCV_Conclu.xlsx
+++ b/Experiments/DBCV_Conclu.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1258" uniqueCount="567">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1311" uniqueCount="585">
   <si>
     <t>Datapoints</t>
   </si>
@@ -1404,9 +1404,6 @@
     <t>(K=64)</t>
   </si>
   <si>
-    <t>(K=32)</t>
-  </si>
-  <si>
     <t>16.595 secs</t>
   </si>
   <si>
@@ -1738,6 +1735,63 @@
   </si>
   <si>
     <t>170.280 secs</t>
+  </si>
+  <si>
+    <t>(K=32)(Batch=128)</t>
+  </si>
+  <si>
+    <t>(K=32)(Batch=256)</t>
+  </si>
+  <si>
+    <t>7.933 secs</t>
+  </si>
+  <si>
+    <t>0.135 secs</t>
+  </si>
+  <si>
+    <t>0.154</t>
+  </si>
+  <si>
+    <t>382.814 secs</t>
+  </si>
+  <si>
+    <t>-0.038</t>
+  </si>
+  <si>
+    <t>101.948 secs</t>
+  </si>
+  <si>
+    <t>6.034 secs</t>
+  </si>
+  <si>
+    <t>0.384 secs</t>
+  </si>
+  <si>
+    <t>146.189 secs</t>
+  </si>
+  <si>
+    <t>5.365 secs</t>
+  </si>
+  <si>
+    <t>13.660 secs</t>
+  </si>
+  <si>
+    <t>0.026</t>
+  </si>
+  <si>
+    <t>145.207 secs</t>
+  </si>
+  <si>
+    <t>5.513 secs</t>
+  </si>
+  <si>
+    <t>0.040 secs</t>
+  </si>
+  <si>
+    <t>-0.011</t>
+  </si>
+  <si>
+    <t>167.093 secs</t>
   </si>
 </sst>
 </file>
@@ -1821,7 +1875,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
@@ -1845,6 +1899,12 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2686,20 +2746,20 @@
       <c r="G21" s="8"/>
     </row>
     <row r="22" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="17" t="s">
+      <c r="B22" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="18" t="s">
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="H22" s="18"/>
-      <c r="I22" s="18"/>
-      <c r="J22" s="18"/>
-      <c r="K22" s="18"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="20"/>
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
     </row>
     <row r="23" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="8" t="s">
@@ -3460,20 +3520,20 @@
       <c r="N47" s="2"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="B48" s="17" t="s">
+      <c r="B48" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="C48" s="17"/>
-      <c r="D48" s="17"/>
-      <c r="E48" s="17"/>
-      <c r="F48" s="17"/>
-      <c r="G48" s="18" t="s">
+      <c r="C48" s="19"/>
+      <c r="D48" s="19"/>
+      <c r="E48" s="19"/>
+      <c r="F48" s="19"/>
+      <c r="G48" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="H48" s="18"/>
-      <c r="I48" s="18"/>
-      <c r="J48" s="18"/>
-      <c r="K48" s="18"/>
+      <c r="H48" s="20"/>
+      <c r="I48" s="20"/>
+      <c r="J48" s="20"/>
+      <c r="K48" s="20"/>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B49" s="8" t="s">
@@ -4156,20 +4216,20 @@
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A24" s="17" t="s">
+      <c r="A24" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="18" t="s">
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="G24" s="18"/>
-      <c r="H24" s="18"/>
-      <c r="I24" s="18"/>
-      <c r="J24" s="18"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="20"/>
+      <c r="J24" s="20"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" s="8" t="s">
@@ -4496,20 +4556,20 @@
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A55" s="17" t="s">
+      <c r="A55" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="B55" s="17"/>
-      <c r="C55" s="17"/>
-      <c r="D55" s="17"/>
-      <c r="E55" s="17"/>
-      <c r="F55" s="18" t="s">
+      <c r="B55" s="19"/>
+      <c r="C55" s="19"/>
+      <c r="D55" s="19"/>
+      <c r="E55" s="19"/>
+      <c r="F55" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="G55" s="18"/>
-      <c r="H55" s="18"/>
-      <c r="I55" s="18"/>
-      <c r="J55" s="18"/>
+      <c r="G55" s="20"/>
+      <c r="H55" s="20"/>
+      <c r="I55" s="20"/>
+      <c r="J55" s="20"/>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A56" s="8" t="s">
@@ -4765,7 +4825,7 @@
         <v>512</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D7" s="7"/>
       <c r="E7" s="8"/>
@@ -4773,7 +4833,7 @@
         <v>2</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H7" s="8" t="s">
         <v>25</v>
@@ -4785,10 +4845,10 @@
         <v>421</v>
       </c>
       <c r="K7" s="6" t="s">
+        <v>462</v>
+      </c>
+      <c r="L7" s="8" t="s">
         <v>463</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>464</v>
       </c>
       <c r="M7" s="8"/>
       <c r="N7" s="8"/>
@@ -4804,7 +4864,7 @@
         <v>512</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D9" s="7"/>
       <c r="E9" s="8"/>
@@ -4812,7 +4872,7 @@
         <v>2</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H9" s="8" t="s">
         <v>36</v>
@@ -4821,13 +4881,13 @@
         <v>175</v>
       </c>
       <c r="J9" s="8" t="s">
+        <v>457</v>
+      </c>
+      <c r="K9" s="6" t="s">
         <v>458</v>
       </c>
-      <c r="K9" s="6" t="s">
+      <c r="L9" s="8" t="s">
         <v>459</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>460</v>
       </c>
       <c r="M9" s="8"/>
       <c r="N9" s="8"/>
@@ -4856,7 +4916,7 @@
         <v>512</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D11" s="7"/>
       <c r="E11" s="8"/>
@@ -4864,7 +4924,7 @@
         <v>2</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H11" s="8" t="s">
         <v>47</v>
@@ -4873,13 +4933,13 @@
         <v>175</v>
       </c>
       <c r="J11" s="8" t="s">
+        <v>467</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>465</v>
+      </c>
+      <c r="L11" s="8" t="s">
         <v>468</v>
-      </c>
-      <c r="K11" s="8" t="s">
-        <v>466</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>469</v>
       </c>
       <c r="M11" s="8"/>
       <c r="N11" s="8"/>
@@ -4955,20 +5015,20 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" s="7"/>
-      <c r="B17" s="17" t="s">
+      <c r="B17" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="C17" s="17"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="18" t="s">
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="H17" s="18"/>
-      <c r="I17" s="18"/>
-      <c r="J17" s="18"/>
-      <c r="K17" s="18"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
       <c r="L17" s="8"/>
       <c r="M17" s="8"/>
       <c r="N17" s="8"/>
@@ -5090,7 +5150,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N126"/>
+  <dimension ref="A1:N144"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -5316,20 +5376,20 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="7"/>
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="18" t="s">
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="H15" s="18"/>
-      <c r="I15" s="18"/>
-      <c r="J15" s="18"/>
-      <c r="K15" s="18"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="7"/>
@@ -5404,7 +5464,7 @@
         <v>211</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>455</v>
+        <v>566</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.35">
@@ -5453,7 +5513,7 @@
         <v>2</v>
       </c>
       <c r="E23" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F23" t="s">
         <v>14</v>
@@ -5462,13 +5522,13 @@
         <v>283</v>
       </c>
       <c r="H23" t="s">
+        <v>471</v>
+      </c>
+      <c r="I23" t="s">
+        <v>470</v>
+      </c>
+      <c r="J23" t="s">
         <v>472</v>
-      </c>
-      <c r="I23" t="s">
-        <v>471</v>
-      </c>
-      <c r="J23" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.35">
@@ -5479,7 +5539,7 @@
         <v>2</v>
       </c>
       <c r="E25" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F25" t="s">
         <v>36</v>
@@ -5488,13 +5548,13 @@
         <v>175</v>
       </c>
       <c r="H25" t="s">
+        <v>475</v>
+      </c>
+      <c r="I25" s="11" t="s">
         <v>476</v>
       </c>
-      <c r="I25" s="11" t="s">
+      <c r="J25" t="s">
         <v>477</v>
-      </c>
-      <c r="J25" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.35">
@@ -5505,7 +5565,7 @@
         <v>2</v>
       </c>
       <c r="E27" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="F27" t="s">
         <v>47</v>
@@ -5514,13 +5574,13 @@
         <v>175</v>
       </c>
       <c r="H27" t="s">
+        <v>483</v>
+      </c>
+      <c r="I27" t="s">
         <v>484</v>
       </c>
-      <c r="I27" t="s">
+      <c r="J27" t="s">
         <v>485</v>
-      </c>
-      <c r="J27" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.35">
@@ -5531,7 +5591,7 @@
         <v>2</v>
       </c>
       <c r="E29" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F29" t="s">
         <v>25</v>
@@ -5543,10 +5603,10 @@
         <v>232</v>
       </c>
       <c r="I29" s="12" t="s">
+        <v>480</v>
+      </c>
+      <c r="J29" t="s">
         <v>481</v>
-      </c>
-      <c r="J29" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.35">
@@ -5566,20 +5626,20 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A33" s="7"/>
-      <c r="B33" s="17" t="s">
+      <c r="B33" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="C33" s="17"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
-      <c r="G33" s="18" t="s">
+      <c r="C33" s="19"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="H33" s="18"/>
-      <c r="I33" s="18"/>
-      <c r="J33" s="18"/>
-      <c r="K33" s="18"/>
+      <c r="H33" s="20"/>
+      <c r="I33" s="20"/>
+      <c r="J33" s="20"/>
+      <c r="K33" s="20"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34" s="7"/>
@@ -5628,10 +5688,10 @@
         <v>102</v>
       </c>
       <c r="E35" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F35" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="G35" s="7" t="s">
         <v>14</v>
@@ -5646,257 +5706,257 @@
         <v>201</v>
       </c>
       <c r="K35" s="7" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="G39" s="9" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="G38" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="H39" s="16" t="s">
-        <v>479</v>
+      <c r="H38" s="16" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A40" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="G40" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="H40" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I40" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J40" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K40" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="L40" s="8" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A41" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E41" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F41" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="G41" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="H41" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="I41" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="J41" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="K41" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="L41" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A42">
-        <v>1000</v>
-      </c>
-      <c r="D42">
-        <v>2</v>
-      </c>
-      <c r="E42" t="s">
-        <v>487</v>
-      </c>
-      <c r="F42" t="s">
+      <c r="A41">
+        <v>1000</v>
+      </c>
+      <c r="D41">
+        <v>2</v>
+      </c>
+      <c r="E41" t="s">
+        <v>568</v>
+      </c>
+      <c r="F41" t="s">
         <v>14</v>
       </c>
-      <c r="G42">
+      <c r="G41">
         <v>291</v>
       </c>
-      <c r="H42" t="s">
-        <v>493</v>
-      </c>
-      <c r="I42" t="s">
-        <v>310</v>
-      </c>
-      <c r="J42" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A44">
-        <v>1000</v>
-      </c>
-      <c r="D44">
-        <v>2</v>
-      </c>
-      <c r="E44" t="s">
-        <v>491</v>
-      </c>
-      <c r="F44" t="s">
+      <c r="H41" t="s">
+        <v>569</v>
+      </c>
+      <c r="I41" t="s">
+        <v>570</v>
+      </c>
+      <c r="J41" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>1000</v>
+      </c>
+      <c r="D43">
+        <v>2</v>
+      </c>
+      <c r="E43" t="s">
+        <v>574</v>
+      </c>
+      <c r="F43" t="s">
         <v>36</v>
       </c>
-      <c r="G44">
-        <v>175</v>
-      </c>
-      <c r="H44" t="s">
-        <v>492</v>
-      </c>
-      <c r="I44" s="11" t="s">
-        <v>494</v>
-      </c>
-      <c r="J44" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A46">
-        <v>1000</v>
-      </c>
-      <c r="D46">
-        <v>2</v>
-      </c>
-      <c r="E46" t="s">
-        <v>497</v>
-      </c>
-      <c r="F46" t="s">
+      <c r="G43">
+        <v>175</v>
+      </c>
+      <c r="H43" t="s">
+        <v>575</v>
+      </c>
+      <c r="I43" s="11" t="s">
+        <v>458</v>
+      </c>
+      <c r="J43" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>1000</v>
+      </c>
+      <c r="D45">
+        <v>2</v>
+      </c>
+      <c r="E45" t="s">
+        <v>577</v>
+      </c>
+      <c r="F45" t="s">
         <v>47</v>
       </c>
-      <c r="G46">
-        <v>175</v>
-      </c>
-      <c r="H46" t="s">
-        <v>498</v>
-      </c>
-      <c r="I46" t="s">
-        <v>499</v>
-      </c>
-      <c r="J46" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A48">
-        <v>1000</v>
-      </c>
-      <c r="D48">
-        <v>2</v>
-      </c>
-      <c r="E48" t="s">
-        <v>475</v>
-      </c>
-      <c r="F48" t="s">
+      <c r="G45">
+        <v>175</v>
+      </c>
+      <c r="H45" t="s">
+        <v>578</v>
+      </c>
+      <c r="I45" t="s">
+        <v>579</v>
+      </c>
+      <c r="J45" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>1000</v>
+      </c>
+      <c r="D47">
+        <v>2</v>
+      </c>
+      <c r="E47" t="s">
+        <v>581</v>
+      </c>
+      <c r="F47" t="s">
         <v>25</v>
       </c>
-      <c r="G48">
-        <v>175</v>
-      </c>
-      <c r="H48" t="s">
-        <v>251</v>
-      </c>
-      <c r="I48" s="12" t="s">
-        <v>481</v>
-      </c>
-      <c r="J48" t="s">
-        <v>496</v>
-      </c>
+      <c r="G47">
+        <v>175</v>
+      </c>
+      <c r="H47" t="s">
+        <v>582</v>
+      </c>
+      <c r="I47" s="12" t="s">
+        <v>583</v>
+      </c>
+      <c r="J47" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A50" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B50" s="8"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="8"/>
+      <c r="E50" s="7"/>
+      <c r="F50" s="8"/>
+      <c r="G50" s="7"/>
+      <c r="H50" s="8"/>
+      <c r="I50" s="7"/>
+      <c r="J50" s="8"/>
+      <c r="K50" s="8"/>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A51" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="B51" s="8"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="8"/>
-      <c r="E51" s="7"/>
-      <c r="F51" s="8"/>
-      <c r="G51" s="7"/>
-      <c r="H51" s="8"/>
-      <c r="I51" s="7"/>
-      <c r="J51" s="8"/>
-      <c r="K51" s="8"/>
+      <c r="A51" s="7"/>
+      <c r="B51" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="C51" s="19"/>
+      <c r="D51" s="19"/>
+      <c r="E51" s="19"/>
+      <c r="F51" s="19"/>
+      <c r="G51" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="H51" s="20"/>
+      <c r="I51" s="20"/>
+      <c r="J51" s="20"/>
+      <c r="K51" s="20"/>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A52" s="7"/>
-      <c r="B52" s="17" t="s">
-        <v>183</v>
-      </c>
-      <c r="C52" s="17"/>
-      <c r="D52" s="17"/>
-      <c r="E52" s="17"/>
-      <c r="F52" s="17"/>
-      <c r="G52" s="18" t="s">
-        <v>187</v>
-      </c>
-      <c r="H52" s="18"/>
-      <c r="I52" s="18"/>
-      <c r="J52" s="18"/>
-      <c r="K52" s="18"/>
+      <c r="B52" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G52" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="H52" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="I52" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="J52" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="K52" s="8" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A53" s="7"/>
+      <c r="A53" s="7">
+        <v>1000</v>
+      </c>
       <c r="B53" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="C53" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="D53" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="E53" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F53" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="G53" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="H53" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="I53" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="J53" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="K53" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A54" s="7">
-        <v>1000</v>
-      </c>
-      <c r="B54" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C54" s="7">
+      <c r="C53" s="7">
         <v>291</v>
       </c>
-      <c r="D54" s="8">
-        <v>110</v>
-      </c>
-      <c r="E54" t="s">
-        <v>310</v>
-      </c>
-      <c r="F54" t="s">
-        <v>488</v>
-      </c>
-      <c r="G54" s="7" t="s">
+      <c r="D53" s="8">
+        <v>92</v>
+      </c>
+      <c r="E53" t="s">
+        <v>570</v>
+      </c>
+      <c r="F53" t="s">
+        <v>571</v>
+      </c>
+      <c r="G53" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="H54" s="8">
-        <v>117</v>
-      </c>
-      <c r="I54" s="7">
-        <v>38</v>
-      </c>
-      <c r="J54" s="6" t="s">
-        <v>489</v>
-      </c>
-      <c r="K54" s="7" t="s">
-        <v>490</v>
+      <c r="H53" s="8">
+        <v>126</v>
+      </c>
+      <c r="I53" s="7">
+        <v>53</v>
+      </c>
+      <c r="J53" s="6" t="s">
+        <v>572</v>
+      </c>
+      <c r="K53" s="7" t="s">
+        <v>573</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.35">
@@ -5904,7 +5964,7 @@
         <v>211</v>
       </c>
       <c r="H57" s="16" t="s">
-        <v>501</v>
+        <v>478</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.35">
@@ -5953,7 +6013,7 @@
         <v>2</v>
       </c>
       <c r="E60" t="s">
-        <v>502</v>
+        <v>486</v>
       </c>
       <c r="F60" t="s">
         <v>14</v>
@@ -5962,13 +6022,13 @@
         <v>291</v>
       </c>
       <c r="H60" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="I60" t="s">
-        <v>503</v>
+        <v>310</v>
       </c>
       <c r="J60" t="s">
-        <v>504</v>
+        <v>487</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.35">
@@ -5979,7 +6039,7 @@
         <v>2</v>
       </c>
       <c r="E62" t="s">
-        <v>509</v>
+        <v>490</v>
       </c>
       <c r="F62" t="s">
         <v>36</v>
@@ -5988,13 +6048,13 @@
         <v>175</v>
       </c>
       <c r="H62" t="s">
-        <v>510</v>
+        <v>491</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>511</v>
+        <v>493</v>
       </c>
       <c r="J62" t="s">
-        <v>512</v>
+        <v>494</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.35">
@@ -6005,7 +6065,7 @@
         <v>2</v>
       </c>
       <c r="E64" t="s">
-        <v>513</v>
+        <v>496</v>
       </c>
       <c r="F64" t="s">
         <v>47</v>
@@ -6014,13 +6074,13 @@
         <v>175</v>
       </c>
       <c r="H64" t="s">
-        <v>514</v>
-      </c>
-      <c r="I64" s="12" t="s">
-        <v>515</v>
+        <v>497</v>
+      </c>
+      <c r="I64" t="s">
+        <v>498</v>
       </c>
       <c r="J64" t="s">
-        <v>516</v>
+        <v>499</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.35">
@@ -6031,7 +6091,7 @@
         <v>2</v>
       </c>
       <c r="E66" t="s">
-        <v>517</v>
+        <v>474</v>
       </c>
       <c r="F66" t="s">
         <v>25</v>
@@ -6040,13 +6100,13 @@
         <v>175</v>
       </c>
       <c r="H66" t="s">
-        <v>518</v>
+        <v>251</v>
       </c>
       <c r="I66" s="12" t="s">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="J66" t="s">
-        <v>519</v>
+        <v>495</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.35">
@@ -6125,28 +6185,28 @@
         <v>291</v>
       </c>
       <c r="D72" s="8">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="E72" t="s">
-        <v>503</v>
+        <v>310</v>
       </c>
       <c r="F72" t="s">
-        <v>504</v>
+        <v>487</v>
       </c>
       <c r="G72" s="7" t="s">
         <v>14</v>
       </c>
       <c r="H72" s="8">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="I72" s="7">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J72" s="6" t="s">
-        <v>505</v>
+        <v>488</v>
       </c>
       <c r="K72" s="7" t="s">
-        <v>506</v>
+        <v>489</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.35">
@@ -6154,7 +6214,7 @@
         <v>211</v>
       </c>
       <c r="H75" s="16" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.35">
@@ -6203,22 +6263,22 @@
         <v>2</v>
       </c>
       <c r="E78" t="s">
-        <v>265</v>
+        <v>501</v>
       </c>
       <c r="F78" t="s">
         <v>14</v>
       </c>
       <c r="G78">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="H78" t="s">
-        <v>520</v>
+        <v>492</v>
       </c>
       <c r="I78" t="s">
-        <v>521</v>
+        <v>502</v>
       </c>
       <c r="J78" t="s">
-        <v>522</v>
+        <v>503</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.35">
@@ -6229,7 +6289,7 @@
         <v>2</v>
       </c>
       <c r="E80" t="s">
-        <v>525</v>
+        <v>508</v>
       </c>
       <c r="F80" t="s">
         <v>36</v>
@@ -6238,13 +6298,13 @@
         <v>175</v>
       </c>
       <c r="H80" t="s">
-        <v>526</v>
+        <v>509</v>
       </c>
       <c r="I80" s="11" t="s">
-        <v>527</v>
+        <v>510</v>
       </c>
       <c r="J80" t="s">
-        <v>528</v>
+        <v>511</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.35">
@@ -6255,7 +6315,7 @@
         <v>2</v>
       </c>
       <c r="E82" t="s">
-        <v>529</v>
+        <v>512</v>
       </c>
       <c r="F82" t="s">
         <v>47</v>
@@ -6264,13 +6324,13 @@
         <v>175</v>
       </c>
       <c r="H82" t="s">
-        <v>531</v>
+        <v>513</v>
       </c>
       <c r="I82" s="12" t="s">
-        <v>530</v>
+        <v>514</v>
       </c>
       <c r="J82" t="s">
-        <v>532</v>
+        <v>515</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.35">
@@ -6281,7 +6341,7 @@
         <v>2</v>
       </c>
       <c r="E84" t="s">
-        <v>533</v>
+        <v>516</v>
       </c>
       <c r="F84" t="s">
         <v>25</v>
@@ -6290,13 +6350,13 @@
         <v>175</v>
       </c>
       <c r="H84" t="s">
-        <v>288</v>
+        <v>517</v>
       </c>
       <c r="I84" s="12" t="s">
-        <v>534</v>
+        <v>488</v>
       </c>
       <c r="J84" t="s">
-        <v>535</v>
+        <v>518</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.35">
@@ -6372,31 +6432,31 @@
         <v>14</v>
       </c>
       <c r="C90" s="7">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="D90" s="8">
         <v>94</v>
       </c>
       <c r="E90" t="s">
-        <v>521</v>
+        <v>502</v>
       </c>
       <c r="F90" t="s">
-        <v>522</v>
+        <v>503</v>
       </c>
       <c r="G90" s="7" t="s">
         <v>14</v>
       </c>
       <c r="H90" s="8">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="I90" s="7">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="J90" s="6" t="s">
-        <v>523</v>
+        <v>504</v>
       </c>
       <c r="K90" s="7" t="s">
-        <v>524</v>
+        <v>505</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.35">
@@ -6404,7 +6464,7 @@
         <v>211</v>
       </c>
       <c r="H93" s="16" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.35">
@@ -6453,22 +6513,22 @@
         <v>2</v>
       </c>
       <c r="E96" t="s">
-        <v>536</v>
+        <v>265</v>
       </c>
       <c r="F96" t="s">
         <v>14</v>
       </c>
       <c r="G96">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="H96" t="s">
-        <v>537</v>
+        <v>519</v>
       </c>
       <c r="I96" t="s">
-        <v>538</v>
+        <v>520</v>
       </c>
       <c r="J96" t="s">
-        <v>539</v>
+        <v>521</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.35">
@@ -6479,7 +6539,7 @@
         <v>2</v>
       </c>
       <c r="E98" t="s">
-        <v>542</v>
+        <v>524</v>
       </c>
       <c r="F98" t="s">
         <v>36</v>
@@ -6488,13 +6548,13 @@
         <v>175</v>
       </c>
       <c r="H98" t="s">
-        <v>543</v>
+        <v>525</v>
       </c>
       <c r="I98" s="11" t="s">
-        <v>544</v>
+        <v>526</v>
       </c>
       <c r="J98" t="s">
-        <v>545</v>
+        <v>527</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.35">
@@ -6505,7 +6565,7 @@
         <v>2</v>
       </c>
       <c r="E100" t="s">
-        <v>483</v>
+        <v>528</v>
       </c>
       <c r="F100" t="s">
         <v>47</v>
@@ -6514,13 +6574,13 @@
         <v>175</v>
       </c>
       <c r="H100" t="s">
-        <v>543</v>
+        <v>530</v>
       </c>
       <c r="I100" s="12" t="s">
-        <v>546</v>
+        <v>529</v>
       </c>
       <c r="J100" t="s">
-        <v>547</v>
+        <v>531</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.35">
@@ -6530,8 +6590,8 @@
       <c r="D102">
         <v>2</v>
       </c>
-      <c r="E102" s="13" t="s">
-        <v>548</v>
+      <c r="E102" t="s">
+        <v>532</v>
       </c>
       <c r="F102" t="s">
         <v>25</v>
@@ -6540,13 +6600,13 @@
         <v>175</v>
       </c>
       <c r="H102" t="s">
-        <v>518</v>
+        <v>288</v>
       </c>
       <c r="I102" s="12" t="s">
-        <v>549</v>
+        <v>533</v>
       </c>
       <c r="J102" t="s">
-        <v>550</v>
+        <v>534</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.35">
@@ -6622,31 +6682,31 @@
         <v>14</v>
       </c>
       <c r="C108" s="7">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="D108" s="8">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="E108" t="s">
-        <v>538</v>
+        <v>520</v>
       </c>
       <c r="F108" t="s">
-        <v>539</v>
+        <v>521</v>
       </c>
       <c r="G108" s="7" t="s">
         <v>14</v>
       </c>
       <c r="H108" s="8">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="I108" s="7">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="J108" s="6" t="s">
-        <v>540</v>
+        <v>522</v>
       </c>
       <c r="K108" s="7" t="s">
-        <v>541</v>
+        <v>523</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.35">
@@ -6654,7 +6714,7 @@
         <v>211</v>
       </c>
       <c r="H111" s="16" t="s">
-        <v>554</v>
+        <v>507</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.35">
@@ -6703,22 +6763,22 @@
         <v>2</v>
       </c>
       <c r="E114" t="s">
-        <v>551</v>
+        <v>535</v>
       </c>
       <c r="F114" t="s">
         <v>14</v>
       </c>
       <c r="G114">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="H114" t="s">
-        <v>420</v>
+        <v>536</v>
       </c>
       <c r="I114" t="s">
-        <v>552</v>
+        <v>537</v>
       </c>
       <c r="J114" t="s">
-        <v>553</v>
+        <v>538</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.35">
@@ -6729,7 +6789,7 @@
         <v>2</v>
       </c>
       <c r="E116" t="s">
-        <v>557</v>
+        <v>541</v>
       </c>
       <c r="F116" t="s">
         <v>36</v>
@@ -6738,13 +6798,13 @@
         <v>175</v>
       </c>
       <c r="H116" t="s">
-        <v>558</v>
+        <v>542</v>
       </c>
       <c r="I116" s="11" t="s">
-        <v>559</v>
+        <v>543</v>
       </c>
       <c r="J116" t="s">
-        <v>560</v>
+        <v>544</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.35">
@@ -6755,7 +6815,7 @@
         <v>2</v>
       </c>
       <c r="E118" t="s">
-        <v>561</v>
+        <v>482</v>
       </c>
       <c r="F118" t="s">
         <v>47</v>
@@ -6764,13 +6824,13 @@
         <v>175</v>
       </c>
       <c r="H118" t="s">
-        <v>562</v>
+        <v>542</v>
       </c>
       <c r="I118" s="12" t="s">
-        <v>267</v>
+        <v>545</v>
       </c>
       <c r="J118" t="s">
-        <v>563</v>
+        <v>546</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.35">
@@ -6781,7 +6841,7 @@
         <v>2</v>
       </c>
       <c r="E120" s="13" t="s">
-        <v>564</v>
+        <v>547</v>
       </c>
       <c r="F120" t="s">
         <v>25</v>
@@ -6790,13 +6850,13 @@
         <v>175</v>
       </c>
       <c r="H120" t="s">
-        <v>565</v>
+        <v>517</v>
       </c>
       <c r="I120" s="12" t="s">
-        <v>523</v>
+        <v>548</v>
       </c>
       <c r="J120" t="s">
-        <v>566</v>
+        <v>549</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.35">
@@ -6872,49 +6932,291 @@
         <v>14</v>
       </c>
       <c r="C126" s="7">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="D126" s="8">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="E126" t="s">
-        <v>552</v>
+        <v>537</v>
       </c>
       <c r="F126" t="s">
-        <v>553</v>
+        <v>538</v>
       </c>
       <c r="G126" s="7" t="s">
         <v>14</v>
       </c>
       <c r="H126" s="8">
+        <v>113</v>
+      </c>
+      <c r="I126" s="7">
+        <v>29</v>
+      </c>
+      <c r="J126" s="6" t="s">
+        <v>539</v>
+      </c>
+      <c r="K126" s="7" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="129" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="G129" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="H129" s="16" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="131" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A131" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B131" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C131" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D131" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E131" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F131" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="G131" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="H131" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I131" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J131" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K131" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="L131" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="132" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A132">
+        <v>1000</v>
+      </c>
+      <c r="D132">
+        <v>2</v>
+      </c>
+      <c r="E132" t="s">
+        <v>550</v>
+      </c>
+      <c r="F132" t="s">
+        <v>14</v>
+      </c>
+      <c r="G132">
+        <v>301</v>
+      </c>
+      <c r="H132" t="s">
+        <v>420</v>
+      </c>
+      <c r="I132" t="s">
+        <v>551</v>
+      </c>
+      <c r="J132" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="134" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A134">
+        <v>1000</v>
+      </c>
+      <c r="D134">
+        <v>2</v>
+      </c>
+      <c r="E134" t="s">
+        <v>556</v>
+      </c>
+      <c r="F134" t="s">
+        <v>36</v>
+      </c>
+      <c r="G134">
+        <v>175</v>
+      </c>
+      <c r="H134" t="s">
+        <v>557</v>
+      </c>
+      <c r="I134" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="J134" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="136" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A136">
+        <v>1000</v>
+      </c>
+      <c r="D136">
+        <v>2</v>
+      </c>
+      <c r="E136" t="s">
+        <v>560</v>
+      </c>
+      <c r="F136" t="s">
+        <v>47</v>
+      </c>
+      <c r="G136">
+        <v>175</v>
+      </c>
+      <c r="H136" t="s">
+        <v>561</v>
+      </c>
+      <c r="I136" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="J136" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="138" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A138">
+        <v>1000</v>
+      </c>
+      <c r="D138">
+        <v>2</v>
+      </c>
+      <c r="E138" s="13" t="s">
+        <v>563</v>
+      </c>
+      <c r="F138" t="s">
+        <v>25</v>
+      </c>
+      <c r="G138">
+        <v>175</v>
+      </c>
+      <c r="H138" t="s">
+        <v>564</v>
+      </c>
+      <c r="I138" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="J138" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="141" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A141" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B141" s="8"/>
+      <c r="C141" s="7"/>
+      <c r="D141" s="8"/>
+      <c r="E141" s="7"/>
+      <c r="F141" s="8"/>
+      <c r="G141" s="7"/>
+      <c r="H141" s="8"/>
+      <c r="I141" s="7"/>
+      <c r="J141" s="8"/>
+      <c r="K141" s="8"/>
+    </row>
+    <row r="142" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A142" s="7"/>
+      <c r="B142" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="C142" s="17"/>
+      <c r="D142" s="17"/>
+      <c r="E142" s="17"/>
+      <c r="F142" s="17"/>
+      <c r="G142" s="18" t="s">
+        <v>187</v>
+      </c>
+      <c r="H142" s="18"/>
+      <c r="I142" s="18"/>
+      <c r="J142" s="18"/>
+      <c r="K142" s="18"/>
+    </row>
+    <row r="143" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A143" s="7"/>
+      <c r="B143" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="C143" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="D143" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="E143" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F143" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G143" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="H143" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="I143" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="J143" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="K143" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="144" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A144" s="7">
+        <v>1000</v>
+      </c>
+      <c r="B144" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C144" s="7">
+        <v>301</v>
+      </c>
+      <c r="D144" s="8">
+        <v>83</v>
+      </c>
+      <c r="E144" t="s">
+        <v>551</v>
+      </c>
+      <c r="F144" t="s">
+        <v>552</v>
+      </c>
+      <c r="G144" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H144" s="8">
         <v>107</v>
       </c>
-      <c r="I126" s="7">
+      <c r="I144" s="7">
         <v>26</v>
       </c>
-      <c r="J126" s="6" t="s">
+      <c r="J144" s="6" t="s">
+        <v>554</v>
+      </c>
+      <c r="K144" s="7" t="s">
         <v>555</v>
       </c>
-      <c r="K126" s="7" t="s">
-        <v>556</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="G124:K124"/>
+  <mergeCells count="6">
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="G15:K15"/>
     <mergeCell ref="B33:F33"/>
     <mergeCell ref="G33:K33"/>
-    <mergeCell ref="B52:F52"/>
-    <mergeCell ref="G52:K52"/>
-    <mergeCell ref="B70:F70"/>
-    <mergeCell ref="G70:K70"/>
-    <mergeCell ref="B88:F88"/>
-    <mergeCell ref="G88:K88"/>
-    <mergeCell ref="B106:F106"/>
-    <mergeCell ref="G106:K106"/>
+    <mergeCell ref="B51:F51"/>
+    <mergeCell ref="G51:K51"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -7143,20 +7445,20 @@
       <c r="J12" s="8"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="18" t="s">
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="G13" s="18"/>
-      <c r="H13" s="18"/>
-      <c r="I13" s="18"/>
-      <c r="J13" s="18"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="20"/>
+      <c r="J13" s="20"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="8" t="s">
@@ -7539,20 +7841,20 @@
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A23" s="17" t="s">
+      <c r="A23" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="18" t="s">
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="G23" s="18"/>
-      <c r="H23" s="18"/>
-      <c r="I23" s="18"/>
-      <c r="J23" s="18"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
+      <c r="I23" s="20"/>
+      <c r="J23" s="20"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" s="8" t="s">
@@ -7941,20 +8243,20 @@
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A28" s="17" t="s">
+      <c r="A28" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="B28" s="17"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="18" t="s">
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="G28" s="18"/>
-      <c r="H28" s="18"/>
-      <c r="I28" s="18"/>
-      <c r="J28" s="18"/>
+      <c r="G28" s="20"/>
+      <c r="H28" s="20"/>
+      <c r="I28" s="20"/>
+      <c r="J28" s="20"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" s="8" t="s">
@@ -8357,20 +8659,20 @@
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A25" s="17" t="s">
+      <c r="A25" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="18" t="s">
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="G25" s="18"/>
-      <c r="H25" s="18"/>
-      <c r="I25" s="18"/>
-      <c r="J25" s="18"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="20"/>
+      <c r="I25" s="20"/>
+      <c r="J25" s="20"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" s="8" t="s">
@@ -8772,20 +9074,20 @@
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A25" s="17" t="s">
+      <c r="A25" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="18" t="s">
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="G25" s="18"/>
-      <c r="H25" s="18"/>
-      <c r="I25" s="18"/>
-      <c r="J25" s="18"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="20"/>
+      <c r="I25" s="20"/>
+      <c r="J25" s="20"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" s="8" t="s">
@@ -9185,20 +9487,20 @@
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A30" s="17" t="s">
+      <c r="A30" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="18" t="s">
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="G30" s="18"/>
-      <c r="H30" s="18"/>
-      <c r="I30" s="18"/>
-      <c r="J30" s="18"/>
+      <c r="G30" s="20"/>
+      <c r="H30" s="20"/>
+      <c r="I30" s="20"/>
+      <c r="J30" s="20"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" s="8" t="s">

--- a/Experiments/DBCV_Conclu.xlsx
+++ b/Experiments/DBCV_Conclu.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\das-sb\Downloads\thesis_documentation\Experiments\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\300\320\321\Studenten\DAS-SB\GIT\thesis_documentation\Experiments\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18190" windowHeight="8510" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17850" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1311" uniqueCount="585">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="604">
   <si>
     <t>Datapoints</t>
   </si>
@@ -1792,6 +1792,63 @@
   </si>
   <si>
     <t>167.093 secs</t>
+  </si>
+  <si>
+    <t>(K=32)(Batch=64)</t>
+  </si>
+  <si>
+    <t>293.732 secs</t>
+  </si>
+  <si>
+    <t>7.606 secs</t>
+  </si>
+  <si>
+    <t>-0.056</t>
+  </si>
+  <si>
+    <t>602.923 secs</t>
+  </si>
+  <si>
+    <t>336.129 secs</t>
+  </si>
+  <si>
+    <t>0.489 secs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.007 </t>
+  </si>
+  <si>
+    <t>481.838 secs</t>
+  </si>
+  <si>
+    <t>227.326 secs</t>
+  </si>
+  <si>
+    <t>51.657 secs</t>
+  </si>
+  <si>
+    <t>0.008</t>
+  </si>
+  <si>
+    <t>492.017 secs</t>
+  </si>
+  <si>
+    <t>280.014 secs</t>
+  </si>
+  <si>
+    <t>1.080 secs</t>
+  </si>
+  <si>
+    <t>0.175</t>
+  </si>
+  <si>
+    <t>994.021 secs</t>
+  </si>
+  <si>
+    <t>-0.016</t>
+  </si>
+  <si>
+    <t>251.324 secs</t>
   </si>
 </sst>
 </file>
@@ -1875,7 +1932,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
@@ -1911,6 +1968,8 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5150,7 +5209,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N144"/>
+  <dimension ref="A1:N181"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -5959,1258 +6018,1510 @@
         <v>573</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="G57" s="9" t="s">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="G56" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="H57" s="16" t="s">
+      <c r="H56" s="16" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A58" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F58" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="G58" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="H58" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I58" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J58" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K58" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="L58" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A59">
+        <v>1000</v>
+      </c>
+      <c r="D59">
+        <v>2</v>
+      </c>
+      <c r="E59" t="s">
+        <v>598</v>
+      </c>
+      <c r="F59" t="s">
+        <v>14</v>
+      </c>
+      <c r="G59">
+        <v>287</v>
+      </c>
+      <c r="H59" t="s">
+        <v>599</v>
+      </c>
+      <c r="I59" t="s">
+        <v>600</v>
+      </c>
+      <c r="J59" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A61">
+        <v>1000</v>
+      </c>
+      <c r="D61">
+        <v>2</v>
+      </c>
+      <c r="E61" t="s">
+        <v>586</v>
+      </c>
+      <c r="F61" t="s">
+        <v>36</v>
+      </c>
+      <c r="G61">
+        <v>175</v>
+      </c>
+      <c r="H61" t="s">
+        <v>587</v>
+      </c>
+      <c r="I61" s="11" t="s">
+        <v>588</v>
+      </c>
+      <c r="J61" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A63">
+        <v>1000</v>
+      </c>
+      <c r="D63">
+        <v>2</v>
+      </c>
+      <c r="E63" t="s">
+        <v>594</v>
+      </c>
+      <c r="F63" t="s">
+        <v>47</v>
+      </c>
+      <c r="G63">
+        <v>175</v>
+      </c>
+      <c r="H63" t="s">
+        <v>595</v>
+      </c>
+      <c r="I63" t="s">
+        <v>596</v>
+      </c>
+      <c r="J63" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A65">
+        <v>1000</v>
+      </c>
+      <c r="D65">
+        <v>2</v>
+      </c>
+      <c r="E65" t="s">
+        <v>590</v>
+      </c>
+      <c r="F65" t="s">
+        <v>25</v>
+      </c>
+      <c r="G65">
+        <v>175</v>
+      </c>
+      <c r="H65" t="s">
+        <v>591</v>
+      </c>
+      <c r="I65" s="12" t="s">
+        <v>592</v>
+      </c>
+      <c r="J65" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A68" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B68" s="8"/>
+      <c r="C68" s="7"/>
+      <c r="D68" s="8"/>
+      <c r="E68" s="7"/>
+      <c r="F68" s="8"/>
+      <c r="G68" s="7"/>
+      <c r="H68" s="8"/>
+      <c r="I68" s="7"/>
+      <c r="J68" s="8"/>
+      <c r="K68" s="8"/>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A69" s="7"/>
+      <c r="B69" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="H69" s="20"/>
+      <c r="I69" s="20"/>
+      <c r="J69" s="20"/>
+      <c r="K69" s="20"/>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A70" s="7"/>
+      <c r="B70" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="D70" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="E70" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F70" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G70" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="H70" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="I70" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="J70" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="K70" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A71" s="7">
+        <v>1000</v>
+      </c>
+      <c r="B71" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C71" s="7">
+        <v>287</v>
+      </c>
+      <c r="D71" s="8">
+        <v>103</v>
+      </c>
+      <c r="E71" t="s">
+        <v>600</v>
+      </c>
+      <c r="F71" t="s">
+        <v>601</v>
+      </c>
+      <c r="G71" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H71" s="21">
+        <v>122</v>
+      </c>
+      <c r="I71" s="22">
+        <v>40</v>
+      </c>
+      <c r="J71" s="10" t="s">
+        <v>602</v>
+      </c>
+      <c r="K71" s="22" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="G94" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="H94" s="16" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A59" s="7" t="s">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A96" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B59" s="7" t="s">
+      <c r="B96" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C59" s="8" t="s">
+      <c r="C96" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D59" s="7" t="s">
+      <c r="D96" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E59" s="8" t="s">
+      <c r="E96" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="F59" s="8" t="s">
+      <c r="F96" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="G59" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="H59" s="8" t="s">
+      <c r="G96" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="H96" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="I59" s="8" t="s">
+      <c r="I96" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="J59" s="8" t="s">
+      <c r="J96" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="K59" s="8" t="s">
+      <c r="K96" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="L59" s="8" t="s">
+      <c r="L96" s="8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A60">
-        <v>1000</v>
-      </c>
-      <c r="D60">
-        <v>2</v>
-      </c>
-      <c r="E60" t="s">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A97">
+        <v>1000</v>
+      </c>
+      <c r="D97">
+        <v>2</v>
+      </c>
+      <c r="E97" t="s">
         <v>486</v>
       </c>
-      <c r="F60" t="s">
+      <c r="F97" t="s">
         <v>14</v>
       </c>
-      <c r="G60">
+      <c r="G97">
         <v>291</v>
       </c>
-      <c r="H60" t="s">
+      <c r="H97" t="s">
         <v>492</v>
       </c>
-      <c r="I60" t="s">
+      <c r="I97" t="s">
         <v>310</v>
       </c>
-      <c r="J60" t="s">
+      <c r="J97" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A62">
-        <v>1000</v>
-      </c>
-      <c r="D62">
-        <v>2</v>
-      </c>
-      <c r="E62" t="s">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A99">
+        <v>1000</v>
+      </c>
+      <c r="D99">
+        <v>2</v>
+      </c>
+      <c r="E99" t="s">
         <v>490</v>
       </c>
-      <c r="F62" t="s">
+      <c r="F99" t="s">
         <v>36</v>
       </c>
-      <c r="G62">
-        <v>175</v>
-      </c>
-      <c r="H62" t="s">
+      <c r="G99">
+        <v>175</v>
+      </c>
+      <c r="H99" t="s">
         <v>491</v>
       </c>
-      <c r="I62" s="11" t="s">
+      <c r="I99" s="11" t="s">
         <v>493</v>
       </c>
-      <c r="J62" t="s">
+      <c r="J99" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A64">
-        <v>1000</v>
-      </c>
-      <c r="D64">
-        <v>2</v>
-      </c>
-      <c r="E64" t="s">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A101">
+        <v>1000</v>
+      </c>
+      <c r="D101">
+        <v>2</v>
+      </c>
+      <c r="E101" t="s">
         <v>496</v>
       </c>
-      <c r="F64" t="s">
+      <c r="F101" t="s">
         <v>47</v>
       </c>
-      <c r="G64">
-        <v>175</v>
-      </c>
-      <c r="H64" t="s">
+      <c r="G101">
+        <v>175</v>
+      </c>
+      <c r="H101" t="s">
         <v>497</v>
       </c>
-      <c r="I64" t="s">
+      <c r="I101" t="s">
         <v>498</v>
       </c>
-      <c r="J64" t="s">
+      <c r="J101" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A66">
-        <v>1000</v>
-      </c>
-      <c r="D66">
-        <v>2</v>
-      </c>
-      <c r="E66" t="s">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A103">
+        <v>1000</v>
+      </c>
+      <c r="D103">
+        <v>2</v>
+      </c>
+      <c r="E103" t="s">
         <v>474</v>
       </c>
-      <c r="F66" t="s">
+      <c r="F103" t="s">
         <v>25</v>
       </c>
-      <c r="G66">
-        <v>175</v>
-      </c>
-      <c r="H66" t="s">
+      <c r="G103">
+        <v>175</v>
+      </c>
+      <c r="H103" t="s">
         <v>251</v>
       </c>
-      <c r="I66" s="12" t="s">
+      <c r="I103" s="12" t="s">
         <v>480</v>
       </c>
-      <c r="J66" t="s">
+      <c r="J103" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A69" s="7" t="s">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A106" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="B69" s="8"/>
-      <c r="C69" s="7"/>
-      <c r="D69" s="8"/>
-      <c r="E69" s="7"/>
-      <c r="F69" s="8"/>
-      <c r="G69" s="7"/>
-      <c r="H69" s="8"/>
-      <c r="I69" s="7"/>
-      <c r="J69" s="8"/>
-      <c r="K69" s="8"/>
-    </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A70" s="7"/>
-      <c r="B70" s="17" t="s">
-        <v>183</v>
-      </c>
-      <c r="C70" s="17"/>
-      <c r="D70" s="17"/>
-      <c r="E70" s="17"/>
-      <c r="F70" s="17"/>
-      <c r="G70" s="18" t="s">
-        <v>187</v>
-      </c>
-      <c r="H70" s="18"/>
-      <c r="I70" s="18"/>
-      <c r="J70" s="18"/>
-      <c r="K70" s="18"/>
-    </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A71" s="7"/>
-      <c r="B71" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="C71" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="D71" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="E71" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F71" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="G71" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="H71" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="I71" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="J71" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="K71" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A72" s="7">
-        <v>1000</v>
-      </c>
-      <c r="B72" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C72" s="7">
-        <v>291</v>
-      </c>
-      <c r="D72" s="8">
-        <v>110</v>
-      </c>
-      <c r="E72" t="s">
-        <v>310</v>
-      </c>
-      <c r="F72" t="s">
-        <v>487</v>
-      </c>
-      <c r="G72" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H72" s="8">
-        <v>117</v>
-      </c>
-      <c r="I72" s="7">
-        <v>38</v>
-      </c>
-      <c r="J72" s="6" t="s">
-        <v>488</v>
-      </c>
-      <c r="K72" s="7" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="G75" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="H75" s="16" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A77" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B77" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C77" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D77" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E77" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F77" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="G77" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="H77" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="I77" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="J77" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="K77" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="L77" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A78">
-        <v>1000</v>
-      </c>
-      <c r="D78">
-        <v>2</v>
-      </c>
-      <c r="E78" t="s">
-        <v>501</v>
-      </c>
-      <c r="F78" t="s">
-        <v>14</v>
-      </c>
-      <c r="G78">
-        <v>291</v>
-      </c>
-      <c r="H78" t="s">
-        <v>492</v>
-      </c>
-      <c r="I78" t="s">
-        <v>502</v>
-      </c>
-      <c r="J78" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A80">
-        <v>1000</v>
-      </c>
-      <c r="D80">
-        <v>2</v>
-      </c>
-      <c r="E80" t="s">
-        <v>508</v>
-      </c>
-      <c r="F80" t="s">
-        <v>36</v>
-      </c>
-      <c r="G80">
-        <v>175</v>
-      </c>
-      <c r="H80" t="s">
-        <v>509</v>
-      </c>
-      <c r="I80" s="11" t="s">
-        <v>510</v>
-      </c>
-      <c r="J80" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A82">
-        <v>1000</v>
-      </c>
-      <c r="D82">
-        <v>2</v>
-      </c>
-      <c r="E82" t="s">
-        <v>512</v>
-      </c>
-      <c r="F82" t="s">
-        <v>47</v>
-      </c>
-      <c r="G82">
-        <v>175</v>
-      </c>
-      <c r="H82" t="s">
-        <v>513</v>
-      </c>
-      <c r="I82" s="12" t="s">
-        <v>514</v>
-      </c>
-      <c r="J82" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A84">
-        <v>1000</v>
-      </c>
-      <c r="D84">
-        <v>2</v>
-      </c>
-      <c r="E84" t="s">
-        <v>516</v>
-      </c>
-      <c r="F84" t="s">
-        <v>25</v>
-      </c>
-      <c r="G84">
-        <v>175</v>
-      </c>
-      <c r="H84" t="s">
-        <v>517</v>
-      </c>
-      <c r="I84" s="12" t="s">
-        <v>488</v>
-      </c>
-      <c r="J84" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A87" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="B87" s="8"/>
-      <c r="C87" s="7"/>
-      <c r="D87" s="8"/>
-      <c r="E87" s="7"/>
-      <c r="F87" s="8"/>
-      <c r="G87" s="7"/>
-      <c r="H87" s="8"/>
-      <c r="I87" s="7"/>
-      <c r="J87" s="8"/>
-      <c r="K87" s="8"/>
-    </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A88" s="7"/>
-      <c r="B88" s="17" t="s">
-        <v>183</v>
-      </c>
-      <c r="C88" s="17"/>
-      <c r="D88" s="17"/>
-      <c r="E88" s="17"/>
-      <c r="F88" s="17"/>
-      <c r="G88" s="18" t="s">
-        <v>187</v>
-      </c>
-      <c r="H88" s="18"/>
-      <c r="I88" s="18"/>
-      <c r="J88" s="18"/>
-      <c r="K88" s="18"/>
-    </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A89" s="7"/>
-      <c r="B89" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="C89" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="D89" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="E89" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F89" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="G89" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="H89" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="I89" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="J89" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="K89" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A90" s="7">
-        <v>1000</v>
-      </c>
-      <c r="B90" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C90" s="7">
-        <v>291</v>
-      </c>
-      <c r="D90" s="8">
-        <v>94</v>
-      </c>
-      <c r="E90" t="s">
-        <v>502</v>
-      </c>
-      <c r="F90" t="s">
-        <v>503</v>
-      </c>
-      <c r="G90" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H90" s="8">
-        <v>113</v>
-      </c>
-      <c r="I90" s="7">
-        <v>39</v>
-      </c>
-      <c r="J90" s="6" t="s">
-        <v>504</v>
-      </c>
-      <c r="K90" s="7" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="G93" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="H93" s="16" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A95" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B95" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C95" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D95" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E95" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F95" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="G95" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="H95" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="I95" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="J95" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="K95" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="L95" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A96">
-        <v>1000</v>
-      </c>
-      <c r="D96">
-        <v>2</v>
-      </c>
-      <c r="E96" t="s">
-        <v>265</v>
-      </c>
-      <c r="F96" t="s">
-        <v>14</v>
-      </c>
-      <c r="G96">
-        <v>296</v>
-      </c>
-      <c r="H96" t="s">
-        <v>519</v>
-      </c>
-      <c r="I96" t="s">
-        <v>520</v>
-      </c>
-      <c r="J96" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A98">
-        <v>1000</v>
-      </c>
-      <c r="D98">
-        <v>2</v>
-      </c>
-      <c r="E98" t="s">
-        <v>524</v>
-      </c>
-      <c r="F98" t="s">
-        <v>36</v>
-      </c>
-      <c r="G98">
-        <v>175</v>
-      </c>
-      <c r="H98" t="s">
-        <v>525</v>
-      </c>
-      <c r="I98" s="11" t="s">
-        <v>526</v>
-      </c>
-      <c r="J98" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A100">
-        <v>1000</v>
-      </c>
-      <c r="D100">
-        <v>2</v>
-      </c>
-      <c r="E100" t="s">
-        <v>528</v>
-      </c>
-      <c r="F100" t="s">
-        <v>47</v>
-      </c>
-      <c r="G100">
-        <v>175</v>
-      </c>
-      <c r="H100" t="s">
-        <v>530</v>
-      </c>
-      <c r="I100" s="12" t="s">
-        <v>529</v>
-      </c>
-      <c r="J100" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A102">
-        <v>1000</v>
-      </c>
-      <c r="D102">
-        <v>2</v>
-      </c>
-      <c r="E102" t="s">
-        <v>532</v>
-      </c>
-      <c r="F102" t="s">
-        <v>25</v>
-      </c>
-      <c r="G102">
-        <v>175</v>
-      </c>
-      <c r="H102" t="s">
-        <v>288</v>
-      </c>
-      <c r="I102" s="12" t="s">
-        <v>533</v>
-      </c>
-      <c r="J102" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A105" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="B105" s="8"/>
-      <c r="C105" s="7"/>
-      <c r="D105" s="8"/>
-      <c r="E105" s="7"/>
-      <c r="F105" s="8"/>
-      <c r="G105" s="7"/>
-      <c r="H105" s="8"/>
-      <c r="I105" s="7"/>
-      <c r="J105" s="8"/>
-      <c r="K105" s="8"/>
-    </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A106" s="7"/>
-      <c r="B106" s="17" t="s">
-        <v>183</v>
-      </c>
-      <c r="C106" s="17"/>
-      <c r="D106" s="17"/>
-      <c r="E106" s="17"/>
-      <c r="F106" s="17"/>
-      <c r="G106" s="18" t="s">
-        <v>187</v>
-      </c>
-      <c r="H106" s="18"/>
-      <c r="I106" s="18"/>
-      <c r="J106" s="18"/>
-      <c r="K106" s="18"/>
+      <c r="B106" s="8"/>
+      <c r="C106" s="7"/>
+      <c r="D106" s="8"/>
+      <c r="E106" s="7"/>
+      <c r="F106" s="8"/>
+      <c r="G106" s="7"/>
+      <c r="H106" s="8"/>
+      <c r="I106" s="7"/>
+      <c r="J106" s="8"/>
+      <c r="K106" s="8"/>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A107" s="7"/>
-      <c r="B107" s="8" t="s">
+      <c r="B107" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="C107" s="17"/>
+      <c r="D107" s="17"/>
+      <c r="E107" s="17"/>
+      <c r="F107" s="17"/>
+      <c r="G107" s="18" t="s">
+        <v>187</v>
+      </c>
+      <c r="H107" s="18"/>
+      <c r="I107" s="18"/>
+      <c r="J107" s="18"/>
+      <c r="K107" s="18"/>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A108" s="7"/>
+      <c r="B108" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="C107" s="7" t="s">
+      <c r="C108" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="D107" s="8" t="s">
+      <c r="D108" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="E107" s="7" t="s">
+      <c r="E108" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F107" s="8" t="s">
+      <c r="F108" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G107" s="8" t="s">
+      <c r="G108" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="H107" s="7" t="s">
+      <c r="H108" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="I107" s="8" t="s">
+      <c r="I108" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="J107" s="7" t="s">
+      <c r="J108" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="K107" s="8" t="s">
+      <c r="K108" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A108" s="7">
-        <v>1000</v>
-      </c>
-      <c r="B108" s="8" t="s">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A109" s="7">
+        <v>1000</v>
+      </c>
+      <c r="B109" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C108" s="7">
-        <v>296</v>
-      </c>
-      <c r="D108" s="8">
-        <v>94</v>
-      </c>
-      <c r="E108" t="s">
-        <v>520</v>
-      </c>
-      <c r="F108" t="s">
-        <v>521</v>
-      </c>
-      <c r="G108" s="7" t="s">
+      <c r="C109" s="7">
+        <v>291</v>
+      </c>
+      <c r="D109" s="8">
+        <v>110</v>
+      </c>
+      <c r="E109" t="s">
+        <v>310</v>
+      </c>
+      <c r="F109" t="s">
+        <v>487</v>
+      </c>
+      <c r="G109" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="H108" s="8">
-        <v>118</v>
-      </c>
-      <c r="I108" s="7">
-        <v>45</v>
-      </c>
-      <c r="J108" s="6" t="s">
-        <v>522</v>
-      </c>
-      <c r="K108" s="7" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="G111" s="9" t="s">
+      <c r="H109" s="8">
+        <v>117</v>
+      </c>
+      <c r="I109" s="7">
+        <v>38</v>
+      </c>
+      <c r="J109" s="6" t="s">
+        <v>488</v>
+      </c>
+      <c r="K109" s="7" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="G112" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="H111" s="16" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A113" s="7" t="s">
+      <c r="H112" s="16" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A114" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B113" s="7" t="s">
+      <c r="B114" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C113" s="8" t="s">
+      <c r="C114" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D113" s="7" t="s">
+      <c r="D114" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E113" s="8" t="s">
+      <c r="E114" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="F113" s="8" t="s">
+      <c r="F114" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="G113" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="H113" s="8" t="s">
+      <c r="G114" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="H114" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="I113" s="8" t="s">
+      <c r="I114" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="J113" s="8" t="s">
+      <c r="J114" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="K113" s="8" t="s">
+      <c r="K114" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="L113" s="8" t="s">
+      <c r="L114" s="8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A114">
-        <v>1000</v>
-      </c>
-      <c r="D114">
-        <v>2</v>
-      </c>
-      <c r="E114" t="s">
-        <v>535</v>
-      </c>
-      <c r="F114" t="s">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A115">
+        <v>1000</v>
+      </c>
+      <c r="D115">
+        <v>2</v>
+      </c>
+      <c r="E115" t="s">
+        <v>501</v>
+      </c>
+      <c r="F115" t="s">
         <v>14</v>
       </c>
-      <c r="G114">
-        <v>289</v>
-      </c>
-      <c r="H114" t="s">
-        <v>536</v>
-      </c>
-      <c r="I114" t="s">
-        <v>537</v>
-      </c>
-      <c r="J114" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A116">
-        <v>1000</v>
-      </c>
-      <c r="D116">
-        <v>2</v>
-      </c>
-      <c r="E116" t="s">
-        <v>541</v>
-      </c>
-      <c r="F116" t="s">
+      <c r="G115">
+        <v>291</v>
+      </c>
+      <c r="H115" t="s">
+        <v>492</v>
+      </c>
+      <c r="I115" t="s">
+        <v>502</v>
+      </c>
+      <c r="J115" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A117">
+        <v>1000</v>
+      </c>
+      <c r="D117">
+        <v>2</v>
+      </c>
+      <c r="E117" t="s">
+        <v>508</v>
+      </c>
+      <c r="F117" t="s">
         <v>36</v>
       </c>
-      <c r="G116">
-        <v>175</v>
-      </c>
-      <c r="H116" t="s">
-        <v>542</v>
-      </c>
-      <c r="I116" s="11" t="s">
-        <v>543</v>
-      </c>
-      <c r="J116" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A118">
-        <v>1000</v>
-      </c>
-      <c r="D118">
-        <v>2</v>
-      </c>
-      <c r="E118" t="s">
-        <v>482</v>
-      </c>
-      <c r="F118" t="s">
+      <c r="G117">
+        <v>175</v>
+      </c>
+      <c r="H117" t="s">
+        <v>509</v>
+      </c>
+      <c r="I117" s="11" t="s">
+        <v>510</v>
+      </c>
+      <c r="J117" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A119">
+        <v>1000</v>
+      </c>
+      <c r="D119">
+        <v>2</v>
+      </c>
+      <c r="E119" t="s">
+        <v>512</v>
+      </c>
+      <c r="F119" t="s">
         <v>47</v>
       </c>
-      <c r="G118">
-        <v>175</v>
-      </c>
-      <c r="H118" t="s">
-        <v>542</v>
-      </c>
-      <c r="I118" s="12" t="s">
-        <v>545</v>
-      </c>
-      <c r="J118" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A120">
-        <v>1000</v>
-      </c>
-      <c r="D120">
-        <v>2</v>
-      </c>
-      <c r="E120" s="13" t="s">
-        <v>547</v>
-      </c>
-      <c r="F120" t="s">
+      <c r="G119">
+        <v>175</v>
+      </c>
+      <c r="H119" t="s">
+        <v>513</v>
+      </c>
+      <c r="I119" s="12" t="s">
+        <v>514</v>
+      </c>
+      <c r="J119" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A121">
+        <v>1000</v>
+      </c>
+      <c r="D121">
+        <v>2</v>
+      </c>
+      <c r="E121" t="s">
+        <v>516</v>
+      </c>
+      <c r="F121" t="s">
         <v>25</v>
       </c>
-      <c r="G120">
-        <v>175</v>
-      </c>
-      <c r="H120" t="s">
+      <c r="G121">
+        <v>175</v>
+      </c>
+      <c r="H121" t="s">
         <v>517</v>
       </c>
-      <c r="I120" s="12" t="s">
-        <v>548</v>
-      </c>
-      <c r="J120" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A123" s="7" t="s">
+      <c r="I121" s="12" t="s">
+        <v>488</v>
+      </c>
+      <c r="J121" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A124" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="B123" s="8"/>
-      <c r="C123" s="7"/>
-      <c r="D123" s="8"/>
-      <c r="E123" s="7"/>
-      <c r="F123" s="8"/>
-      <c r="G123" s="7"/>
-      <c r="H123" s="8"/>
-      <c r="I123" s="7"/>
-      <c r="J123" s="8"/>
-      <c r="K123" s="8"/>
-    </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A124" s="7"/>
-      <c r="B124" s="17" t="s">
-        <v>183</v>
-      </c>
-      <c r="C124" s="17"/>
-      <c r="D124" s="17"/>
-      <c r="E124" s="17"/>
-      <c r="F124" s="17"/>
-      <c r="G124" s="18" t="s">
-        <v>187</v>
-      </c>
-      <c r="H124" s="18"/>
-      <c r="I124" s="18"/>
-      <c r="J124" s="18"/>
-      <c r="K124" s="18"/>
+      <c r="B124" s="8"/>
+      <c r="C124" s="7"/>
+      <c r="D124" s="8"/>
+      <c r="E124" s="7"/>
+      <c r="F124" s="8"/>
+      <c r="G124" s="7"/>
+      <c r="H124" s="8"/>
+      <c r="I124" s="7"/>
+      <c r="J124" s="8"/>
+      <c r="K124" s="8"/>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A125" s="7"/>
-      <c r="B125" s="8" t="s">
+      <c r="B125" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="C125" s="17"/>
+      <c r="D125" s="17"/>
+      <c r="E125" s="17"/>
+      <c r="F125" s="17"/>
+      <c r="G125" s="18" t="s">
+        <v>187</v>
+      </c>
+      <c r="H125" s="18"/>
+      <c r="I125" s="18"/>
+      <c r="J125" s="18"/>
+      <c r="K125" s="18"/>
+    </row>
+    <row r="126" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A126" s="7"/>
+      <c r="B126" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="C125" s="7" t="s">
+      <c r="C126" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="D125" s="8" t="s">
+      <c r="D126" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="E125" s="7" t="s">
+      <c r="E126" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F125" s="8" t="s">
+      <c r="F126" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G125" s="8" t="s">
+      <c r="G126" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="H125" s="7" t="s">
+      <c r="H126" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="I125" s="8" t="s">
+      <c r="I126" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="J125" s="7" t="s">
+      <c r="J126" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="K125" s="8" t="s">
+      <c r="K126" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A126" s="7">
-        <v>1000</v>
-      </c>
-      <c r="B126" s="8" t="s">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A127" s="7">
+        <v>1000</v>
+      </c>
+      <c r="B127" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C126" s="7">
-        <v>289</v>
-      </c>
-      <c r="D126" s="8">
+      <c r="C127" s="7">
+        <v>291</v>
+      </c>
+      <c r="D127" s="8">
+        <v>94</v>
+      </c>
+      <c r="E127" t="s">
+        <v>502</v>
+      </c>
+      <c r="F127" t="s">
+        <v>503</v>
+      </c>
+      <c r="G127" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H127" s="8">
         <v>113</v>
       </c>
-      <c r="E126" t="s">
-        <v>537</v>
-      </c>
-      <c r="F126" t="s">
-        <v>538</v>
-      </c>
-      <c r="G126" s="7" t="s">
+      <c r="I127" s="7">
+        <v>39</v>
+      </c>
+      <c r="J127" s="6" t="s">
+        <v>504</v>
+      </c>
+      <c r="K127" s="7" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="130" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="G130" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="H130" s="16" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="132" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A132" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B132" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C132" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D132" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E132" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F132" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="G132" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="H132" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I132" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J132" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K132" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="L132" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="133" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A133">
+        <v>1000</v>
+      </c>
+      <c r="D133">
+        <v>2</v>
+      </c>
+      <c r="E133" t="s">
+        <v>265</v>
+      </c>
+      <c r="F133" t="s">
         <v>14</v>
       </c>
-      <c r="H126" s="8">
-        <v>113</v>
-      </c>
-      <c r="I126" s="7">
-        <v>29</v>
-      </c>
-      <c r="J126" s="6" t="s">
-        <v>539</v>
-      </c>
-      <c r="K126" s="7" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="G129" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="H129" s="16" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A131" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B131" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C131" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D131" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E131" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F131" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="G131" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="H131" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="I131" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="J131" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="K131" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="L131" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A132">
-        <v>1000</v>
-      </c>
-      <c r="D132">
-        <v>2</v>
-      </c>
-      <c r="E132" t="s">
-        <v>550</v>
-      </c>
-      <c r="F132" t="s">
-        <v>14</v>
-      </c>
-      <c r="G132">
-        <v>301</v>
-      </c>
-      <c r="H132" t="s">
-        <v>420</v>
-      </c>
-      <c r="I132" t="s">
-        <v>551</v>
-      </c>
-      <c r="J132" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A134">
-        <v>1000</v>
-      </c>
-      <c r="D134">
-        <v>2</v>
-      </c>
-      <c r="E134" t="s">
-        <v>556</v>
-      </c>
-      <c r="F134" t="s">
+      <c r="G133">
+        <v>296</v>
+      </c>
+      <c r="H133" t="s">
+        <v>519</v>
+      </c>
+      <c r="I133" t="s">
+        <v>520</v>
+      </c>
+      <c r="J133" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="135" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A135">
+        <v>1000</v>
+      </c>
+      <c r="D135">
+        <v>2</v>
+      </c>
+      <c r="E135" t="s">
+        <v>524</v>
+      </c>
+      <c r="F135" t="s">
         <v>36</v>
       </c>
-      <c r="G134">
-        <v>175</v>
-      </c>
-      <c r="H134" t="s">
-        <v>557</v>
-      </c>
-      <c r="I134" s="11" t="s">
-        <v>558</v>
-      </c>
-      <c r="J134" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A136">
-        <v>1000</v>
-      </c>
-      <c r="D136">
-        <v>2</v>
-      </c>
-      <c r="E136" t="s">
-        <v>560</v>
-      </c>
-      <c r="F136" t="s">
+      <c r="G135">
+        <v>175</v>
+      </c>
+      <c r="H135" t="s">
+        <v>525</v>
+      </c>
+      <c r="I135" s="11" t="s">
+        <v>526</v>
+      </c>
+      <c r="J135" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="137" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A137">
+        <v>1000</v>
+      </c>
+      <c r="D137">
+        <v>2</v>
+      </c>
+      <c r="E137" t="s">
+        <v>528</v>
+      </c>
+      <c r="F137" t="s">
         <v>47</v>
       </c>
-      <c r="G136">
-        <v>175</v>
-      </c>
-      <c r="H136" t="s">
-        <v>561</v>
-      </c>
-      <c r="I136" s="12" t="s">
-        <v>267</v>
-      </c>
-      <c r="J136" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A138">
-        <v>1000</v>
-      </c>
-      <c r="D138">
-        <v>2</v>
-      </c>
-      <c r="E138" s="13" t="s">
-        <v>563</v>
-      </c>
-      <c r="F138" t="s">
+      <c r="G137">
+        <v>175</v>
+      </c>
+      <c r="H137" t="s">
+        <v>530</v>
+      </c>
+      <c r="I137" s="12" t="s">
+        <v>529</v>
+      </c>
+      <c r="J137" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="139" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A139">
+        <v>1000</v>
+      </c>
+      <c r="D139">
+        <v>2</v>
+      </c>
+      <c r="E139" t="s">
+        <v>532</v>
+      </c>
+      <c r="F139" t="s">
         <v>25</v>
       </c>
-      <c r="G138">
-        <v>175</v>
-      </c>
-      <c r="H138" t="s">
-        <v>564</v>
-      </c>
-      <c r="I138" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="J138" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A141" s="7" t="s">
+      <c r="G139">
+        <v>175</v>
+      </c>
+      <c r="H139" t="s">
+        <v>288</v>
+      </c>
+      <c r="I139" s="12" t="s">
+        <v>533</v>
+      </c>
+      <c r="J139" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="142" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A142" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="B141" s="8"/>
-      <c r="C141" s="7"/>
-      <c r="D141" s="8"/>
-      <c r="E141" s="7"/>
-      <c r="F141" s="8"/>
-      <c r="G141" s="7"/>
-      <c r="H141" s="8"/>
-      <c r="I141" s="7"/>
-      <c r="J141" s="8"/>
-      <c r="K141" s="8"/>
-    </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A142" s="7"/>
-      <c r="B142" s="17" t="s">
-        <v>183</v>
-      </c>
-      <c r="C142" s="17"/>
-      <c r="D142" s="17"/>
-      <c r="E142" s="17"/>
-      <c r="F142" s="17"/>
-      <c r="G142" s="18" t="s">
-        <v>187</v>
-      </c>
-      <c r="H142" s="18"/>
-      <c r="I142" s="18"/>
-      <c r="J142" s="18"/>
-      <c r="K142" s="18"/>
+      <c r="B142" s="8"/>
+      <c r="C142" s="7"/>
+      <c r="D142" s="8"/>
+      <c r="E142" s="7"/>
+      <c r="F142" s="8"/>
+      <c r="G142" s="7"/>
+      <c r="H142" s="8"/>
+      <c r="I142" s="7"/>
+      <c r="J142" s="8"/>
+      <c r="K142" s="8"/>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A143" s="7"/>
-      <c r="B143" s="8" t="s">
+      <c r="B143" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="C143" s="17"/>
+      <c r="D143" s="17"/>
+      <c r="E143" s="17"/>
+      <c r="F143" s="17"/>
+      <c r="G143" s="18" t="s">
+        <v>187</v>
+      </c>
+      <c r="H143" s="18"/>
+      <c r="I143" s="18"/>
+      <c r="J143" s="18"/>
+      <c r="K143" s="18"/>
+    </row>
+    <row r="144" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A144" s="7"/>
+      <c r="B144" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="C143" s="7" t="s">
+      <c r="C144" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="D143" s="8" t="s">
+      <c r="D144" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="E143" s="7" t="s">
+      <c r="E144" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F143" s="8" t="s">
+      <c r="F144" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G143" s="8" t="s">
+      <c r="G144" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="H143" s="7" t="s">
+      <c r="H144" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="I143" s="8" t="s">
+      <c r="I144" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="J143" s="7" t="s">
+      <c r="J144" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="K143" s="8" t="s">
+      <c r="K144" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A144" s="7">
-        <v>1000</v>
-      </c>
-      <c r="B144" s="8" t="s">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A145" s="7">
+        <v>1000</v>
+      </c>
+      <c r="B145" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C144" s="7">
+      <c r="C145" s="7">
+        <v>296</v>
+      </c>
+      <c r="D145" s="8">
+        <v>94</v>
+      </c>
+      <c r="E145" t="s">
+        <v>520</v>
+      </c>
+      <c r="F145" t="s">
+        <v>521</v>
+      </c>
+      <c r="G145" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H145" s="8">
+        <v>118</v>
+      </c>
+      <c r="I145" s="7">
+        <v>45</v>
+      </c>
+      <c r="J145" s="6" t="s">
+        <v>522</v>
+      </c>
+      <c r="K145" s="7" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="148" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="G148" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="H148" s="16" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="150" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A150" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B150" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C150" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D150" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E150" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F150" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="G150" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="H150" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I150" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J150" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K150" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="L150" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="151" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A151">
+        <v>1000</v>
+      </c>
+      <c r="D151">
+        <v>2</v>
+      </c>
+      <c r="E151" t="s">
+        <v>535</v>
+      </c>
+      <c r="F151" t="s">
+        <v>14</v>
+      </c>
+      <c r="G151">
+        <v>289</v>
+      </c>
+      <c r="H151" t="s">
+        <v>536</v>
+      </c>
+      <c r="I151" t="s">
+        <v>537</v>
+      </c>
+      <c r="J151" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="153" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A153">
+        <v>1000</v>
+      </c>
+      <c r="D153">
+        <v>2</v>
+      </c>
+      <c r="E153" t="s">
+        <v>541</v>
+      </c>
+      <c r="F153" t="s">
+        <v>36</v>
+      </c>
+      <c r="G153">
+        <v>175</v>
+      </c>
+      <c r="H153" t="s">
+        <v>542</v>
+      </c>
+      <c r="I153" s="11" t="s">
+        <v>543</v>
+      </c>
+      <c r="J153" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="155" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A155">
+        <v>1000</v>
+      </c>
+      <c r="D155">
+        <v>2</v>
+      </c>
+      <c r="E155" t="s">
+        <v>482</v>
+      </c>
+      <c r="F155" t="s">
+        <v>47</v>
+      </c>
+      <c r="G155">
+        <v>175</v>
+      </c>
+      <c r="H155" t="s">
+        <v>542</v>
+      </c>
+      <c r="I155" s="12" t="s">
+        <v>545</v>
+      </c>
+      <c r="J155" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="157" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A157">
+        <v>1000</v>
+      </c>
+      <c r="D157">
+        <v>2</v>
+      </c>
+      <c r="E157" s="13" t="s">
+        <v>547</v>
+      </c>
+      <c r="F157" t="s">
+        <v>25</v>
+      </c>
+      <c r="G157">
+        <v>175</v>
+      </c>
+      <c r="H157" t="s">
+        <v>517</v>
+      </c>
+      <c r="I157" s="12" t="s">
+        <v>548</v>
+      </c>
+      <c r="J157" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="160" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A160" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B160" s="8"/>
+      <c r="C160" s="7"/>
+      <c r="D160" s="8"/>
+      <c r="E160" s="7"/>
+      <c r="F160" s="8"/>
+      <c r="G160" s="7"/>
+      <c r="H160" s="8"/>
+      <c r="I160" s="7"/>
+      <c r="J160" s="8"/>
+      <c r="K160" s="8"/>
+    </row>
+    <row r="161" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A161" s="7"/>
+      <c r="B161" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="C161" s="17"/>
+      <c r="D161" s="17"/>
+      <c r="E161" s="17"/>
+      <c r="F161" s="17"/>
+      <c r="G161" s="18" t="s">
+        <v>187</v>
+      </c>
+      <c r="H161" s="18"/>
+      <c r="I161" s="18"/>
+      <c r="J161" s="18"/>
+      <c r="K161" s="18"/>
+    </row>
+    <row r="162" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A162" s="7"/>
+      <c r="B162" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="C162" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="D162" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="E162" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F162" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G162" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="H162" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="I162" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="J162" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="K162" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="163" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A163" s="7">
+        <v>1000</v>
+      </c>
+      <c r="B163" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C163" s="7">
+        <v>289</v>
+      </c>
+      <c r="D163" s="8">
+        <v>113</v>
+      </c>
+      <c r="E163" t="s">
+        <v>537</v>
+      </c>
+      <c r="F163" t="s">
+        <v>538</v>
+      </c>
+      <c r="G163" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H163" s="8">
+        <v>113</v>
+      </c>
+      <c r="I163" s="7">
+        <v>29</v>
+      </c>
+      <c r="J163" s="6" t="s">
+        <v>539</v>
+      </c>
+      <c r="K163" s="7" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="166" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="G166" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="H166" s="16" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="168" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A168" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B168" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C168" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D168" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E168" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F168" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="G168" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="H168" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I168" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J168" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K168" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="L168" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="169" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A169">
+        <v>1000</v>
+      </c>
+      <c r="D169">
+        <v>2</v>
+      </c>
+      <c r="E169" t="s">
+        <v>550</v>
+      </c>
+      <c r="F169" t="s">
+        <v>14</v>
+      </c>
+      <c r="G169">
         <v>301</v>
       </c>
-      <c r="D144" s="8">
+      <c r="H169" t="s">
+        <v>420</v>
+      </c>
+      <c r="I169" t="s">
+        <v>551</v>
+      </c>
+      <c r="J169" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="171" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A171">
+        <v>1000</v>
+      </c>
+      <c r="D171">
+        <v>2</v>
+      </c>
+      <c r="E171" t="s">
+        <v>556</v>
+      </c>
+      <c r="F171" t="s">
+        <v>36</v>
+      </c>
+      <c r="G171">
+        <v>175</v>
+      </c>
+      <c r="H171" t="s">
+        <v>557</v>
+      </c>
+      <c r="I171" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="J171" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="173" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A173">
+        <v>1000</v>
+      </c>
+      <c r="D173">
+        <v>2</v>
+      </c>
+      <c r="E173" t="s">
+        <v>560</v>
+      </c>
+      <c r="F173" t="s">
+        <v>47</v>
+      </c>
+      <c r="G173">
+        <v>175</v>
+      </c>
+      <c r="H173" t="s">
+        <v>561</v>
+      </c>
+      <c r="I173" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="J173" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="175" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A175">
+        <v>1000</v>
+      </c>
+      <c r="D175">
+        <v>2</v>
+      </c>
+      <c r="E175" s="13" t="s">
+        <v>563</v>
+      </c>
+      <c r="F175" t="s">
+        <v>25</v>
+      </c>
+      <c r="G175">
+        <v>175</v>
+      </c>
+      <c r="H175" t="s">
+        <v>564</v>
+      </c>
+      <c r="I175" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="J175" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="178" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A178" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B178" s="8"/>
+      <c r="C178" s="7"/>
+      <c r="D178" s="8"/>
+      <c r="E178" s="7"/>
+      <c r="F178" s="8"/>
+      <c r="G178" s="7"/>
+      <c r="H178" s="8"/>
+      <c r="I178" s="7"/>
+      <c r="J178" s="8"/>
+      <c r="K178" s="8"/>
+    </row>
+    <row r="179" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A179" s="7"/>
+      <c r="B179" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="C179" s="17"/>
+      <c r="D179" s="17"/>
+      <c r="E179" s="17"/>
+      <c r="F179" s="17"/>
+      <c r="G179" s="18" t="s">
+        <v>187</v>
+      </c>
+      <c r="H179" s="18"/>
+      <c r="I179" s="18"/>
+      <c r="J179" s="18"/>
+      <c r="K179" s="18"/>
+    </row>
+    <row r="180" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A180" s="7"/>
+      <c r="B180" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="C180" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="D180" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="E180" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F180" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G180" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="H180" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="I180" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="J180" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="K180" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="181" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A181" s="7">
+        <v>1000</v>
+      </c>
+      <c r="B181" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C181" s="7">
+        <v>301</v>
+      </c>
+      <c r="D181" s="8">
         <v>83</v>
       </c>
-      <c r="E144" t="s">
+      <c r="E181" t="s">
         <v>551</v>
       </c>
-      <c r="F144" t="s">
+      <c r="F181" t="s">
         <v>552</v>
       </c>
-      <c r="G144" s="7" t="s">
+      <c r="G181" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="H144" s="8">
+      <c r="H181" s="8">
         <v>107</v>
       </c>
-      <c r="I144" s="7">
+      <c r="I181" s="7">
         <v>26</v>
       </c>
-      <c r="J144" s="6" t="s">
+      <c r="J181" s="6" t="s">
         <v>554</v>
       </c>
-      <c r="K144" s="7" t="s">
+      <c r="K181" s="7" t="s">
         <v>555</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="8">
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="G69:K69"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="G15:K15"/>
     <mergeCell ref="B33:F33"/>

--- a/Experiments/DBCV_Conclu.xlsx
+++ b/Experiments/DBCV_Conclu.xlsx
@@ -9,26 +9,27 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17850" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17850" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet10" sheetId="10" r:id="rId2"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
-    <sheet name="Sheet4" sheetId="4" r:id="rId5"/>
-    <sheet name="Sheet5" sheetId="5" r:id="rId6"/>
-    <sheet name="Sheet6" sheetId="6" r:id="rId7"/>
-    <sheet name="Sheet7" sheetId="7" r:id="rId8"/>
-    <sheet name="Sheet8" sheetId="8" r:id="rId9"/>
-    <sheet name="Sheet9" sheetId="9" r:id="rId10"/>
+    <sheet name="Sheet11" sheetId="11" r:id="rId4"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId5"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId6"/>
+    <sheet name="Sheet5" sheetId="5" r:id="rId7"/>
+    <sheet name="Sheet6" sheetId="6" r:id="rId8"/>
+    <sheet name="Sheet7" sheetId="7" r:id="rId9"/>
+    <sheet name="Sheet8" sheetId="8" r:id="rId10"/>
+    <sheet name="Sheet9" sheetId="9" r:id="rId11"/>
   </sheets>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="604">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1376" uniqueCount="614">
   <si>
     <t>Datapoints</t>
   </si>
@@ -79,15 +80,6 @@
   </si>
   <si>
     <t>32.530secs</t>
-  </si>
-  <si>
-    <t>4.476 secs</t>
-  </si>
-  <si>
-    <t>0.124</t>
-  </si>
-  <si>
-    <t>396.234 secs</t>
   </si>
   <si>
     <t>0.459 secs</t>
@@ -624,30 +616,9 @@
     <t>54.398 secs</t>
   </si>
   <si>
-    <t>6.252 secs</t>
-  </si>
-  <si>
-    <t>303 clusters</t>
-  </si>
-  <si>
-    <t>0.202 secs</t>
-  </si>
-  <si>
-    <t>0.190</t>
-  </si>
-  <si>
-    <t>333.944 secs</t>
-  </si>
-  <si>
-    <t>99 outliers</t>
-  </si>
-  <si>
     <t>-0.021</t>
   </si>
   <si>
-    <t>86.070 secs</t>
-  </si>
-  <si>
     <t>6.575 secs</t>
   </si>
   <si>
@@ -696,18 +667,6 @@
     <t>5.901 secs</t>
   </si>
   <si>
-    <t>0.181 secs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.173 </t>
-  </si>
-  <si>
-    <t>329.048 secs</t>
-  </si>
-  <si>
-    <t>76.765 secs</t>
-  </si>
-  <si>
     <t>0.471 secs</t>
   </si>
   <si>
@@ -756,18 +715,6 @@
     <t>337.313 secs</t>
   </si>
   <si>
-    <t>314 clusters</t>
-  </si>
-  <si>
-    <t>120 outliers</t>
-  </si>
-  <si>
-    <t>-0.060</t>
-  </si>
-  <si>
-    <t>78.882 secs</t>
-  </si>
-  <si>
     <t>4.872 secs</t>
   </si>
   <si>
@@ -870,12 +817,6 @@
     <t>295.402 secs</t>
   </si>
   <si>
-    <t>-0.070</t>
-  </si>
-  <si>
-    <t>78.698 secs</t>
-  </si>
-  <si>
     <t>3.059 secs</t>
   </si>
   <si>
@@ -918,24 +859,12 @@
     <t>2.748 secs</t>
   </si>
   <si>
-    <t>0.112 secs</t>
-  </si>
-  <si>
     <t>123.917 secs</t>
   </si>
   <si>
     <t>1.434 secs</t>
   </si>
   <si>
-    <t>0.156</t>
-  </si>
-  <si>
-    <t>244.027 secs</t>
-  </si>
-  <si>
-    <t>107.670 secs</t>
-  </si>
-  <si>
     <t>141.890 secs</t>
   </si>
   <si>
@@ -966,21 +895,9 @@
     <t>2.673 secs</t>
   </si>
   <si>
-    <t>0.116 secs</t>
-  </si>
-  <si>
     <t>0.182</t>
   </si>
   <si>
-    <t>262.840 secs</t>
-  </si>
-  <si>
-    <t>0.001</t>
-  </si>
-  <si>
-    <t>110.979 secs</t>
-  </si>
-  <si>
     <t>147.240 secs</t>
   </si>
   <si>
@@ -1017,24 +934,12 @@
     <t>2.851 secs</t>
   </si>
   <si>
-    <t>0.113</t>
-  </si>
-  <si>
     <t>164.529 secs</t>
   </si>
   <si>
     <t>7.996 secs</t>
   </si>
   <si>
-    <t xml:space="preserve">0.135 </t>
-  </si>
-  <si>
-    <t>294.543 secs</t>
-  </si>
-  <si>
-    <t>81.233 secs</t>
-  </si>
-  <si>
     <t>-0.028</t>
   </si>
   <si>
@@ -1344,9 +1249,6 @@
     <t>2.876 secs</t>
   </si>
   <si>
-    <t>0.117 secs</t>
-  </si>
-  <si>
     <t>3.102 secs</t>
   </si>
   <si>
@@ -1356,15 +1258,6 @@
     <t>193.242 secs</t>
   </si>
   <si>
-    <t>0.087</t>
-  </si>
-  <si>
-    <t>319.429 secs</t>
-  </si>
-  <si>
-    <t>49.106 secs</t>
-  </si>
-  <si>
     <t>2.517 secs</t>
   </si>
   <si>
@@ -1446,21 +1339,6 @@
     <t>101.925 secs</t>
   </si>
   <si>
-    <t>3.744 secs</t>
-  </si>
-  <si>
-    <t>0.197</t>
-  </si>
-  <si>
-    <t>0.123 secs</t>
-  </si>
-  <si>
-    <t>234.075 secs</t>
-  </si>
-  <si>
-    <t>56.809 secs</t>
-  </si>
-  <si>
     <t>3.731 secs</t>
   </si>
   <si>
@@ -1743,12 +1621,6 @@
     <t>(K=32)(Batch=256)</t>
   </si>
   <si>
-    <t>7.933 secs</t>
-  </si>
-  <si>
-    <t>0.135 secs</t>
-  </si>
-  <si>
     <t>0.154</t>
   </si>
   <si>
@@ -1833,29 +1705,188 @@
     <t>492.017 secs</t>
   </si>
   <si>
-    <t>280.014 secs</t>
-  </si>
-  <si>
     <t>1.080 secs</t>
   </si>
   <si>
-    <t>0.175</t>
-  </si>
-  <si>
-    <t>994.021 secs</t>
-  </si>
-  <si>
-    <t>-0.016</t>
-  </si>
-  <si>
-    <t>251.324 secs</t>
+    <t>Average Similarity</t>
+  </si>
+  <si>
+    <t>Distance Metric</t>
+  </si>
+  <si>
+    <t>agglomerative</t>
+  </si>
+  <si>
+    <t>Hausdorff</t>
+  </si>
+  <si>
+    <t>Average Dist</t>
+  </si>
+  <si>
+    <t>Dataset Size(rep Objs)</t>
+  </si>
+  <si>
+    <t># rep Objs</t>
+  </si>
+  <si>
+    <t>Dataset Size(test)</t>
+  </si>
+  <si>
+    <t>0.138</t>
+  </si>
+  <si>
+    <t>multi-hdbscan</t>
+  </si>
+  <si>
+    <t>0.170</t>
+  </si>
+  <si>
+    <t>143.024 secs</t>
+  </si>
+  <si>
+    <t>0.228 secs</t>
+  </si>
+  <si>
+    <t>437.956 secs</t>
+  </si>
+  <si>
+    <t>113.242 secs</t>
+  </si>
+  <si>
+    <t>145.809 secs</t>
+  </si>
+  <si>
+    <t>0.186</t>
+  </si>
+  <si>
+    <t>489.133 secs</t>
+  </si>
+  <si>
+    <t>307 clusters</t>
+  </si>
+  <si>
+    <t>93 outliers</t>
+  </si>
+  <si>
+    <t>129.881 secs</t>
+  </si>
+  <si>
+    <t>194.555 secs</t>
+  </si>
+  <si>
+    <t>0.620 secs</t>
+  </si>
+  <si>
+    <t>0.185</t>
+  </si>
+  <si>
+    <t>689.203 secs</t>
+  </si>
+  <si>
+    <t>203.029 secs</t>
+  </si>
+  <si>
+    <t>144.855 secs</t>
+  </si>
+  <si>
+    <t>0.178 secs</t>
+  </si>
+  <si>
+    <t>0.177</t>
+  </si>
+  <si>
+    <t>730.026 secs</t>
+  </si>
+  <si>
+    <t>194.454 secs</t>
+  </si>
+  <si>
+    <t>-0.035</t>
+  </si>
+  <si>
+    <t>210.596 secs</t>
+  </si>
+  <si>
+    <t>0.725 secs</t>
+  </si>
+  <si>
+    <t>0.164</t>
+  </si>
+  <si>
+    <t>718.808 secs</t>
+  </si>
+  <si>
+    <t>198.859 secs</t>
+  </si>
+  <si>
+    <t>0.538 secs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.148 </t>
+  </si>
+  <si>
+    <t>639.097 secs</t>
+  </si>
+  <si>
+    <t>-0.044</t>
+  </si>
+  <si>
+    <t>151.091 secs</t>
+  </si>
+  <si>
+    <t>0.158</t>
+  </si>
+  <si>
+    <t>562.223 secs</t>
+  </si>
+  <si>
+    <t>173.888 secs</t>
+  </si>
+  <si>
+    <t>0.419 secs</t>
+  </si>
+  <si>
+    <t>0.168</t>
+  </si>
+  <si>
+    <t>621.601 secs</t>
+  </si>
+  <si>
+    <t>-0.002</t>
+  </si>
+  <si>
+    <t>160.056 secs</t>
+  </si>
+  <si>
+    <t>0.135</t>
+  </si>
+  <si>
+    <t>551.979 secs</t>
+  </si>
+  <si>
+    <t>-0.053</t>
+  </si>
+  <si>
+    <t>130.375 secs</t>
+  </si>
+  <si>
+    <t>0.550 secs</t>
+  </si>
+  <si>
+    <t>0.101</t>
+  </si>
+  <si>
+    <t>526.278 secs</t>
+  </si>
+  <si>
+    <t>116.512 secs</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1898,6 +1929,19 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1932,7 +1976,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
@@ -1962,14 +2006,22 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2275,7 +2327,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:N74"/>
+  <dimension ref="A1:N75"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.36328125" style="7" bestFit="1" customWidth="1"/>
@@ -2296,7 +2348,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G1" s="9" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -2361,58 +2413,58 @@
         <v>2</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>17</v>
+        <v>567</v>
       </c>
       <c r="H5" s="8" t="s">
         <v>14</v>
       </c>
       <c r="I5" s="3">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>15</v>
+        <v>568</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>18</v>
+        <v>257</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>19</v>
+        <v>569</v>
       </c>
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
     </row>
     <row r="6" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="3">
-        <v>1000</v>
-      </c>
-      <c r="B6" s="3">
+      <c r="A6" s="23">
+        <v>1000</v>
+      </c>
+      <c r="B6" s="23">
         <v>512</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="23">
+        <v>154</v>
+      </c>
+      <c r="E6" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="25"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="I6" s="23">
+        <v>169</v>
+      </c>
+      <c r="J6" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="K6" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="L6" s="24" t="s">
         <v>21</v>
-      </c>
-      <c r="D6" s="3">
-        <v>154</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" s="3">
-        <v>169</v>
-      </c>
-      <c r="J6" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
@@ -2425,30 +2477,30 @@
         <v>512</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D7" s="3">
         <v>154</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="2"/>
       <c r="H7" s="8" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="I7" s="3">
         <v>175</v>
       </c>
       <c r="J7" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="K7" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="L7" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
@@ -2461,7 +2513,7 @@
         <v>512</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="2"/>
@@ -2469,22 +2521,22 @@
         <v>2</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="I8" s="3">
         <v>175</v>
       </c>
       <c r="J8" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="K8" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="K8" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="L8" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
@@ -2497,7 +2549,7 @@
         <v>512</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="2"/>
@@ -2505,22 +2557,22 @@
         <v>2</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I9" s="3">
         <v>175</v>
       </c>
       <c r="J9" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="K9" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="K9" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="L9" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
@@ -2533,30 +2585,30 @@
         <v>512</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D10" s="3">
         <v>154</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="2"/>
       <c r="H10" s="8" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I10" s="3">
         <v>175</v>
       </c>
       <c r="J10" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="K10" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K10" s="2" t="s">
-        <v>45</v>
-      </c>
       <c r="L10" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
@@ -2569,36 +2621,36 @@
         <v>512</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D11" s="3">
         <v>154</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="2"/>
       <c r="H11" s="8" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="I11" s="3">
         <v>175</v>
       </c>
       <c r="J11" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="K11" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="K11" s="4" t="s">
-        <v>51</v>
-      </c>
       <c r="L11" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -2609,7 +2661,7 @@
         <v>512</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D12" s="1"/>
       <c r="E12" s="2"/>
@@ -2617,22 +2669,22 @@
         <v>2</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="I12" s="3">
         <v>175</v>
       </c>
       <c r="J12" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="K12" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="K12" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="L12" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
@@ -2651,33 +2703,33 @@
       <c r="N13" s="2"/>
     </row>
     <row r="14" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="7">
-        <v>1000</v>
-      </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="7">
-        <v>2</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>235</v>
-      </c>
-      <c r="H14" s="8" t="s">
+      <c r="A14" s="25">
+        <v>1000</v>
+      </c>
+      <c r="B14" s="25"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="25">
+        <v>2</v>
+      </c>
+      <c r="G14" s="24" t="s">
+        <v>221</v>
+      </c>
+      <c r="H14" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="I14" s="7">
+      <c r="I14" s="25">
         <v>314</v>
       </c>
-      <c r="J14" s="8" t="s">
-        <v>236</v>
-      </c>
-      <c r="K14" s="8" t="s">
-        <v>237</v>
-      </c>
-      <c r="L14" s="8" t="s">
-        <v>238</v>
+      <c r="J14" s="24" t="s">
+        <v>222</v>
+      </c>
+      <c r="K14" s="24" t="s">
+        <v>223</v>
+      </c>
+      <c r="L14" s="24" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -2700,22 +2752,22 @@
         <v>2</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>243</v>
+        <v>225</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I16" s="7">
         <v>175</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>244</v>
+        <v>226</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>245</v>
+        <v>227</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>246</v>
+        <v>228</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -2739,22 +2791,22 @@
         <v>2</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>247</v>
+        <v>229</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="I18" s="7">
         <v>175</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>248</v>
+        <v>230</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>245</v>
+        <v>227</v>
       </c>
       <c r="L18" s="8" t="s">
-        <v>249</v>
+        <v>231</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -2778,22 +2830,22 @@
         <v>2</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>250</v>
+        <v>232</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="I20" s="7">
         <v>175</v>
       </c>
       <c r="J20" s="8" t="s">
-        <v>251</v>
+        <v>233</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>252</v>
+        <v>234</v>
       </c>
       <c r="L20" s="8" t="s">
-        <v>253</v>
+        <v>235</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -2805,30 +2857,30 @@
       <c r="G21" s="8"/>
     </row>
     <row r="22" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="19" t="s">
-        <v>183</v>
-      </c>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="H22" s="20"/>
-      <c r="I22" s="20"/>
-      <c r="J22" s="20"/>
-      <c r="K22" s="20"/>
+      <c r="B22" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="22" t="s">
+        <v>184</v>
+      </c>
+      <c r="H22" s="22"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="22"/>
+      <c r="K22" s="22"/>
     </row>
     <row r="23" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="8" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>10</v>
@@ -2837,13 +2889,13 @@
         <v>11</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="J23" s="7" t="s">
         <v>10</v>
@@ -2859,80 +2911,55 @@
       <c r="B24" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>240</v>
+      <c r="C24" s="7">
+        <v>288</v>
+      </c>
+      <c r="D24" s="8">
+        <v>94</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>237</v>
+        <v>257</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>238</v>
+        <v>569</v>
       </c>
       <c r="G24" s="7" t="s">
         <v>14</v>
       </c>
       <c r="H24" s="8">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="I24" s="7">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>241</v>
+        <v>195</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>242</v>
+        <v>570</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="2"/>
-      <c r="K25" s="2"/>
-      <c r="L25" s="2"/>
-      <c r="M25" s="2"/>
-      <c r="N25" s="2"/>
+      <c r="A25" s="7">
+        <v>1000</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" s="8"/>
+      <c r="J25" s="6"/>
+      <c r="K25" s="7"/>
     </row>
     <row r="26" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="3">
-        <v>2000</v>
-      </c>
-      <c r="B26" s="3">
-        <v>512</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>60</v>
-      </c>
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="2"/>
       <c r="D26" s="1"/>
       <c r="E26" s="2"/>
-      <c r="F26" s="3">
-        <v>2</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H26" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="I26" s="3">
-        <v>175</v>
-      </c>
-      <c r="J26" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="L26" s="2" t="s">
-        <v>63</v>
-      </c>
+      <c r="F26" s="1"/>
+      <c r="G26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
     </row>
@@ -2944,30 +2971,30 @@
         <v>512</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D27" s="3">
-        <v>154</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F27" s="1"/>
-      <c r="G27" s="2"/>
+        <v>57</v>
+      </c>
+      <c r="D27" s="1"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="3">
+        <v>2</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="H27" s="8" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="I27" s="3">
         <v>175</v>
       </c>
       <c r="J27" s="8" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="M27" s="2"/>
       <c r="N27" s="2"/>
@@ -2980,35 +3007,33 @@
         <v>512</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>135</v>
+        <v>62</v>
       </c>
       <c r="D28" s="3">
         <v>154</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>136</v>
+        <v>63</v>
       </c>
       <c r="F28" s="1"/>
       <c r="G28" s="2"/>
       <c r="H28" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="I28" s="7">
+        <v>22</v>
+      </c>
+      <c r="I28" s="3">
         <v>175</v>
       </c>
       <c r="J28" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="K28" s="6" t="s">
-        <v>138</v>
+        <v>61</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>139</v>
+        <v>65</v>
       </c>
       <c r="M28" s="2"/>
-      <c r="N28" s="2" t="s">
-        <v>69</v>
-      </c>
+      <c r="N28" s="2"/>
     </row>
     <row r="29" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="3">
@@ -3018,33 +3043,35 @@
         <v>512</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D29" s="1"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="3">
-        <v>2</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>72</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="D29" s="3">
+        <v>154</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F29" s="1"/>
+      <c r="G29" s="2"/>
       <c r="H29" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="I29" s="3">
+        <v>44</v>
+      </c>
+      <c r="I29" s="7">
         <v>175</v>
       </c>
       <c r="J29" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>73</v>
+        <v>131</v>
+      </c>
+      <c r="K29" s="6" t="s">
+        <v>135</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>74</v>
+        <v>136</v>
       </c>
       <c r="M29" s="2"/>
-      <c r="N29" s="2"/>
+      <c r="N29" s="2" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="30" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="3">
@@ -3054,30 +3081,30 @@
         <v>512</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D30" s="3">
-        <v>154</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F30" s="1"/>
-      <c r="G30" s="2"/>
+        <v>68</v>
+      </c>
+      <c r="D30" s="1"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="3">
+        <v>2</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>69</v>
+      </c>
       <c r="H30" s="8" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="I30" s="3">
-        <v>363</v>
+        <v>175</v>
       </c>
       <c r="J30" s="8" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="L30" s="5" t="s">
-        <v>79</v>
+        <v>70</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>71</v>
       </c>
       <c r="M30" s="2"/>
       <c r="N30" s="2"/>
@@ -3090,30 +3117,30 @@
         <v>512</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D31" s="1"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="3">
-        <v>2</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>82</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="D31" s="3">
+        <v>154</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F31" s="1"/>
+      <c r="G31" s="2"/>
       <c r="H31" s="8" t="s">
         <v>14</v>
       </c>
       <c r="I31" s="3">
-        <v>605</v>
+        <v>363</v>
       </c>
       <c r="J31" s="8" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="L31" s="2" t="s">
-        <v>84</v>
+        <v>75</v>
+      </c>
+      <c r="L31" s="5" t="s">
+        <v>76</v>
       </c>
       <c r="M31" s="2"/>
       <c r="N31" s="2"/>
@@ -3126,30 +3153,30 @@
         <v>512</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D32" s="3">
-        <v>154</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="F32" s="1"/>
-      <c r="G32" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="D32" s="1"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="3">
+        <v>2</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>79</v>
+      </c>
       <c r="H32" s="8" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="I32" s="3">
-        <v>175</v>
+        <v>605</v>
       </c>
       <c r="J32" s="8" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="M32" s="2"/>
       <c r="N32" s="2"/>
@@ -3162,44 +3189,67 @@
         <v>512</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D33" s="1"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="3">
-        <v>2</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>92</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="D33" s="3">
+        <v>154</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F33" s="1"/>
+      <c r="G33" s="2"/>
       <c r="H33" s="8" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I33" s="3">
         <v>175</v>
       </c>
       <c r="J33" s="8" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="M33" s="2"/>
       <c r="N33" s="2"/>
     </row>
     <row r="34" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="1"/>
-      <c r="B34" s="1"/>
-      <c r="C34" s="2"/>
+      <c r="A34" s="3">
+        <v>2000</v>
+      </c>
+      <c r="B34" s="3">
+        <v>512</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>88</v>
+      </c>
       <c r="D34" s="1"/>
       <c r="E34" s="2"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="2"/>
-      <c r="K34" s="2"/>
-      <c r="L34" s="2"/>
+      <c r="F34" s="3">
+        <v>2</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H34" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="I34" s="3">
+        <v>175</v>
+      </c>
+      <c r="J34" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="K34" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="L34" s="2" t="s">
+        <v>91</v>
+      </c>
       <c r="M34" s="2"/>
       <c r="N34" s="2"/>
     </row>
@@ -3217,151 +3267,126 @@
       <c r="N35" s="2"/>
     </row>
     <row r="36" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="3">
-        <v>5000</v>
-      </c>
-      <c r="B36" s="3">
-        <v>512</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>96</v>
-      </c>
+      <c r="A36" s="1"/>
+      <c r="B36" s="1"/>
+      <c r="C36" s="2"/>
       <c r="D36" s="1"/>
       <c r="E36" s="2"/>
-      <c r="F36" s="3">
-        <v>2</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="H36" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="I36" s="3">
-        <v>1586</v>
-      </c>
-      <c r="J36" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="K36" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="L36" s="8" t="s">
-        <v>117</v>
-      </c>
+      <c r="F36" s="1"/>
+      <c r="G36" s="2"/>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
       <c r="M36" s="2"/>
       <c r="N36" s="2"/>
     </row>
     <row r="37" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="1">
+      <c r="A37" s="3">
         <v>5000</v>
       </c>
-      <c r="B37" s="1">
+      <c r="B37" s="3">
         <v>512</v>
       </c>
-      <c r="C37" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="D37" s="1">
-        <v>154</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="F37" s="1"/>
-      <c r="G37" s="2"/>
+      <c r="C37" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D37" s="1"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="3">
+        <v>2</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>94</v>
+      </c>
       <c r="H37" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I37" s="7">
+      <c r="I37" s="3">
+        <v>1586</v>
+      </c>
+      <c r="J37" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="K37" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="L37" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M37" s="2"/>
+      <c r="N37" s="2"/>
+    </row>
+    <row r="38" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="1">
+        <v>5000</v>
+      </c>
+      <c r="B38" s="1">
+        <v>512</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="D38" s="1">
+        <v>154</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F38" s="1"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I38" s="7">
         <v>914</v>
       </c>
-      <c r="J37" s="8" t="s">
+      <c r="J38" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="K38" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="K37" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="L37" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="M37" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="N37" s="2"/>
-    </row>
-    <row r="38" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="3">
+      <c r="L38" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="M38" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="N38" s="2"/>
+    </row>
+    <row r="39" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="3">
         <v>5000</v>
       </c>
-      <c r="B38" s="3">
+      <c r="B39" s="3">
         <v>512</v>
       </c>
-      <c r="C38" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="D38" s="1"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="3">
-        <v>2</v>
-      </c>
-      <c r="G38" s="2" t="s">
+      <c r="C39" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D39" s="1"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="3">
+        <v>2</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="H39" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="I39" s="3">
+        <v>175</v>
+      </c>
+      <c r="J39" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="K39" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="H38" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="I38" s="3">
-        <v>175</v>
-      </c>
-      <c r="J38" s="8" t="s">
+      <c r="L39" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="K38" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="L38" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="M38" s="2"/>
-      <c r="N38" s="2"/>
-    </row>
-    <row r="39" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="1">
-        <v>5000</v>
-      </c>
-      <c r="B39" s="1">
-        <v>512</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D39" s="1">
-        <v>154</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="F39" s="1"/>
-      <c r="G39" s="2"/>
-      <c r="H39" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I39" s="7">
-        <v>175</v>
-      </c>
-      <c r="J39" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="K39" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="L39" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="M39" s="2" t="s">
-        <v>69</v>
-      </c>
+      <c r="M39" s="2"/>
       <c r="N39" s="2"/>
     </row>
     <row r="40" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3371,33 +3396,35 @@
       <c r="B40" s="1">
         <v>512</v>
       </c>
-      <c r="C40" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="D40" s="1"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="1">
-        <v>2</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="H40" s="8" t="s">
-        <v>47</v>
+      <c r="C40" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D40" s="1">
+        <v>154</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F40" s="1"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="6" t="s">
+        <v>33</v>
       </c>
       <c r="I40" s="7">
         <v>175</v>
       </c>
       <c r="J40" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="K40" s="6" t="s">
-        <v>112</v>
+        <v>103</v>
+      </c>
+      <c r="K40" s="2" t="s">
+        <v>104</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="M40" s="2"/>
+        <v>105</v>
+      </c>
+      <c r="M40" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="N40" s="2"/>
     </row>
     <row r="41" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3408,37 +3435,33 @@
         <v>512</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="D41" s="1">
-        <v>154</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F41" s="1"/>
-      <c r="G41" s="2"/>
+        <v>106</v>
+      </c>
+      <c r="D41" s="1"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="1">
+        <v>2</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>107</v>
+      </c>
       <c r="H41" s="8" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="I41" s="7">
         <v>175</v>
       </c>
       <c r="J41" s="8" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="K41" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="L41" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="M41" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="N41" s="2" t="s">
-        <v>69</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="L41" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="M41" s="2"/>
+      <c r="N41" s="2"/>
     </row>
     <row r="42" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
@@ -3448,33 +3471,37 @@
         <v>512</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="D42" s="1"/>
-      <c r="E42" s="2"/>
-      <c r="F42" s="1">
-        <v>2</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>128</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="D42" s="1">
+        <v>154</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F42" s="1"/>
+      <c r="G42" s="2"/>
       <c r="H42" s="8" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="I42" s="7">
         <v>175</v>
       </c>
       <c r="J42" s="8" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="K42" s="6" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="L42" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="M42" s="2"/>
-      <c r="N42" s="2"/>
+        <v>117</v>
+      </c>
+      <c r="M42" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="N42" s="2" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="43" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
@@ -3484,51 +3511,71 @@
         <v>512</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="D43" s="1">
-        <v>154</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="F43" s="1"/>
-      <c r="G43" s="2"/>
+        <v>124</v>
+      </c>
+      <c r="D43" s="1"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="1">
+        <v>2</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>125</v>
+      </c>
       <c r="H43" s="8" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="I43" s="7">
         <v>175</v>
       </c>
       <c r="J43" s="8" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="K43" s="6" t="s">
-        <v>150</v>
+        <v>126</v>
       </c>
       <c r="L43" s="8" t="s">
-        <v>151</v>
+        <v>127</v>
       </c>
       <c r="M43" s="2"/>
       <c r="N43" s="2"/>
     </row>
     <row r="44" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="1"/>
-      <c r="B44" s="2"/>
-      <c r="C44" s="1"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="1"/>
-      <c r="F44" s="2"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="2"/>
-      <c r="I44" s="1"/>
-      <c r="J44" s="2"/>
-      <c r="K44" s="2"/>
-      <c r="L44" s="2"/>
+      <c r="A44" s="1">
+        <v>5000</v>
+      </c>
+      <c r="B44" s="1">
+        <v>512</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="D44" s="1">
+        <v>154</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F44" s="1"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I44" s="7">
+        <v>175</v>
+      </c>
+      <c r="J44" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="K44" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="L44" s="8" t="s">
+        <v>148</v>
+      </c>
       <c r="M44" s="2"/>
       <c r="N44" s="2"/>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="1"/>
       <c r="B45" s="2"/>
       <c r="C45" s="1"/>
@@ -3561,9 +3608,7 @@
       <c r="N46" s="2"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A47" s="1" t="s">
-        <v>102</v>
-      </c>
+      <c r="A47" s="1"/>
       <c r="B47" s="2"/>
       <c r="C47" s="1"/>
       <c r="D47" s="2"/>
@@ -3579,167 +3624,153 @@
       <c r="N47" s="2"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="B48" s="19" t="s">
+      <c r="A48" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B48" s="2"/>
+      <c r="C48" s="1"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="1"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="1"/>
+      <c r="J48" s="2"/>
+      <c r="K48" s="2"/>
+      <c r="L48" s="2"/>
+      <c r="M48" s="2"/>
+      <c r="N48" s="2"/>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B49" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="C49" s="21"/>
+      <c r="D49" s="21"/>
+      <c r="E49" s="21"/>
+      <c r="F49" s="21"/>
+      <c r="G49" s="22" t="s">
+        <v>184</v>
+      </c>
+      <c r="H49" s="22"/>
+      <c r="I49" s="22"/>
+      <c r="J49" s="22"/>
+      <c r="K49" s="22"/>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B50" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="D50" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="C48" s="19"/>
-      <c r="D48" s="19"/>
-      <c r="E48" s="19"/>
-      <c r="F48" s="19"/>
-      <c r="G48" s="20" t="s">
+      <c r="E50" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G50" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="H50" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="I50" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="J50" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="K50" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A51" s="7">
+        <v>1000</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="E51" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="H48" s="20"/>
-      <c r="I48" s="20"/>
-      <c r="J48" s="20"/>
-      <c r="K48" s="20"/>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B49" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="D49" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="E49" s="7" t="s">
+      <c r="F51" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="G51" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H51" s="8">
+        <v>80</v>
+      </c>
+      <c r="I51" s="7">
+        <v>39</v>
+      </c>
+      <c r="J51" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="K51" s="7" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="G66" s="9" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A67" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B67" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D67" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E67" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F67" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G67" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="H67" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="I67" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J67" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="K67" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="F49" s="8" t="s">
+      <c r="L67" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G49" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="H49" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="I49" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="J49" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="K49" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A50" s="7">
-        <v>1000</v>
-      </c>
-      <c r="B50" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="D50" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="E50" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="F50" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="G50" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H50" s="8">
-        <v>80</v>
-      </c>
-      <c r="I50" s="7">
-        <v>39</v>
-      </c>
-      <c r="J50" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="K50" s="7" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="G65" s="9" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A66" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B66" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C66" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D66" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E66" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="F66" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="G66" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="H66" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="I66" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="J66" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="K66" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="L66" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="M66" s="8" t="s">
+      <c r="M67" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N66" s="8" t="s">
+      <c r="N67" s="8" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A67" s="7">
-        <v>1000</v>
-      </c>
-      <c r="B67" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C67" s="7">
-        <v>165</v>
-      </c>
-      <c r="D67" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="E67" s="7">
-        <v>512</v>
-      </c>
-      <c r="F67" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="G67" s="7">
-        <v>154</v>
-      </c>
-      <c r="H67" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="K67" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="L67" s="8" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.35">
@@ -3750,28 +3781,28 @@
         <v>14</v>
       </c>
       <c r="C68" s="7">
-        <v>323</v>
+        <v>165</v>
       </c>
       <c r="D68" s="8" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="E68" s="7">
         <v>512</v>
       </c>
       <c r="F68" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="I68" s="7">
-        <v>2</v>
-      </c>
-      <c r="J68" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="K68" s="8" t="s">
-        <v>148</v>
+        <v>138</v>
+      </c>
+      <c r="G68" s="7">
+        <v>154</v>
+      </c>
+      <c r="H68" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="K68" s="6" t="s">
+        <v>140</v>
       </c>
       <c r="L68" s="8" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.35">
@@ -3779,31 +3810,31 @@
         <v>1000</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="C69" s="7">
-        <v>175</v>
+        <v>323</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="E69" s="7">
         <v>512</v>
       </c>
       <c r="F69" s="8" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="I69" s="7">
         <v>2</v>
       </c>
       <c r="J69" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="K69" s="6" t="s">
-        <v>161</v>
+        <v>144</v>
+      </c>
+      <c r="K69" s="8" t="s">
+        <v>145</v>
       </c>
       <c r="L69" s="8" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.35">
@@ -3811,34 +3842,31 @@
         <v>1000</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C70" s="7">
         <v>175</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="E70" s="7">
         <v>512</v>
       </c>
       <c r="F70" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="G70" s="7">
-        <v>154</v>
-      </c>
-      <c r="H70" s="8" t="s">
-        <v>164</v>
+        <v>150</v>
+      </c>
+      <c r="I70" s="7">
+        <v>2</v>
+      </c>
+      <c r="J70" s="8" t="s">
+        <v>151</v>
       </c>
       <c r="K70" s="6" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="L70" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="N70" s="8" t="s">
-        <v>69</v>
+        <v>152</v>
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.35">
@@ -3846,31 +3874,34 @@
         <v>1000</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C71" s="7">
         <v>175</v>
       </c>
       <c r="D71" s="8" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E71" s="7">
         <v>512</v>
       </c>
       <c r="F71" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="I71" s="7">
-        <v>2</v>
-      </c>
-      <c r="J71" s="8" t="s">
-        <v>158</v>
+        <v>160</v>
+      </c>
+      <c r="G71" s="7">
+        <v>154</v>
+      </c>
+      <c r="H71" s="8" t="s">
+        <v>161</v>
       </c>
       <c r="K71" s="6" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="L71" s="8" t="s">
-        <v>160</v>
+        <v>163</v>
+      </c>
+      <c r="N71" s="8" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.35">
@@ -3878,31 +3909,31 @@
         <v>1000</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>167</v>
+        <v>33</v>
       </c>
       <c r="C72" s="7">
         <v>175</v>
       </c>
       <c r="D72" s="8" t="s">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="E72" s="7">
         <v>512</v>
       </c>
       <c r="F72" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="G72" s="7">
         <v>154</v>
       </c>
-      <c r="H72" s="8" t="s">
-        <v>170</v>
+      <c r="I72" s="7">
+        <v>2</v>
+      </c>
+      <c r="J72" s="8" t="s">
+        <v>155</v>
       </c>
       <c r="K72" s="6" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="L72" s="8" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.35">
@@ -3910,31 +3941,31 @@
         <v>1000</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>25</v>
+        <v>164</v>
       </c>
       <c r="C73" s="7">
         <v>175</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="E73" s="7">
         <v>512</v>
       </c>
       <c r="F73" s="8" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="G73" s="7">
         <v>154</v>
       </c>
       <c r="H73" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="K73" s="10" t="s">
-        <v>176</v>
+        <v>167</v>
+      </c>
+      <c r="K73" s="6" t="s">
+        <v>168</v>
       </c>
       <c r="L73" s="8" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.35">
@@ -3942,37 +3973,69 @@
         <v>1000</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C74" s="7">
         <v>175</v>
       </c>
       <c r="D74" s="8" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="E74" s="7">
         <v>512</v>
       </c>
       <c r="F74" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="G74" s="7">
+        <v>154</v>
+      </c>
+      <c r="H74" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="K74" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="L74" s="8" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A75" s="7">
+        <v>1000</v>
+      </c>
+      <c r="B75" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C75" s="7">
+        <v>175</v>
+      </c>
+      <c r="D75" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="E75" s="7">
+        <v>512</v>
+      </c>
+      <c r="F75" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="I75" s="7">
+        <v>2</v>
+      </c>
+      <c r="J75" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="K75" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="L75" s="8" t="s">
         <v>179</v>
-      </c>
-      <c r="I74" s="7">
-        <v>2</v>
-      </c>
-      <c r="J74" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="K74" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="L74" s="8" t="s">
-        <v>182</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B48:F48"/>
-    <mergeCell ref="G48:K48"/>
+    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="G49:K49"/>
     <mergeCell ref="B22:F22"/>
     <mergeCell ref="G22:K22"/>
   </mergeCells>
@@ -3982,6 +4045,424 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L33"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="2" width="14.08984375" customWidth="1"/>
+    <col min="3" max="3" width="13.36328125" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" customWidth="1"/>
+    <col min="5" max="5" width="12.81640625" customWidth="1"/>
+    <col min="6" max="6" width="17.36328125" customWidth="1"/>
+    <col min="7" max="7" width="14.6328125" customWidth="1"/>
+    <col min="8" max="8" width="14.54296875" customWidth="1"/>
+    <col min="9" max="9" width="14.08984375" customWidth="1"/>
+    <col min="10" max="10" width="16.08984375" customWidth="1"/>
+    <col min="11" max="11" width="43.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A1" s="7"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="H1" s="8"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" s="7"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" s="7"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>1000</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5" t="s">
+        <v>297</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5">
+        <v>290</v>
+      </c>
+      <c r="H5" t="s">
+        <v>170</v>
+      </c>
+      <c r="I5" t="s">
+        <v>606</v>
+      </c>
+      <c r="J5" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>1000</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7" t="s">
+        <v>298</v>
+      </c>
+      <c r="F7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7">
+        <v>175</v>
+      </c>
+      <c r="H7" t="s">
+        <v>299</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="J7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>1000</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9" t="s">
+        <v>302</v>
+      </c>
+      <c r="F9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G9">
+        <v>175</v>
+      </c>
+      <c r="H9" t="s">
+        <v>303</v>
+      </c>
+      <c r="I9" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="J9" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>1000</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>306</v>
+      </c>
+      <c r="F11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11">
+        <v>175</v>
+      </c>
+      <c r="H11" t="s">
+        <v>233</v>
+      </c>
+      <c r="I11" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="J11" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A12" s="8"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A13" s="26">
+        <v>1000</v>
+      </c>
+      <c r="B13" s="26"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" s="26">
+        <v>245</v>
+      </c>
+      <c r="H13" s="26" t="s">
+        <v>256</v>
+      </c>
+      <c r="I13" s="27" t="s">
+        <v>311</v>
+      </c>
+      <c r="J13" s="26" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>1000</v>
+      </c>
+      <c r="F15" t="s">
+        <v>33</v>
+      </c>
+      <c r="G15">
+        <v>175</v>
+      </c>
+      <c r="H15" t="s">
+        <v>308</v>
+      </c>
+      <c r="I15" s="12" t="s">
+        <v>309</v>
+      </c>
+      <c r="J15" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>1000</v>
+      </c>
+      <c r="F17" t="s">
+        <v>44</v>
+      </c>
+      <c r="G17">
+        <v>175</v>
+      </c>
+      <c r="H17" t="s">
+        <v>314</v>
+      </c>
+      <c r="I17" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="J17" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>1000</v>
+      </c>
+      <c r="F19" t="s">
+        <v>22</v>
+      </c>
+      <c r="G19">
+        <v>175</v>
+      </c>
+      <c r="H19" t="s">
+        <v>175</v>
+      </c>
+      <c r="I19" s="12" t="s">
+        <v>317</v>
+      </c>
+      <c r="J19" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A30" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="B30" s="21"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="22" t="s">
+        <v>184</v>
+      </c>
+      <c r="G30" s="22"/>
+      <c r="H30" s="22"/>
+      <c r="I30" s="22"/>
+      <c r="J30" s="22"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A31" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="I31" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="J31" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A32" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B32" s="7">
+        <v>290</v>
+      </c>
+      <c r="C32" s="8">
+        <v>107</v>
+      </c>
+      <c r="D32" t="s">
+        <v>606</v>
+      </c>
+      <c r="E32" t="s">
+        <v>607</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G32" s="8">
+        <v>115</v>
+      </c>
+      <c r="H32" s="7">
+        <v>31</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>608</v>
+      </c>
+      <c r="J32" s="7" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>14</v>
+      </c>
+      <c r="B33">
+        <v>245</v>
+      </c>
+      <c r="C33">
+        <v>275</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="E33" t="s">
+        <v>312</v>
+      </c>
+      <c r="F33" t="s">
+        <v>14</v>
+      </c>
+      <c r="G33">
+        <v>143</v>
+      </c>
+      <c r="H33">
+        <v>91</v>
+      </c>
+      <c r="I33" s="12" t="s">
+        <v>313</v>
+      </c>
+      <c r="J33" s="14">
+        <v>76609</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="F30:J30"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L58"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -4007,7 +4488,7 @@
       <c r="E1" s="7"/>
       <c r="F1" s="8"/>
       <c r="G1" s="9" t="s">
-        <v>405</v>
+        <v>373</v>
       </c>
       <c r="H1" s="8"/>
       <c r="I1" s="7"/>
@@ -4086,22 +4567,22 @@
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>434</v>
+        <v>402</v>
       </c>
       <c r="F5" t="s">
         <v>14</v>
       </c>
       <c r="G5">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="H5" t="s">
-        <v>435</v>
+        <v>610</v>
       </c>
       <c r="I5" t="s">
-        <v>439</v>
+        <v>611</v>
       </c>
       <c r="J5" t="s">
-        <v>440</v>
+        <v>612</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
@@ -4112,22 +4593,22 @@
         <v>2</v>
       </c>
       <c r="E7" t="s">
-        <v>436</v>
+        <v>403</v>
       </c>
       <c r="F7" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G7">
         <v>175</v>
       </c>
       <c r="H7" t="s">
-        <v>437</v>
+        <v>404</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="J7" t="s">
-        <v>438</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.35">
@@ -4138,22 +4619,22 @@
         <v>2</v>
       </c>
       <c r="E9" t="s">
-        <v>445</v>
+        <v>409</v>
       </c>
       <c r="F9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G9">
         <v>175</v>
       </c>
       <c r="H9" t="s">
-        <v>446</v>
+        <v>410</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>447</v>
+        <v>411</v>
       </c>
       <c r="J9" t="s">
-        <v>448</v>
+        <v>412</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
@@ -4164,22 +4645,22 @@
         <v>2</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>442</v>
+        <v>406</v>
       </c>
       <c r="F11" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G11">
         <v>175</v>
       </c>
       <c r="H11" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>443</v>
+        <v>407</v>
       </c>
       <c r="J11" t="s">
-        <v>444</v>
+        <v>408</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
@@ -4195,23 +4676,27 @@
       <c r="J12" s="8"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A13">
-        <v>1000</v>
-      </c>
-      <c r="F13" t="s">
+      <c r="A13" s="26">
+        <v>1000</v>
+      </c>
+      <c r="B13" s="26"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="26">
         <v>253</v>
       </c>
-      <c r="H13" t="s">
-        <v>406</v>
-      </c>
-      <c r="I13" s="12" t="s">
-        <v>407</v>
-      </c>
-      <c r="J13" t="s">
-        <v>408</v>
+      <c r="H13" s="26" t="s">
+        <v>374</v>
+      </c>
+      <c r="I13" s="27" t="s">
+        <v>375</v>
+      </c>
+      <c r="J13" s="26" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.35">
@@ -4219,19 +4704,19 @@
         <v>1000</v>
       </c>
       <c r="F15" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G15">
         <v>175</v>
       </c>
       <c r="H15" t="s">
-        <v>411</v>
+        <v>379</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="J15" t="s">
-        <v>412</v>
+        <v>380</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.35">
@@ -4239,19 +4724,19 @@
         <v>1000</v>
       </c>
       <c r="F17" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G17">
         <v>175</v>
       </c>
       <c r="H17" t="s">
-        <v>413</v>
+        <v>381</v>
       </c>
       <c r="I17" s="12" t="s">
-        <v>415</v>
+        <v>383</v>
       </c>
       <c r="J17" t="s">
-        <v>416</v>
+        <v>384</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.35">
@@ -4259,46 +4744,46 @@
         <v>1000</v>
       </c>
       <c r="F19" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G19">
         <v>175</v>
       </c>
       <c r="H19" t="s">
-        <v>414</v>
+        <v>382</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>417</v>
+        <v>385</v>
       </c>
       <c r="J19" t="s">
-        <v>418</v>
+        <v>386</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A24" s="19" t="s">
-        <v>183</v>
-      </c>
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="G24" s="20"/>
-      <c r="H24" s="20"/>
-      <c r="I24" s="20"/>
-      <c r="J24" s="20"/>
+      <c r="A24" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="B24" s="21"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="22" t="s">
+        <v>184</v>
+      </c>
+      <c r="G24" s="22"/>
+      <c r="H24" s="22"/>
+      <c r="I24" s="22"/>
+      <c r="J24" s="22"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" s="8" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D25" s="7" t="s">
         <v>10</v>
@@ -4307,13 +4792,13 @@
         <v>11</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="I25" s="7" t="s">
         <v>10</v>
@@ -4327,31 +4812,31 @@
         <v>14</v>
       </c>
       <c r="B26" s="7">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C26" s="8">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D26" t="s">
-        <v>439</v>
+        <v>611</v>
       </c>
       <c r="E26" t="s">
-        <v>440</v>
+        <v>612</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>14</v>
       </c>
       <c r="G26" s="8">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="H26" s="7">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>343</v>
+        <v>411</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>441</v>
+        <v>613</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.35">
@@ -4365,10 +4850,10 @@
         <v>255</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>407</v>
+        <v>375</v>
       </c>
       <c r="E27" t="s">
-        <v>408</v>
+        <v>376</v>
       </c>
       <c r="F27" t="s">
         <v>14</v>
@@ -4380,10 +4865,10 @@
         <v>81</v>
       </c>
       <c r="I27" s="12" t="s">
-        <v>409</v>
+        <v>377</v>
       </c>
       <c r="J27" s="14" t="s">
-        <v>410</v>
+        <v>378</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.35">
@@ -4394,7 +4879,7 @@
       <c r="E32" s="7"/>
       <c r="F32" s="8"/>
       <c r="G32" s="9" t="s">
-        <v>419</v>
+        <v>387</v>
       </c>
       <c r="H32" s="8"/>
       <c r="I32" s="7"/>
@@ -4484,7 +4969,7 @@
         <v>2</v>
       </c>
       <c r="F38" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G38">
         <v>175</v>
@@ -4499,7 +4984,7 @@
         <v>2</v>
       </c>
       <c r="F40" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G40">
         <v>175</v>
@@ -4515,7 +5000,7 @@
       </c>
       <c r="E42" s="13"/>
       <c r="F42" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G42">
         <v>175</v>
@@ -4545,13 +5030,13 @@
         <v>303</v>
       </c>
       <c r="H44" t="s">
-        <v>420</v>
+        <v>388</v>
       </c>
       <c r="I44" s="12" t="s">
-        <v>421</v>
+        <v>389</v>
       </c>
       <c r="J44" t="s">
-        <v>422</v>
+        <v>390</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.35">
@@ -4559,19 +5044,19 @@
         <v>1000</v>
       </c>
       <c r="F46" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G46">
         <v>175</v>
       </c>
       <c r="H46" t="s">
-        <v>425</v>
+        <v>393</v>
       </c>
       <c r="I46" s="12" t="s">
-        <v>426</v>
+        <v>394</v>
       </c>
       <c r="J46" t="s">
-        <v>427</v>
+        <v>395</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.35">
@@ -4579,19 +5064,19 @@
         <v>1000</v>
       </c>
       <c r="F48" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G48">
         <v>175</v>
       </c>
       <c r="H48" t="s">
-        <v>431</v>
+        <v>399</v>
       </c>
       <c r="I48" s="12" t="s">
-        <v>432</v>
+        <v>400</v>
       </c>
       <c r="J48" t="s">
-        <v>433</v>
+        <v>401</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.35">
@@ -4599,46 +5084,46 @@
         <v>1000</v>
       </c>
       <c r="F50" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G50">
         <v>175</v>
       </c>
       <c r="H50" t="s">
-        <v>428</v>
+        <v>396</v>
       </c>
       <c r="I50" s="12" t="s">
-        <v>429</v>
+        <v>397</v>
       </c>
       <c r="J50" t="s">
-        <v>430</v>
+        <v>398</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A55" s="19" t="s">
-        <v>183</v>
-      </c>
-      <c r="B55" s="19"/>
-      <c r="C55" s="19"/>
-      <c r="D55" s="19"/>
-      <c r="E55" s="19"/>
-      <c r="F55" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="G55" s="20"/>
-      <c r="H55" s="20"/>
-      <c r="I55" s="20"/>
-      <c r="J55" s="20"/>
+      <c r="A55" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="B55" s="21"/>
+      <c r="C55" s="21"/>
+      <c r="D55" s="21"/>
+      <c r="E55" s="21"/>
+      <c r="F55" s="22" t="s">
+        <v>184</v>
+      </c>
+      <c r="G55" s="22"/>
+      <c r="H55" s="22"/>
+      <c r="I55" s="22"/>
+      <c r="J55" s="22"/>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A56" s="8" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D56" s="7" t="s">
         <v>10</v>
@@ -4647,13 +5132,13 @@
         <v>11</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="H56" s="8" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="I56" s="7" t="s">
         <v>10</v>
@@ -4687,10 +5172,10 @@
         <v>137</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>421</v>
+        <v>389</v>
       </c>
       <c r="E58" t="s">
-        <v>422</v>
+        <v>390</v>
       </c>
       <c r="F58" t="s">
         <v>14</v>
@@ -4702,10 +5187,10 @@
         <v>64</v>
       </c>
       <c r="I58" s="12" t="s">
-        <v>423</v>
+        <v>391</v>
       </c>
       <c r="J58" s="14" t="s">
-        <v>424</v>
+        <v>392</v>
       </c>
     </row>
   </sheetData>
@@ -4747,7 +5232,7 @@
       <c r="E1" s="7"/>
       <c r="F1" s="8"/>
       <c r="G1" s="9" t="s">
-        <v>449</v>
+        <v>413</v>
       </c>
       <c r="H1" s="8"/>
       <c r="I1" s="7"/>
@@ -4832,7 +5317,7 @@
         <v>512</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>450</v>
+        <v>414</v>
       </c>
       <c r="D5" s="7"/>
       <c r="E5" s="8"/>
@@ -4840,7 +5325,7 @@
         <v>2</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>451</v>
+        <v>415</v>
       </c>
       <c r="H5" s="8" t="s">
         <v>14</v>
@@ -4852,10 +5337,10 @@
         <v>15</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>452</v>
+        <v>416</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>453</v>
+        <v>417</v>
       </c>
       <c r="M5" s="8"/>
       <c r="N5" s="8"/>
@@ -4884,7 +5369,7 @@
         <v>512</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>460</v>
+        <v>424</v>
       </c>
       <c r="D7" s="7"/>
       <c r="E7" s="8"/>
@@ -4892,22 +5377,22 @@
         <v>2</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>461</v>
+        <v>425</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="I7" s="3">
         <v>175</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>421</v>
+        <v>389</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>462</v>
+        <v>426</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>463</v>
+        <v>427</v>
       </c>
       <c r="M7" s="8"/>
       <c r="N7" s="8"/>
@@ -4923,7 +5408,7 @@
         <v>512</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>455</v>
+        <v>419</v>
       </c>
       <c r="D9" s="7"/>
       <c r="E9" s="8"/>
@@ -4931,22 +5416,22 @@
         <v>2</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>456</v>
+        <v>420</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I9" s="3">
         <v>175</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>457</v>
+        <v>421</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>458</v>
+        <v>422</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>459</v>
+        <v>423</v>
       </c>
       <c r="M9" s="8"/>
       <c r="N9" s="8"/>
@@ -4975,7 +5460,7 @@
         <v>512</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>464</v>
+        <v>428</v>
       </c>
       <c r="D11" s="7"/>
       <c r="E11" s="8"/>
@@ -4983,22 +5468,22 @@
         <v>2</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>466</v>
+        <v>430</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="I11" s="3">
         <v>175</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>467</v>
+        <v>431</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>465</v>
+        <v>429</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>468</v>
+        <v>432</v>
       </c>
       <c r="M11" s="8"/>
       <c r="N11" s="8"/>
@@ -5056,7 +5541,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B16" s="8"/>
       <c r="C16" s="7"/>
@@ -5074,20 +5559,20 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" s="7"/>
-      <c r="B17" s="19" t="s">
-        <v>183</v>
-      </c>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="H17" s="20"/>
-      <c r="I17" s="20"/>
-      <c r="J17" s="20"/>
-      <c r="K17" s="20"/>
+      <c r="B17" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21"/>
+      <c r="G17" s="22" t="s">
+        <v>184</v>
+      </c>
+      <c r="H17" s="22"/>
+      <c r="I17" s="22"/>
+      <c r="J17" s="22"/>
+      <c r="K17" s="22"/>
       <c r="L17" s="8"/>
       <c r="M17" s="8"/>
       <c r="N17" s="8"/>
@@ -5095,13 +5580,13 @@
     <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" s="7"/>
       <c r="B18" s="8" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>10</v>
@@ -5110,13 +5595,13 @@
         <v>11</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="J18" s="7" t="s">
         <v>10</v>
@@ -5142,10 +5627,10 @@
         <v>105</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>452</v>
+        <v>416</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>453</v>
+        <v>417</v>
       </c>
       <c r="G19" s="7" t="s">
         <v>14</v>
@@ -5157,7 +5642,7 @@
         <v>53</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="K19" s="7">
         <v>65340</v>
@@ -5232,10 +5717,10 @@
       <c r="E1" s="7"/>
       <c r="F1" s="8"/>
       <c r="G1" s="9" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="H1" s="16" t="s">
-        <v>454</v>
+        <v>418</v>
       </c>
       <c r="I1" s="7"/>
       <c r="J1" s="8"/>
@@ -5322,22 +5807,22 @@
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>195</v>
+        <v>571</v>
       </c>
       <c r="F5" t="s">
         <v>14</v>
       </c>
       <c r="G5">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="H5" t="s">
-        <v>197</v>
+        <v>170</v>
       </c>
       <c r="I5" t="s">
-        <v>198</v>
+        <v>572</v>
       </c>
       <c r="J5" t="s">
-        <v>199</v>
+        <v>573</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.35">
@@ -5348,22 +5833,22 @@
         <v>2</v>
       </c>
       <c r="E7" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="F7" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G7">
         <v>175</v>
       </c>
       <c r="H7" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="J7" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
@@ -5374,22 +5859,22 @@
         <v>2</v>
       </c>
       <c r="E9" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="F9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G9">
         <v>175</v>
       </c>
       <c r="H9" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="I9" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="J9" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
@@ -5400,27 +5885,27 @@
         <v>2</v>
       </c>
       <c r="E11" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="F11" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G11">
         <v>175</v>
       </c>
       <c r="H11" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="I11" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="J11" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="7"/>
@@ -5435,31 +5920,31 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="7"/>
-      <c r="B15" s="19" t="s">
-        <v>183</v>
-      </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="H15" s="20"/>
-      <c r="I15" s="20"/>
-      <c r="J15" s="20"/>
-      <c r="K15" s="20"/>
+      <c r="B15" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="22" t="s">
+        <v>184</v>
+      </c>
+      <c r="H15" s="22"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="22"/>
+      <c r="K15" s="22"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="7"/>
       <c r="B16" s="8" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>10</v>
@@ -5468,13 +5953,13 @@
         <v>11</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="J16" s="7" t="s">
         <v>10</v>
@@ -5491,16 +5976,16 @@
         <v>14</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>196</v>
+        <v>574</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>200</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>199</v>
+        <v>575</v>
+      </c>
+      <c r="E17" t="s">
+        <v>572</v>
+      </c>
+      <c r="F17" t="s">
+        <v>573</v>
       </c>
       <c r="G17" s="7" t="s">
         <v>14</v>
@@ -5509,21 +5994,21 @@
         <v>126</v>
       </c>
       <c r="I17" s="7">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>201</v>
+        <v>513</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>202</v>
+        <v>576</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="G20" s="9" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>566</v>
+        <v>525</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.35">
@@ -5572,22 +6057,22 @@
         <v>2</v>
       </c>
       <c r="E23" t="s">
-        <v>469</v>
+        <v>577</v>
       </c>
       <c r="F23" t="s">
         <v>14</v>
       </c>
       <c r="G23">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="H23" t="s">
-        <v>471</v>
+        <v>578</v>
       </c>
       <c r="I23" t="s">
-        <v>470</v>
+        <v>579</v>
       </c>
       <c r="J23" t="s">
-        <v>472</v>
+        <v>580</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.35">
@@ -5598,22 +6083,22 @@
         <v>2</v>
       </c>
       <c r="E25" t="s">
-        <v>474</v>
+        <v>433</v>
       </c>
       <c r="F25" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G25">
         <v>175</v>
       </c>
       <c r="H25" t="s">
-        <v>475</v>
+        <v>434</v>
       </c>
       <c r="I25" s="11" t="s">
-        <v>476</v>
+        <v>435</v>
       </c>
       <c r="J25" t="s">
-        <v>477</v>
+        <v>436</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.35">
@@ -5624,22 +6109,22 @@
         <v>2</v>
       </c>
       <c r="E27" t="s">
-        <v>482</v>
+        <v>441</v>
       </c>
       <c r="F27" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G27">
         <v>175</v>
       </c>
       <c r="H27" t="s">
-        <v>483</v>
+        <v>442</v>
       </c>
       <c r="I27" t="s">
-        <v>484</v>
+        <v>443</v>
       </c>
       <c r="J27" t="s">
-        <v>485</v>
+        <v>444</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.35">
@@ -5650,27 +6135,27 @@
         <v>2</v>
       </c>
       <c r="E29" t="s">
-        <v>479</v>
+        <v>438</v>
       </c>
       <c r="F29" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G29">
         <v>175</v>
       </c>
       <c r="H29" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="I29" s="12" t="s">
-        <v>480</v>
+        <v>439</v>
       </c>
       <c r="J29" t="s">
-        <v>481</v>
+        <v>440</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A32" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B32" s="8"/>
       <c r="C32" s="7"/>
@@ -5685,31 +6170,31 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A33" s="7"/>
-      <c r="B33" s="19" t="s">
-        <v>183</v>
-      </c>
-      <c r="C33" s="19"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="H33" s="20"/>
-      <c r="I33" s="20"/>
-      <c r="J33" s="20"/>
-      <c r="K33" s="20"/>
+      <c r="B33" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="21"/>
+      <c r="G33" s="22" t="s">
+        <v>184</v>
+      </c>
+      <c r="H33" s="22"/>
+      <c r="I33" s="22"/>
+      <c r="J33" s="22"/>
+      <c r="K33" s="22"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34" s="7"/>
       <c r="B34" s="8" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E34" s="7" t="s">
         <v>10</v>
@@ -5718,13 +6203,13 @@
         <v>11</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="I34" s="8" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="J34" s="7" t="s">
         <v>10</v>
@@ -5741,39 +6226,39 @@
         <v>14</v>
       </c>
       <c r="C35" s="7">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="D35" s="8">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E35" t="s">
-        <v>470</v>
+        <v>579</v>
       </c>
       <c r="F35" t="s">
-        <v>472</v>
+        <v>580</v>
       </c>
       <c r="G35" s="7" t="s">
         <v>14</v>
       </c>
       <c r="H35" s="8">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="I35" s="7">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>201</v>
+        <v>513</v>
       </c>
       <c r="K35" s="7" t="s">
-        <v>473</v>
+        <v>581</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.35">
       <c r="G38" s="9" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="H38" s="16" t="s">
-        <v>567</v>
+        <v>526</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.35">
@@ -5822,7 +6307,7 @@
         <v>2</v>
       </c>
       <c r="E41" t="s">
-        <v>568</v>
+        <v>582</v>
       </c>
       <c r="F41" t="s">
         <v>14</v>
@@ -5831,13 +6316,13 @@
         <v>291</v>
       </c>
       <c r="H41" t="s">
-        <v>569</v>
+        <v>583</v>
       </c>
       <c r="I41" t="s">
-        <v>570</v>
+        <v>527</v>
       </c>
       <c r="J41" t="s">
-        <v>571</v>
+        <v>528</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.35">
@@ -5848,22 +6333,22 @@
         <v>2</v>
       </c>
       <c r="E43" t="s">
-        <v>574</v>
+        <v>531</v>
       </c>
       <c r="F43" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G43">
         <v>175</v>
       </c>
       <c r="H43" t="s">
-        <v>575</v>
+        <v>532</v>
       </c>
       <c r="I43" s="11" t="s">
-        <v>458</v>
+        <v>422</v>
       </c>
       <c r="J43" t="s">
-        <v>576</v>
+        <v>533</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.35">
@@ -5874,22 +6359,22 @@
         <v>2</v>
       </c>
       <c r="E45" t="s">
-        <v>577</v>
+        <v>534</v>
       </c>
       <c r="F45" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G45">
         <v>175</v>
       </c>
       <c r="H45" t="s">
-        <v>578</v>
+        <v>535</v>
       </c>
       <c r="I45" t="s">
-        <v>579</v>
+        <v>536</v>
       </c>
       <c r="J45" t="s">
-        <v>580</v>
+        <v>537</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.35">
@@ -5900,27 +6385,27 @@
         <v>2</v>
       </c>
       <c r="E47" t="s">
-        <v>581</v>
+        <v>538</v>
       </c>
       <c r="F47" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G47">
         <v>175</v>
       </c>
       <c r="H47" t="s">
-        <v>582</v>
+        <v>539</v>
       </c>
       <c r="I47" s="12" t="s">
-        <v>583</v>
+        <v>540</v>
       </c>
       <c r="J47" t="s">
-        <v>584</v>
+        <v>541</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A50" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B50" s="8"/>
       <c r="C50" s="7"/>
@@ -5935,31 +6420,31 @@
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A51" s="7"/>
-      <c r="B51" s="19" t="s">
-        <v>183</v>
-      </c>
-      <c r="C51" s="19"/>
-      <c r="D51" s="19"/>
-      <c r="E51" s="19"/>
-      <c r="F51" s="19"/>
-      <c r="G51" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="H51" s="20"/>
-      <c r="I51" s="20"/>
-      <c r="J51" s="20"/>
-      <c r="K51" s="20"/>
+      <c r="B51" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="C51" s="21"/>
+      <c r="D51" s="21"/>
+      <c r="E51" s="21"/>
+      <c r="F51" s="21"/>
+      <c r="G51" s="22" t="s">
+        <v>184</v>
+      </c>
+      <c r="H51" s="22"/>
+      <c r="I51" s="22"/>
+      <c r="J51" s="22"/>
+      <c r="K51" s="22"/>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A52" s="7"/>
       <c r="B52" s="8" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E52" s="7" t="s">
         <v>10</v>
@@ -5968,13 +6453,13 @@
         <v>11</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="H52" s="7" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="I52" s="8" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="J52" s="7" t="s">
         <v>10</v>
@@ -5997,10 +6482,10 @@
         <v>92</v>
       </c>
       <c r="E53" t="s">
-        <v>570</v>
+        <v>527</v>
       </c>
       <c r="F53" t="s">
-        <v>571</v>
+        <v>528</v>
       </c>
       <c r="G53" s="7" t="s">
         <v>14</v>
@@ -6012,18 +6497,18 @@
         <v>53</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>572</v>
+        <v>529</v>
       </c>
       <c r="K53" s="7" t="s">
-        <v>573</v>
+        <v>530</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.35">
       <c r="G56" s="9" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="H56" s="16" t="s">
-        <v>585</v>
+        <v>542</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.35">
@@ -6072,22 +6557,22 @@
         <v>2</v>
       </c>
       <c r="E59" t="s">
-        <v>598</v>
+        <v>586</v>
       </c>
       <c r="F59" t="s">
         <v>14</v>
       </c>
       <c r="G59">
-        <v>287</v>
+        <v>300</v>
       </c>
       <c r="H59" t="s">
-        <v>599</v>
+        <v>555</v>
       </c>
       <c r="I59" t="s">
-        <v>600</v>
+        <v>584</v>
       </c>
       <c r="J59" t="s">
-        <v>601</v>
+        <v>585</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.35">
@@ -6098,22 +6583,22 @@
         <v>2</v>
       </c>
       <c r="E61" t="s">
-        <v>586</v>
+        <v>543</v>
       </c>
       <c r="F61" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G61">
         <v>175</v>
       </c>
       <c r="H61" t="s">
-        <v>587</v>
+        <v>544</v>
       </c>
       <c r="I61" s="11" t="s">
-        <v>588</v>
+        <v>545</v>
       </c>
       <c r="J61" t="s">
-        <v>589</v>
+        <v>546</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.35">
@@ -6124,22 +6609,22 @@
         <v>2</v>
       </c>
       <c r="E63" t="s">
-        <v>594</v>
+        <v>551</v>
       </c>
       <c r="F63" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G63">
         <v>175</v>
       </c>
       <c r="H63" t="s">
-        <v>595</v>
+        <v>552</v>
       </c>
       <c r="I63" t="s">
-        <v>596</v>
+        <v>553</v>
       </c>
       <c r="J63" t="s">
-        <v>597</v>
+        <v>554</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.35">
@@ -6150,27 +6635,27 @@
         <v>2</v>
       </c>
       <c r="E65" t="s">
-        <v>590</v>
+        <v>547</v>
       </c>
       <c r="F65" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G65">
         <v>175</v>
       </c>
       <c r="H65" t="s">
-        <v>591</v>
+        <v>548</v>
       </c>
       <c r="I65" s="12" t="s">
-        <v>592</v>
+        <v>549</v>
       </c>
       <c r="J65" t="s">
-        <v>593</v>
+        <v>550</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A68" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B68" s="8"/>
       <c r="C68" s="7"/>
@@ -6185,31 +6670,31 @@
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A69" s="7"/>
-      <c r="B69" s="19" t="s">
-        <v>183</v>
-      </c>
-      <c r="C69" s="19"/>
-      <c r="D69" s="19"/>
-      <c r="E69" s="19"/>
-      <c r="F69" s="19"/>
-      <c r="G69" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="H69" s="20"/>
-      <c r="I69" s="20"/>
-      <c r="J69" s="20"/>
-      <c r="K69" s="20"/>
+      <c r="B69" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="C69" s="21"/>
+      <c r="D69" s="21"/>
+      <c r="E69" s="21"/>
+      <c r="F69" s="21"/>
+      <c r="G69" s="22" t="s">
+        <v>184</v>
+      </c>
+      <c r="H69" s="22"/>
+      <c r="I69" s="22"/>
+      <c r="J69" s="22"/>
+      <c r="K69" s="22"/>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A70" s="7"/>
       <c r="B70" s="8" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E70" s="7" t="s">
         <v>10</v>
@@ -6218,13 +6703,13 @@
         <v>11</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="H70" s="7" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="I70" s="8" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="J70" s="7" t="s">
         <v>10</v>
@@ -6241,39 +6726,39 @@
         <v>14</v>
       </c>
       <c r="C71" s="7">
-        <v>287</v>
+        <v>300</v>
       </c>
       <c r="D71" s="8">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="E71" t="s">
-        <v>600</v>
+        <v>584</v>
       </c>
       <c r="F71" t="s">
-        <v>601</v>
+        <v>585</v>
       </c>
       <c r="G71" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="H71" s="21">
-        <v>122</v>
-      </c>
-      <c r="I71" s="22">
-        <v>40</v>
+      <c r="H71" s="19">
+        <v>128</v>
+      </c>
+      <c r="I71" s="20">
+        <v>41</v>
       </c>
       <c r="J71" s="10" t="s">
-        <v>602</v>
-      </c>
-      <c r="K71" s="22" t="s">
-        <v>603</v>
+        <v>587</v>
+      </c>
+      <c r="K71" s="20" t="s">
+        <v>588</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.35">
       <c r="G94" s="9" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="H94" s="16" t="s">
-        <v>478</v>
+        <v>437</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.35">
@@ -6322,7 +6807,7 @@
         <v>2</v>
       </c>
       <c r="E97" t="s">
-        <v>486</v>
+        <v>445</v>
       </c>
       <c r="F97" t="s">
         <v>14</v>
@@ -6331,13 +6816,13 @@
         <v>291</v>
       </c>
       <c r="H97" t="s">
-        <v>492</v>
+        <v>451</v>
       </c>
       <c r="I97" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
       <c r="J97" t="s">
-        <v>487</v>
+        <v>446</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.35">
@@ -6348,22 +6833,22 @@
         <v>2</v>
       </c>
       <c r="E99" t="s">
-        <v>490</v>
+        <v>449</v>
       </c>
       <c r="F99" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G99">
         <v>175</v>
       </c>
       <c r="H99" t="s">
-        <v>491</v>
+        <v>450</v>
       </c>
       <c r="I99" s="11" t="s">
-        <v>493</v>
+        <v>452</v>
       </c>
       <c r="J99" t="s">
-        <v>494</v>
+        <v>453</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.35">
@@ -6374,22 +6859,22 @@
         <v>2</v>
       </c>
       <c r="E101" t="s">
-        <v>496</v>
+        <v>455</v>
       </c>
       <c r="F101" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G101">
         <v>175</v>
       </c>
       <c r="H101" t="s">
-        <v>497</v>
+        <v>456</v>
       </c>
       <c r="I101" t="s">
-        <v>498</v>
+        <v>457</v>
       </c>
       <c r="J101" t="s">
-        <v>499</v>
+        <v>458</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.35">
@@ -6400,27 +6885,27 @@
         <v>2</v>
       </c>
       <c r="E103" t="s">
-        <v>474</v>
+        <v>433</v>
       </c>
       <c r="F103" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G103">
         <v>175</v>
       </c>
       <c r="H103" t="s">
-        <v>251</v>
+        <v>233</v>
       </c>
       <c r="I103" s="12" t="s">
-        <v>480</v>
+        <v>439</v>
       </c>
       <c r="J103" t="s">
-        <v>495</v>
+        <v>454</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A106" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B106" s="8"/>
       <c r="C106" s="7"/>
@@ -6436,14 +6921,14 @@
     <row r="107" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A107" s="7"/>
       <c r="B107" s="17" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C107" s="17"/>
       <c r="D107" s="17"/>
       <c r="E107" s="17"/>
       <c r="F107" s="17"/>
       <c r="G107" s="18" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H107" s="18"/>
       <c r="I107" s="18"/>
@@ -6453,13 +6938,13 @@
     <row r="108" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A108" s="7"/>
       <c r="B108" s="8" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C108" s="7" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D108" s="8" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E108" s="7" t="s">
         <v>10</v>
@@ -6468,13 +6953,13 @@
         <v>11</v>
       </c>
       <c r="G108" s="8" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="H108" s="7" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="I108" s="8" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="J108" s="7" t="s">
         <v>10</v>
@@ -6497,10 +6982,10 @@
         <v>110</v>
       </c>
       <c r="E109" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
       <c r="F109" t="s">
-        <v>487</v>
+        <v>446</v>
       </c>
       <c r="G109" s="7" t="s">
         <v>14</v>
@@ -6512,18 +6997,18 @@
         <v>38</v>
       </c>
       <c r="J109" s="6" t="s">
-        <v>488</v>
+        <v>447</v>
       </c>
       <c r="K109" s="7" t="s">
-        <v>489</v>
+        <v>448</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.35">
       <c r="G112" s="9" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="H112" s="16" t="s">
-        <v>500</v>
+        <v>459</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.35">
@@ -6572,7 +7057,7 @@
         <v>2</v>
       </c>
       <c r="E115" t="s">
-        <v>501</v>
+        <v>460</v>
       </c>
       <c r="F115" t="s">
         <v>14</v>
@@ -6581,13 +7066,13 @@
         <v>291</v>
       </c>
       <c r="H115" t="s">
-        <v>492</v>
+        <v>451</v>
       </c>
       <c r="I115" t="s">
-        <v>502</v>
+        <v>461</v>
       </c>
       <c r="J115" t="s">
-        <v>503</v>
+        <v>462</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.35">
@@ -6598,22 +7083,22 @@
         <v>2</v>
       </c>
       <c r="E117" t="s">
-        <v>508</v>
+        <v>467</v>
       </c>
       <c r="F117" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G117">
         <v>175</v>
       </c>
       <c r="H117" t="s">
-        <v>509</v>
+        <v>468</v>
       </c>
       <c r="I117" s="11" t="s">
-        <v>510</v>
+        <v>469</v>
       </c>
       <c r="J117" t="s">
-        <v>511</v>
+        <v>470</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.35">
@@ -6624,22 +7109,22 @@
         <v>2</v>
       </c>
       <c r="E119" t="s">
-        <v>512</v>
+        <v>471</v>
       </c>
       <c r="F119" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G119">
         <v>175</v>
       </c>
       <c r="H119" t="s">
-        <v>513</v>
+        <v>472</v>
       </c>
       <c r="I119" s="12" t="s">
-        <v>514</v>
+        <v>473</v>
       </c>
       <c r="J119" t="s">
-        <v>515</v>
+        <v>474</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.35">
@@ -6650,27 +7135,27 @@
         <v>2</v>
       </c>
       <c r="E121" t="s">
-        <v>516</v>
+        <v>475</v>
       </c>
       <c r="F121" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G121">
         <v>175</v>
       </c>
       <c r="H121" t="s">
-        <v>517</v>
+        <v>476</v>
       </c>
       <c r="I121" s="12" t="s">
-        <v>488</v>
+        <v>447</v>
       </c>
       <c r="J121" t="s">
-        <v>518</v>
+        <v>477</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A124" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B124" s="8"/>
       <c r="C124" s="7"/>
@@ -6686,14 +7171,14 @@
     <row r="125" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A125" s="7"/>
       <c r="B125" s="17" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C125" s="17"/>
       <c r="D125" s="17"/>
       <c r="E125" s="17"/>
       <c r="F125" s="17"/>
       <c r="G125" s="18" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H125" s="18"/>
       <c r="I125" s="18"/>
@@ -6703,13 +7188,13 @@
     <row r="126" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A126" s="7"/>
       <c r="B126" s="8" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C126" s="7" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D126" s="8" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E126" s="7" t="s">
         <v>10</v>
@@ -6718,13 +7203,13 @@
         <v>11</v>
       </c>
       <c r="G126" s="8" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="H126" s="7" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="I126" s="8" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="J126" s="7" t="s">
         <v>10</v>
@@ -6747,10 +7232,10 @@
         <v>94</v>
       </c>
       <c r="E127" t="s">
-        <v>502</v>
+        <v>461</v>
       </c>
       <c r="F127" t="s">
-        <v>503</v>
+        <v>462</v>
       </c>
       <c r="G127" s="7" t="s">
         <v>14</v>
@@ -6762,18 +7247,18 @@
         <v>39</v>
       </c>
       <c r="J127" s="6" t="s">
-        <v>504</v>
+        <v>463</v>
       </c>
       <c r="K127" s="7" t="s">
-        <v>505</v>
+        <v>464</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.35">
       <c r="G130" s="9" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="H130" s="16" t="s">
-        <v>506</v>
+        <v>465</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.35">
@@ -6822,7 +7307,7 @@
         <v>2</v>
       </c>
       <c r="E133" t="s">
-        <v>265</v>
+        <v>247</v>
       </c>
       <c r="F133" t="s">
         <v>14</v>
@@ -6831,13 +7316,13 @@
         <v>296</v>
       </c>
       <c r="H133" t="s">
-        <v>519</v>
+        <v>478</v>
       </c>
       <c r="I133" t="s">
-        <v>520</v>
+        <v>479</v>
       </c>
       <c r="J133" t="s">
-        <v>521</v>
+        <v>480</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.35">
@@ -6848,22 +7333,22 @@
         <v>2</v>
       </c>
       <c r="E135" t="s">
-        <v>524</v>
+        <v>483</v>
       </c>
       <c r="F135" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G135">
         <v>175</v>
       </c>
       <c r="H135" t="s">
-        <v>525</v>
+        <v>484</v>
       </c>
       <c r="I135" s="11" t="s">
-        <v>526</v>
+        <v>485</v>
       </c>
       <c r="J135" t="s">
-        <v>527</v>
+        <v>486</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.35">
@@ -6874,22 +7359,22 @@
         <v>2</v>
       </c>
       <c r="E137" t="s">
-        <v>528</v>
+        <v>487</v>
       </c>
       <c r="F137" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G137">
         <v>175</v>
       </c>
       <c r="H137" t="s">
-        <v>530</v>
+        <v>489</v>
       </c>
       <c r="I137" s="12" t="s">
-        <v>529</v>
+        <v>488</v>
       </c>
       <c r="J137" t="s">
-        <v>531</v>
+        <v>490</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.35">
@@ -6900,27 +7385,27 @@
         <v>2</v>
       </c>
       <c r="E139" t="s">
-        <v>532</v>
+        <v>491</v>
       </c>
       <c r="F139" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G139">
         <v>175</v>
       </c>
       <c r="H139" t="s">
-        <v>288</v>
+        <v>268</v>
       </c>
       <c r="I139" s="12" t="s">
-        <v>533</v>
+        <v>492</v>
       </c>
       <c r="J139" t="s">
-        <v>534</v>
+        <v>493</v>
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A142" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B142" s="8"/>
       <c r="C142" s="7"/>
@@ -6936,14 +7421,14 @@
     <row r="143" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A143" s="7"/>
       <c r="B143" s="17" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C143" s="17"/>
       <c r="D143" s="17"/>
       <c r="E143" s="17"/>
       <c r="F143" s="17"/>
       <c r="G143" s="18" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H143" s="18"/>
       <c r="I143" s="18"/>
@@ -6953,13 +7438,13 @@
     <row r="144" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A144" s="7"/>
       <c r="B144" s="8" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C144" s="7" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D144" s="8" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E144" s="7" t="s">
         <v>10</v>
@@ -6968,13 +7453,13 @@
         <v>11</v>
       </c>
       <c r="G144" s="8" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="H144" s="7" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="I144" s="8" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="J144" s="7" t="s">
         <v>10</v>
@@ -6997,10 +7482,10 @@
         <v>94</v>
       </c>
       <c r="E145" t="s">
-        <v>520</v>
+        <v>479</v>
       </c>
       <c r="F145" t="s">
-        <v>521</v>
+        <v>480</v>
       </c>
       <c r="G145" s="7" t="s">
         <v>14</v>
@@ -7012,18 +7497,18 @@
         <v>45</v>
       </c>
       <c r="J145" s="6" t="s">
-        <v>522</v>
+        <v>481</v>
       </c>
       <c r="K145" s="7" t="s">
-        <v>523</v>
+        <v>482</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.35">
       <c r="G148" s="9" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="H148" s="16" t="s">
-        <v>507</v>
+        <v>466</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.35">
@@ -7072,7 +7557,7 @@
         <v>2</v>
       </c>
       <c r="E151" t="s">
-        <v>535</v>
+        <v>494</v>
       </c>
       <c r="F151" t="s">
         <v>14</v>
@@ -7081,13 +7566,13 @@
         <v>289</v>
       </c>
       <c r="H151" t="s">
-        <v>536</v>
+        <v>495</v>
       </c>
       <c r="I151" t="s">
-        <v>537</v>
+        <v>496</v>
       </c>
       <c r="J151" t="s">
-        <v>538</v>
+        <v>497</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.35">
@@ -7098,22 +7583,22 @@
         <v>2</v>
       </c>
       <c r="E153" t="s">
-        <v>541</v>
+        <v>500</v>
       </c>
       <c r="F153" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G153">
         <v>175</v>
       </c>
       <c r="H153" t="s">
-        <v>542</v>
+        <v>501</v>
       </c>
       <c r="I153" s="11" t="s">
-        <v>543</v>
+        <v>502</v>
       </c>
       <c r="J153" t="s">
-        <v>544</v>
+        <v>503</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.35">
@@ -7124,22 +7609,22 @@
         <v>2</v>
       </c>
       <c r="E155" t="s">
-        <v>482</v>
+        <v>441</v>
       </c>
       <c r="F155" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G155">
         <v>175</v>
       </c>
       <c r="H155" t="s">
-        <v>542</v>
+        <v>501</v>
       </c>
       <c r="I155" s="12" t="s">
-        <v>545</v>
+        <v>504</v>
       </c>
       <c r="J155" t="s">
-        <v>546</v>
+        <v>505</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.35">
@@ -7150,27 +7635,27 @@
         <v>2</v>
       </c>
       <c r="E157" s="13" t="s">
-        <v>547</v>
+        <v>506</v>
       </c>
       <c r="F157" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G157">
         <v>175</v>
       </c>
       <c r="H157" t="s">
-        <v>517</v>
+        <v>476</v>
       </c>
       <c r="I157" s="12" t="s">
-        <v>548</v>
+        <v>507</v>
       </c>
       <c r="J157" t="s">
-        <v>549</v>
+        <v>508</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A160" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B160" s="8"/>
       <c r="C160" s="7"/>
@@ -7186,14 +7671,14 @@
     <row r="161" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A161" s="7"/>
       <c r="B161" s="17" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C161" s="17"/>
       <c r="D161" s="17"/>
       <c r="E161" s="17"/>
       <c r="F161" s="17"/>
       <c r="G161" s="18" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H161" s="18"/>
       <c r="I161" s="18"/>
@@ -7203,13 +7688,13 @@
     <row r="162" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A162" s="7"/>
       <c r="B162" s="8" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C162" s="7" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D162" s="8" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E162" s="7" t="s">
         <v>10</v>
@@ -7218,13 +7703,13 @@
         <v>11</v>
       </c>
       <c r="G162" s="8" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="H162" s="7" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="I162" s="8" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="J162" s="7" t="s">
         <v>10</v>
@@ -7247,10 +7732,10 @@
         <v>113</v>
       </c>
       <c r="E163" t="s">
-        <v>537</v>
+        <v>496</v>
       </c>
       <c r="F163" t="s">
-        <v>538</v>
+        <v>497</v>
       </c>
       <c r="G163" s="7" t="s">
         <v>14</v>
@@ -7262,18 +7747,18 @@
         <v>29</v>
       </c>
       <c r="J163" s="6" t="s">
-        <v>539</v>
+        <v>498</v>
       </c>
       <c r="K163" s="7" t="s">
-        <v>540</v>
+        <v>499</v>
       </c>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.35">
       <c r="G166" s="9" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="H166" s="16" t="s">
-        <v>553</v>
+        <v>512</v>
       </c>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.35">
@@ -7322,7 +7807,7 @@
         <v>2</v>
       </c>
       <c r="E169" t="s">
-        <v>550</v>
+        <v>509</v>
       </c>
       <c r="F169" t="s">
         <v>14</v>
@@ -7331,13 +7816,13 @@
         <v>301</v>
       </c>
       <c r="H169" t="s">
-        <v>420</v>
+        <v>388</v>
       </c>
       <c r="I169" t="s">
-        <v>551</v>
+        <v>510</v>
       </c>
       <c r="J169" t="s">
-        <v>552</v>
+        <v>511</v>
       </c>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.35">
@@ -7348,22 +7833,22 @@
         <v>2</v>
       </c>
       <c r="E171" t="s">
-        <v>556</v>
+        <v>515</v>
       </c>
       <c r="F171" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G171">
         <v>175</v>
       </c>
       <c r="H171" t="s">
-        <v>557</v>
+        <v>516</v>
       </c>
       <c r="I171" s="11" t="s">
-        <v>558</v>
+        <v>517</v>
       </c>
       <c r="J171" t="s">
-        <v>559</v>
+        <v>518</v>
       </c>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.35">
@@ -7374,22 +7859,22 @@
         <v>2</v>
       </c>
       <c r="E173" t="s">
-        <v>560</v>
+        <v>519</v>
       </c>
       <c r="F173" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G173">
         <v>175</v>
       </c>
       <c r="H173" t="s">
-        <v>561</v>
+        <v>520</v>
       </c>
       <c r="I173" s="12" t="s">
-        <v>267</v>
+        <v>249</v>
       </c>
       <c r="J173" t="s">
-        <v>562</v>
+        <v>521</v>
       </c>
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.35">
@@ -7400,27 +7885,27 @@
         <v>2</v>
       </c>
       <c r="E175" s="13" t="s">
-        <v>563</v>
+        <v>522</v>
       </c>
       <c r="F175" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G175">
         <v>175</v>
       </c>
       <c r="H175" t="s">
-        <v>564</v>
+        <v>523</v>
       </c>
       <c r="I175" s="12" t="s">
-        <v>522</v>
+        <v>481</v>
       </c>
       <c r="J175" t="s">
-        <v>565</v>
+        <v>524</v>
       </c>
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A178" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B178" s="8"/>
       <c r="C178" s="7"/>
@@ -7436,14 +7921,14 @@
     <row r="179" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A179" s="7"/>
       <c r="B179" s="17" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C179" s="17"/>
       <c r="D179" s="17"/>
       <c r="E179" s="17"/>
       <c r="F179" s="17"/>
       <c r="G179" s="18" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H179" s="18"/>
       <c r="I179" s="18"/>
@@ -7453,13 +7938,13 @@
     <row r="180" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A180" s="7"/>
       <c r="B180" s="8" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C180" s="7" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D180" s="8" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E180" s="7" t="s">
         <v>10</v>
@@ -7468,13 +7953,13 @@
         <v>11</v>
       </c>
       <c r="G180" s="8" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="H180" s="7" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="I180" s="8" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="J180" s="7" t="s">
         <v>10</v>
@@ -7497,10 +7982,10 @@
         <v>83</v>
       </c>
       <c r="E181" t="s">
-        <v>551</v>
+        <v>510</v>
       </c>
       <c r="F181" t="s">
-        <v>552</v>
+        <v>511</v>
       </c>
       <c r="G181" s="7" t="s">
         <v>14</v>
@@ -7512,10 +7997,10 @@
         <v>26</v>
       </c>
       <c r="J181" s="6" t="s">
-        <v>554</v>
+        <v>513</v>
       </c>
       <c r="K181" s="7" t="s">
-        <v>555</v>
+        <v>514</v>
       </c>
     </row>
   </sheetData>
@@ -7535,6 +8020,88 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="3" width="20.81640625" customWidth="1"/>
+    <col min="4" max="4" width="15.1796875" customWidth="1"/>
+    <col min="5" max="5" width="14.08984375" customWidth="1"/>
+    <col min="6" max="6" width="12.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>561</v>
+      </c>
+      <c r="B2" t="s">
+        <v>562</v>
+      </c>
+      <c r="C2" t="s">
+        <v>563</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>557</v>
+      </c>
+      <c r="F2" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>949647</v>
+      </c>
+      <c r="B3">
+        <v>175</v>
+      </c>
+      <c r="C3">
+        <v>49981</v>
+      </c>
+      <c r="D3" t="s">
+        <v>558</v>
+      </c>
+      <c r="E3" t="s">
+        <v>559</v>
+      </c>
+      <c r="F3" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>949647</v>
+      </c>
+      <c r="B4">
+        <v>175</v>
+      </c>
+      <c r="C4">
+        <v>49981</v>
+      </c>
+      <c r="D4" t="s">
+        <v>565</v>
+      </c>
+      <c r="E4" t="s">
+        <v>559</v>
+      </c>
+      <c r="F4" t="s">
+        <v>566</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -7559,7 +8126,7 @@
       <c r="E1" s="7"/>
       <c r="F1" s="8"/>
       <c r="G1" s="9" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="H1" s="8"/>
       <c r="I1" s="7"/>
@@ -7647,22 +8214,22 @@
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="F5" t="s">
         <v>14</v>
       </c>
       <c r="G5">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="H5" t="s">
-        <v>219</v>
+        <v>589</v>
       </c>
       <c r="I5" t="s">
-        <v>220</v>
+        <v>590</v>
       </c>
       <c r="J5" t="s">
-        <v>221</v>
+        <v>591</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.35">
@@ -7673,22 +8240,22 @@
         <v>2</v>
       </c>
       <c r="E7" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="F7" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G7">
         <v>175</v>
       </c>
       <c r="H7" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="J7" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
@@ -7699,22 +8266,22 @@
         <v>2</v>
       </c>
       <c r="E9" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="F9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G9">
         <v>175</v>
       </c>
       <c r="H9" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="I9" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="J9" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
@@ -7725,22 +8292,22 @@
         <v>2</v>
       </c>
       <c r="E11" t="s">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="F11" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G11">
         <v>175</v>
       </c>
       <c r="H11" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="J11" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
@@ -7756,30 +8323,30 @@
       <c r="J12" s="8"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A13" s="19" t="s">
-        <v>183</v>
-      </c>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="G13" s="20"/>
-      <c r="H13" s="20"/>
-      <c r="I13" s="20"/>
-      <c r="J13" s="20"/>
+      <c r="A13" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="22" t="s">
+        <v>184</v>
+      </c>
+      <c r="G13" s="22"/>
+      <c r="H13" s="22"/>
+      <c r="I13" s="22"/>
+      <c r="J13" s="22"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="8" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>10</v>
@@ -7788,13 +8355,13 @@
         <v>11</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="I14" s="7" t="s">
         <v>10</v>
@@ -7808,31 +8375,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="7">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="C15" s="8">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D15" t="s">
-        <v>220</v>
+        <v>590</v>
       </c>
       <c r="E15" t="s">
-        <v>221</v>
+        <v>591</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>14</v>
       </c>
       <c r="G15" s="8">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="H15" s="7">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>57</v>
+        <v>485</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>222</v>
+        <v>592</v>
       </c>
     </row>
   </sheetData>
@@ -7844,7 +8411,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N26"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -7871,7 +8438,7 @@
       <c r="E1" s="7"/>
       <c r="F1" s="8"/>
       <c r="G1" s="9" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="H1" s="8"/>
       <c r="I1" s="7"/>
@@ -7959,7 +8526,7 @@
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>255</v>
+        <v>237</v>
       </c>
       <c r="F5" t="s">
         <v>14</v>
@@ -7968,13 +8535,13 @@
         <v>307</v>
       </c>
       <c r="H5" t="s">
-        <v>256</v>
+        <v>238</v>
       </c>
       <c r="I5" t="s">
-        <v>261</v>
+        <v>243</v>
       </c>
       <c r="J5" t="s">
-        <v>262</v>
+        <v>244</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.35">
@@ -7985,22 +8552,22 @@
         <v>2</v>
       </c>
       <c r="E7" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
       <c r="F7" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G7">
         <v>175</v>
       </c>
       <c r="H7" t="s">
-        <v>258</v>
+        <v>240</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="J7" t="s">
-        <v>260</v>
+        <v>242</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
@@ -8011,22 +8578,22 @@
         <v>2</v>
       </c>
       <c r="E9" t="s">
-        <v>265</v>
+        <v>247</v>
       </c>
       <c r="F9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G9">
         <v>175</v>
       </c>
       <c r="H9" t="s">
-        <v>266</v>
+        <v>248</v>
       </c>
       <c r="I9" t="s">
-        <v>267</v>
+        <v>249</v>
       </c>
       <c r="J9" t="s">
-        <v>268</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
@@ -8037,22 +8604,22 @@
         <v>2</v>
       </c>
       <c r="E11" t="s">
-        <v>269</v>
+        <v>251</v>
       </c>
       <c r="F11" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G11">
         <v>175</v>
       </c>
       <c r="H11" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>271</v>
+        <v>253</v>
       </c>
       <c r="J11" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
@@ -8082,13 +8649,13 @@
         <v>2</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>393</v>
+        <v>361</v>
       </c>
       <c r="I13" s="15" t="s">
-        <v>394</v>
+        <v>362</v>
       </c>
       <c r="J13" s="15" t="s">
-        <v>395</v>
+        <v>363</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
@@ -8096,19 +8663,19 @@
         <v>1000</v>
       </c>
       <c r="F15" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G15">
         <v>175</v>
       </c>
       <c r="H15" t="s">
-        <v>396</v>
+        <v>364</v>
       </c>
       <c r="I15" s="11" t="s">
-        <v>397</v>
+        <v>365</v>
       </c>
       <c r="J15" t="s">
-        <v>398</v>
+        <v>366</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.35">
@@ -8116,19 +8683,19 @@
         <v>1000</v>
       </c>
       <c r="F17" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G17">
         <v>175</v>
       </c>
       <c r="H17" t="s">
-        <v>399</v>
+        <v>367</v>
       </c>
       <c r="I17" s="12" t="s">
-        <v>400</v>
+        <v>368</v>
       </c>
       <c r="J17" t="s">
-        <v>401</v>
+        <v>369</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.35">
@@ -8136,46 +8703,46 @@
         <v>1000</v>
       </c>
       <c r="F19" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G19">
         <v>175</v>
       </c>
       <c r="H19" t="s">
-        <v>402</v>
+        <v>370</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>403</v>
+        <v>371</v>
       </c>
       <c r="J19" t="s">
-        <v>404</v>
+        <v>372</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A23" s="19" t="s">
-        <v>183</v>
-      </c>
-      <c r="B23" s="19"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="G23" s="20"/>
-      <c r="H23" s="20"/>
-      <c r="I23" s="20"/>
-      <c r="J23" s="20"/>
+      <c r="A23" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="B23" s="21"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="22" t="s">
+        <v>184</v>
+      </c>
+      <c r="G23" s="22"/>
+      <c r="H23" s="22"/>
+      <c r="I23" s="22"/>
+      <c r="J23" s="22"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" s="8" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D24" s="7" t="s">
         <v>10</v>
@@ -8184,13 +8751,13 @@
         <v>11</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="I24" s="7" t="s">
         <v>10</v>
@@ -8210,10 +8777,10 @@
         <v>84</v>
       </c>
       <c r="D25" t="s">
-        <v>261</v>
+        <v>243</v>
       </c>
       <c r="E25" t="s">
-        <v>262</v>
+        <v>244</v>
       </c>
       <c r="F25" s="7" t="s">
         <v>14</v>
@@ -8225,10 +8792,10 @@
         <v>37</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>263</v>
+        <v>245</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>264</v>
+        <v>246</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.35">
@@ -8242,10 +8809,10 @@
         <v>0</v>
       </c>
       <c r="D26" t="s">
-        <v>394</v>
+        <v>362</v>
       </c>
       <c r="E26" t="s">
-        <v>395</v>
+        <v>363</v>
       </c>
       <c r="F26" s="8"/>
     </row>
@@ -8259,7 +8826,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L31"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -8285,7 +8852,7 @@
       <c r="E1" s="7"/>
       <c r="F1" s="8"/>
       <c r="G1" s="9" t="s">
-        <v>273</v>
+        <v>255</v>
       </c>
       <c r="H1" s="8"/>
       <c r="I1" s="7"/>
@@ -8364,22 +8931,22 @@
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>279</v>
+        <v>259</v>
       </c>
       <c r="F5" t="s">
         <v>14</v>
       </c>
       <c r="G5">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="H5" t="s">
-        <v>274</v>
+        <v>593</v>
       </c>
       <c r="I5" t="s">
-        <v>275</v>
+        <v>594</v>
       </c>
       <c r="J5" t="s">
-        <v>276</v>
+        <v>595</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
@@ -8390,22 +8957,22 @@
         <v>2</v>
       </c>
       <c r="E7" t="s">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="F7" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G7">
         <v>175</v>
       </c>
       <c r="H7" t="s">
-        <v>281</v>
+        <v>261</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>282</v>
+        <v>262</v>
       </c>
       <c r="J7" t="s">
-        <v>283</v>
+        <v>263</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.35">
@@ -8416,22 +8983,22 @@
         <v>2</v>
       </c>
       <c r="E9" t="s">
-        <v>284</v>
+        <v>264</v>
       </c>
       <c r="F9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G9">
         <v>175</v>
       </c>
       <c r="H9" t="s">
-        <v>285</v>
+        <v>265</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="J9" t="s">
-        <v>286</v>
+        <v>266</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
@@ -8442,22 +9009,22 @@
         <v>2</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="F11" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G11">
         <v>175</v>
       </c>
       <c r="H11" t="s">
-        <v>288</v>
+        <v>268</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>289</v>
+        <v>269</v>
       </c>
       <c r="J11" t="s">
-        <v>290</v>
+        <v>270</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
@@ -8473,23 +9040,27 @@
       <c r="J12" s="8"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A13">
-        <v>1000</v>
-      </c>
-      <c r="F13" t="s">
+      <c r="A13" s="26">
+        <v>1000</v>
+      </c>
+      <c r="B13" s="26"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="26">
         <v>217</v>
       </c>
-      <c r="H13" t="s">
-        <v>379</v>
-      </c>
-      <c r="I13" s="12" t="s">
-        <v>383</v>
-      </c>
-      <c r="J13" t="s">
-        <v>384</v>
+      <c r="H13" s="26" t="s">
+        <v>347</v>
+      </c>
+      <c r="I13" s="27" t="s">
+        <v>351</v>
+      </c>
+      <c r="J13" s="26" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.35">
@@ -8497,19 +9068,19 @@
         <v>1000</v>
       </c>
       <c r="F15" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G15">
         <v>175</v>
       </c>
       <c r="H15" t="s">
-        <v>380</v>
+        <v>348</v>
       </c>
       <c r="I15" s="11" t="s">
-        <v>381</v>
+        <v>349</v>
       </c>
       <c r="J15" t="s">
-        <v>382</v>
+        <v>350</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.35">
@@ -8517,19 +9088,19 @@
         <v>1000</v>
       </c>
       <c r="F17" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G17">
         <v>175</v>
       </c>
       <c r="H17" s="14" t="s">
-        <v>389</v>
+        <v>357</v>
       </c>
       <c r="I17" s="12" t="s">
-        <v>387</v>
+        <v>355</v>
       </c>
       <c r="J17" t="s">
-        <v>388</v>
+        <v>356</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.35">
@@ -8538,46 +9109,46 @@
       </c>
       <c r="E19" s="13"/>
       <c r="F19" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G19">
         <v>175</v>
       </c>
       <c r="H19" t="s">
-        <v>390</v>
+        <v>358</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>391</v>
+        <v>359</v>
       </c>
       <c r="J19" t="s">
-        <v>392</v>
+        <v>360</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A28" s="19" t="s">
-        <v>183</v>
-      </c>
-      <c r="B28" s="19"/>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="G28" s="20"/>
-      <c r="H28" s="20"/>
-      <c r="I28" s="20"/>
-      <c r="J28" s="20"/>
+      <c r="A28" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="22" t="s">
+        <v>184</v>
+      </c>
+      <c r="G28" s="22"/>
+      <c r="H28" s="22"/>
+      <c r="I28" s="22"/>
+      <c r="J28" s="22"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" s="8" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D29" s="7" t="s">
         <v>10</v>
@@ -8586,13 +9157,13 @@
         <v>11</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="I29" s="7" t="s">
         <v>10</v>
@@ -8606,31 +9177,31 @@
         <v>14</v>
       </c>
       <c r="B30" s="7">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="C30" s="8">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D30" t="s">
-        <v>275</v>
+        <v>257</v>
       </c>
       <c r="E30" t="s">
-        <v>276</v>
+        <v>258</v>
       </c>
       <c r="F30" s="7" t="s">
         <v>14</v>
       </c>
       <c r="G30" s="8">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="H30" s="7">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>277</v>
+        <v>596</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>278</v>
+        <v>597</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.35">
@@ -8644,10 +9215,10 @@
         <v>266</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>383</v>
+        <v>351</v>
       </c>
       <c r="E31" t="s">
-        <v>384</v>
+        <v>352</v>
       </c>
       <c r="F31" s="8" t="s">
         <v>14</v>
@@ -8659,10 +9230,10 @@
         <v>77</v>
       </c>
       <c r="I31" s="12" t="s">
-        <v>385</v>
+        <v>353</v>
       </c>
       <c r="J31" t="s">
-        <v>386</v>
+        <v>354</v>
       </c>
     </row>
   </sheetData>
@@ -8675,7 +9246,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L28"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -8701,7 +9272,7 @@
       <c r="E1" s="7"/>
       <c r="F1" s="8"/>
       <c r="G1" s="9" t="s">
-        <v>291</v>
+        <v>271</v>
       </c>
       <c r="H1" s="8"/>
       <c r="I1" s="7"/>
@@ -8780,22 +9351,22 @@
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>292</v>
+        <v>272</v>
       </c>
       <c r="F5" t="s">
         <v>14</v>
       </c>
       <c r="G5">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="H5" t="s">
-        <v>293</v>
+        <v>421</v>
       </c>
       <c r="I5" t="s">
-        <v>296</v>
+        <v>598</v>
       </c>
       <c r="J5" t="s">
-        <v>297</v>
+        <v>599</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
@@ -8806,22 +9377,22 @@
         <v>2</v>
       </c>
       <c r="E7" t="s">
-        <v>294</v>
+        <v>273</v>
       </c>
       <c r="F7" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G7">
         <v>175</v>
       </c>
       <c r="H7" t="s">
-        <v>295</v>
+        <v>274</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="J7" t="s">
-        <v>299</v>
+        <v>275</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.35">
@@ -8832,22 +9403,22 @@
         <v>2</v>
       </c>
       <c r="E9" t="s">
-        <v>301</v>
+        <v>277</v>
       </c>
       <c r="F9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G9">
         <v>175</v>
       </c>
       <c r="H9" t="s">
-        <v>302</v>
+        <v>278</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>303</v>
+        <v>279</v>
       </c>
       <c r="J9" t="s">
-        <v>304</v>
+        <v>280</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
@@ -8858,22 +9429,22 @@
         <v>2</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>305</v>
+        <v>281</v>
       </c>
       <c r="F11" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G11">
         <v>175</v>
       </c>
       <c r="H11" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>306</v>
+        <v>282</v>
       </c>
       <c r="J11" t="s">
-        <v>307</v>
+        <v>283</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
@@ -8889,23 +9460,27 @@
       <c r="J12" s="8"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A13">
-        <v>1000</v>
-      </c>
-      <c r="F13" t="s">
+      <c r="A13" s="26">
+        <v>1000</v>
+      </c>
+      <c r="B13" s="26"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="26">
         <v>228</v>
       </c>
-      <c r="H13" t="s">
-        <v>365</v>
-      </c>
-      <c r="I13" s="12" t="s">
-        <v>366</v>
-      </c>
-      <c r="J13" t="s">
-        <v>367</v>
+      <c r="H13" s="26" t="s">
+        <v>333</v>
+      </c>
+      <c r="I13" s="27" t="s">
+        <v>334</v>
+      </c>
+      <c r="J13" s="26" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.35">
@@ -8913,19 +9488,19 @@
         <v>1000</v>
       </c>
       <c r="F15" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G15">
         <v>175</v>
       </c>
       <c r="H15" t="s">
-        <v>370</v>
+        <v>338</v>
       </c>
       <c r="I15" s="11" t="s">
-        <v>371</v>
+        <v>339</v>
       </c>
       <c r="J15" t="s">
-        <v>372</v>
+        <v>340</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.35">
@@ -8933,19 +9508,19 @@
         <v>1000</v>
       </c>
       <c r="F17" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G17">
         <v>175</v>
       </c>
       <c r="H17" t="s">
-        <v>373</v>
+        <v>341</v>
       </c>
       <c r="I17" s="12" t="s">
-        <v>375</v>
+        <v>343</v>
       </c>
       <c r="J17" t="s">
-        <v>376</v>
+        <v>344</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.35">
@@ -8954,46 +9529,46 @@
       </c>
       <c r="E19" s="13"/>
       <c r="F19" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G19">
         <v>175</v>
       </c>
       <c r="H19" t="s">
-        <v>374</v>
+        <v>342</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>377</v>
+        <v>345</v>
       </c>
       <c r="J19" t="s">
-        <v>378</v>
+        <v>346</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A25" s="19" t="s">
-        <v>183</v>
-      </c>
-      <c r="B25" s="19"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="G25" s="20"/>
-      <c r="H25" s="20"/>
-      <c r="I25" s="20"/>
-      <c r="J25" s="20"/>
+      <c r="A25" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="22" t="s">
+        <v>184</v>
+      </c>
+      <c r="G25" s="22"/>
+      <c r="H25" s="22"/>
+      <c r="I25" s="22"/>
+      <c r="J25" s="22"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" s="8" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>10</v>
@@ -9002,13 +9577,13 @@
         <v>11</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="I26" s="7" t="s">
         <v>10</v>
@@ -9022,31 +9597,31 @@
         <v>14</v>
       </c>
       <c r="B27" s="7">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C27" s="8">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="D27" t="s">
-        <v>296</v>
+        <v>598</v>
       </c>
       <c r="E27" t="s">
-        <v>297</v>
+        <v>599</v>
       </c>
       <c r="F27" s="7" t="s">
         <v>14</v>
       </c>
       <c r="G27" s="8">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H27" s="7">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>298</v>
+        <v>600</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.35">
@@ -9060,10 +9635,10 @@
         <v>285</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>366</v>
+        <v>334</v>
       </c>
       <c r="E28" t="s">
-        <v>367</v>
+        <v>335</v>
       </c>
       <c r="F28" t="s">
         <v>14</v>
@@ -9075,10 +9650,10 @@
         <v>79</v>
       </c>
       <c r="I28" s="12" t="s">
-        <v>368</v>
+        <v>336</v>
       </c>
       <c r="J28" t="s">
-        <v>369</v>
+        <v>337</v>
       </c>
     </row>
   </sheetData>
@@ -9090,7 +9665,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L28"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -9116,7 +9691,7 @@
       <c r="E1" s="7"/>
       <c r="F1" s="8"/>
       <c r="G1" s="9" t="s">
-        <v>300</v>
+        <v>276</v>
       </c>
       <c r="H1" s="8"/>
       <c r="I1" s="7"/>
@@ -9195,22 +9770,22 @@
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="F5" t="s">
         <v>14</v>
       </c>
       <c r="G5">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H5" t="s">
-        <v>309</v>
+        <v>601</v>
       </c>
       <c r="I5" t="s">
-        <v>310</v>
+        <v>602</v>
       </c>
       <c r="J5" t="s">
-        <v>311</v>
+        <v>603</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
@@ -9221,22 +9796,22 @@
         <v>2</v>
       </c>
       <c r="E7" t="s">
-        <v>314</v>
+        <v>286</v>
       </c>
       <c r="F7" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G7">
         <v>175</v>
       </c>
       <c r="H7" t="s">
-        <v>315</v>
+        <v>287</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="J7" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.35">
@@ -9247,22 +9822,22 @@
         <v>2</v>
       </c>
       <c r="E9" t="s">
-        <v>318</v>
+        <v>290</v>
       </c>
       <c r="F9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G9">
         <v>175</v>
       </c>
       <c r="H9" t="s">
-        <v>319</v>
+        <v>291</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>317</v>
+        <v>289</v>
       </c>
       <c r="J9" t="s">
-        <v>320</v>
+        <v>292</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
@@ -9273,22 +9848,22 @@
         <v>2</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>321</v>
+        <v>293</v>
       </c>
       <c r="F11" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G11">
         <v>175</v>
       </c>
       <c r="H11" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>322</v>
+        <v>294</v>
       </c>
       <c r="J11" t="s">
-        <v>323</v>
+        <v>295</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
@@ -9304,23 +9879,27 @@
       <c r="J12" s="8"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A13">
-        <v>1000</v>
-      </c>
-      <c r="F13" t="s">
+      <c r="A13" s="26">
+        <v>1000</v>
+      </c>
+      <c r="B13" s="26"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="26">
         <v>240</v>
       </c>
-      <c r="H13" t="s">
-        <v>351</v>
-      </c>
-      <c r="I13" s="12" t="s">
-        <v>353</v>
-      </c>
-      <c r="J13" s="14" t="s">
-        <v>357</v>
+      <c r="H13" s="26" t="s">
+        <v>319</v>
+      </c>
+      <c r="I13" s="27" t="s">
+        <v>321</v>
+      </c>
+      <c r="J13" s="28" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.35">
@@ -9328,19 +9907,19 @@
         <v>1000</v>
       </c>
       <c r="F15" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G15">
         <v>175</v>
       </c>
       <c r="H15" t="s">
-        <v>352</v>
+        <v>320</v>
       </c>
       <c r="I15" s="11" t="s">
-        <v>356</v>
+        <v>324</v>
       </c>
       <c r="J15" t="s">
-        <v>358</v>
+        <v>326</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.35">
@@ -9348,19 +9927,19 @@
         <v>1000</v>
       </c>
       <c r="F17" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G17">
         <v>175</v>
       </c>
       <c r="H17" t="s">
-        <v>359</v>
+        <v>327</v>
       </c>
       <c r="I17" s="12" t="s">
-        <v>360</v>
+        <v>328</v>
       </c>
       <c r="J17" t="s">
-        <v>361</v>
+        <v>329</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.35">
@@ -9369,46 +9948,46 @@
       </c>
       <c r="E19" s="13"/>
       <c r="F19" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G19">
         <v>175</v>
       </c>
       <c r="H19" t="s">
-        <v>362</v>
+        <v>330</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>363</v>
+        <v>331</v>
       </c>
       <c r="J19" t="s">
-        <v>364</v>
+        <v>332</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A25" s="19" t="s">
-        <v>183</v>
-      </c>
-      <c r="B25" s="19"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="G25" s="20"/>
-      <c r="H25" s="20"/>
-      <c r="I25" s="20"/>
-      <c r="J25" s="20"/>
+      <c r="A25" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="22" t="s">
+        <v>184</v>
+      </c>
+      <c r="G25" s="22"/>
+      <c r="H25" s="22"/>
+      <c r="I25" s="22"/>
+      <c r="J25" s="22"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" s="8" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>10</v>
@@ -9417,13 +9996,13 @@
         <v>11</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="I26" s="7" t="s">
         <v>10</v>
@@ -9437,16 +10016,16 @@
         <v>14</v>
       </c>
       <c r="B27" s="7">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C27" s="8">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D27" t="s">
-        <v>310</v>
+        <v>602</v>
       </c>
       <c r="E27" t="s">
-        <v>311</v>
+        <v>603</v>
       </c>
       <c r="F27" s="7" t="s">
         <v>14</v>
@@ -9455,13 +10034,13 @@
         <v>118</v>
       </c>
       <c r="H27" s="7">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>312</v>
+        <v>604</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>313</v>
+        <v>605</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.35">
@@ -9475,7 +10054,7 @@
         <v>252</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>353</v>
+        <v>321</v>
       </c>
       <c r="E28" s="14">
         <v>246380</v>
@@ -9490,10 +10069,10 @@
         <v>84</v>
       </c>
       <c r="I28" s="12" t="s">
-        <v>354</v>
+        <v>322</v>
       </c>
       <c r="J28" t="s">
-        <v>355</v>
+        <v>323</v>
       </c>
     </row>
   </sheetData>
@@ -9503,418 +10082,4 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L33"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="2" width="14.08984375" customWidth="1"/>
-    <col min="3" max="3" width="13.36328125" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" customWidth="1"/>
-    <col min="5" max="5" width="12.81640625" customWidth="1"/>
-    <col min="6" max="6" width="17.36328125" customWidth="1"/>
-    <col min="7" max="7" width="14.6328125" customWidth="1"/>
-    <col min="8" max="8" width="14.54296875" customWidth="1"/>
-    <col min="9" max="9" width="14.08984375" customWidth="1"/>
-    <col min="10" max="10" width="16.08984375" customWidth="1"/>
-    <col min="11" max="11" width="43.1796875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A1" s="7"/>
-      <c r="B1" s="8"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="9" t="s">
-        <v>324</v>
-      </c>
-      <c r="H1" s="8"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" s="7"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3" s="7"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A4" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="J4" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="K4" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="L4" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A5">
-        <v>1000</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5" t="s">
-        <v>325</v>
-      </c>
-      <c r="F5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5">
-        <v>289</v>
-      </c>
-      <c r="H5" t="s">
-        <v>326</v>
-      </c>
-      <c r="I5" t="s">
-        <v>329</v>
-      </c>
-      <c r="J5" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A7">
-        <v>1000</v>
-      </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-      <c r="E7" t="s">
-        <v>327</v>
-      </c>
-      <c r="F7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G7">
-        <v>175</v>
-      </c>
-      <c r="H7" t="s">
-        <v>328</v>
-      </c>
-      <c r="I7" s="11" t="s">
-        <v>332</v>
-      </c>
-      <c r="J7" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A9">
-        <v>1000</v>
-      </c>
-      <c r="D9">
-        <v>2</v>
-      </c>
-      <c r="E9" t="s">
-        <v>334</v>
-      </c>
-      <c r="F9" t="s">
-        <v>47</v>
-      </c>
-      <c r="G9">
-        <v>175</v>
-      </c>
-      <c r="H9" t="s">
-        <v>335</v>
-      </c>
-      <c r="I9" s="12" t="s">
-        <v>336</v>
-      </c>
-      <c r="J9" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A11">
-        <v>1000</v>
-      </c>
-      <c r="D11">
-        <v>2</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>338</v>
-      </c>
-      <c r="F11" t="s">
-        <v>25</v>
-      </c>
-      <c r="G11">
-        <v>175</v>
-      </c>
-      <c r="H11" t="s">
-        <v>251</v>
-      </c>
-      <c r="I11" s="12" t="s">
-        <v>233</v>
-      </c>
-      <c r="J11" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A12" s="8"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A13">
-        <v>1000</v>
-      </c>
-      <c r="F13" t="s">
-        <v>14</v>
-      </c>
-      <c r="G13">
-        <v>245</v>
-      </c>
-      <c r="H13" t="s">
-        <v>274</v>
-      </c>
-      <c r="I13" s="12" t="s">
-        <v>343</v>
-      </c>
-      <c r="J13" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A15">
-        <v>1000</v>
-      </c>
-      <c r="F15" t="s">
-        <v>36</v>
-      </c>
-      <c r="G15">
-        <v>175</v>
-      </c>
-      <c r="H15" t="s">
-        <v>340</v>
-      </c>
-      <c r="I15" s="12" t="s">
-        <v>341</v>
-      </c>
-      <c r="J15" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A17">
-        <v>1000</v>
-      </c>
-      <c r="F17" t="s">
-        <v>47</v>
-      </c>
-      <c r="G17">
-        <v>175</v>
-      </c>
-      <c r="H17" t="s">
-        <v>346</v>
-      </c>
-      <c r="I17" s="12" t="s">
-        <v>347</v>
-      </c>
-      <c r="J17" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A19">
-        <v>1000</v>
-      </c>
-      <c r="F19" t="s">
-        <v>25</v>
-      </c>
-      <c r="G19">
-        <v>175</v>
-      </c>
-      <c r="H19" t="s">
-        <v>178</v>
-      </c>
-      <c r="I19" s="12" t="s">
-        <v>349</v>
-      </c>
-      <c r="J19" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A30" s="19" t="s">
-        <v>183</v>
-      </c>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="G30" s="20"/>
-      <c r="H30" s="20"/>
-      <c r="I30" s="20"/>
-      <c r="J30" s="20"/>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A31" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F31" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="G31" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="H31" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="I31" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="J31" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A32" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B32" s="7">
-        <v>289</v>
-      </c>
-      <c r="C32" s="8">
-        <v>97</v>
-      </c>
-      <c r="D32" t="s">
-        <v>329</v>
-      </c>
-      <c r="E32" t="s">
-        <v>330</v>
-      </c>
-      <c r="F32" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G32" s="8">
-        <v>117</v>
-      </c>
-      <c r="H32" s="7">
-        <v>35</v>
-      </c>
-      <c r="I32" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="J32" s="7" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>14</v>
-      </c>
-      <c r="B33">
-        <v>245</v>
-      </c>
-      <c r="C33">
-        <v>275</v>
-      </c>
-      <c r="D33" s="12" t="s">
-        <v>343</v>
-      </c>
-      <c r="E33" t="s">
-        <v>344</v>
-      </c>
-      <c r="F33" t="s">
-        <v>14</v>
-      </c>
-      <c r="G33">
-        <v>143</v>
-      </c>
-      <c r="H33">
-        <v>91</v>
-      </c>
-      <c r="I33" s="12" t="s">
-        <v>345</v>
-      </c>
-      <c r="J33" s="14">
-        <v>76609</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A30:E30"/>
-    <mergeCell ref="F30:J30"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>
--- a/Experiments/DBCV_Conclu.xlsx
+++ b/Experiments/DBCV_Conclu.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17850" activeTab="10"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17850" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1376" uniqueCount="614">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1378" uniqueCount="616">
   <si>
     <t>Datapoints</t>
   </si>
@@ -1880,6 +1880,12 @@
   </si>
   <si>
     <t>116.512 secs</t>
+  </si>
+  <si>
+    <t>kmedoids</t>
+  </si>
+  <si>
+    <t>0.134</t>
   </si>
 </sst>
 </file>
@@ -2008,12 +2014,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="3" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -2022,6 +2022,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2434,36 +2440,36 @@
       <c r="N5" s="2"/>
     </row>
     <row r="6" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="23">
-        <v>1000</v>
-      </c>
-      <c r="B6" s="23">
+      <c r="A6" s="21">
+        <v>1000</v>
+      </c>
+      <c r="B6" s="21">
         <v>512</v>
       </c>
-      <c r="C6" s="24" t="s">
+      <c r="C6" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="23">
+      <c r="D6" s="21">
         <v>154</v>
       </c>
-      <c r="E6" s="24" t="s">
+      <c r="E6" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="25"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="24" t="s">
+      <c r="F6" s="23"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="I6" s="23">
+      <c r="I6" s="21">
         <v>169</v>
       </c>
-      <c r="J6" s="24" t="s">
+      <c r="J6" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="K6" s="24" t="s">
+      <c r="K6" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="L6" s="24" t="s">
+      <c r="L6" s="22" t="s">
         <v>21</v>
       </c>
       <c r="M6" s="2"/>
@@ -2703,32 +2709,32 @@
       <c r="N13" s="2"/>
     </row>
     <row r="14" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="25">
-        <v>1000</v>
-      </c>
-      <c r="B14" s="25"/>
-      <c r="C14" s="24"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="25">
-        <v>2</v>
-      </c>
-      <c r="G14" s="24" t="s">
+      <c r="A14" s="23">
+        <v>1000</v>
+      </c>
+      <c r="B14" s="23"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="23">
+        <v>2</v>
+      </c>
+      <c r="G14" s="22" t="s">
         <v>221</v>
       </c>
-      <c r="H14" s="24" t="s">
+      <c r="H14" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="I14" s="25">
+      <c r="I14" s="23">
         <v>314</v>
       </c>
-      <c r="J14" s="24" t="s">
+      <c r="J14" s="22" t="s">
         <v>222</v>
       </c>
-      <c r="K14" s="24" t="s">
+      <c r="K14" s="22" t="s">
         <v>223</v>
       </c>
-      <c r="L14" s="24" t="s">
+      <c r="L14" s="22" t="s">
         <v>224</v>
       </c>
     </row>
@@ -2857,20 +2863,20 @@
       <c r="G21" s="8"/>
     </row>
     <row r="22" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="21" t="s">
+      <c r="B22" s="27" t="s">
         <v>180</v>
       </c>
-      <c r="C22" s="21"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="22" t="s">
+      <c r="C22" s="27"/>
+      <c r="D22" s="27"/>
+      <c r="E22" s="27"/>
+      <c r="F22" s="27"/>
+      <c r="G22" s="28" t="s">
         <v>184</v>
       </c>
-      <c r="H22" s="22"/>
-      <c r="I22" s="22"/>
-      <c r="J22" s="22"/>
-      <c r="K22" s="22"/>
+      <c r="H22" s="28"/>
+      <c r="I22" s="28"/>
+      <c r="J22" s="28"/>
+      <c r="K22" s="28"/>
     </row>
     <row r="23" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="8" t="s">
@@ -3642,20 +3648,20 @@
       <c r="N48" s="2"/>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B49" s="21" t="s">
+      <c r="B49" s="27" t="s">
         <v>180</v>
       </c>
-      <c r="C49" s="21"/>
-      <c r="D49" s="21"/>
-      <c r="E49" s="21"/>
-      <c r="F49" s="21"/>
-      <c r="G49" s="22" t="s">
+      <c r="C49" s="27"/>
+      <c r="D49" s="27"/>
+      <c r="E49" s="27"/>
+      <c r="F49" s="27"/>
+      <c r="G49" s="28" t="s">
         <v>184</v>
       </c>
-      <c r="H49" s="22"/>
-      <c r="I49" s="22"/>
-      <c r="J49" s="22"/>
-      <c r="K49" s="22"/>
+      <c r="H49" s="28"/>
+      <c r="I49" s="28"/>
+      <c r="J49" s="28"/>
+      <c r="K49" s="28"/>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B50" s="8" t="s">
@@ -4257,26 +4263,26 @@
       <c r="J12" s="8"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A13" s="26">
-        <v>1000</v>
-      </c>
-      <c r="B13" s="26"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="26" t="s">
+      <c r="A13" s="24">
+        <v>1000</v>
+      </c>
+      <c r="B13" s="24"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="G13" s="26">
+      <c r="G13" s="24">
         <v>245</v>
       </c>
-      <c r="H13" s="26" t="s">
+      <c r="H13" s="24" t="s">
         <v>256</v>
       </c>
-      <c r="I13" s="27" t="s">
+      <c r="I13" s="25" t="s">
         <v>311</v>
       </c>
-      <c r="J13" s="26" t="s">
+      <c r="J13" s="24" t="s">
         <v>312</v>
       </c>
     </row>
@@ -4341,20 +4347,20 @@
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A30" s="21" t="s">
+      <c r="A30" s="27" t="s">
         <v>180</v>
       </c>
-      <c r="B30" s="21"/>
-      <c r="C30" s="21"/>
-      <c r="D30" s="21"/>
-      <c r="E30" s="21"/>
-      <c r="F30" s="22" t="s">
+      <c r="B30" s="27"/>
+      <c r="C30" s="27"/>
+      <c r="D30" s="27"/>
+      <c r="E30" s="27"/>
+      <c r="F30" s="28" t="s">
         <v>184</v>
       </c>
-      <c r="G30" s="22"/>
-      <c r="H30" s="22"/>
-      <c r="I30" s="22"/>
-      <c r="J30" s="22"/>
+      <c r="G30" s="28"/>
+      <c r="H30" s="28"/>
+      <c r="I30" s="28"/>
+      <c r="J30" s="28"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" s="8" t="s">
@@ -4676,26 +4682,26 @@
       <c r="J12" s="8"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A13" s="26">
-        <v>1000</v>
-      </c>
-      <c r="B13" s="26"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="26" t="s">
+      <c r="A13" s="24">
+        <v>1000</v>
+      </c>
+      <c r="B13" s="24"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="G13" s="26">
+      <c r="G13" s="24">
         <v>253</v>
       </c>
-      <c r="H13" s="26" t="s">
+      <c r="H13" s="24" t="s">
         <v>374</v>
       </c>
-      <c r="I13" s="27" t="s">
+      <c r="I13" s="25" t="s">
         <v>375</v>
       </c>
-      <c r="J13" s="26" t="s">
+      <c r="J13" s="24" t="s">
         <v>376</v>
       </c>
     </row>
@@ -4760,20 +4766,20 @@
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A24" s="21" t="s">
+      <c r="A24" s="27" t="s">
         <v>180</v>
       </c>
-      <c r="B24" s="21"/>
-      <c r="C24" s="21"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="22" t="s">
+      <c r="B24" s="27"/>
+      <c r="C24" s="27"/>
+      <c r="D24" s="27"/>
+      <c r="E24" s="27"/>
+      <c r="F24" s="28" t="s">
         <v>184</v>
       </c>
-      <c r="G24" s="22"/>
-      <c r="H24" s="22"/>
-      <c r="I24" s="22"/>
-      <c r="J24" s="22"/>
+      <c r="G24" s="28"/>
+      <c r="H24" s="28"/>
+      <c r="I24" s="28"/>
+      <c r="J24" s="28"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" s="8" t="s">
@@ -5100,20 +5106,20 @@
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A55" s="21" t="s">
+      <c r="A55" s="27" t="s">
         <v>180</v>
       </c>
-      <c r="B55" s="21"/>
-      <c r="C55" s="21"/>
-      <c r="D55" s="21"/>
-      <c r="E55" s="21"/>
-      <c r="F55" s="22" t="s">
+      <c r="B55" s="27"/>
+      <c r="C55" s="27"/>
+      <c r="D55" s="27"/>
+      <c r="E55" s="27"/>
+      <c r="F55" s="28" t="s">
         <v>184</v>
       </c>
-      <c r="G55" s="22"/>
-      <c r="H55" s="22"/>
-      <c r="I55" s="22"/>
-      <c r="J55" s="22"/>
+      <c r="G55" s="28"/>
+      <c r="H55" s="28"/>
+      <c r="I55" s="28"/>
+      <c r="J55" s="28"/>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A56" s="8" t="s">
@@ -5559,20 +5565,20 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" s="7"/>
-      <c r="B17" s="21" t="s">
+      <c r="B17" s="27" t="s">
         <v>180</v>
       </c>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="22" t="s">
+      <c r="C17" s="27"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="27"/>
+      <c r="F17" s="27"/>
+      <c r="G17" s="28" t="s">
         <v>184</v>
       </c>
-      <c r="H17" s="22"/>
-      <c r="I17" s="22"/>
-      <c r="J17" s="22"/>
-      <c r="K17" s="22"/>
+      <c r="H17" s="28"/>
+      <c r="I17" s="28"/>
+      <c r="J17" s="28"/>
+      <c r="K17" s="28"/>
       <c r="L17" s="8"/>
       <c r="M17" s="8"/>
       <c r="N17" s="8"/>
@@ -5920,20 +5926,20 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="7"/>
-      <c r="B15" s="21" t="s">
+      <c r="B15" s="27" t="s">
         <v>180</v>
       </c>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="22" t="s">
+      <c r="C15" s="27"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="28" t="s">
         <v>184</v>
       </c>
-      <c r="H15" s="22"/>
-      <c r="I15" s="22"/>
-      <c r="J15" s="22"/>
-      <c r="K15" s="22"/>
+      <c r="H15" s="28"/>
+      <c r="I15" s="28"/>
+      <c r="J15" s="28"/>
+      <c r="K15" s="28"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="7"/>
@@ -6170,20 +6176,20 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A33" s="7"/>
-      <c r="B33" s="21" t="s">
+      <c r="B33" s="27" t="s">
         <v>180</v>
       </c>
-      <c r="C33" s="21"/>
-      <c r="D33" s="21"/>
-      <c r="E33" s="21"/>
-      <c r="F33" s="21"/>
-      <c r="G33" s="22" t="s">
+      <c r="C33" s="27"/>
+      <c r="D33" s="27"/>
+      <c r="E33" s="27"/>
+      <c r="F33" s="27"/>
+      <c r="G33" s="28" t="s">
         <v>184</v>
       </c>
-      <c r="H33" s="22"/>
-      <c r="I33" s="22"/>
-      <c r="J33" s="22"/>
-      <c r="K33" s="22"/>
+      <c r="H33" s="28"/>
+      <c r="I33" s="28"/>
+      <c r="J33" s="28"/>
+      <c r="K33" s="28"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34" s="7"/>
@@ -6420,20 +6426,20 @@
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A51" s="7"/>
-      <c r="B51" s="21" t="s">
+      <c r="B51" s="27" t="s">
         <v>180</v>
       </c>
-      <c r="C51" s="21"/>
-      <c r="D51" s="21"/>
-      <c r="E51" s="21"/>
-      <c r="F51" s="21"/>
-      <c r="G51" s="22" t="s">
+      <c r="C51" s="27"/>
+      <c r="D51" s="27"/>
+      <c r="E51" s="27"/>
+      <c r="F51" s="27"/>
+      <c r="G51" s="28" t="s">
         <v>184</v>
       </c>
-      <c r="H51" s="22"/>
-      <c r="I51" s="22"/>
-      <c r="J51" s="22"/>
-      <c r="K51" s="22"/>
+      <c r="H51" s="28"/>
+      <c r="I51" s="28"/>
+      <c r="J51" s="28"/>
+      <c r="K51" s="28"/>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A52" s="7"/>
@@ -6670,20 +6676,20 @@
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A69" s="7"/>
-      <c r="B69" s="21" t="s">
+      <c r="B69" s="27" t="s">
         <v>180</v>
       </c>
-      <c r="C69" s="21"/>
-      <c r="D69" s="21"/>
-      <c r="E69" s="21"/>
-      <c r="F69" s="21"/>
-      <c r="G69" s="22" t="s">
+      <c r="C69" s="27"/>
+      <c r="D69" s="27"/>
+      <c r="E69" s="27"/>
+      <c r="F69" s="27"/>
+      <c r="G69" s="28" t="s">
         <v>184</v>
       </c>
-      <c r="H69" s="22"/>
-      <c r="I69" s="22"/>
-      <c r="J69" s="22"/>
-      <c r="K69" s="22"/>
+      <c r="H69" s="28"/>
+      <c r="I69" s="28"/>
+      <c r="J69" s="28"/>
+      <c r="K69" s="28"/>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A70" s="7"/>
@@ -8021,7 +8027,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="3" width="20.81640625" customWidth="1"/>
@@ -8093,6 +8099,14 @@
       </c>
       <c r="F4" t="s">
         <v>566</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D5" t="s">
+        <v>614</v>
+      </c>
+      <c r="F5" t="s">
+        <v>615</v>
       </c>
     </row>
   </sheetData>
@@ -8323,20 +8337,20 @@
       <c r="J12" s="8"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="27" t="s">
         <v>180</v>
       </c>
-      <c r="B13" s="21"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="22" t="s">
+      <c r="B13" s="27"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="28" t="s">
         <v>184</v>
       </c>
-      <c r="G13" s="22"/>
-      <c r="H13" s="22"/>
-      <c r="I13" s="22"/>
-      <c r="J13" s="22"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="28"/>
+      <c r="I13" s="28"/>
+      <c r="J13" s="28"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="8" t="s">
@@ -8719,20 +8733,20 @@
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A23" s="21" t="s">
+      <c r="A23" s="27" t="s">
         <v>180</v>
       </c>
-      <c r="B23" s="21"/>
-      <c r="C23" s="21"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="22" t="s">
+      <c r="B23" s="27"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="27"/>
+      <c r="F23" s="28" t="s">
         <v>184</v>
       </c>
-      <c r="G23" s="22"/>
-      <c r="H23" s="22"/>
-      <c r="I23" s="22"/>
-      <c r="J23" s="22"/>
+      <c r="G23" s="28"/>
+      <c r="H23" s="28"/>
+      <c r="I23" s="28"/>
+      <c r="J23" s="28"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" s="8" t="s">
@@ -9040,26 +9054,26 @@
       <c r="J12" s="8"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A13" s="26">
-        <v>1000</v>
-      </c>
-      <c r="B13" s="26"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="26" t="s">
+      <c r="A13" s="24">
+        <v>1000</v>
+      </c>
+      <c r="B13" s="24"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="G13" s="26">
+      <c r="G13" s="24">
         <v>217</v>
       </c>
-      <c r="H13" s="26" t="s">
+      <c r="H13" s="24" t="s">
         <v>347</v>
       </c>
-      <c r="I13" s="27" t="s">
+      <c r="I13" s="25" t="s">
         <v>351</v>
       </c>
-      <c r="J13" s="26" t="s">
+      <c r="J13" s="24" t="s">
         <v>352</v>
       </c>
     </row>
@@ -9125,20 +9139,20 @@
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A28" s="21" t="s">
+      <c r="A28" s="27" t="s">
         <v>180</v>
       </c>
-      <c r="B28" s="21"/>
-      <c r="C28" s="21"/>
-      <c r="D28" s="21"/>
-      <c r="E28" s="21"/>
-      <c r="F28" s="22" t="s">
+      <c r="B28" s="27"/>
+      <c r="C28" s="27"/>
+      <c r="D28" s="27"/>
+      <c r="E28" s="27"/>
+      <c r="F28" s="28" t="s">
         <v>184</v>
       </c>
-      <c r="G28" s="22"/>
-      <c r="H28" s="22"/>
-      <c r="I28" s="22"/>
-      <c r="J28" s="22"/>
+      <c r="G28" s="28"/>
+      <c r="H28" s="28"/>
+      <c r="I28" s="28"/>
+      <c r="J28" s="28"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" s="8" t="s">
@@ -9460,26 +9474,26 @@
       <c r="J12" s="8"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A13" s="26">
-        <v>1000</v>
-      </c>
-      <c r="B13" s="26"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="26" t="s">
+      <c r="A13" s="24">
+        <v>1000</v>
+      </c>
+      <c r="B13" s="24"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="G13" s="26">
+      <c r="G13" s="24">
         <v>228</v>
       </c>
-      <c r="H13" s="26" t="s">
+      <c r="H13" s="24" t="s">
         <v>333</v>
       </c>
-      <c r="I13" s="27" t="s">
+      <c r="I13" s="25" t="s">
         <v>334</v>
       </c>
-      <c r="J13" s="26" t="s">
+      <c r="J13" s="24" t="s">
         <v>335</v>
       </c>
     </row>
@@ -9545,20 +9559,20 @@
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A25" s="21" t="s">
+      <c r="A25" s="27" t="s">
         <v>180</v>
       </c>
-      <c r="B25" s="21"/>
-      <c r="C25" s="21"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="22" t="s">
+      <c r="B25" s="27"/>
+      <c r="C25" s="27"/>
+      <c r="D25" s="27"/>
+      <c r="E25" s="27"/>
+      <c r="F25" s="28" t="s">
         <v>184</v>
       </c>
-      <c r="G25" s="22"/>
-      <c r="H25" s="22"/>
-      <c r="I25" s="22"/>
-      <c r="J25" s="22"/>
+      <c r="G25" s="28"/>
+      <c r="H25" s="28"/>
+      <c r="I25" s="28"/>
+      <c r="J25" s="28"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" s="8" t="s">
@@ -9879,26 +9893,26 @@
       <c r="J12" s="8"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A13" s="26">
-        <v>1000</v>
-      </c>
-      <c r="B13" s="26"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="26" t="s">
+      <c r="A13" s="24">
+        <v>1000</v>
+      </c>
+      <c r="B13" s="24"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="G13" s="26">
+      <c r="G13" s="24">
         <v>240</v>
       </c>
-      <c r="H13" s="26" t="s">
+      <c r="H13" s="24" t="s">
         <v>319</v>
       </c>
-      <c r="I13" s="27" t="s">
+      <c r="I13" s="25" t="s">
         <v>321</v>
       </c>
-      <c r="J13" s="28" t="s">
+      <c r="J13" s="26" t="s">
         <v>325</v>
       </c>
     </row>
@@ -9964,20 +9978,20 @@
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A25" s="21" t="s">
+      <c r="A25" s="27" t="s">
         <v>180</v>
       </c>
-      <c r="B25" s="21"/>
-      <c r="C25" s="21"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="22" t="s">
+      <c r="B25" s="27"/>
+      <c r="C25" s="27"/>
+      <c r="D25" s="27"/>
+      <c r="E25" s="27"/>
+      <c r="F25" s="28" t="s">
         <v>184</v>
       </c>
-      <c r="G25" s="22"/>
-      <c r="H25" s="22"/>
-      <c r="I25" s="22"/>
-      <c r="J25" s="22"/>
+      <c r="G25" s="28"/>
+      <c r="H25" s="28"/>
+      <c r="I25" s="28"/>
+      <c r="J25" s="28"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" s="8" t="s">

--- a/Experiments/DBCV_Conclu.xlsx
+++ b/Experiments/DBCV_Conclu.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\300\320\321\Studenten\DAS-SB\GIT\thesis_documentation\Experiments\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\das-sb\Downloads\thesis_documentation\Experiments\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1378" uniqueCount="616">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1382" uniqueCount="618">
   <si>
     <t>Datapoints</t>
   </si>
@@ -1886,6 +1886,12 @@
   </si>
   <si>
     <t>0.134</t>
+  </si>
+  <si>
+    <t>spectral</t>
+  </si>
+  <si>
+    <t>0.155</t>
   </si>
 </sst>
 </file>
@@ -8027,7 +8033,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="3" width="20.81640625" customWidth="1"/>
@@ -8086,7 +8092,7 @@
         <v>949647</v>
       </c>
       <c r="B4">
-        <v>175</v>
+        <v>94</v>
       </c>
       <c r="C4">
         <v>49981</v>
@@ -8102,11 +8108,43 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>949647</v>
+      </c>
+      <c r="B5">
+        <v>175</v>
+      </c>
+      <c r="C5">
+        <v>49981</v>
+      </c>
       <c r="D5" t="s">
         <v>614</v>
       </c>
+      <c r="E5" t="s">
+        <v>559</v>
+      </c>
       <c r="F5" t="s">
         <v>615</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>949647</v>
+      </c>
+      <c r="B6">
+        <v>175</v>
+      </c>
+      <c r="C6">
+        <v>49981</v>
+      </c>
+      <c r="D6" t="s">
+        <v>616</v>
+      </c>
+      <c r="E6" t="s">
+        <v>559</v>
+      </c>
+      <c r="F6" t="s">
+        <v>617</v>
       </c>
     </row>
   </sheetData>

--- a/Experiments/DBCV_Conclu.xlsx
+++ b/Experiments/DBCV_Conclu.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\das-sb\Downloads\thesis_documentation\Experiments\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A2D5C8C-9138-4E3A-BDC0-FBB8D1508B28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17850" activeTab="3"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1382" uniqueCount="618">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1383" uniqueCount="619">
   <si>
     <t>Datapoints</t>
   </si>
@@ -1893,11 +1894,14 @@
   <si>
     <t>0.155</t>
   </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1988,10 +1992,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -2001,33 +2004,22 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2335,31 +2327,31 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:N75"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.36328125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.90625" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.90625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.90625" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.54296875" style="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.54296875" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.90625" style="8" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.54296875" style="7" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.54296875" style="8" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.6328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.08984375" style="8" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="29.90625" style="8" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="80.90625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.90625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.6328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="29.90625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="80.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="6" t="s">
         <v>202</v>
       </c>
     </row>
@@ -2372,960 +2364,909 @@
       <c r="B4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" t="s">
         <v>5</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" t="s">
         <v>7</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" t="s">
         <v>1</v>
       </c>
-      <c r="I4" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="J4" s="8" t="s">
+      <c r="I4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J4" t="s">
         <v>3</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" t="s">
         <v>10</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="L4" t="s">
         <v>11</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="M4" t="s">
         <v>12</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="N4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="3">
-        <v>1000</v>
-      </c>
-      <c r="B5" s="3">
+      <c r="A5" s="2">
+        <v>1000</v>
+      </c>
+      <c r="B5" s="2">
         <v>512</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" t="s">
         <v>16</v>
       </c>
       <c r="D5" s="1"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="3">
-        <v>2</v>
-      </c>
-      <c r="G5" s="2" t="s">
+      <c r="E5"/>
+      <c r="F5" s="2">
+        <v>2</v>
+      </c>
+      <c r="G5" t="s">
         <v>567</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H5" t="s">
         <v>14</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="2">
         <v>288</v>
       </c>
-      <c r="J5" s="8" t="s">
+      <c r="J5" t="s">
         <v>568</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="K5" t="s">
         <v>257</v>
       </c>
-      <c r="L5" s="2" t="s">
+      <c r="L5" t="s">
         <v>569</v>
       </c>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
     </row>
     <row r="6" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="21">
-        <v>1000</v>
-      </c>
-      <c r="B6" s="21">
+      <c r="A6" s="11">
+        <v>1000</v>
+      </c>
+      <c r="B6" s="11">
         <v>512</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="21">
+      <c r="D6" s="11">
         <v>154</v>
       </c>
-      <c r="E6" s="22" t="s">
+      <c r="E6" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="23"/>
-      <c r="G6" s="22"/>
-      <c r="H6" s="22" t="s">
+      <c r="F6" s="13"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="I6" s="21">
+      <c r="I6" s="11">
         <v>169</v>
       </c>
-      <c r="J6" s="22" t="s">
+      <c r="J6" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="K6" s="22" t="s">
+      <c r="K6" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="L6" s="22" t="s">
+      <c r="L6" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
     </row>
     <row r="7" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="3">
-        <v>1000</v>
-      </c>
-      <c r="B7" s="3">
+      <c r="A7" s="2">
+        <v>1000</v>
+      </c>
+      <c r="B7" s="2">
         <v>512</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="2">
         <v>154</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" t="s">
         <v>25</v>
       </c>
       <c r="F7" s="1"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="8" t="s">
+      <c r="G7"/>
+      <c r="H7" t="s">
         <v>22</v>
       </c>
-      <c r="I7" s="3">
-        <v>175</v>
-      </c>
-      <c r="J7" s="8" t="s">
+      <c r="I7" s="2">
+        <v>175</v>
+      </c>
+      <c r="J7" t="s">
         <v>23</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="K7" t="s">
         <v>26</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="L7" t="s">
         <v>27</v>
       </c>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
     </row>
     <row r="8" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="3">
-        <v>1000</v>
-      </c>
-      <c r="B8" s="3">
+      <c r="A8" s="2">
+        <v>1000</v>
+      </c>
+      <c r="B8" s="2">
         <v>512</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" t="s">
         <v>29</v>
       </c>
       <c r="D8" s="1"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="3">
-        <v>2</v>
-      </c>
-      <c r="G8" s="2" t="s">
+      <c r="E8"/>
+      <c r="F8" s="2">
+        <v>2</v>
+      </c>
+      <c r="G8" t="s">
         <v>30</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="H8" t="s">
         <v>22</v>
       </c>
-      <c r="I8" s="3">
-        <v>175</v>
-      </c>
-      <c r="J8" s="8" t="s">
+      <c r="I8" s="2">
+        <v>175</v>
+      </c>
+      <c r="J8" t="s">
         <v>28</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="K8" t="s">
         <v>31</v>
       </c>
-      <c r="L8" s="2" t="s">
+      <c r="L8" t="s">
         <v>32</v>
       </c>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
     </row>
     <row r="9" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="3">
-        <v>1000</v>
-      </c>
-      <c r="B9" s="3">
+      <c r="A9" s="2">
+        <v>1000</v>
+      </c>
+      <c r="B9" s="2">
         <v>512</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" t="s">
         <v>35</v>
       </c>
       <c r="D9" s="1"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="3">
-        <v>2</v>
-      </c>
-      <c r="G9" s="2" t="s">
+      <c r="E9"/>
+      <c r="F9" s="2">
+        <v>2</v>
+      </c>
+      <c r="G9" t="s">
         <v>36</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" t="s">
         <v>33</v>
       </c>
-      <c r="I9" s="3">
-        <v>175</v>
-      </c>
-      <c r="J9" s="8" t="s">
+      <c r="I9" s="2">
+        <v>175</v>
+      </c>
+      <c r="J9" t="s">
         <v>34</v>
       </c>
-      <c r="K9" s="2" t="s">
+      <c r="K9" t="s">
         <v>37</v>
       </c>
-      <c r="L9" s="2" t="s">
+      <c r="L9" t="s">
         <v>38</v>
       </c>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
     </row>
     <row r="10" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="3">
-        <v>1000</v>
-      </c>
-      <c r="B10" s="3">
+      <c r="A10" s="2">
+        <v>1000</v>
+      </c>
+      <c r="B10" s="2">
         <v>512</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" t="s">
         <v>40</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="2">
         <v>154</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" t="s">
         <v>41</v>
       </c>
       <c r="F10" s="1"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="8" t="s">
+      <c r="G10"/>
+      <c r="H10" t="s">
         <v>33</v>
       </c>
-      <c r="I10" s="3">
-        <v>175</v>
-      </c>
-      <c r="J10" s="8" t="s">
+      <c r="I10" s="2">
+        <v>175</v>
+      </c>
+      <c r="J10" t="s">
         <v>39</v>
       </c>
-      <c r="K10" s="2" t="s">
+      <c r="K10" t="s">
         <v>42</v>
       </c>
-      <c r="L10" s="2" t="s">
+      <c r="L10" t="s">
         <v>43</v>
       </c>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
     </row>
     <row r="11" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="3">
-        <v>1000</v>
-      </c>
-      <c r="B11" s="3">
+      <c r="A11" s="2">
+        <v>1000</v>
+      </c>
+      <c r="B11" s="2">
         <v>512</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" t="s">
         <v>46</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="2">
         <v>154</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" t="s">
         <v>47</v>
       </c>
       <c r="F11" s="1"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="8" t="s">
+      <c r="G11"/>
+      <c r="H11" t="s">
         <v>44</v>
       </c>
-      <c r="I11" s="3">
-        <v>175</v>
-      </c>
-      <c r="J11" s="8" t="s">
+      <c r="I11" s="2">
+        <v>175</v>
+      </c>
+      <c r="J11" t="s">
         <v>45</v>
       </c>
-      <c r="K11" s="4" t="s">
+      <c r="K11" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="L11" s="2" t="s">
+      <c r="L11" t="s">
         <v>49</v>
       </c>
-      <c r="M11" s="2" t="s">
+      <c r="M11" t="s">
         <v>50</v>
       </c>
-      <c r="N11" s="2" t="s">
+      <c r="N11" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="3">
-        <v>1000</v>
-      </c>
-      <c r="B12" s="3">
+      <c r="A12" s="2">
+        <v>1000</v>
+      </c>
+      <c r="B12" s="2">
         <v>512</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" t="s">
         <v>52</v>
       </c>
       <c r="D12" s="1"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="3">
-        <v>2</v>
-      </c>
-      <c r="G12" s="2" t="s">
+      <c r="E12"/>
+      <c r="F12" s="2">
+        <v>2</v>
+      </c>
+      <c r="G12" t="s">
         <v>53</v>
       </c>
-      <c r="H12" s="8" t="s">
+      <c r="H12" t="s">
         <v>44</v>
       </c>
-      <c r="I12" s="3">
-        <v>175</v>
-      </c>
-      <c r="J12" s="8" t="s">
+      <c r="I12" s="2">
+        <v>175</v>
+      </c>
+      <c r="J12" t="s">
         <v>51</v>
       </c>
-      <c r="K12" s="2" t="s">
+      <c r="K12" t="s">
         <v>54</v>
       </c>
-      <c r="L12" s="2" t="s">
+      <c r="L12" t="s">
         <v>55</v>
       </c>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
     </row>
     <row r="13" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="1"/>
       <c r="B13" s="1"/>
-      <c r="C13" s="2"/>
+      <c r="C13"/>
       <c r="D13" s="1"/>
-      <c r="E13" s="2"/>
+      <c r="E13"/>
       <c r="F13" s="1"/>
-      <c r="G13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
+      <c r="G13"/>
     </row>
     <row r="14" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="23">
-        <v>1000</v>
-      </c>
-      <c r="B14" s="23"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="23">
-        <v>2</v>
-      </c>
-      <c r="G14" s="22" t="s">
+      <c r="A14" s="13">
+        <v>1000</v>
+      </c>
+      <c r="B14" s="13"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="13">
+        <v>2</v>
+      </c>
+      <c r="G14" s="12" t="s">
         <v>221</v>
       </c>
-      <c r="H14" s="22" t="s">
+      <c r="H14" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="I14" s="23">
+      <c r="I14" s="13">
         <v>314</v>
       </c>
-      <c r="J14" s="22" t="s">
+      <c r="J14" s="12" t="s">
         <v>222</v>
       </c>
-      <c r="K14" s="22" t="s">
+      <c r="K14" s="12" t="s">
         <v>223</v>
       </c>
-      <c r="L14" s="22" t="s">
+      <c r="L14" s="12" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="7"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="8"/>
+      <c r="B15" s="1"/>
+      <c r="C15"/>
+      <c r="D15" s="1"/>
+      <c r="E15"/>
+      <c r="F15" s="1"/>
+      <c r="G15"/>
     </row>
     <row r="16" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="7">
-        <v>1000</v>
-      </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="7">
-        <v>2</v>
-      </c>
-      <c r="G16" s="8" t="s">
+      <c r="A16" s="1">
+        <v>1000</v>
+      </c>
+      <c r="B16" s="1"/>
+      <c r="C16"/>
+      <c r="D16" s="1"/>
+      <c r="E16"/>
+      <c r="F16" s="1">
+        <v>2</v>
+      </c>
+      <c r="G16" t="s">
         <v>225</v>
       </c>
-      <c r="H16" s="8" t="s">
+      <c r="H16" t="s">
         <v>33</v>
       </c>
-      <c r="I16" s="7">
-        <v>175</v>
-      </c>
-      <c r="J16" s="8" t="s">
+      <c r="I16" s="1">
+        <v>175</v>
+      </c>
+      <c r="J16" t="s">
         <v>226</v>
       </c>
-      <c r="K16" s="6" t="s">
+      <c r="K16" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="L16" s="8" t="s">
+      <c r="L16" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="7"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="8"/>
-      <c r="K17" s="6"/>
+      <c r="B17" s="1"/>
+      <c r="C17"/>
+      <c r="D17" s="1"/>
+      <c r="E17"/>
+      <c r="F17" s="1"/>
+      <c r="G17"/>
+      <c r="K17" s="5"/>
     </row>
     <row r="18" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="7">
-        <v>1000</v>
-      </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="7">
-        <v>2</v>
-      </c>
-      <c r="G18" s="8" t="s">
+      <c r="A18" s="1">
+        <v>1000</v>
+      </c>
+      <c r="B18" s="1"/>
+      <c r="C18"/>
+      <c r="D18" s="1"/>
+      <c r="E18"/>
+      <c r="F18" s="1">
+        <v>2</v>
+      </c>
+      <c r="G18" t="s">
         <v>229</v>
       </c>
-      <c r="H18" s="8" t="s">
+      <c r="H18" t="s">
         <v>44</v>
       </c>
-      <c r="I18" s="7">
-        <v>175</v>
-      </c>
-      <c r="J18" s="8" t="s">
+      <c r="I18" s="1">
+        <v>175</v>
+      </c>
+      <c r="J18" t="s">
         <v>230</v>
       </c>
-      <c r="K18" s="6" t="s">
+      <c r="K18" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="L18" s="8" t="s">
+      <c r="L18" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="7"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="8"/>
-      <c r="K19" s="6"/>
+      <c r="B19" s="1"/>
+      <c r="C19"/>
+      <c r="D19" s="1"/>
+      <c r="E19"/>
+      <c r="F19" s="1"/>
+      <c r="G19"/>
+      <c r="K19" s="5"/>
     </row>
     <row r="20" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="7">
-        <v>1000</v>
-      </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="7">
-        <v>2</v>
-      </c>
-      <c r="G20" s="8" t="s">
+      <c r="A20" s="1">
+        <v>1000</v>
+      </c>
+      <c r="B20" s="1"/>
+      <c r="C20"/>
+      <c r="D20" s="1"/>
+      <c r="E20"/>
+      <c r="F20" s="1">
+        <v>2</v>
+      </c>
+      <c r="G20" t="s">
         <v>232</v>
       </c>
-      <c r="H20" s="8" t="s">
+      <c r="H20" t="s">
         <v>22</v>
       </c>
-      <c r="I20" s="7">
-        <v>175</v>
-      </c>
-      <c r="J20" s="8" t="s">
+      <c r="I20" s="1">
+        <v>175</v>
+      </c>
+      <c r="J20" t="s">
         <v>233</v>
       </c>
-      <c r="K20" s="6" t="s">
+      <c r="K20" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="L20" s="8" t="s">
+      <c r="L20" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="7"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="8"/>
+      <c r="B21" s="1"/>
+      <c r="C21"/>
+      <c r="D21" s="1"/>
+      <c r="E21"/>
+      <c r="F21" s="1"/>
+      <c r="G21"/>
     </row>
     <row r="22" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="27" t="s">
+      <c r="B22" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="C22" s="27"/>
-      <c r="D22" s="27"/>
-      <c r="E22" s="27"/>
-      <c r="F22" s="27"/>
-      <c r="G22" s="28" t="s">
+      <c r="C22" s="15"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="H22" s="28"/>
-      <c r="I22" s="28"/>
-      <c r="J22" s="28"/>
-      <c r="K22" s="28"/>
+      <c r="H22" s="16"/>
+      <c r="I22" s="16"/>
+      <c r="J22" s="16"/>
+      <c r="K22" s="16"/>
     </row>
     <row r="23" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="8" t="s">
+      <c r="B23" t="s">
         <v>181</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="D23" t="s">
         <v>183</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="E23" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F23" s="8" t="s">
+      <c r="F23" t="s">
         <v>11</v>
       </c>
-      <c r="G23" s="8" t="s">
+      <c r="G23" t="s">
         <v>181</v>
       </c>
-      <c r="H23" s="7" t="s">
+      <c r="H23" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="I23" s="8" t="s">
+      <c r="I23" t="s">
         <v>189</v>
       </c>
-      <c r="J23" s="7" t="s">
+      <c r="J23" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="K23" s="8" t="s">
+      <c r="K23" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="7">
-        <v>1000</v>
-      </c>
-      <c r="B24" s="8" t="s">
+      <c r="A24" s="1">
+        <v>1000</v>
+      </c>
+      <c r="B24" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="7">
+      <c r="C24" s="1">
         <v>288</v>
       </c>
-      <c r="D24" s="8">
+      <c r="D24">
         <v>94</v>
       </c>
-      <c r="E24" s="8" t="s">
+      <c r="E24" t="s">
         <v>257</v>
       </c>
-      <c r="F24" s="8" t="s">
+      <c r="F24" t="s">
         <v>569</v>
       </c>
-      <c r="G24" s="7" t="s">
+      <c r="G24" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H24" s="8">
+      <c r="H24">
         <v>111</v>
       </c>
-      <c r="I24" s="7">
+      <c r="I24" s="1">
         <v>33</v>
       </c>
-      <c r="J24" s="6" t="s">
+      <c r="J24" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="K24" s="7" t="s">
+      <c r="K24" s="1" t="s">
         <v>570</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="7">
-        <v>1000</v>
-      </c>
-      <c r="B25" s="8" t="s">
+      <c r="A25" s="1">
+        <v>1000</v>
+      </c>
+      <c r="B25" t="s">
         <v>14</v>
       </c>
-      <c r="E25" s="8"/>
-      <c r="J25" s="6"/>
-      <c r="K25" s="7"/>
+      <c r="E25"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="1"/>
     </row>
     <row r="26" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="1"/>
       <c r="B26" s="1"/>
-      <c r="C26" s="2"/>
+      <c r="C26"/>
       <c r="D26" s="1"/>
-      <c r="E26" s="2"/>
+      <c r="E26"/>
       <c r="F26" s="1"/>
-      <c r="G26" s="2"/>
-      <c r="K26" s="2"/>
-      <c r="L26" s="2"/>
-      <c r="M26" s="2"/>
-      <c r="N26" s="2"/>
+      <c r="G26"/>
     </row>
     <row r="27" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="3">
+      <c r="A27" s="2">
         <v>2000</v>
       </c>
-      <c r="B27" s="3">
+      <c r="B27" s="2">
         <v>512</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" t="s">
         <v>57</v>
       </c>
       <c r="D27" s="1"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="3">
-        <v>2</v>
-      </c>
-      <c r="G27" s="2" t="s">
+      <c r="E27"/>
+      <c r="F27" s="2">
+        <v>2</v>
+      </c>
+      <c r="G27" t="s">
         <v>58</v>
       </c>
-      <c r="H27" s="8" t="s">
+      <c r="H27" t="s">
         <v>22</v>
       </c>
-      <c r="I27" s="3">
-        <v>175</v>
-      </c>
-      <c r="J27" s="8" t="s">
+      <c r="I27" s="2">
+        <v>175</v>
+      </c>
+      <c r="J27" t="s">
         <v>56</v>
       </c>
-      <c r="K27" s="2" t="s">
+      <c r="K27" t="s">
         <v>59</v>
       </c>
-      <c r="L27" s="2" t="s">
+      <c r="L27" t="s">
         <v>60</v>
       </c>
-      <c r="M27" s="2"/>
-      <c r="N27" s="2"/>
     </row>
     <row r="28" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="3">
+      <c r="A28" s="2">
         <v>2000</v>
       </c>
-      <c r="B28" s="3">
+      <c r="B28" s="2">
         <v>512</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" t="s">
         <v>62</v>
       </c>
-      <c r="D28" s="3">
+      <c r="D28" s="2">
         <v>154</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="E28" t="s">
         <v>63</v>
       </c>
       <c r="F28" s="1"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="8" t="s">
+      <c r="G28"/>
+      <c r="H28" t="s">
         <v>22</v>
       </c>
-      <c r="I28" s="3">
-        <v>175</v>
-      </c>
-      <c r="J28" s="8" t="s">
+      <c r="I28" s="2">
+        <v>175</v>
+      </c>
+      <c r="J28" t="s">
         <v>61</v>
       </c>
-      <c r="K28" s="2" t="s">
+      <c r="K28" t="s">
         <v>64</v>
       </c>
-      <c r="L28" s="2" t="s">
+      <c r="L28" t="s">
         <v>65</v>
       </c>
-      <c r="M28" s="2"/>
-      <c r="N28" s="2"/>
     </row>
     <row r="29" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="3">
+      <c r="A29" s="2">
         <v>2000</v>
       </c>
-      <c r="B29" s="3">
+      <c r="B29" s="2">
         <v>512</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" t="s">
         <v>132</v>
       </c>
-      <c r="D29" s="3">
+      <c r="D29" s="2">
         <v>154</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="E29" t="s">
         <v>133</v>
       </c>
       <c r="F29" s="1"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="8" t="s">
+      <c r="G29"/>
+      <c r="H29" t="s">
         <v>44</v>
       </c>
-      <c r="I29" s="7">
-        <v>175</v>
-      </c>
-      <c r="J29" s="8" t="s">
+      <c r="I29" s="1">
+        <v>175</v>
+      </c>
+      <c r="J29" t="s">
         <v>131</v>
       </c>
-      <c r="K29" s="6" t="s">
+      <c r="K29" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="L29" s="2" t="s">
+      <c r="L29" t="s">
         <v>136</v>
       </c>
-      <c r="M29" s="2"/>
-      <c r="N29" s="2" t="s">
+      <c r="N29" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="3">
+      <c r="A30" s="2">
         <v>2000</v>
       </c>
-      <c r="B30" s="3">
+      <c r="B30" s="2">
         <v>512</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" t="s">
         <v>68</v>
       </c>
       <c r="D30" s="1"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="3">
-        <v>2</v>
-      </c>
-      <c r="G30" s="2" t="s">
+      <c r="E30"/>
+      <c r="F30" s="2">
+        <v>2</v>
+      </c>
+      <c r="G30" t="s">
         <v>69</v>
       </c>
-      <c r="H30" s="8" t="s">
+      <c r="H30" t="s">
         <v>44</v>
       </c>
-      <c r="I30" s="3">
-        <v>175</v>
-      </c>
-      <c r="J30" s="8" t="s">
+      <c r="I30" s="2">
+        <v>175</v>
+      </c>
+      <c r="J30" t="s">
         <v>67</v>
       </c>
-      <c r="K30" s="2" t="s">
+      <c r="K30" t="s">
         <v>70</v>
       </c>
-      <c r="L30" s="2" t="s">
+      <c r="L30" t="s">
         <v>71</v>
       </c>
-      <c r="M30" s="2"/>
-      <c r="N30" s="2"/>
     </row>
     <row r="31" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="3">
+      <c r="A31" s="2">
         <v>2000</v>
       </c>
-      <c r="B31" s="3">
+      <c r="B31" s="2">
         <v>512</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" t="s">
         <v>73</v>
       </c>
-      <c r="D31" s="3">
+      <c r="D31" s="2">
         <v>154</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="E31" t="s">
         <v>74</v>
       </c>
       <c r="F31" s="1"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="8" t="s">
+      <c r="G31"/>
+      <c r="H31" t="s">
         <v>14</v>
       </c>
-      <c r="I31" s="3">
+      <c r="I31" s="2">
         <v>363</v>
       </c>
-      <c r="J31" s="8" t="s">
+      <c r="J31" t="s">
         <v>72</v>
       </c>
-      <c r="K31" s="2" t="s">
+      <c r="K31" t="s">
         <v>75</v>
       </c>
-      <c r="L31" s="5" t="s">
+      <c r="L31" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="M31" s="2"/>
-      <c r="N31" s="2"/>
     </row>
     <row r="32" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="3">
+      <c r="A32" s="2">
         <v>2000</v>
       </c>
-      <c r="B32" s="3">
+      <c r="B32" s="2">
         <v>512</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" t="s">
         <v>78</v>
       </c>
       <c r="D32" s="1"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="3">
-        <v>2</v>
-      </c>
-      <c r="G32" s="2" t="s">
+      <c r="E32"/>
+      <c r="F32" s="2">
+        <v>2</v>
+      </c>
+      <c r="G32" t="s">
         <v>79</v>
       </c>
-      <c r="H32" s="8" t="s">
+      <c r="H32" t="s">
         <v>14</v>
       </c>
-      <c r="I32" s="3">
+      <c r="I32" s="2">
         <v>605</v>
       </c>
-      <c r="J32" s="8" t="s">
+      <c r="J32" t="s">
         <v>77</v>
       </c>
-      <c r="K32" s="2" t="s">
+      <c r="K32" t="s">
         <v>80</v>
       </c>
-      <c r="L32" s="2" t="s">
+      <c r="L32" t="s">
         <v>81</v>
       </c>
-      <c r="M32" s="2"/>
-      <c r="N32" s="2"/>
     </row>
     <row r="33" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="3">
+      <c r="A33" s="2">
         <v>2000</v>
       </c>
-      <c r="B33" s="3">
+      <c r="B33" s="2">
         <v>512</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" t="s">
         <v>83</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="2">
         <v>154</v>
       </c>
-      <c r="E33" s="2" t="s">
+      <c r="E33" t="s">
         <v>84</v>
       </c>
       <c r="F33" s="1"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="8" t="s">
+      <c r="G33"/>
+      <c r="H33" t="s">
         <v>33</v>
       </c>
-      <c r="I33" s="3">
-        <v>175</v>
-      </c>
-      <c r="J33" s="8" t="s">
+      <c r="I33" s="2">
+        <v>175</v>
+      </c>
+      <c r="J33" t="s">
         <v>82</v>
       </c>
-      <c r="K33" s="2" t="s">
+      <c r="K33" t="s">
         <v>85</v>
       </c>
-      <c r="L33" s="2" t="s">
+      <c r="L33" t="s">
         <v>86</v>
       </c>
-      <c r="M33" s="2"/>
-      <c r="N33" s="2"/>
     </row>
     <row r="34" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="3">
+      <c r="A34" s="2">
         <v>2000</v>
       </c>
-      <c r="B34" s="3">
+      <c r="B34" s="2">
         <v>512</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" t="s">
         <v>88</v>
       </c>
       <c r="D34" s="1"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="3">
-        <v>2</v>
-      </c>
-      <c r="G34" s="2" t="s">
+      <c r="E34"/>
+      <c r="F34" s="2">
+        <v>2</v>
+      </c>
+      <c r="G34" t="s">
         <v>89</v>
       </c>
-      <c r="H34" s="8" t="s">
+      <c r="H34" t="s">
         <v>33</v>
       </c>
-      <c r="I34" s="3">
-        <v>175</v>
-      </c>
-      <c r="J34" s="8" t="s">
+      <c r="I34" s="2">
+        <v>175</v>
+      </c>
+      <c r="J34" t="s">
         <v>87</v>
       </c>
-      <c r="K34" s="2" t="s">
+      <c r="K34" t="s">
         <v>90</v>
       </c>
-      <c r="L34" s="2" t="s">
+      <c r="L34" t="s">
         <v>91</v>
       </c>
-      <c r="M34" s="2"/>
-      <c r="N34" s="2"/>
     </row>
     <row r="35" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="1"/>
       <c r="B35" s="1"/>
-      <c r="C35" s="2"/>
+      <c r="C35"/>
       <c r="D35" s="1"/>
-      <c r="E35" s="2"/>
+      <c r="E35"/>
       <c r="F35" s="1"/>
-      <c r="G35" s="2"/>
-      <c r="K35" s="2"/>
-      <c r="L35" s="2"/>
-      <c r="M35" s="2"/>
-      <c r="N35" s="2"/>
+      <c r="G35"/>
     </row>
     <row r="36" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="1"/>
       <c r="B36" s="1"/>
-      <c r="C36" s="2"/>
+      <c r="C36"/>
       <c r="D36" s="1"/>
-      <c r="E36" s="2"/>
+      <c r="E36"/>
       <c r="F36" s="1"/>
-      <c r="G36" s="2"/>
-      <c r="K36" s="2"/>
-      <c r="L36" s="2"/>
-      <c r="M36" s="2"/>
-      <c r="N36" s="2"/>
+      <c r="G36"/>
     </row>
     <row r="37" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="3">
+      <c r="A37" s="2">
         <v>5000</v>
       </c>
-      <c r="B37" s="3">
+      <c r="B37" s="2">
         <v>512</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" t="s">
         <v>93</v>
       </c>
       <c r="D37" s="1"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="3">
-        <v>2</v>
-      </c>
-      <c r="G37" s="2" t="s">
+      <c r="E37"/>
+      <c r="F37" s="2">
+        <v>2</v>
+      </c>
+      <c r="G37" t="s">
         <v>94</v>
       </c>
-      <c r="H37" s="8" t="s">
+      <c r="H37" t="s">
         <v>14</v>
       </c>
-      <c r="I37" s="3">
+      <c r="I37" s="2">
         <v>1586</v>
       </c>
-      <c r="J37" s="8" t="s">
+      <c r="J37" t="s">
         <v>92</v>
       </c>
-      <c r="K37" s="8" t="s">
+      <c r="K37" t="s">
         <v>113</v>
       </c>
-      <c r="L37" s="8" t="s">
+      <c r="L37" t="s">
         <v>114</v>
       </c>
-      <c r="M37" s="2"/>
-      <c r="N37" s="2"/>
     </row>
     <row r="38" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
@@ -3334,72 +3275,69 @@
       <c r="B38" s="1">
         <v>512</v>
       </c>
-      <c r="C38" s="8" t="s">
+      <c r="C38" t="s">
         <v>119</v>
       </c>
       <c r="D38" s="1">
         <v>154</v>
       </c>
-      <c r="E38" s="2" t="s">
+      <c r="E38" t="s">
         <v>120</v>
       </c>
       <c r="F38" s="1"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="8" t="s">
+      <c r="G38"/>
+      <c r="H38" t="s">
         <v>14</v>
       </c>
-      <c r="I38" s="7">
+      <c r="I38" s="1">
         <v>914</v>
       </c>
-      <c r="J38" s="8" t="s">
+      <c r="J38" t="s">
         <v>118</v>
       </c>
-      <c r="K38" s="6" t="s">
+      <c r="K38" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="L38" s="8" t="s">
+      <c r="L38" t="s">
         <v>122</v>
       </c>
-      <c r="M38" s="8" t="s">
+      <c r="M38" t="s">
         <v>66</v>
       </c>
-      <c r="N38" s="2"/>
     </row>
     <row r="39" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="3">
+      <c r="A39" s="2">
         <v>5000</v>
       </c>
-      <c r="B39" s="3">
+      <c r="B39" s="2">
         <v>512</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" t="s">
         <v>96</v>
       </c>
       <c r="D39" s="1"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="3">
-        <v>2</v>
-      </c>
-      <c r="G39" s="2" t="s">
+      <c r="E39"/>
+      <c r="F39" s="2">
+        <v>2</v>
+      </c>
+      <c r="G39" t="s">
         <v>97</v>
       </c>
-      <c r="H39" s="8" t="s">
+      <c r="H39" t="s">
         <v>33</v>
       </c>
-      <c r="I39" s="3">
-        <v>175</v>
-      </c>
-      <c r="J39" s="8" t="s">
+      <c r="I39" s="2">
+        <v>175</v>
+      </c>
+      <c r="J39" t="s">
         <v>95</v>
       </c>
-      <c r="K39" s="6" t="s">
+      <c r="K39" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="L39" s="2" t="s">
+      <c r="L39" t="s">
         <v>98</v>
       </c>
-      <c r="M39" s="2"/>
-      <c r="N39" s="2"/>
     </row>
     <row r="40" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
@@ -3408,36 +3346,35 @@
       <c r="B40" s="1">
         <v>512</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" t="s">
         <v>101</v>
       </c>
       <c r="D40" s="1">
         <v>154</v>
       </c>
-      <c r="E40" s="2" t="s">
+      <c r="E40" t="s">
         <v>102</v>
       </c>
       <c r="F40" s="1"/>
-      <c r="G40" s="2"/>
-      <c r="H40" s="6" t="s">
+      <c r="G40"/>
+      <c r="H40" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="I40" s="7">
-        <v>175</v>
-      </c>
-      <c r="J40" s="8" t="s">
+      <c r="I40" s="1">
+        <v>175</v>
+      </c>
+      <c r="J40" t="s">
         <v>103</v>
       </c>
-      <c r="K40" s="2" t="s">
+      <c r="K40" t="s">
         <v>104</v>
       </c>
-      <c r="L40" s="2" t="s">
+      <c r="L40" t="s">
         <v>105</v>
       </c>
-      <c r="M40" s="2" t="s">
+      <c r="M40" t="s">
         <v>66</v>
       </c>
-      <c r="N40" s="2"/>
     </row>
     <row r="41" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
@@ -3446,34 +3383,32 @@
       <c r="B41" s="1">
         <v>512</v>
       </c>
-      <c r="C41" s="8" t="s">
+      <c r="C41" t="s">
         <v>106</v>
       </c>
       <c r="D41" s="1"/>
-      <c r="E41" s="2"/>
+      <c r="E41"/>
       <c r="F41" s="1">
         <v>2</v>
       </c>
-      <c r="G41" s="2" t="s">
+      <c r="G41" t="s">
         <v>107</v>
       </c>
-      <c r="H41" s="8" t="s">
+      <c r="H41" t="s">
         <v>44</v>
       </c>
-      <c r="I41" s="7">
-        <v>175</v>
-      </c>
-      <c r="J41" s="8" t="s">
+      <c r="I41" s="1">
+        <v>175</v>
+      </c>
+      <c r="J41" t="s">
         <v>108</v>
       </c>
-      <c r="K41" s="6" t="s">
+      <c r="K41" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="L41" s="2" t="s">
+      <c r="L41" t="s">
         <v>110</v>
       </c>
-      <c r="M41" s="2"/>
-      <c r="N41" s="2"/>
     </row>
     <row r="42" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
@@ -3482,36 +3417,36 @@
       <c r="B42" s="1">
         <v>512</v>
       </c>
-      <c r="C42" s="8" t="s">
+      <c r="C42" t="s">
         <v>111</v>
       </c>
       <c r="D42" s="1">
         <v>154</v>
       </c>
-      <c r="E42" s="2" t="s">
+      <c r="E42" t="s">
         <v>112</v>
       </c>
       <c r="F42" s="1"/>
-      <c r="G42" s="2"/>
-      <c r="H42" s="8" t="s">
+      <c r="G42"/>
+      <c r="H42" t="s">
         <v>44</v>
       </c>
-      <c r="I42" s="7">
-        <v>175</v>
-      </c>
-      <c r="J42" s="8" t="s">
+      <c r="I42" s="1">
+        <v>175</v>
+      </c>
+      <c r="J42" t="s">
         <v>115</v>
       </c>
-      <c r="K42" s="6" t="s">
+      <c r="K42" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="L42" s="8" t="s">
+      <c r="L42" t="s">
         <v>117</v>
       </c>
-      <c r="M42" s="8" t="s">
+      <c r="M42" t="s">
         <v>66</v>
       </c>
-      <c r="N42" s="2" t="s">
+      <c r="N42" t="s">
         <v>66</v>
       </c>
     </row>
@@ -3522,34 +3457,32 @@
       <c r="B43" s="1">
         <v>512</v>
       </c>
-      <c r="C43" s="8" t="s">
+      <c r="C43" t="s">
         <v>124</v>
       </c>
       <c r="D43" s="1"/>
-      <c r="E43" s="2"/>
+      <c r="E43"/>
       <c r="F43" s="1">
         <v>2</v>
       </c>
-      <c r="G43" s="2" t="s">
+      <c r="G43" t="s">
         <v>125</v>
       </c>
-      <c r="H43" s="8" t="s">
+      <c r="H43" t="s">
         <v>22</v>
       </c>
-      <c r="I43" s="7">
-        <v>175</v>
-      </c>
-      <c r="J43" s="8" t="s">
+      <c r="I43" s="1">
+        <v>175</v>
+      </c>
+      <c r="J43" t="s">
         <v>123</v>
       </c>
-      <c r="K43" s="6" t="s">
+      <c r="K43" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="L43" s="8" t="s">
+      <c r="L43" t="s">
         <v>127</v>
       </c>
-      <c r="M43" s="2"/>
-      <c r="N43" s="2"/>
     </row>
     <row r="44" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
@@ -3558,489 +3491,427 @@
       <c r="B44" s="1">
         <v>512</v>
       </c>
-      <c r="C44" s="8" t="s">
+      <c r="C44" t="s">
         <v>129</v>
       </c>
       <c r="D44" s="1">
         <v>154</v>
       </c>
-      <c r="E44" s="2" t="s">
+      <c r="E44" t="s">
         <v>130</v>
       </c>
       <c r="F44" s="1"/>
-      <c r="G44" s="2"/>
-      <c r="H44" s="8" t="s">
+      <c r="G44"/>
+      <c r="H44" t="s">
         <v>22</v>
       </c>
-      <c r="I44" s="7">
-        <v>175</v>
-      </c>
-      <c r="J44" s="8" t="s">
+      <c r="I44" s="1">
+        <v>175</v>
+      </c>
+      <c r="J44" t="s">
         <v>128</v>
       </c>
-      <c r="K44" s="6" t="s">
+      <c r="K44" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="L44" s="8" t="s">
+      <c r="L44" t="s">
         <v>148</v>
       </c>
-      <c r="M44" s="2"/>
-      <c r="N44" s="2"/>
-    </row>
-    <row r="45" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="1"/>
-      <c r="B45" s="2"/>
-      <c r="C45" s="1"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="1"/>
-      <c r="F45" s="2"/>
-      <c r="G45" s="1"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="1"/>
-      <c r="J45" s="2"/>
-      <c r="K45" s="2"/>
-      <c r="L45" s="2"/>
-      <c r="M45" s="2"/>
-      <c r="N45" s="2"/>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A46" s="1"/>
-      <c r="B46" s="2"/>
-      <c r="C46" s="1"/>
-      <c r="D46" s="2"/>
-      <c r="E46" s="1"/>
-      <c r="F46" s="2"/>
-      <c r="G46" s="1"/>
-      <c r="H46" s="2"/>
-      <c r="I46" s="1"/>
-      <c r="J46" s="2"/>
-      <c r="K46" s="2"/>
-      <c r="L46" s="2"/>
-      <c r="M46" s="2"/>
-      <c r="N46" s="2"/>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A47" s="1"/>
-      <c r="B47" s="2"/>
-      <c r="C47" s="1"/>
-      <c r="D47" s="2"/>
-      <c r="E47" s="1"/>
-      <c r="F47" s="2"/>
-      <c r="G47" s="1"/>
-      <c r="H47" s="2"/>
-      <c r="I47" s="1"/>
-      <c r="J47" s="2"/>
-      <c r="K47" s="2"/>
-      <c r="L47" s="2"/>
-      <c r="M47" s="2"/>
-      <c r="N47" s="2"/>
-    </row>
+    </row>
+    <row r="45" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="48" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B48" s="2"/>
-      <c r="C48" s="1"/>
-      <c r="D48" s="2"/>
-      <c r="E48" s="1"/>
-      <c r="F48" s="2"/>
-      <c r="G48" s="1"/>
-      <c r="H48" s="2"/>
-      <c r="I48" s="1"/>
-      <c r="J48" s="2"/>
-      <c r="K48" s="2"/>
-      <c r="L48" s="2"/>
-      <c r="M48" s="2"/>
-      <c r="N48" s="2"/>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B49" s="27" t="s">
+      <c r="B49" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="C49" s="27"/>
-      <c r="D49" s="27"/>
-      <c r="E49" s="27"/>
-      <c r="F49" s="27"/>
-      <c r="G49" s="28" t="s">
+      <c r="C49" s="15"/>
+      <c r="D49" s="15"/>
+      <c r="E49" s="15"/>
+      <c r="F49" s="15"/>
+      <c r="G49" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="H49" s="28"/>
-      <c r="I49" s="28"/>
-      <c r="J49" s="28"/>
-      <c r="K49" s="28"/>
+      <c r="H49" s="16"/>
+      <c r="I49" s="16"/>
+      <c r="J49" s="16"/>
+      <c r="K49" s="16"/>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B50" s="8" t="s">
+      <c r="B50" t="s">
         <v>181</v>
       </c>
-      <c r="C50" s="7" t="s">
+      <c r="C50" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="D50" s="8" t="s">
+      <c r="D50" t="s">
         <v>183</v>
       </c>
-      <c r="E50" s="7" t="s">
+      <c r="E50" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F50" s="8" t="s">
+      <c r="F50" t="s">
         <v>11</v>
       </c>
-      <c r="G50" s="8" t="s">
+      <c r="G50" t="s">
         <v>181</v>
       </c>
-      <c r="H50" s="7" t="s">
+      <c r="H50" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="I50" s="8" t="s">
+      <c r="I50" t="s">
         <v>189</v>
       </c>
-      <c r="J50" s="7" t="s">
+      <c r="J50" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="K50" s="8" t="s">
+      <c r="K50" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A51" s="7">
-        <v>1000</v>
-      </c>
-      <c r="B51" s="8" t="s">
+      <c r="A51" s="1">
+        <v>1000</v>
+      </c>
+      <c r="B51" t="s">
         <v>14</v>
       </c>
-      <c r="C51" s="7" t="s">
+      <c r="C51" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="D51" s="8" t="s">
+      <c r="D51" t="s">
         <v>186</v>
       </c>
-      <c r="E51" s="7" t="s">
+      <c r="E51" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="F51" s="8" t="s">
+      <c r="F51" t="s">
         <v>188</v>
       </c>
-      <c r="G51" s="7" t="s">
+      <c r="G51" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H51" s="8">
+      <c r="H51">
         <v>80</v>
       </c>
-      <c r="I51" s="7">
+      <c r="I51" s="1">
         <v>39</v>
       </c>
-      <c r="J51" s="6" t="s">
+      <c r="J51" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="K51" s="7" t="s">
+      <c r="K51" s="1" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="G66" s="9" t="s">
+      <c r="G66" s="6" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A67" s="7" t="s">
+      <c r="A67" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B67" s="8" t="s">
+      <c r="B67" t="s">
         <v>1</v>
       </c>
-      <c r="C67" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D67" s="8" t="s">
+      <c r="C67" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D67" t="s">
         <v>3</v>
       </c>
-      <c r="E67" s="7" t="s">
+      <c r="E67" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F67" s="8" t="s">
+      <c r="F67" t="s">
         <v>5</v>
       </c>
-      <c r="G67" s="7" t="s">
+      <c r="G67" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H67" s="8" t="s">
+      <c r="H67" t="s">
         <v>7</v>
       </c>
-      <c r="I67" s="7" t="s">
+      <c r="I67" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J67" s="8" t="s">
+      <c r="J67" t="s">
         <v>9</v>
       </c>
-      <c r="K67" s="8" t="s">
+      <c r="K67" t="s">
         <v>10</v>
       </c>
-      <c r="L67" s="8" t="s">
+      <c r="L67" t="s">
         <v>11</v>
       </c>
-      <c r="M67" s="8" t="s">
+      <c r="M67" t="s">
         <v>12</v>
       </c>
-      <c r="N67" s="8" t="s">
+      <c r="N67" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A68" s="7">
-        <v>1000</v>
-      </c>
-      <c r="B68" s="8" t="s">
+      <c r="A68" s="1">
+        <v>1000</v>
+      </c>
+      <c r="B68" t="s">
         <v>14</v>
       </c>
-      <c r="C68" s="7">
+      <c r="C68" s="1">
         <v>165</v>
       </c>
-      <c r="D68" s="8" t="s">
+      <c r="D68" t="s">
         <v>137</v>
       </c>
-      <c r="E68" s="7">
+      <c r="E68" s="1">
         <v>512</v>
       </c>
-      <c r="F68" s="8" t="s">
+      <c r="F68" t="s">
         <v>138</v>
       </c>
-      <c r="G68" s="7">
+      <c r="G68" s="1">
         <v>154</v>
       </c>
-      <c r="H68" s="8" t="s">
+      <c r="H68" t="s">
         <v>139</v>
       </c>
-      <c r="K68" s="6" t="s">
+      <c r="K68" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="L68" s="8" t="s">
+      <c r="L68" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A69" s="7">
-        <v>1000</v>
-      </c>
-      <c r="B69" s="8" t="s">
+      <c r="A69" s="1">
+        <v>1000</v>
+      </c>
+      <c r="B69" t="s">
         <v>14</v>
       </c>
-      <c r="C69" s="7">
+      <c r="C69" s="1">
         <v>323</v>
       </c>
-      <c r="D69" s="8" t="s">
+      <c r="D69" t="s">
         <v>142</v>
       </c>
-      <c r="E69" s="7">
+      <c r="E69" s="1">
         <v>512</v>
       </c>
-      <c r="F69" s="8" t="s">
+      <c r="F69" t="s">
         <v>143</v>
       </c>
-      <c r="I69" s="7">
-        <v>2</v>
-      </c>
-      <c r="J69" s="8" t="s">
+      <c r="I69" s="1">
+        <v>2</v>
+      </c>
+      <c r="J69" t="s">
         <v>144</v>
       </c>
-      <c r="K69" s="8" t="s">
+      <c r="K69" t="s">
         <v>145</v>
       </c>
-      <c r="L69" s="8" t="s">
+      <c r="L69" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A70" s="7">
-        <v>1000</v>
-      </c>
-      <c r="B70" s="8" t="s">
+      <c r="A70" s="1">
+        <v>1000</v>
+      </c>
+      <c r="B70" t="s">
         <v>44</v>
       </c>
-      <c r="C70" s="7">
-        <v>175</v>
-      </c>
-      <c r="D70" s="8" t="s">
+      <c r="C70" s="1">
+        <v>175</v>
+      </c>
+      <c r="D70" t="s">
         <v>149</v>
       </c>
-      <c r="E70" s="7">
+      <c r="E70" s="1">
         <v>512</v>
       </c>
-      <c r="F70" s="8" t="s">
+      <c r="F70" t="s">
         <v>150</v>
       </c>
-      <c r="I70" s="7">
-        <v>2</v>
-      </c>
-      <c r="J70" s="8" t="s">
+      <c r="I70" s="1">
+        <v>2</v>
+      </c>
+      <c r="J70" t="s">
         <v>151</v>
       </c>
-      <c r="K70" s="6" t="s">
+      <c r="K70" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="L70" s="8" t="s">
+      <c r="L70" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A71" s="7">
-        <v>1000</v>
-      </c>
-      <c r="B71" s="8" t="s">
+      <c r="A71" s="1">
+        <v>1000</v>
+      </c>
+      <c r="B71" t="s">
         <v>44</v>
       </c>
-      <c r="C71" s="7">
-        <v>175</v>
-      </c>
-      <c r="D71" s="8" t="s">
+      <c r="C71" s="1">
+        <v>175</v>
+      </c>
+      <c r="D71" t="s">
         <v>159</v>
       </c>
-      <c r="E71" s="7">
+      <c r="E71" s="1">
         <v>512</v>
       </c>
-      <c r="F71" s="8" t="s">
+      <c r="F71" t="s">
         <v>160</v>
       </c>
-      <c r="G71" s="7">
+      <c r="G71" s="1">
         <v>154</v>
       </c>
-      <c r="H71" s="8" t="s">
+      <c r="H71" t="s">
         <v>161</v>
       </c>
-      <c r="K71" s="6" t="s">
+      <c r="K71" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="L71" s="8" t="s">
+      <c r="L71" t="s">
         <v>163</v>
       </c>
-      <c r="N71" s="8" t="s">
+      <c r="N71" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A72" s="7">
-        <v>1000</v>
-      </c>
-      <c r="B72" s="8" t="s">
+      <c r="A72" s="1">
+        <v>1000</v>
+      </c>
+      <c r="B72" t="s">
         <v>33</v>
       </c>
-      <c r="C72" s="7">
-        <v>175</v>
-      </c>
-      <c r="D72" s="8" t="s">
+      <c r="C72" s="1">
+        <v>175</v>
+      </c>
+      <c r="D72" t="s">
         <v>153</v>
       </c>
-      <c r="E72" s="7">
+      <c r="E72" s="1">
         <v>512</v>
       </c>
-      <c r="F72" s="8" t="s">
+      <c r="F72" t="s">
         <v>154</v>
       </c>
-      <c r="I72" s="7">
-        <v>2</v>
-      </c>
-      <c r="J72" s="8" t="s">
+      <c r="I72" s="1">
+        <v>2</v>
+      </c>
+      <c r="J72" t="s">
         <v>155</v>
       </c>
-      <c r="K72" s="6" t="s">
+      <c r="K72" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="L72" s="8" t="s">
+      <c r="L72" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A73" s="7">
-        <v>1000</v>
-      </c>
-      <c r="B73" s="8" t="s">
+      <c r="A73" s="1">
+        <v>1000</v>
+      </c>
+      <c r="B73" t="s">
         <v>164</v>
       </c>
-      <c r="C73" s="7">
-        <v>175</v>
-      </c>
-      <c r="D73" s="8" t="s">
+      <c r="C73" s="1">
+        <v>175</v>
+      </c>
+      <c r="D73" t="s">
         <v>165</v>
       </c>
-      <c r="E73" s="7">
+      <c r="E73" s="1">
         <v>512</v>
       </c>
-      <c r="F73" s="8" t="s">
+      <c r="F73" t="s">
         <v>166</v>
       </c>
-      <c r="G73" s="7">
+      <c r="G73" s="1">
         <v>154</v>
       </c>
-      <c r="H73" s="8" t="s">
+      <c r="H73" t="s">
         <v>167</v>
       </c>
-      <c r="K73" s="6" t="s">
+      <c r="K73" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="L73" s="8" t="s">
+      <c r="L73" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A74" s="7">
-        <v>1000</v>
-      </c>
-      <c r="B74" s="8" t="s">
+      <c r="A74" s="1">
+        <v>1000</v>
+      </c>
+      <c r="B74" t="s">
         <v>22</v>
       </c>
-      <c r="C74" s="7">
-        <v>175</v>
-      </c>
-      <c r="D74" s="8" t="s">
+      <c r="C74" s="1">
+        <v>175</v>
+      </c>
+      <c r="D74" t="s">
         <v>170</v>
       </c>
-      <c r="E74" s="7">
+      <c r="E74" s="1">
         <v>512</v>
       </c>
-      <c r="F74" s="8" t="s">
+      <c r="F74" t="s">
         <v>171</v>
       </c>
-      <c r="G74" s="7">
+      <c r="G74" s="1">
         <v>154</v>
       </c>
-      <c r="H74" s="8" t="s">
+      <c r="H74" t="s">
         <v>172</v>
       </c>
-      <c r="K74" s="10" t="s">
+      <c r="K74" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="L74" s="8" t="s">
+      <c r="L74" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A75" s="7">
-        <v>1000</v>
-      </c>
-      <c r="B75" s="8" t="s">
+      <c r="A75" s="1">
+        <v>1000</v>
+      </c>
+      <c r="B75" t="s">
         <v>22</v>
       </c>
-      <c r="C75" s="7">
-        <v>175</v>
-      </c>
-      <c r="D75" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="E75" s="7">
+      <c r="C75" s="1">
+        <v>175</v>
+      </c>
+      <c r="D75" t="s">
+        <v>175</v>
+      </c>
+      <c r="E75" s="1">
         <v>512</v>
       </c>
-      <c r="F75" s="8" t="s">
+      <c r="F75" t="s">
         <v>176</v>
       </c>
-      <c r="I75" s="7">
-        <v>2</v>
-      </c>
-      <c r="J75" s="8" t="s">
+      <c r="I75" s="1">
+        <v>2</v>
+      </c>
+      <c r="J75" t="s">
         <v>177</v>
       </c>
-      <c r="K75" s="10" t="s">
+      <c r="K75" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="L75" s="8" t="s">
+      <c r="L75" t="s">
         <v>179</v>
       </c>
     </row>
@@ -4057,7 +3928,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:L33"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -4074,81 +3945,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A1" s="7"/>
-      <c r="B1" s="8"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="9" t="s">
+      <c r="A1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="G1" s="6" t="s">
         <v>296</v>
       </c>
-      <c r="H1" s="8"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
+      <c r="I1" s="1"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" s="7"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
+      <c r="A2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="I2" s="1"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3" s="7"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
+      <c r="A3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="I3" s="1"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" t="s">
         <v>1</v>
       </c>
-      <c r="G4" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="H4" s="8" t="s">
+      <c r="G4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H4" t="s">
         <v>3</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="I4" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="J4" t="s">
         <v>11</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="K4" t="s">
         <v>12</v>
       </c>
-      <c r="L4" s="8" t="s">
+      <c r="L4" t="s">
         <v>13</v>
       </c>
     </row>
@@ -4197,7 +4050,7 @@
       <c r="H7" t="s">
         <v>299</v>
       </c>
-      <c r="I7" s="11" t="s">
+      <c r="I7" s="5" t="s">
         <v>300</v>
       </c>
       <c r="J7" t="s">
@@ -4223,7 +4076,7 @@
       <c r="H9" t="s">
         <v>303</v>
       </c>
-      <c r="I9" s="12" t="s">
+      <c r="I9" s="5" t="s">
         <v>304</v>
       </c>
       <c r="J9" t="s">
@@ -4237,7 +4090,7 @@
       <c r="D11">
         <v>2</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="E11" t="s">
         <v>306</v>
       </c>
       <c r="F11" t="s">
@@ -4249,7 +4102,7 @@
       <c r="H11" t="s">
         <v>233</v>
       </c>
-      <c r="I11" s="12" t="s">
+      <c r="I11" s="5" t="s">
         <v>219</v>
       </c>
       <c r="J11" t="s">
@@ -4257,38 +4110,32 @@
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A12" s="8"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
+      <c r="B12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="H12" s="1"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A13" s="24">
-        <v>1000</v>
-      </c>
-      <c r="B13" s="24"/>
-      <c r="C13" s="24"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="24" t="s">
+      <c r="A13" s="12">
+        <v>1000</v>
+      </c>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="G13" s="24">
+      <c r="G13" s="12">
         <v>245</v>
       </c>
-      <c r="H13" s="24" t="s">
+      <c r="H13" s="12" t="s">
         <v>256</v>
       </c>
-      <c r="I13" s="25" t="s">
+      <c r="I13" s="14" t="s">
         <v>311</v>
       </c>
-      <c r="J13" s="24" t="s">
+      <c r="J13" s="12" t="s">
         <v>312</v>
       </c>
     </row>
@@ -4305,7 +4152,7 @@
       <c r="H15" t="s">
         <v>308</v>
       </c>
-      <c r="I15" s="12" t="s">
+      <c r="I15" s="5" t="s">
         <v>309</v>
       </c>
       <c r="J15" t="s">
@@ -4325,7 +4172,7 @@
       <c r="H17" t="s">
         <v>314</v>
       </c>
-      <c r="I17" s="12" t="s">
+      <c r="I17" s="5" t="s">
         <v>315</v>
       </c>
       <c r="J17" t="s">
@@ -4345,7 +4192,7 @@
       <c r="H19" t="s">
         <v>175</v>
       </c>
-      <c r="I19" s="12" t="s">
+      <c r="I19" s="5" t="s">
         <v>317</v>
       </c>
       <c r="J19" t="s">
@@ -4353,61 +4200,61 @@
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A30" s="27" t="s">
+      <c r="A30" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="B30" s="27"/>
-      <c r="C30" s="27"/>
-      <c r="D30" s="27"/>
-      <c r="E30" s="27"/>
-      <c r="F30" s="28" t="s">
+      <c r="B30" s="15"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="G30" s="28"/>
-      <c r="H30" s="28"/>
-      <c r="I30" s="28"/>
-      <c r="J30" s="28"/>
+      <c r="G30" s="16"/>
+      <c r="H30" s="16"/>
+      <c r="I30" s="16"/>
+      <c r="J30" s="16"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A31" s="8" t="s">
+      <c r="A31" t="s">
         <v>181</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="B31" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="C31" t="s">
         <v>183</v>
       </c>
-      <c r="D31" s="7" t="s">
+      <c r="D31" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E31" s="8" t="s">
+      <c r="E31" t="s">
         <v>11</v>
       </c>
-      <c r="F31" s="8" t="s">
+      <c r="F31" t="s">
         <v>181</v>
       </c>
-      <c r="G31" s="7" t="s">
+      <c r="G31" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="H31" s="8" t="s">
+      <c r="H31" t="s">
         <v>189</v>
       </c>
-      <c r="I31" s="7" t="s">
+      <c r="I31" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J31" s="8" t="s">
+      <c r="J31" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A32" s="8" t="s">
+      <c r="A32" t="s">
         <v>14</v>
       </c>
-      <c r="B32" s="7">
+      <c r="B32" s="1">
         <v>290</v>
       </c>
-      <c r="C32" s="8">
+      <c r="C32">
         <v>107</v>
       </c>
       <c r="D32" t="s">
@@ -4416,19 +4263,19 @@
       <c r="E32" t="s">
         <v>607</v>
       </c>
-      <c r="F32" s="7" t="s">
+      <c r="F32" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G32" s="8">
+      <c r="G32">
         <v>115</v>
       </c>
-      <c r="H32" s="7">
+      <c r="H32" s="1">
         <v>31</v>
       </c>
-      <c r="I32" s="6" t="s">
+      <c r="I32" s="5" t="s">
         <v>608</v>
       </c>
-      <c r="J32" s="7" t="s">
+      <c r="J32" s="1" t="s">
         <v>609</v>
       </c>
     </row>
@@ -4442,7 +4289,7 @@
       <c r="C33">
         <v>275</v>
       </c>
-      <c r="D33" s="12" t="s">
+      <c r="D33" s="5" t="s">
         <v>311</v>
       </c>
       <c r="E33" t="s">
@@ -4457,10 +4304,10 @@
       <c r="H33">
         <v>91</v>
       </c>
-      <c r="I33" s="12" t="s">
+      <c r="I33" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="J33" s="14">
+      <c r="J33" s="1">
         <v>76609</v>
       </c>
     </row>
@@ -4475,7 +4322,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:L58"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -4493,81 +4340,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A1" s="7"/>
-      <c r="B1" s="8"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="9" t="s">
+      <c r="A1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="G1" s="6" t="s">
         <v>373</v>
       </c>
-      <c r="H1" s="8"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
+      <c r="I1" s="1"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" s="7"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
+      <c r="A2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="I2" s="1"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3" s="7"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
+      <c r="A3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="I3" s="1"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" t="s">
         <v>1</v>
       </c>
-      <c r="G4" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="H4" s="8" t="s">
+      <c r="G4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H4" t="s">
         <v>3</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="I4" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="J4" t="s">
         <v>11</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="K4" t="s">
         <v>12</v>
       </c>
-      <c r="L4" s="8" t="s">
+      <c r="L4" t="s">
         <v>13</v>
       </c>
     </row>
@@ -4616,7 +4445,7 @@
       <c r="H7" t="s">
         <v>404</v>
       </c>
-      <c r="I7" s="11" t="s">
+      <c r="I7" s="5" t="s">
         <v>156</v>
       </c>
       <c r="J7" t="s">
@@ -4642,7 +4471,7 @@
       <c r="H9" t="s">
         <v>410</v>
       </c>
-      <c r="I9" s="12" t="s">
+      <c r="I9" s="5" t="s">
         <v>411</v>
       </c>
       <c r="J9" t="s">
@@ -4656,7 +4485,7 @@
       <c r="D11">
         <v>2</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="E11" t="s">
         <v>406</v>
       </c>
       <c r="F11" t="s">
@@ -4668,7 +4497,7 @@
       <c r="H11" t="s">
         <v>175</v>
       </c>
-      <c r="I11" s="12" t="s">
+      <c r="I11" s="5" t="s">
         <v>407</v>
       </c>
       <c r="J11" t="s">
@@ -4676,38 +4505,32 @@
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A12" s="8"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
+      <c r="B12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="H12" s="1"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A13" s="24">
-        <v>1000</v>
-      </c>
-      <c r="B13" s="24"/>
-      <c r="C13" s="24"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="24" t="s">
+      <c r="A13" s="12">
+        <v>1000</v>
+      </c>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="G13" s="24">
+      <c r="G13" s="12">
         <v>253</v>
       </c>
-      <c r="H13" s="24" t="s">
+      <c r="H13" s="12" t="s">
         <v>374</v>
       </c>
-      <c r="I13" s="25" t="s">
+      <c r="I13" s="14" t="s">
         <v>375</v>
       </c>
-      <c r="J13" s="24" t="s">
+      <c r="J13" s="12" t="s">
         <v>376</v>
       </c>
     </row>
@@ -4724,14 +4547,14 @@
       <c r="H15" t="s">
         <v>379</v>
       </c>
-      <c r="I15" s="12" t="s">
+      <c r="I15" s="5" t="s">
         <v>168</v>
       </c>
       <c r="J15" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>1000</v>
       </c>
@@ -4744,14 +4567,14 @@
       <c r="H17" t="s">
         <v>381</v>
       </c>
-      <c r="I17" s="12" t="s">
+      <c r="I17" s="5" t="s">
         <v>383</v>
       </c>
       <c r="J17" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>1000</v>
       </c>
@@ -4764,69 +4587,69 @@
       <c r="H19" t="s">
         <v>382</v>
       </c>
-      <c r="I19" s="12" t="s">
+      <c r="I19" s="5" t="s">
         <v>385</v>
       </c>
       <c r="J19" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A24" s="27" t="s">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A24" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="B24" s="27"/>
-      <c r="C24" s="27"/>
-      <c r="D24" s="27"/>
-      <c r="E24" s="27"/>
-      <c r="F24" s="28" t="s">
+      <c r="B24" s="15"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="G24" s="28"/>
-      <c r="H24" s="28"/>
-      <c r="I24" s="28"/>
-      <c r="J24" s="28"/>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A25" s="8" t="s">
+      <c r="G24" s="16"/>
+      <c r="H24" s="16"/>
+      <c r="I24" s="16"/>
+      <c r="J24" s="16"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
         <v>181</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" t="s">
         <v>183</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="D25" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E25" s="8" t="s">
+      <c r="E25" t="s">
         <v>11</v>
       </c>
-      <c r="F25" s="8" t="s">
+      <c r="F25" t="s">
         <v>181</v>
       </c>
-      <c r="G25" s="7" t="s">
+      <c r="G25" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="H25" s="8" t="s">
+      <c r="H25" t="s">
         <v>189</v>
       </c>
-      <c r="I25" s="7" t="s">
+      <c r="I25" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J25" s="8" t="s">
+      <c r="J25" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A26" s="8" t="s">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
         <v>14</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B26" s="1">
         <v>296</v>
       </c>
-      <c r="C26" s="8">
+      <c r="C26">
         <v>108</v>
       </c>
       <c r="D26" t="s">
@@ -4835,23 +4658,23 @@
       <c r="E26" t="s">
         <v>612</v>
       </c>
-      <c r="F26" s="7" t="s">
+      <c r="F26" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G26" s="8">
+      <c r="G26">
         <v>111</v>
       </c>
-      <c r="H26" s="7">
+      <c r="H26" s="1">
         <v>26</v>
       </c>
-      <c r="I26" s="6" t="s">
+      <c r="I26" s="5" t="s">
         <v>411</v>
       </c>
-      <c r="J26" s="7" t="s">
+      <c r="J26" s="1" t="s">
         <v>613</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>14</v>
       </c>
@@ -4861,7 +4684,7 @@
       <c r="C27">
         <v>255</v>
       </c>
-      <c r="D27" s="12" t="s">
+      <c r="D27" s="5" t="s">
         <v>375</v>
       </c>
       <c r="E27" t="s">
@@ -4876,89 +4699,71 @@
       <c r="H27">
         <v>81</v>
       </c>
-      <c r="I27" s="12" t="s">
+      <c r="I27" s="5" t="s">
         <v>377</v>
       </c>
-      <c r="J27" s="14" t="s">
+      <c r="J27" s="1" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A32" s="7"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="9" t="s">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="G32" s="6" t="s">
         <v>387</v>
       </c>
-      <c r="H32" s="8"/>
-      <c r="I32" s="7"/>
-      <c r="J32" s="8"/>
-      <c r="K32" s="8"/>
+      <c r="I32" s="1"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A33" s="7"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="8"/>
-      <c r="G33" s="7"/>
-      <c r="H33" s="8"/>
-      <c r="I33" s="7"/>
-      <c r="J33" s="8"/>
-      <c r="K33" s="8"/>
+      <c r="A33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="I33" s="1"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A34" s="7"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="7"/>
-      <c r="H34" s="8"/>
-      <c r="I34" s="7"/>
-      <c r="J34" s="8"/>
-      <c r="K34" s="8"/>
+      <c r="A34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="I34" s="1"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A35" s="7" t="s">
+      <c r="A35" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B35" s="7" t="s">
+      <c r="B35" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="C35" t="s">
         <v>7</v>
       </c>
-      <c r="D35" s="7" t="s">
+      <c r="D35" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E35" s="8" t="s">
+      <c r="E35" t="s">
         <v>9</v>
       </c>
-      <c r="F35" s="8" t="s">
+      <c r="F35" t="s">
         <v>1</v>
       </c>
-      <c r="G35" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="H35" s="8" t="s">
+      <c r="G35" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H35" t="s">
         <v>3</v>
       </c>
-      <c r="I35" s="8" t="s">
+      <c r="I35" t="s">
         <v>10</v>
       </c>
-      <c r="J35" s="8" t="s">
+      <c r="J35" t="s">
         <v>11</v>
       </c>
-      <c r="K35" s="8" t="s">
+      <c r="K35" t="s">
         <v>12</v>
       </c>
-      <c r="L35" s="8" t="s">
+      <c r="L35" t="s">
         <v>13</v>
       </c>
     </row>
@@ -4986,7 +4791,7 @@
       <c r="G38">
         <v>175</v>
       </c>
-      <c r="I38" s="11"/>
+      <c r="I38" s="5"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A40">
@@ -5001,7 +4806,7 @@
       <c r="G40">
         <v>175</v>
       </c>
-      <c r="I40" s="12"/>
+      <c r="I40" s="5"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A42">
@@ -5010,26 +4815,19 @@
       <c r="D42">
         <v>2</v>
       </c>
-      <c r="E42" s="13"/>
       <c r="F42" t="s">
         <v>22</v>
       </c>
       <c r="G42">
         <v>175</v>
       </c>
-      <c r="I42" s="12"/>
+      <c r="I42" s="5"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A43" s="8"/>
-      <c r="B43" s="7"/>
-      <c r="C43" s="8"/>
-      <c r="D43" s="7"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="7"/>
-      <c r="G43" s="8"/>
-      <c r="H43" s="7"/>
-      <c r="I43" s="8"/>
-      <c r="J43" s="8"/>
+      <c r="B43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="H43" s="1"/>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A44">
@@ -5044,7 +4842,7 @@
       <c r="H44" t="s">
         <v>388</v>
       </c>
-      <c r="I44" s="12" t="s">
+      <c r="I44" s="5" t="s">
         <v>389</v>
       </c>
       <c r="J44" t="s">
@@ -5064,7 +4862,7 @@
       <c r="H46" t="s">
         <v>393</v>
       </c>
-      <c r="I46" s="12" t="s">
+      <c r="I46" s="5" t="s">
         <v>394</v>
       </c>
       <c r="J46" t="s">
@@ -5084,7 +4882,7 @@
       <c r="H48" t="s">
         <v>399</v>
       </c>
-      <c r="I48" s="12" t="s">
+      <c r="I48" s="5" t="s">
         <v>400</v>
       </c>
       <c r="J48" t="s">
@@ -5104,7 +4902,7 @@
       <c r="H50" t="s">
         <v>396</v>
       </c>
-      <c r="I50" s="12" t="s">
+      <c r="I50" s="5" t="s">
         <v>397</v>
       </c>
       <c r="J50" t="s">
@@ -5112,66 +4910,64 @@
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A55" s="27" t="s">
+      <c r="A55" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="B55" s="27"/>
-      <c r="C55" s="27"/>
-      <c r="D55" s="27"/>
-      <c r="E55" s="27"/>
-      <c r="F55" s="28" t="s">
+      <c r="B55" s="15"/>
+      <c r="C55" s="15"/>
+      <c r="D55" s="15"/>
+      <c r="E55" s="15"/>
+      <c r="F55" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="G55" s="28"/>
-      <c r="H55" s="28"/>
-      <c r="I55" s="28"/>
-      <c r="J55" s="28"/>
+      <c r="G55" s="16"/>
+      <c r="H55" s="16"/>
+      <c r="I55" s="16"/>
+      <c r="J55" s="16"/>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A56" s="8" t="s">
+      <c r="A56" t="s">
         <v>181</v>
       </c>
-      <c r="B56" s="7" t="s">
+      <c r="B56" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="C56" s="8" t="s">
+      <c r="C56" t="s">
         <v>183</v>
       </c>
-      <c r="D56" s="7" t="s">
+      <c r="D56" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E56" s="8" t="s">
+      <c r="E56" t="s">
         <v>11</v>
       </c>
-      <c r="F56" s="8" t="s">
+      <c r="F56" t="s">
         <v>181</v>
       </c>
-      <c r="G56" s="7" t="s">
+      <c r="G56" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="H56" s="8" t="s">
+      <c r="H56" t="s">
         <v>189</v>
       </c>
-      <c r="I56" s="7" t="s">
+      <c r="I56" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J56" s="8" t="s">
+      <c r="J56" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A57" s="8" t="s">
+      <c r="A57" t="s">
         <v>14</v>
       </c>
-      <c r="B57" s="7"/>
-      <c r="C57" s="8"/>
-      <c r="F57" s="7" t="s">
+      <c r="B57" s="1"/>
+      <c r="F57" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G57" s="8"/>
-      <c r="H57" s="7"/>
-      <c r="I57" s="6"/>
-      <c r="J57" s="7"/>
+      <c r="H57" s="1"/>
+      <c r="I57" s="5"/>
+      <c r="J57" s="1"/>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
@@ -5183,7 +4979,7 @@
       <c r="C58">
         <v>137</v>
       </c>
-      <c r="D58" s="12" t="s">
+      <c r="D58" s="5" t="s">
         <v>389</v>
       </c>
       <c r="E58" t="s">
@@ -5198,10 +4994,10 @@
       <c r="H58">
         <v>64</v>
       </c>
-      <c r="I58" s="12" t="s">
+      <c r="I58" s="5" t="s">
         <v>391</v>
       </c>
-      <c r="J58" s="14" t="s">
+      <c r="J58" s="1" t="s">
         <v>392</v>
       </c>
     </row>
@@ -5217,7 +5013,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:N21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -5237,463 +5033,347 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A1" s="7"/>
-      <c r="B1" s="8"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="9" t="s">
+      <c r="A1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="G1" s="6" t="s">
         <v>413</v>
       </c>
-      <c r="H1" s="8"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
+      <c r="I1" s="1"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A2" s="7"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
+      <c r="A2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="I2" s="1"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A3" s="7"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
+      <c r="A3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="I3" s="1"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" t="s">
         <v>1</v>
       </c>
-      <c r="I4" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="J4" s="8" t="s">
+      <c r="I4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J4" t="s">
         <v>3</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="K4" t="s">
         <v>10</v>
       </c>
-      <c r="L4" s="8" t="s">
+      <c r="L4" t="s">
         <v>11</v>
       </c>
-      <c r="M4" s="8" t="s">
+      <c r="M4" t="s">
         <v>12</v>
       </c>
-      <c r="N4" s="8" t="s">
+      <c r="N4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A5" s="3">
-        <v>1000</v>
-      </c>
-      <c r="B5" s="3">
+      <c r="A5" s="2">
+        <v>1000</v>
+      </c>
+      <c r="B5" s="2">
         <v>512</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" t="s">
         <v>414</v>
       </c>
-      <c r="D5" s="7"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="3">
-        <v>2</v>
-      </c>
-      <c r="G5" s="7" t="s">
+      <c r="D5" s="1"/>
+      <c r="F5" s="2">
+        <v>2</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H5" t="s">
         <v>14</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="2">
         <v>289</v>
       </c>
-      <c r="J5" s="8" t="s">
+      <c r="J5" t="s">
         <v>15</v>
       </c>
-      <c r="K5" s="8" t="s">
+      <c r="K5" t="s">
         <v>416</v>
       </c>
-      <c r="L5" s="8" t="s">
+      <c r="L5" t="s">
         <v>417</v>
       </c>
-      <c r="M5" s="8"/>
-      <c r="N5" s="8"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
-      <c r="M6" s="8"/>
-      <c r="N6" s="8"/>
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="F6" s="1"/>
+      <c r="I6" s="2"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A7" s="3">
-        <v>1000</v>
-      </c>
-      <c r="B7" s="3">
+      <c r="A7" s="2">
+        <v>1000</v>
+      </c>
+      <c r="B7" s="2">
         <v>512</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" t="s">
         <v>424</v>
       </c>
-      <c r="D7" s="7"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="3">
-        <v>2</v>
-      </c>
-      <c r="G7" s="8" t="s">
+      <c r="D7" s="1"/>
+      <c r="F7" s="2">
+        <v>2</v>
+      </c>
+      <c r="G7" t="s">
         <v>425</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="H7" t="s">
         <v>22</v>
       </c>
-      <c r="I7" s="3">
-        <v>175</v>
-      </c>
-      <c r="J7" s="8" t="s">
+      <c r="I7" s="2">
+        <v>175</v>
+      </c>
+      <c r="J7" t="s">
         <v>389</v>
       </c>
-      <c r="K7" s="6" t="s">
+      <c r="K7" s="5" t="s">
         <v>426</v>
       </c>
-      <c r="L7" s="8" t="s">
+      <c r="L7" t="s">
         <v>427</v>
       </c>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="N8" s="8"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A9" s="3">
-        <v>1000</v>
-      </c>
-      <c r="B9" s="3">
+      <c r="A9" s="2">
+        <v>1000</v>
+      </c>
+      <c r="B9" s="2">
         <v>512</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" t="s">
         <v>419</v>
       </c>
-      <c r="D9" s="7"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="3">
-        <v>2</v>
-      </c>
-      <c r="G9" s="8" t="s">
+      <c r="D9" s="1"/>
+      <c r="F9" s="2">
+        <v>2</v>
+      </c>
+      <c r="G9" t="s">
         <v>420</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" t="s">
         <v>33</v>
       </c>
-      <c r="I9" s="3">
-        <v>175</v>
-      </c>
-      <c r="J9" s="8" t="s">
+      <c r="I9" s="2">
+        <v>175</v>
+      </c>
+      <c r="J9" t="s">
         <v>421</v>
       </c>
-      <c r="K9" s="6" t="s">
+      <c r="K9" s="5" t="s">
         <v>422</v>
       </c>
-      <c r="L9" s="8" t="s">
+      <c r="L9" t="s">
         <v>423</v>
       </c>
-      <c r="M9" s="8"/>
-      <c r="N9" s="8"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8"/>
-      <c r="N10" s="8"/>
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="F10" s="1"/>
+      <c r="I10" s="2"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A11" s="3">
-        <v>1000</v>
-      </c>
-      <c r="B11" s="3">
+      <c r="A11" s="2">
+        <v>1000</v>
+      </c>
+      <c r="B11" s="2">
         <v>512</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" t="s">
         <v>428</v>
       </c>
-      <c r="D11" s="7"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="3">
-        <v>2</v>
-      </c>
-      <c r="G11" s="8" t="s">
+      <c r="D11" s="1"/>
+      <c r="F11" s="2">
+        <v>2</v>
+      </c>
+      <c r="G11" t="s">
         <v>430</v>
       </c>
-      <c r="H11" s="8" t="s">
+      <c r="H11" t="s">
         <v>44</v>
       </c>
-      <c r="I11" s="3">
-        <v>175</v>
-      </c>
-      <c r="J11" s="8" t="s">
+      <c r="I11" s="2">
+        <v>175</v>
+      </c>
+      <c r="J11" t="s">
         <v>431</v>
       </c>
-      <c r="K11" s="8" t="s">
+      <c r="K11" t="s">
         <v>429</v>
       </c>
-      <c r="L11" s="8" t="s">
+      <c r="L11" t="s">
         <v>432</v>
       </c>
-      <c r="M11" s="8"/>
-      <c r="N11" s="8"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="N12" s="8"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="8"/>
-      <c r="M13" s="8"/>
-      <c r="N13" s="8"/>
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="I13" s="1"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8"/>
-      <c r="L14" s="8"/>
-      <c r="M14" s="8"/>
-      <c r="N14" s="8"/>
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="I14" s="1"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="8"/>
-      <c r="M15" s="8"/>
-      <c r="N15" s="8"/>
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="I15" s="1"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B16" s="8"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8"/>
-      <c r="L16" s="8"/>
-      <c r="M16" s="8"/>
-      <c r="N16" s="8"/>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A17" s="7"/>
-      <c r="B17" s="27" t="s">
+      <c r="C16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="I16" s="1"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A17" s="1"/>
+      <c r="B17" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="C17" s="27"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="27"/>
-      <c r="F17" s="27"/>
-      <c r="G17" s="28" t="s">
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="H17" s="28"/>
-      <c r="I17" s="28"/>
-      <c r="J17" s="28"/>
-      <c r="K17" s="28"/>
-      <c r="L17" s="8"/>
-      <c r="M17" s="8"/>
-      <c r="N17" s="8"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A18" s="7"/>
-      <c r="B18" s="8" t="s">
+      <c r="H17" s="16"/>
+      <c r="I17" s="16"/>
+      <c r="J17" s="16"/>
+      <c r="K17" s="16"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A18" s="1"/>
+      <c r="B18" t="s">
         <v>181</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" t="s">
         <v>183</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F18" s="8" t="s">
+      <c r="F18" t="s">
         <v>11</v>
       </c>
-      <c r="G18" s="8" t="s">
+      <c r="G18" t="s">
         <v>181</v>
       </c>
-      <c r="H18" s="7" t="s">
+      <c r="H18" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="I18" s="8" t="s">
+      <c r="I18" t="s">
         <v>189</v>
       </c>
-      <c r="J18" s="7" t="s">
+      <c r="J18" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="K18" s="8" t="s">
+      <c r="K18" t="s">
         <v>11</v>
       </c>
-      <c r="L18" s="8"/>
-      <c r="M18" s="8"/>
-      <c r="N18" s="8"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A19" s="7">
-        <v>1000</v>
-      </c>
-      <c r="B19" s="8" t="s">
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A19" s="1">
+        <v>1000</v>
+      </c>
+      <c r="B19" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="1">
         <v>289</v>
       </c>
-      <c r="D19" s="8">
+      <c r="D19">
         <v>105</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="E19" t="s">
         <v>416</v>
       </c>
-      <c r="F19" s="8" t="s">
+      <c r="F19" t="s">
         <v>417</v>
       </c>
-      <c r="G19" s="7" t="s">
+      <c r="G19" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H19" s="8">
+      <c r="H19">
         <v>127</v>
       </c>
-      <c r="I19" s="7">
+      <c r="I19" s="1">
         <v>53</v>
       </c>
-      <c r="J19" s="6" t="s">
+      <c r="J19" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="K19" s="7">
+      <c r="K19" s="1">
         <v>65340</v>
       </c>
-      <c r="L19" s="8"/>
-      <c r="M19" s="8"/>
-      <c r="N19" s="8"/>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="7"/>
-      <c r="J20" s="8"/>
-      <c r="K20" s="6"/>
-      <c r="L20" s="8"/>
-      <c r="M20" s="8"/>
-      <c r="N20" s="8"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="7"/>
-      <c r="J21" s="8"/>
-      <c r="K21" s="8"/>
-      <c r="L21" s="8"/>
-      <c r="M21" s="8"/>
-      <c r="N21" s="8"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="K20" s="5"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="I21" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5705,8 +5385,8 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N181"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:L181"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -5721,97 +5401,71 @@
     <col min="11" max="11" width="27.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A1" s="7"/>
-      <c r="B1" s="8"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="9" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="G1" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H1" s="8" t="s">
         <v>418</v>
       </c>
-      <c r="I1" s="7"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
-      <c r="M1" s="8"/>
-      <c r="N1" s="8"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A2" s="7"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8"/>
-      <c r="N2" s="8"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A3" s="7"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="8"/>
-      <c r="N3" s="8"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A4" s="7" t="s">
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" t="s">
         <v>1</v>
       </c>
-      <c r="G4" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="H4" s="8" t="s">
+      <c r="G4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H4" t="s">
         <v>3</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="I4" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="J4" t="s">
         <v>11</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="K4" t="s">
         <v>12</v>
       </c>
-      <c r="L4" s="8" t="s">
+      <c r="L4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>1000</v>
       </c>
@@ -5837,7 +5491,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>1000</v>
       </c>
@@ -5856,14 +5510,14 @@
       <c r="H7" t="s">
         <v>194</v>
       </c>
-      <c r="I7" s="11" t="s">
+      <c r="I7" s="5" t="s">
         <v>195</v>
       </c>
       <c r="J7" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>1000</v>
       </c>
@@ -5889,7 +5543,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>1000</v>
       </c>
@@ -5915,82 +5569,76 @@
         <v>206</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A14" s="7" t="s">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A14" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B14" s="8"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A15" s="7"/>
-      <c r="B15" s="27" t="s">
+      <c r="C14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="I14" s="1"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A15" s="1"/>
+      <c r="B15" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="C15" s="27"/>
-      <c r="D15" s="27"/>
-      <c r="E15" s="27"/>
-      <c r="F15" s="27"/>
-      <c r="G15" s="28" t="s">
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="H15" s="28"/>
-      <c r="I15" s="28"/>
-      <c r="J15" s="28"/>
-      <c r="K15" s="28"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A16" s="7"/>
-      <c r="B16" s="8" t="s">
+      <c r="H15" s="16"/>
+      <c r="I15" s="16"/>
+      <c r="J15" s="16"/>
+      <c r="K15" s="16"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A16" s="1"/>
+      <c r="B16" t="s">
         <v>181</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" t="s">
         <v>183</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="F16" t="s">
         <v>11</v>
       </c>
-      <c r="G16" s="8" t="s">
+      <c r="G16" t="s">
         <v>181</v>
       </c>
-      <c r="H16" s="7" t="s">
+      <c r="H16" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="I16" s="8" t="s">
+      <c r="I16" t="s">
         <v>189</v>
       </c>
-      <c r="J16" s="7" t="s">
+      <c r="J16" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="K16" s="8" t="s">
+      <c r="K16" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A17" s="7">
-        <v>1000</v>
-      </c>
-      <c r="B17" s="8" t="s">
+      <c r="A17" s="1">
+        <v>1000</v>
+      </c>
+      <c r="B17" t="s">
         <v>14</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="1" t="s">
         <v>574</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" t="s">
         <v>575</v>
       </c>
       <c r="E17" t="s">
@@ -5999,65 +5647,65 @@
       <c r="F17" t="s">
         <v>573</v>
       </c>
-      <c r="G17" s="7" t="s">
+      <c r="G17" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H17" s="8">
+      <c r="H17">
         <v>126</v>
       </c>
-      <c r="I17" s="7">
+      <c r="I17" s="1">
         <v>38</v>
       </c>
-      <c r="J17" s="6" t="s">
+      <c r="J17" s="5" t="s">
         <v>513</v>
       </c>
-      <c r="K17" s="7" t="s">
+      <c r="K17" s="1" t="s">
         <v>576</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="G20" s="9" t="s">
+      <c r="G20" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="H20" s="16" t="s">
+      <c r="H20" s="8" t="s">
         <v>525</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" t="s">
         <v>7</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D22" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E22" s="8" t="s">
+      <c r="E22" t="s">
         <v>9</v>
       </c>
-      <c r="F22" s="8" t="s">
+      <c r="F22" t="s">
         <v>1</v>
       </c>
-      <c r="G22" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="H22" s="8" t="s">
+      <c r="G22" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H22" t="s">
         <v>3</v>
       </c>
-      <c r="I22" s="8" t="s">
+      <c r="I22" t="s">
         <v>10</v>
       </c>
-      <c r="J22" s="8" t="s">
+      <c r="J22" t="s">
         <v>11</v>
       </c>
-      <c r="K22" s="8" t="s">
+      <c r="K22" t="s">
         <v>12</v>
       </c>
-      <c r="L22" s="8" t="s">
+      <c r="L22" t="s">
         <v>13</v>
       </c>
     </row>
@@ -6106,7 +5754,7 @@
       <c r="H25" t="s">
         <v>434</v>
       </c>
-      <c r="I25" s="11" t="s">
+      <c r="I25" s="5" t="s">
         <v>435</v>
       </c>
       <c r="J25" t="s">
@@ -6158,7 +5806,7 @@
       <c r="H29" t="s">
         <v>218</v>
       </c>
-      <c r="I29" s="12" t="s">
+      <c r="I29" s="5" t="s">
         <v>439</v>
       </c>
       <c r="J29" t="s">
@@ -6166,81 +5814,75 @@
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A32" s="7" t="s">
+      <c r="A32" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B32" s="8"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="7"/>
-      <c r="H32" s="8"/>
-      <c r="I32" s="7"/>
-      <c r="J32" s="8"/>
-      <c r="K32" s="8"/>
+      <c r="C32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="I32" s="1"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A33" s="7"/>
-      <c r="B33" s="27" t="s">
+      <c r="A33" s="1"/>
+      <c r="B33" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="C33" s="27"/>
-      <c r="D33" s="27"/>
-      <c r="E33" s="27"/>
-      <c r="F33" s="27"/>
-      <c r="G33" s="28" t="s">
+      <c r="C33" s="15"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="H33" s="28"/>
-      <c r="I33" s="28"/>
-      <c r="J33" s="28"/>
-      <c r="K33" s="28"/>
+      <c r="H33" s="16"/>
+      <c r="I33" s="16"/>
+      <c r="J33" s="16"/>
+      <c r="K33" s="16"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A34" s="7"/>
-      <c r="B34" s="8" t="s">
+      <c r="A34" s="1"/>
+      <c r="B34" t="s">
         <v>181</v>
       </c>
-      <c r="C34" s="7" t="s">
+      <c r="C34" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="D34" s="8" t="s">
+      <c r="D34" t="s">
         <v>183</v>
       </c>
-      <c r="E34" s="7" t="s">
+      <c r="E34" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F34" s="8" t="s">
+      <c r="F34" t="s">
         <v>11</v>
       </c>
-      <c r="G34" s="8" t="s">
+      <c r="G34" t="s">
         <v>181</v>
       </c>
-      <c r="H34" s="7" t="s">
+      <c r="H34" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="I34" s="8" t="s">
+      <c r="I34" t="s">
         <v>189</v>
       </c>
-      <c r="J34" s="7" t="s">
+      <c r="J34" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="K34" s="8" t="s">
+      <c r="K34" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A35" s="7">
-        <v>1000</v>
-      </c>
-      <c r="B35" s="8" t="s">
+      <c r="A35" s="1">
+        <v>1000</v>
+      </c>
+      <c r="B35" t="s">
         <v>14</v>
       </c>
-      <c r="C35" s="7">
+      <c r="C35" s="1">
         <v>279</v>
       </c>
-      <c r="D35" s="8">
+      <c r="D35">
         <v>96</v>
       </c>
       <c r="E35" t="s">
@@ -6249,65 +5891,65 @@
       <c r="F35" t="s">
         <v>580</v>
       </c>
-      <c r="G35" s="7" t="s">
+      <c r="G35" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H35" s="8">
+      <c r="H35">
         <v>122</v>
       </c>
-      <c r="I35" s="7">
+      <c r="I35" s="1">
         <v>51</v>
       </c>
-      <c r="J35" s="6" t="s">
+      <c r="J35" s="5" t="s">
         <v>513</v>
       </c>
-      <c r="K35" s="7" t="s">
+      <c r="K35" s="1" t="s">
         <v>581</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="G38" s="9" t="s">
+      <c r="G38" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="H38" s="16" t="s">
+      <c r="H38" s="8" t="s">
         <v>526</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A40" s="7" t="s">
+      <c r="A40" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B40" s="7" t="s">
+      <c r="B40" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C40" s="8" t="s">
+      <c r="C40" t="s">
         <v>7</v>
       </c>
-      <c r="D40" s="7" t="s">
+      <c r="D40" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E40" s="8" t="s">
+      <c r="E40" t="s">
         <v>9</v>
       </c>
-      <c r="F40" s="8" t="s">
+      <c r="F40" t="s">
         <v>1</v>
       </c>
-      <c r="G40" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="H40" s="8" t="s">
+      <c r="G40" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H40" t="s">
         <v>3</v>
       </c>
-      <c r="I40" s="8" t="s">
+      <c r="I40" t="s">
         <v>10</v>
       </c>
-      <c r="J40" s="8" t="s">
+      <c r="J40" t="s">
         <v>11</v>
       </c>
-      <c r="K40" s="8" t="s">
+      <c r="K40" t="s">
         <v>12</v>
       </c>
-      <c r="L40" s="8" t="s">
+      <c r="L40" t="s">
         <v>13</v>
       </c>
     </row>
@@ -6356,7 +5998,7 @@
       <c r="H43" t="s">
         <v>532</v>
       </c>
-      <c r="I43" s="11" t="s">
+      <c r="I43" s="5" t="s">
         <v>422</v>
       </c>
       <c r="J43" t="s">
@@ -6408,7 +6050,7 @@
       <c r="H47" t="s">
         <v>539</v>
       </c>
-      <c r="I47" s="12" t="s">
+      <c r="I47" s="5" t="s">
         <v>540</v>
       </c>
       <c r="J47" t="s">
@@ -6416,81 +6058,75 @@
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A50" s="7" t="s">
+      <c r="A50" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B50" s="8"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="7"/>
-      <c r="F50" s="8"/>
-      <c r="G50" s="7"/>
-      <c r="H50" s="8"/>
-      <c r="I50" s="7"/>
-      <c r="J50" s="8"/>
-      <c r="K50" s="8"/>
+      <c r="C50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="I50" s="1"/>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A51" s="7"/>
-      <c r="B51" s="27" t="s">
+      <c r="A51" s="1"/>
+      <c r="B51" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="C51" s="27"/>
-      <c r="D51" s="27"/>
-      <c r="E51" s="27"/>
-      <c r="F51" s="27"/>
-      <c r="G51" s="28" t="s">
+      <c r="C51" s="15"/>
+      <c r="D51" s="15"/>
+      <c r="E51" s="15"/>
+      <c r="F51" s="15"/>
+      <c r="G51" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="H51" s="28"/>
-      <c r="I51" s="28"/>
-      <c r="J51" s="28"/>
-      <c r="K51" s="28"/>
+      <c r="H51" s="16"/>
+      <c r="I51" s="16"/>
+      <c r="J51" s="16"/>
+      <c r="K51" s="16"/>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A52" s="7"/>
-      <c r="B52" s="8" t="s">
+      <c r="A52" s="1"/>
+      <c r="B52" t="s">
         <v>181</v>
       </c>
-      <c r="C52" s="7" t="s">
+      <c r="C52" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="D52" s="8" t="s">
+      <c r="D52" t="s">
         <v>183</v>
       </c>
-      <c r="E52" s="7" t="s">
+      <c r="E52" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F52" s="8" t="s">
+      <c r="F52" t="s">
         <v>11</v>
       </c>
-      <c r="G52" s="8" t="s">
+      <c r="G52" t="s">
         <v>181</v>
       </c>
-      <c r="H52" s="7" t="s">
+      <c r="H52" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="I52" s="8" t="s">
+      <c r="I52" t="s">
         <v>189</v>
       </c>
-      <c r="J52" s="7" t="s">
+      <c r="J52" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="K52" s="8" t="s">
+      <c r="K52" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A53" s="7">
-        <v>1000</v>
-      </c>
-      <c r="B53" s="8" t="s">
+      <c r="A53" s="1">
+        <v>1000</v>
+      </c>
+      <c r="B53" t="s">
         <v>14</v>
       </c>
-      <c r="C53" s="7">
+      <c r="C53" s="1">
         <v>291</v>
       </c>
-      <c r="D53" s="8">
+      <c r="D53">
         <v>92</v>
       </c>
       <c r="E53" t="s">
@@ -6499,65 +6135,65 @@
       <c r="F53" t="s">
         <v>528</v>
       </c>
-      <c r="G53" s="7" t="s">
+      <c r="G53" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H53" s="8">
+      <c r="H53">
         <v>126</v>
       </c>
-      <c r="I53" s="7">
+      <c r="I53" s="1">
         <v>53</v>
       </c>
-      <c r="J53" s="6" t="s">
+      <c r="J53" s="5" t="s">
         <v>529</v>
       </c>
-      <c r="K53" s="7" t="s">
+      <c r="K53" s="1" t="s">
         <v>530</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="G56" s="9" t="s">
+      <c r="G56" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="H56" s="16" t="s">
+      <c r="H56" s="8" t="s">
         <v>542</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A58" s="7" t="s">
+      <c r="A58" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B58" s="7" t="s">
+      <c r="B58" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C58" s="8" t="s">
+      <c r="C58" t="s">
         <v>7</v>
       </c>
-      <c r="D58" s="7" t="s">
+      <c r="D58" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E58" s="8" t="s">
+      <c r="E58" t="s">
         <v>9</v>
       </c>
-      <c r="F58" s="8" t="s">
+      <c r="F58" t="s">
         <v>1</v>
       </c>
-      <c r="G58" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="H58" s="8" t="s">
+      <c r="G58" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H58" t="s">
         <v>3</v>
       </c>
-      <c r="I58" s="8" t="s">
+      <c r="I58" t="s">
         <v>10</v>
       </c>
-      <c r="J58" s="8" t="s">
+      <c r="J58" t="s">
         <v>11</v>
       </c>
-      <c r="K58" s="8" t="s">
+      <c r="K58" t="s">
         <v>12</v>
       </c>
-      <c r="L58" s="8" t="s">
+      <c r="L58" t="s">
         <v>13</v>
       </c>
     </row>
@@ -6606,7 +6242,7 @@
       <c r="H61" t="s">
         <v>544</v>
       </c>
-      <c r="I61" s="11" t="s">
+      <c r="I61" s="5" t="s">
         <v>545</v>
       </c>
       <c r="J61" t="s">
@@ -6658,7 +6294,7 @@
       <c r="H65" t="s">
         <v>548</v>
       </c>
-      <c r="I65" s="12" t="s">
+      <c r="I65" s="5" t="s">
         <v>549</v>
       </c>
       <c r="J65" t="s">
@@ -6666,81 +6302,75 @@
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A68" s="7" t="s">
+      <c r="A68" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B68" s="8"/>
-      <c r="C68" s="7"/>
-      <c r="D68" s="8"/>
-      <c r="E68" s="7"/>
-      <c r="F68" s="8"/>
-      <c r="G68" s="7"/>
-      <c r="H68" s="8"/>
-      <c r="I68" s="7"/>
-      <c r="J68" s="8"/>
-      <c r="K68" s="8"/>
+      <c r="C68" s="1"/>
+      <c r="E68" s="1"/>
+      <c r="G68" s="1"/>
+      <c r="I68" s="1"/>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A69" s="7"/>
-      <c r="B69" s="27" t="s">
+      <c r="A69" s="1"/>
+      <c r="B69" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="C69" s="27"/>
-      <c r="D69" s="27"/>
-      <c r="E69" s="27"/>
-      <c r="F69" s="27"/>
-      <c r="G69" s="28" t="s">
+      <c r="C69" s="15"/>
+      <c r="D69" s="15"/>
+      <c r="E69" s="15"/>
+      <c r="F69" s="15"/>
+      <c r="G69" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="H69" s="28"/>
-      <c r="I69" s="28"/>
-      <c r="J69" s="28"/>
-      <c r="K69" s="28"/>
+      <c r="H69" s="16"/>
+      <c r="I69" s="16"/>
+      <c r="J69" s="16"/>
+      <c r="K69" s="16"/>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A70" s="7"/>
-      <c r="B70" s="8" t="s">
+      <c r="A70" s="1"/>
+      <c r="B70" t="s">
         <v>181</v>
       </c>
-      <c r="C70" s="7" t="s">
+      <c r="C70" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="D70" s="8" t="s">
+      <c r="D70" t="s">
         <v>183</v>
       </c>
-      <c r="E70" s="7" t="s">
+      <c r="E70" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F70" s="8" t="s">
+      <c r="F70" t="s">
         <v>11</v>
       </c>
-      <c r="G70" s="8" t="s">
+      <c r="G70" t="s">
         <v>181</v>
       </c>
-      <c r="H70" s="7" t="s">
+      <c r="H70" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="I70" s="8" t="s">
+      <c r="I70" t="s">
         <v>189</v>
       </c>
-      <c r="J70" s="7" t="s">
+      <c r="J70" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="K70" s="8" t="s">
+      <c r="K70" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A71" s="7">
-        <v>1000</v>
-      </c>
-      <c r="B71" s="8" t="s">
+      <c r="A71" s="1">
+        <v>1000</v>
+      </c>
+      <c r="B71" t="s">
         <v>14</v>
       </c>
-      <c r="C71" s="7">
+      <c r="C71" s="1">
         <v>300</v>
       </c>
-      <c r="D71" s="8">
+      <c r="D71">
         <v>85</v>
       </c>
       <c r="E71" t="s">
@@ -6749,65 +6379,65 @@
       <c r="F71" t="s">
         <v>585</v>
       </c>
-      <c r="G71" s="7" t="s">
+      <c r="G71" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H71" s="19">
+      <c r="H71">
         <v>128</v>
       </c>
-      <c r="I71" s="20">
+      <c r="I71" s="1">
         <v>41</v>
       </c>
-      <c r="J71" s="10" t="s">
+      <c r="J71" s="5" t="s">
         <v>587</v>
       </c>
-      <c r="K71" s="20" t="s">
+      <c r="K71" s="1" t="s">
         <v>588</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="G94" s="9" t="s">
+      <c r="G94" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="H94" s="16" t="s">
+      <c r="H94" s="8" t="s">
         <v>437</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A96" s="7" t="s">
+      <c r="A96" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B96" s="7" t="s">
+      <c r="B96" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C96" s="8" t="s">
+      <c r="C96" t="s">
         <v>7</v>
       </c>
-      <c r="D96" s="7" t="s">
+      <c r="D96" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E96" s="8" t="s">
+      <c r="E96" t="s">
         <v>9</v>
       </c>
-      <c r="F96" s="8" t="s">
+      <c r="F96" t="s">
         <v>1</v>
       </c>
-      <c r="G96" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="H96" s="8" t="s">
+      <c r="G96" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H96" t="s">
         <v>3</v>
       </c>
-      <c r="I96" s="8" t="s">
+      <c r="I96" t="s">
         <v>10</v>
       </c>
-      <c r="J96" s="8" t="s">
+      <c r="J96" t="s">
         <v>11</v>
       </c>
-      <c r="K96" s="8" t="s">
+      <c r="K96" t="s">
         <v>12</v>
       </c>
-      <c r="L96" s="8" t="s">
+      <c r="L96" t="s">
         <v>13</v>
       </c>
     </row>
@@ -6856,7 +6486,7 @@
       <c r="H99" t="s">
         <v>450</v>
       </c>
-      <c r="I99" s="11" t="s">
+      <c r="I99" s="5" t="s">
         <v>452</v>
       </c>
       <c r="J99" t="s">
@@ -6908,7 +6538,7 @@
       <c r="H103" t="s">
         <v>233</v>
       </c>
-      <c r="I103" s="12" t="s">
+      <c r="I103" s="5" t="s">
         <v>439</v>
       </c>
       <c r="J103" t="s">
@@ -6916,81 +6546,75 @@
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A106" s="7" t="s">
+      <c r="A106" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B106" s="8"/>
-      <c r="C106" s="7"/>
-      <c r="D106" s="8"/>
-      <c r="E106" s="7"/>
-      <c r="F106" s="8"/>
-      <c r="G106" s="7"/>
-      <c r="H106" s="8"/>
-      <c r="I106" s="7"/>
-      <c r="J106" s="8"/>
-      <c r="K106" s="8"/>
+      <c r="C106" s="1"/>
+      <c r="E106" s="1"/>
+      <c r="G106" s="1"/>
+      <c r="I106" s="1"/>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A107" s="7"/>
-      <c r="B107" s="17" t="s">
+      <c r="A107" s="1"/>
+      <c r="B107" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="C107" s="17"/>
-      <c r="D107" s="17"/>
-      <c r="E107" s="17"/>
-      <c r="F107" s="17"/>
-      <c r="G107" s="18" t="s">
+      <c r="C107" s="9"/>
+      <c r="D107" s="9"/>
+      <c r="E107" s="9"/>
+      <c r="F107" s="9"/>
+      <c r="G107" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="H107" s="18"/>
-      <c r="I107" s="18"/>
-      <c r="J107" s="18"/>
-      <c r="K107" s="18"/>
+      <c r="H107" s="10"/>
+      <c r="I107" s="10"/>
+      <c r="J107" s="10"/>
+      <c r="K107" s="10"/>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A108" s="7"/>
-      <c r="B108" s="8" t="s">
+      <c r="A108" s="1"/>
+      <c r="B108" t="s">
         <v>181</v>
       </c>
-      <c r="C108" s="7" t="s">
+      <c r="C108" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="D108" s="8" t="s">
+      <c r="D108" t="s">
         <v>183</v>
       </c>
-      <c r="E108" s="7" t="s">
+      <c r="E108" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F108" s="8" t="s">
+      <c r="F108" t="s">
         <v>11</v>
       </c>
-      <c r="G108" s="8" t="s">
+      <c r="G108" t="s">
         <v>181</v>
       </c>
-      <c r="H108" s="7" t="s">
+      <c r="H108" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="I108" s="8" t="s">
+      <c r="I108" t="s">
         <v>189</v>
       </c>
-      <c r="J108" s="7" t="s">
+      <c r="J108" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="K108" s="8" t="s">
+      <c r="K108" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A109" s="7">
-        <v>1000</v>
-      </c>
-      <c r="B109" s="8" t="s">
+      <c r="A109" s="1">
+        <v>1000</v>
+      </c>
+      <c r="B109" t="s">
         <v>14</v>
       </c>
-      <c r="C109" s="7">
+      <c r="C109" s="1">
         <v>291</v>
       </c>
-      <c r="D109" s="8">
+      <c r="D109">
         <v>110</v>
       </c>
       <c r="E109" t="s">
@@ -6999,65 +6623,65 @@
       <c r="F109" t="s">
         <v>446</v>
       </c>
-      <c r="G109" s="7" t="s">
+      <c r="G109" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H109" s="8">
+      <c r="H109">
         <v>117</v>
       </c>
-      <c r="I109" s="7">
+      <c r="I109" s="1">
         <v>38</v>
       </c>
-      <c r="J109" s="6" t="s">
+      <c r="J109" s="5" t="s">
         <v>447</v>
       </c>
-      <c r="K109" s="7" t="s">
+      <c r="K109" s="1" t="s">
         <v>448</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="G112" s="9" t="s">
+      <c r="G112" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="H112" s="16" t="s">
+      <c r="H112" s="8" t="s">
         <v>459</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A114" s="7" t="s">
+      <c r="A114" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B114" s="7" t="s">
+      <c r="B114" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C114" s="8" t="s">
+      <c r="C114" t="s">
         <v>7</v>
       </c>
-      <c r="D114" s="7" t="s">
+      <c r="D114" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E114" s="8" t="s">
+      <c r="E114" t="s">
         <v>9</v>
       </c>
-      <c r="F114" s="8" t="s">
+      <c r="F114" t="s">
         <v>1</v>
       </c>
-      <c r="G114" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="H114" s="8" t="s">
+      <c r="G114" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H114" t="s">
         <v>3</v>
       </c>
-      <c r="I114" s="8" t="s">
+      <c r="I114" t="s">
         <v>10</v>
       </c>
-      <c r="J114" s="8" t="s">
+      <c r="J114" t="s">
         <v>11</v>
       </c>
-      <c r="K114" s="8" t="s">
+      <c r="K114" t="s">
         <v>12</v>
       </c>
-      <c r="L114" s="8" t="s">
+      <c r="L114" t="s">
         <v>13</v>
       </c>
     </row>
@@ -7106,7 +6730,7 @@
       <c r="H117" t="s">
         <v>468</v>
       </c>
-      <c r="I117" s="11" t="s">
+      <c r="I117" s="5" t="s">
         <v>469</v>
       </c>
       <c r="J117" t="s">
@@ -7132,7 +6756,7 @@
       <c r="H119" t="s">
         <v>472</v>
       </c>
-      <c r="I119" s="12" t="s">
+      <c r="I119" s="5" t="s">
         <v>473</v>
       </c>
       <c r="J119" t="s">
@@ -7158,7 +6782,7 @@
       <c r="H121" t="s">
         <v>476</v>
       </c>
-      <c r="I121" s="12" t="s">
+      <c r="I121" s="5" t="s">
         <v>447</v>
       </c>
       <c r="J121" t="s">
@@ -7166,81 +6790,75 @@
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A124" s="7" t="s">
+      <c r="A124" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B124" s="8"/>
-      <c r="C124" s="7"/>
-      <c r="D124" s="8"/>
-      <c r="E124" s="7"/>
-      <c r="F124" s="8"/>
-      <c r="G124" s="7"/>
-      <c r="H124" s="8"/>
-      <c r="I124" s="7"/>
-      <c r="J124" s="8"/>
-      <c r="K124" s="8"/>
+      <c r="C124" s="1"/>
+      <c r="E124" s="1"/>
+      <c r="G124" s="1"/>
+      <c r="I124" s="1"/>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A125" s="7"/>
-      <c r="B125" s="17" t="s">
+      <c r="A125" s="1"/>
+      <c r="B125" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="C125" s="17"/>
-      <c r="D125" s="17"/>
-      <c r="E125" s="17"/>
-      <c r="F125" s="17"/>
-      <c r="G125" s="18" t="s">
+      <c r="C125" s="9"/>
+      <c r="D125" s="9"/>
+      <c r="E125" s="9"/>
+      <c r="F125" s="9"/>
+      <c r="G125" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="H125" s="18"/>
-      <c r="I125" s="18"/>
-      <c r="J125" s="18"/>
-      <c r="K125" s="18"/>
+      <c r="H125" s="10"/>
+      <c r="I125" s="10"/>
+      <c r="J125" s="10"/>
+      <c r="K125" s="10"/>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A126" s="7"/>
-      <c r="B126" s="8" t="s">
+      <c r="A126" s="1"/>
+      <c r="B126" t="s">
         <v>181</v>
       </c>
-      <c r="C126" s="7" t="s">
+      <c r="C126" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="D126" s="8" t="s">
+      <c r="D126" t="s">
         <v>183</v>
       </c>
-      <c r="E126" s="7" t="s">
+      <c r="E126" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F126" s="8" t="s">
+      <c r="F126" t="s">
         <v>11</v>
       </c>
-      <c r="G126" s="8" t="s">
+      <c r="G126" t="s">
         <v>181</v>
       </c>
-      <c r="H126" s="7" t="s">
+      <c r="H126" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="I126" s="8" t="s">
+      <c r="I126" t="s">
         <v>189</v>
       </c>
-      <c r="J126" s="7" t="s">
+      <c r="J126" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="K126" s="8" t="s">
+      <c r="K126" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A127" s="7">
-        <v>1000</v>
-      </c>
-      <c r="B127" s="8" t="s">
+      <c r="A127" s="1">
+        <v>1000</v>
+      </c>
+      <c r="B127" t="s">
         <v>14</v>
       </c>
-      <c r="C127" s="7">
+      <c r="C127" s="1">
         <v>291</v>
       </c>
-      <c r="D127" s="8">
+      <c r="D127">
         <v>94</v>
       </c>
       <c r="E127" t="s">
@@ -7249,65 +6867,65 @@
       <c r="F127" t="s">
         <v>462</v>
       </c>
-      <c r="G127" s="7" t="s">
+      <c r="G127" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H127" s="8">
+      <c r="H127">
         <v>113</v>
       </c>
-      <c r="I127" s="7">
+      <c r="I127" s="1">
         <v>39</v>
       </c>
-      <c r="J127" s="6" t="s">
+      <c r="J127" s="5" t="s">
         <v>463</v>
       </c>
-      <c r="K127" s="7" t="s">
+      <c r="K127" s="1" t="s">
         <v>464</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="G130" s="9" t="s">
+      <c r="G130" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="H130" s="16" t="s">
+      <c r="H130" s="8" t="s">
         <v>465</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A132" s="7" t="s">
+      <c r="A132" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B132" s="7" t="s">
+      <c r="B132" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C132" s="8" t="s">
+      <c r="C132" t="s">
         <v>7</v>
       </c>
-      <c r="D132" s="7" t="s">
+      <c r="D132" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E132" s="8" t="s">
+      <c r="E132" t="s">
         <v>9</v>
       </c>
-      <c r="F132" s="8" t="s">
+      <c r="F132" t="s">
         <v>1</v>
       </c>
-      <c r="G132" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="H132" s="8" t="s">
+      <c r="G132" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H132" t="s">
         <v>3</v>
       </c>
-      <c r="I132" s="8" t="s">
+      <c r="I132" t="s">
         <v>10</v>
       </c>
-      <c r="J132" s="8" t="s">
+      <c r="J132" t="s">
         <v>11</v>
       </c>
-      <c r="K132" s="8" t="s">
+      <c r="K132" t="s">
         <v>12</v>
       </c>
-      <c r="L132" s="8" t="s">
+      <c r="L132" t="s">
         <v>13</v>
       </c>
     </row>
@@ -7356,7 +6974,7 @@
       <c r="H135" t="s">
         <v>484</v>
       </c>
-      <c r="I135" s="11" t="s">
+      <c r="I135" s="5" t="s">
         <v>485</v>
       </c>
       <c r="J135" t="s">
@@ -7382,7 +7000,7 @@
       <c r="H137" t="s">
         <v>489</v>
       </c>
-      <c r="I137" s="12" t="s">
+      <c r="I137" s="5" t="s">
         <v>488</v>
       </c>
       <c r="J137" t="s">
@@ -7408,7 +7026,7 @@
       <c r="H139" t="s">
         <v>268</v>
       </c>
-      <c r="I139" s="12" t="s">
+      <c r="I139" s="5" t="s">
         <v>492</v>
       </c>
       <c r="J139" t="s">
@@ -7416,81 +7034,75 @@
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A142" s="7" t="s">
+      <c r="A142" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B142" s="8"/>
-      <c r="C142" s="7"/>
-      <c r="D142" s="8"/>
-      <c r="E142" s="7"/>
-      <c r="F142" s="8"/>
-      <c r="G142" s="7"/>
-      <c r="H142" s="8"/>
-      <c r="I142" s="7"/>
-      <c r="J142" s="8"/>
-      <c r="K142" s="8"/>
+      <c r="C142" s="1"/>
+      <c r="E142" s="1"/>
+      <c r="G142" s="1"/>
+      <c r="I142" s="1"/>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A143" s="7"/>
-      <c r="B143" s="17" t="s">
+      <c r="A143" s="1"/>
+      <c r="B143" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="C143" s="17"/>
-      <c r="D143" s="17"/>
-      <c r="E143" s="17"/>
-      <c r="F143" s="17"/>
-      <c r="G143" s="18" t="s">
+      <c r="C143" s="9"/>
+      <c r="D143" s="9"/>
+      <c r="E143" s="9"/>
+      <c r="F143" s="9"/>
+      <c r="G143" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="H143" s="18"/>
-      <c r="I143" s="18"/>
-      <c r="J143" s="18"/>
-      <c r="K143" s="18"/>
+      <c r="H143" s="10"/>
+      <c r="I143" s="10"/>
+      <c r="J143" s="10"/>
+      <c r="K143" s="10"/>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A144" s="7"/>
-      <c r="B144" s="8" t="s">
+      <c r="A144" s="1"/>
+      <c r="B144" t="s">
         <v>181</v>
       </c>
-      <c r="C144" s="7" t="s">
+      <c r="C144" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="D144" s="8" t="s">
+      <c r="D144" t="s">
         <v>183</v>
       </c>
-      <c r="E144" s="7" t="s">
+      <c r="E144" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F144" s="8" t="s">
+      <c r="F144" t="s">
         <v>11</v>
       </c>
-      <c r="G144" s="8" t="s">
+      <c r="G144" t="s">
         <v>181</v>
       </c>
-      <c r="H144" s="7" t="s">
+      <c r="H144" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="I144" s="8" t="s">
+      <c r="I144" t="s">
         <v>189</v>
       </c>
-      <c r="J144" s="7" t="s">
+      <c r="J144" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="K144" s="8" t="s">
+      <c r="K144" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A145" s="7">
-        <v>1000</v>
-      </c>
-      <c r="B145" s="8" t="s">
+      <c r="A145" s="1">
+        <v>1000</v>
+      </c>
+      <c r="B145" t="s">
         <v>14</v>
       </c>
-      <c r="C145" s="7">
+      <c r="C145" s="1">
         <v>296</v>
       </c>
-      <c r="D145" s="8">
+      <c r="D145">
         <v>94</v>
       </c>
       <c r="E145" t="s">
@@ -7499,65 +7111,65 @@
       <c r="F145" t="s">
         <v>480</v>
       </c>
-      <c r="G145" s="7" t="s">
+      <c r="G145" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H145" s="8">
+      <c r="H145">
         <v>118</v>
       </c>
-      <c r="I145" s="7">
+      <c r="I145" s="1">
         <v>45</v>
       </c>
-      <c r="J145" s="6" t="s">
+      <c r="J145" s="5" t="s">
         <v>481</v>
       </c>
-      <c r="K145" s="7" t="s">
+      <c r="K145" s="1" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="G148" s="9" t="s">
+      <c r="G148" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="H148" s="16" t="s">
+      <c r="H148" s="8" t="s">
         <v>466</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A150" s="7" t="s">
+      <c r="A150" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B150" s="7" t="s">
+      <c r="B150" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C150" s="8" t="s">
+      <c r="C150" t="s">
         <v>7</v>
       </c>
-      <c r="D150" s="7" t="s">
+      <c r="D150" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E150" s="8" t="s">
+      <c r="E150" t="s">
         <v>9</v>
       </c>
-      <c r="F150" s="8" t="s">
+      <c r="F150" t="s">
         <v>1</v>
       </c>
-      <c r="G150" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="H150" s="8" t="s">
+      <c r="G150" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H150" t="s">
         <v>3</v>
       </c>
-      <c r="I150" s="8" t="s">
+      <c r="I150" t="s">
         <v>10</v>
       </c>
-      <c r="J150" s="8" t="s">
+      <c r="J150" t="s">
         <v>11</v>
       </c>
-      <c r="K150" s="8" t="s">
+      <c r="K150" t="s">
         <v>12</v>
       </c>
-      <c r="L150" s="8" t="s">
+      <c r="L150" t="s">
         <v>13</v>
       </c>
     </row>
@@ -7606,7 +7218,7 @@
       <c r="H153" t="s">
         <v>501</v>
       </c>
-      <c r="I153" s="11" t="s">
+      <c r="I153" s="5" t="s">
         <v>502</v>
       </c>
       <c r="J153" t="s">
@@ -7632,7 +7244,7 @@
       <c r="H155" t="s">
         <v>501</v>
       </c>
-      <c r="I155" s="12" t="s">
+      <c r="I155" s="5" t="s">
         <v>504</v>
       </c>
       <c r="J155" t="s">
@@ -7646,7 +7258,7 @@
       <c r="D157">
         <v>2</v>
       </c>
-      <c r="E157" s="13" t="s">
+      <c r="E157" t="s">
         <v>506</v>
       </c>
       <c r="F157" t="s">
@@ -7658,7 +7270,7 @@
       <c r="H157" t="s">
         <v>476</v>
       </c>
-      <c r="I157" s="12" t="s">
+      <c r="I157" s="5" t="s">
         <v>507</v>
       </c>
       <c r="J157" t="s">
@@ -7666,81 +7278,75 @@
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A160" s="7" t="s">
+      <c r="A160" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B160" s="8"/>
-      <c r="C160" s="7"/>
-      <c r="D160" s="8"/>
-      <c r="E160" s="7"/>
-      <c r="F160" s="8"/>
-      <c r="G160" s="7"/>
-      <c r="H160" s="8"/>
-      <c r="I160" s="7"/>
-      <c r="J160" s="8"/>
-      <c r="K160" s="8"/>
+      <c r="C160" s="1"/>
+      <c r="E160" s="1"/>
+      <c r="G160" s="1"/>
+      <c r="I160" s="1"/>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A161" s="7"/>
-      <c r="B161" s="17" t="s">
+      <c r="A161" s="1"/>
+      <c r="B161" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="C161" s="17"/>
-      <c r="D161" s="17"/>
-      <c r="E161" s="17"/>
-      <c r="F161" s="17"/>
-      <c r="G161" s="18" t="s">
+      <c r="C161" s="9"/>
+      <c r="D161" s="9"/>
+      <c r="E161" s="9"/>
+      <c r="F161" s="9"/>
+      <c r="G161" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="H161" s="18"/>
-      <c r="I161" s="18"/>
-      <c r="J161" s="18"/>
-      <c r="K161" s="18"/>
+      <c r="H161" s="10"/>
+      <c r="I161" s="10"/>
+      <c r="J161" s="10"/>
+      <c r="K161" s="10"/>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A162" s="7"/>
-      <c r="B162" s="8" t="s">
+      <c r="A162" s="1"/>
+      <c r="B162" t="s">
         <v>181</v>
       </c>
-      <c r="C162" s="7" t="s">
+      <c r="C162" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="D162" s="8" t="s">
+      <c r="D162" t="s">
         <v>183</v>
       </c>
-      <c r="E162" s="7" t="s">
+      <c r="E162" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F162" s="8" t="s">
+      <c r="F162" t="s">
         <v>11</v>
       </c>
-      <c r="G162" s="8" t="s">
+      <c r="G162" t="s">
         <v>181</v>
       </c>
-      <c r="H162" s="7" t="s">
+      <c r="H162" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="I162" s="8" t="s">
+      <c r="I162" t="s">
         <v>189</v>
       </c>
-      <c r="J162" s="7" t="s">
+      <c r="J162" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="K162" s="8" t="s">
+      <c r="K162" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A163" s="7">
-        <v>1000</v>
-      </c>
-      <c r="B163" s="8" t="s">
+      <c r="A163" s="1">
+        <v>1000</v>
+      </c>
+      <c r="B163" t="s">
         <v>14</v>
       </c>
-      <c r="C163" s="7">
+      <c r="C163" s="1">
         <v>289</v>
       </c>
-      <c r="D163" s="8">
+      <c r="D163">
         <v>113</v>
       </c>
       <c r="E163" t="s">
@@ -7749,65 +7355,65 @@
       <c r="F163" t="s">
         <v>497</v>
       </c>
-      <c r="G163" s="7" t="s">
+      <c r="G163" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H163" s="8">
+      <c r="H163">
         <v>113</v>
       </c>
-      <c r="I163" s="7">
+      <c r="I163" s="1">
         <v>29</v>
       </c>
-      <c r="J163" s="6" t="s">
+      <c r="J163" s="5" t="s">
         <v>498</v>
       </c>
-      <c r="K163" s="7" t="s">
+      <c r="K163" s="1" t="s">
         <v>499</v>
       </c>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="G166" s="9" t="s">
+      <c r="G166" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="H166" s="16" t="s">
+      <c r="H166" s="8" t="s">
         <v>512</v>
       </c>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A168" s="7" t="s">
+      <c r="A168" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B168" s="7" t="s">
+      <c r="B168" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C168" s="8" t="s">
+      <c r="C168" t="s">
         <v>7</v>
       </c>
-      <c r="D168" s="7" t="s">
+      <c r="D168" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E168" s="8" t="s">
+      <c r="E168" t="s">
         <v>9</v>
       </c>
-      <c r="F168" s="8" t="s">
+      <c r="F168" t="s">
         <v>1</v>
       </c>
-      <c r="G168" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="H168" s="8" t="s">
+      <c r="G168" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H168" t="s">
         <v>3</v>
       </c>
-      <c r="I168" s="8" t="s">
+      <c r="I168" t="s">
         <v>10</v>
       </c>
-      <c r="J168" s="8" t="s">
+      <c r="J168" t="s">
         <v>11</v>
       </c>
-      <c r="K168" s="8" t="s">
+      <c r="K168" t="s">
         <v>12</v>
       </c>
-      <c r="L168" s="8" t="s">
+      <c r="L168" t="s">
         <v>13</v>
       </c>
     </row>
@@ -7856,7 +7462,7 @@
       <c r="H171" t="s">
         <v>516</v>
       </c>
-      <c r="I171" s="11" t="s">
+      <c r="I171" s="5" t="s">
         <v>517</v>
       </c>
       <c r="J171" t="s">
@@ -7882,7 +7488,7 @@
       <c r="H173" t="s">
         <v>520</v>
       </c>
-      <c r="I173" s="12" t="s">
+      <c r="I173" s="5" t="s">
         <v>249</v>
       </c>
       <c r="J173" t="s">
@@ -7896,7 +7502,7 @@
       <c r="D175">
         <v>2</v>
       </c>
-      <c r="E175" s="13" t="s">
+      <c r="E175" t="s">
         <v>522</v>
       </c>
       <c r="F175" t="s">
@@ -7908,7 +7514,7 @@
       <c r="H175" t="s">
         <v>523</v>
       </c>
-      <c r="I175" s="12" t="s">
+      <c r="I175" s="5" t="s">
         <v>481</v>
       </c>
       <c r="J175" t="s">
@@ -7916,81 +7522,75 @@
       </c>
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A178" s="7" t="s">
+      <c r="A178" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B178" s="8"/>
-      <c r="C178" s="7"/>
-      <c r="D178" s="8"/>
-      <c r="E178" s="7"/>
-      <c r="F178" s="8"/>
-      <c r="G178" s="7"/>
-      <c r="H178" s="8"/>
-      <c r="I178" s="7"/>
-      <c r="J178" s="8"/>
-      <c r="K178" s="8"/>
+      <c r="C178" s="1"/>
+      <c r="E178" s="1"/>
+      <c r="G178" s="1"/>
+      <c r="I178" s="1"/>
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A179" s="7"/>
-      <c r="B179" s="17" t="s">
+      <c r="A179" s="1"/>
+      <c r="B179" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="C179" s="17"/>
-      <c r="D179" s="17"/>
-      <c r="E179" s="17"/>
-      <c r="F179" s="17"/>
-      <c r="G179" s="18" t="s">
+      <c r="C179" s="9"/>
+      <c r="D179" s="9"/>
+      <c r="E179" s="9"/>
+      <c r="F179" s="9"/>
+      <c r="G179" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="H179" s="18"/>
-      <c r="I179" s="18"/>
-      <c r="J179" s="18"/>
-      <c r="K179" s="18"/>
+      <c r="H179" s="10"/>
+      <c r="I179" s="10"/>
+      <c r="J179" s="10"/>
+      <c r="K179" s="10"/>
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A180" s="7"/>
-      <c r="B180" s="8" t="s">
+      <c r="A180" s="1"/>
+      <c r="B180" t="s">
         <v>181</v>
       </c>
-      <c r="C180" s="7" t="s">
+      <c r="C180" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="D180" s="8" t="s">
+      <c r="D180" t="s">
         <v>183</v>
       </c>
-      <c r="E180" s="7" t="s">
+      <c r="E180" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F180" s="8" t="s">
+      <c r="F180" t="s">
         <v>11</v>
       </c>
-      <c r="G180" s="8" t="s">
+      <c r="G180" t="s">
         <v>181</v>
       </c>
-      <c r="H180" s="7" t="s">
+      <c r="H180" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="I180" s="8" t="s">
+      <c r="I180" t="s">
         <v>189</v>
       </c>
-      <c r="J180" s="7" t="s">
+      <c r="J180" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="K180" s="8" t="s">
+      <c r="K180" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="181" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A181" s="7">
-        <v>1000</v>
-      </c>
-      <c r="B181" s="8" t="s">
+      <c r="A181" s="1">
+        <v>1000</v>
+      </c>
+      <c r="B181" t="s">
         <v>14</v>
       </c>
-      <c r="C181" s="7">
+      <c r="C181" s="1">
         <v>301</v>
       </c>
-      <c r="D181" s="8">
+      <c r="D181">
         <v>83</v>
       </c>
       <c r="E181" t="s">
@@ -7999,19 +7599,19 @@
       <c r="F181" t="s">
         <v>511</v>
       </c>
-      <c r="G181" s="7" t="s">
+      <c r="G181" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H181" s="8">
+      <c r="H181">
         <v>107</v>
       </c>
-      <c r="I181" s="7">
+      <c r="I181" s="1">
         <v>26</v>
       </c>
-      <c r="J181" s="6" t="s">
+      <c r="J181" s="5" t="s">
         <v>513</v>
       </c>
-      <c r="K181" s="7" t="s">
+      <c r="K181" s="1" t="s">
         <v>514</v>
       </c>
     </row>
@@ -8032,7 +7632,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -8154,8 +7754,8 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:L15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.36328125" customWidth="1"/>
@@ -8170,95 +7770,68 @@
     <col min="11" max="11" width="27.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A1" s="7"/>
-      <c r="B1" s="8"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="9" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="G1" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="H1" s="8"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
-      <c r="M1" s="8"/>
-      <c r="N1" s="8"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A2" s="7"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8"/>
-      <c r="N2" s="8"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A3" s="7"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="8"/>
-      <c r="N3" s="8"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A4" s="7" t="s">
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" t="s">
         <v>1</v>
       </c>
-      <c r="G4" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="H4" s="8" t="s">
+      <c r="G4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H4" t="s">
         <v>3</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="I4" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="J4" t="s">
         <v>11</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="K4" t="s">
         <v>12</v>
       </c>
-      <c r="L4" s="8" t="s">
+      <c r="L4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>1000</v>
       </c>
@@ -8284,7 +7857,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>1000</v>
       </c>
@@ -8303,14 +7876,14 @@
       <c r="H7" t="s">
         <v>209</v>
       </c>
-      <c r="I7" s="11" t="s">
+      <c r="I7" s="5" t="s">
         <v>210</v>
       </c>
       <c r="J7" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>1000</v>
       </c>
@@ -8336,7 +7909,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>1000</v>
       </c>
@@ -8355,81 +7928,75 @@
       <c r="H11" t="s">
         <v>218</v>
       </c>
-      <c r="I11" s="12" t="s">
+      <c r="I11" s="5" t="s">
         <v>219</v>
       </c>
       <c r="J11" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A12" s="8"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A13" s="27" t="s">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="H12" s="1"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A13" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="B13" s="27"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="27"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="28" t="s">
+      <c r="B13" s="15"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="G13" s="28"/>
-      <c r="H13" s="28"/>
-      <c r="I13" s="28"/>
-      <c r="J13" s="28"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A14" s="8" t="s">
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="16"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>181</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" t="s">
         <v>183</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" t="s">
         <v>11</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F14" t="s">
         <v>181</v>
       </c>
-      <c r="G14" s="7" t="s">
+      <c r="G14" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="H14" s="8" t="s">
+      <c r="H14" t="s">
         <v>189</v>
       </c>
-      <c r="I14" s="7" t="s">
+      <c r="I14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J14" s="8" t="s">
+      <c r="J14" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A15" s="8" t="s">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="1">
         <v>293</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15">
         <v>95</v>
       </c>
       <c r="D15" t="s">
@@ -8438,19 +8005,19 @@
       <c r="E15" t="s">
         <v>591</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G15" s="8">
+      <c r="G15">
         <v>122</v>
       </c>
-      <c r="H15" s="7">
+      <c r="H15" s="1">
         <v>41</v>
       </c>
-      <c r="I15" s="6" t="s">
+      <c r="I15" s="5" t="s">
         <v>485</v>
       </c>
-      <c r="J15" s="7" t="s">
+      <c r="J15" s="1" t="s">
         <v>592</v>
       </c>
     </row>
@@ -8464,8 +8031,8 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N26"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:L26"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.453125" customWidth="1"/>
@@ -8482,95 +8049,68 @@
     <col min="12" max="12" width="79" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A1" s="7"/>
-      <c r="B1" s="8"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="9" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="G1" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="H1" s="8"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
-      <c r="M1" s="8"/>
-      <c r="N1" s="8"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A2" s="7"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8"/>
-      <c r="N2" s="8"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A3" s="7"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="8"/>
-      <c r="N3" s="8"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A4" s="7" t="s">
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" t="s">
         <v>1</v>
       </c>
-      <c r="G4" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="H4" s="8" t="s">
+      <c r="G4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H4" t="s">
         <v>3</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="I4" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="J4" t="s">
         <v>11</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="K4" t="s">
         <v>12</v>
       </c>
-      <c r="L4" s="8" t="s">
+      <c r="L4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>1000</v>
       </c>
@@ -8596,7 +8136,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>1000</v>
       </c>
@@ -8615,14 +8155,14 @@
       <c r="H7" t="s">
         <v>240</v>
       </c>
-      <c r="I7" s="11" t="s">
+      <c r="I7" s="5" t="s">
         <v>241</v>
       </c>
       <c r="J7" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>1000</v>
       </c>
@@ -8648,7 +8188,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>1000</v>
       </c>
@@ -8667,50 +8207,44 @@
       <c r="H11" t="s">
         <v>252</v>
       </c>
-      <c r="I11" s="12" t="s">
+      <c r="I11" s="5" t="s">
         <v>253</v>
       </c>
       <c r="J11" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A12" s="8"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A13" s="15">
-        <v>1000</v>
-      </c>
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15" t="s">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="H12" s="1"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A13" s="7">
+        <v>1000</v>
+      </c>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="G13" s="15">
-        <v>2</v>
-      </c>
-      <c r="H13" s="15" t="s">
+      <c r="G13" s="7">
+        <v>2</v>
+      </c>
+      <c r="H13" s="7" t="s">
         <v>361</v>
       </c>
-      <c r="I13" s="15" t="s">
+      <c r="I13" s="7" t="s">
         <v>362</v>
       </c>
-      <c r="J13" s="15" t="s">
+      <c r="J13" s="7" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>1000</v>
       </c>
@@ -8723,7 +8257,7 @@
       <c r="H15" t="s">
         <v>364</v>
       </c>
-      <c r="I15" s="11" t="s">
+      <c r="I15" s="5" t="s">
         <v>365</v>
       </c>
       <c r="J15" t="s">
@@ -8743,7 +8277,7 @@
       <c r="H17" t="s">
         <v>367</v>
       </c>
-      <c r="I17" s="12" t="s">
+      <c r="I17" s="5" t="s">
         <v>368</v>
       </c>
       <c r="J17" t="s">
@@ -8763,7 +8297,7 @@
       <c r="H19" t="s">
         <v>370</v>
       </c>
-      <c r="I19" s="12" t="s">
+      <c r="I19" s="5" t="s">
         <v>371</v>
       </c>
       <c r="J19" t="s">
@@ -8771,61 +8305,61 @@
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A23" s="27" t="s">
+      <c r="A23" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="B23" s="27"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="27"/>
-      <c r="F23" s="28" t="s">
+      <c r="B23" s="15"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="G23" s="28"/>
-      <c r="H23" s="28"/>
-      <c r="I23" s="28"/>
-      <c r="J23" s="28"/>
+      <c r="G23" s="16"/>
+      <c r="H23" s="16"/>
+      <c r="I23" s="16"/>
+      <c r="J23" s="16"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A24" s="8" t="s">
+      <c r="A24" t="s">
         <v>181</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" t="s">
         <v>183</v>
       </c>
-      <c r="D24" s="7" t="s">
+      <c r="D24" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E24" s="8" t="s">
+      <c r="E24" t="s">
         <v>11</v>
       </c>
-      <c r="F24" s="8" t="s">
+      <c r="F24" t="s">
         <v>181</v>
       </c>
-      <c r="G24" s="7" t="s">
+      <c r="G24" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="H24" s="8" t="s">
+      <c r="H24" t="s">
         <v>189</v>
       </c>
-      <c r="I24" s="7" t="s">
+      <c r="I24" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J24" s="8" t="s">
+      <c r="J24" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A25" s="8" t="s">
+      <c r="A25" t="s">
         <v>14</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B25" s="1">
         <v>307</v>
       </c>
-      <c r="C25" s="8">
+      <c r="C25">
         <v>84</v>
       </c>
       <c r="D25" t="s">
@@ -8834,24 +8368,24 @@
       <c r="E25" t="s">
         <v>244</v>
       </c>
-      <c r="F25" s="7" t="s">
+      <c r="F25" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G25" s="8">
+      <c r="G25">
         <v>122</v>
       </c>
-      <c r="H25" s="7">
+      <c r="H25" s="1">
         <v>37</v>
       </c>
-      <c r="I25" s="6" t="s">
+      <c r="I25" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="J25" s="7" t="s">
+      <c r="J25" s="1" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A26" s="8" t="s">
+      <c r="A26" t="s">
         <v>14</v>
       </c>
       <c r="B26">
@@ -8866,7 +8400,6 @@
       <c r="E26" t="s">
         <v>363</v>
       </c>
-      <c r="F26" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -8879,7 +8412,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:L31"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -8897,81 +8430,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A1" s="7"/>
-      <c r="B1" s="8"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="9" t="s">
+      <c r="A1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="G1" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="H1" s="8"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
+      <c r="I1" s="1"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" s="7"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
+      <c r="A2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="I2" s="1"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3" s="7"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
+      <c r="A3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="I3" s="1"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" t="s">
         <v>1</v>
       </c>
-      <c r="G4" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="H4" s="8" t="s">
+      <c r="G4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H4" t="s">
         <v>3</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="I4" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="J4" t="s">
         <v>11</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="K4" t="s">
         <v>12</v>
       </c>
-      <c r="L4" s="8" t="s">
+      <c r="L4" t="s">
         <v>13</v>
       </c>
     </row>
@@ -9020,7 +8535,7 @@
       <c r="H7" t="s">
         <v>261</v>
       </c>
-      <c r="I7" s="11" t="s">
+      <c r="I7" s="5" t="s">
         <v>262</v>
       </c>
       <c r="J7" t="s">
@@ -9046,7 +8561,7 @@
       <c r="H9" t="s">
         <v>265</v>
       </c>
-      <c r="I9" s="12" t="s">
+      <c r="I9" s="5" t="s">
         <v>219</v>
       </c>
       <c r="J9" t="s">
@@ -9060,7 +8575,7 @@
       <c r="D11">
         <v>2</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="E11" t="s">
         <v>267</v>
       </c>
       <c r="F11" t="s">
@@ -9072,7 +8587,7 @@
       <c r="H11" t="s">
         <v>268</v>
       </c>
-      <c r="I11" s="12" t="s">
+      <c r="I11" s="5" t="s">
         <v>269</v>
       </c>
       <c r="J11" t="s">
@@ -9080,38 +8595,32 @@
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A12" s="8"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
+      <c r="B12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="H12" s="1"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A13" s="24">
-        <v>1000</v>
-      </c>
-      <c r="B13" s="24"/>
-      <c r="C13" s="24"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="24" t="s">
+      <c r="A13" s="12">
+        <v>1000</v>
+      </c>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="G13" s="24">
+      <c r="G13" s="12">
         <v>217</v>
       </c>
-      <c r="H13" s="24" t="s">
+      <c r="H13" s="12" t="s">
         <v>347</v>
       </c>
-      <c r="I13" s="25" t="s">
+      <c r="I13" s="14" t="s">
         <v>351</v>
       </c>
-      <c r="J13" s="24" t="s">
+      <c r="J13" s="12" t="s">
         <v>352</v>
       </c>
     </row>
@@ -9128,7 +8637,7 @@
       <c r="H15" t="s">
         <v>348</v>
       </c>
-      <c r="I15" s="11" t="s">
+      <c r="I15" s="5" t="s">
         <v>349</v>
       </c>
       <c r="J15" t="s">
@@ -9145,10 +8654,10 @@
       <c r="G17">
         <v>175</v>
       </c>
-      <c r="H17" s="14" t="s">
+      <c r="H17" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="I17" s="12" t="s">
+      <c r="I17" s="5" t="s">
         <v>355</v>
       </c>
       <c r="J17" t="s">
@@ -9159,7 +8668,6 @@
       <c r="A19">
         <v>1000</v>
       </c>
-      <c r="E19" s="13"/>
       <c r="F19" t="s">
         <v>22</v>
       </c>
@@ -9169,7 +8677,7 @@
       <c r="H19" t="s">
         <v>358</v>
       </c>
-      <c r="I19" s="12" t="s">
+      <c r="I19" s="5" t="s">
         <v>359</v>
       </c>
       <c r="J19" t="s">
@@ -9177,61 +8685,61 @@
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A28" s="27" t="s">
+      <c r="A28" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="B28" s="27"/>
-      <c r="C28" s="27"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="27"/>
-      <c r="F28" s="28" t="s">
+      <c r="B28" s="15"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="G28" s="28"/>
-      <c r="H28" s="28"/>
-      <c r="I28" s="28"/>
-      <c r="J28" s="28"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="16"/>
+      <c r="I28" s="16"/>
+      <c r="J28" s="16"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A29" s="8" t="s">
+      <c r="A29" t="s">
         <v>181</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B29" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="C29" t="s">
         <v>183</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="D29" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E29" s="8" t="s">
+      <c r="E29" t="s">
         <v>11</v>
       </c>
-      <c r="F29" s="8" t="s">
+      <c r="F29" t="s">
         <v>181</v>
       </c>
-      <c r="G29" s="7" t="s">
+      <c r="G29" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="H29" s="8" t="s">
+      <c r="H29" t="s">
         <v>189</v>
       </c>
-      <c r="I29" s="7" t="s">
+      <c r="I29" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J29" s="8" t="s">
+      <c r="J29" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A30" s="8" t="s">
+      <c r="A30" t="s">
         <v>14</v>
       </c>
-      <c r="B30" s="7">
+      <c r="B30" s="1">
         <v>286</v>
       </c>
-      <c r="C30" s="8">
+      <c r="C30">
         <v>88</v>
       </c>
       <c r="D30" t="s">
@@ -9240,24 +8748,24 @@
       <c r="E30" t="s">
         <v>258</v>
       </c>
-      <c r="F30" s="7" t="s">
+      <c r="F30" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G30" s="8">
+      <c r="G30">
         <v>104</v>
       </c>
-      <c r="H30" s="7">
+      <c r="H30" s="1">
         <v>28</v>
       </c>
-      <c r="I30" s="6" t="s">
+      <c r="I30" s="5" t="s">
         <v>596</v>
       </c>
-      <c r="J30" s="7" t="s">
+      <c r="J30" s="1" t="s">
         <v>597</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A31" s="8" t="s">
+      <c r="A31" t="s">
         <v>14</v>
       </c>
       <c r="B31">
@@ -9266,13 +8774,13 @@
       <c r="C31">
         <v>266</v>
       </c>
-      <c r="D31" s="12" t="s">
+      <c r="D31" s="5" t="s">
         <v>351</v>
       </c>
       <c r="E31" t="s">
         <v>352</v>
       </c>
-      <c r="F31" s="8" t="s">
+      <c r="F31" t="s">
         <v>14</v>
       </c>
       <c r="G31">
@@ -9281,7 +8789,7 @@
       <c r="H31">
         <v>77</v>
       </c>
-      <c r="I31" s="12" t="s">
+      <c r="I31" s="5" t="s">
         <v>353</v>
       </c>
       <c r="J31" t="s">
@@ -9299,7 +8807,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:L28"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -9317,81 +8825,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A1" s="7"/>
-      <c r="B1" s="8"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="9" t="s">
+      <c r="A1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="G1" s="6" t="s">
         <v>271</v>
       </c>
-      <c r="H1" s="8"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
+      <c r="I1" s="1"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" s="7"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
+      <c r="A2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="I2" s="1"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3" s="7"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
+      <c r="A3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="I3" s="1"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" t="s">
         <v>1</v>
       </c>
-      <c r="G4" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="H4" s="8" t="s">
+      <c r="G4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H4" t="s">
         <v>3</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="I4" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="J4" t="s">
         <v>11</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="K4" t="s">
         <v>12</v>
       </c>
-      <c r="L4" s="8" t="s">
+      <c r="L4" t="s">
         <v>13</v>
       </c>
     </row>
@@ -9440,7 +8930,7 @@
       <c r="H7" t="s">
         <v>274</v>
       </c>
-      <c r="I7" s="11" t="s">
+      <c r="I7" s="5" t="s">
         <v>192</v>
       </c>
       <c r="J7" t="s">
@@ -9466,7 +8956,7 @@
       <c r="H9" t="s">
         <v>278</v>
       </c>
-      <c r="I9" s="12" t="s">
+      <c r="I9" s="5" t="s">
         <v>279</v>
       </c>
       <c r="J9" t="s">
@@ -9480,7 +8970,7 @@
       <c r="D11">
         <v>2</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="E11" t="s">
         <v>281</v>
       </c>
       <c r="F11" t="s">
@@ -9492,7 +8982,7 @@
       <c r="H11" t="s">
         <v>218</v>
       </c>
-      <c r="I11" s="12" t="s">
+      <c r="I11" s="5" t="s">
         <v>282</v>
       </c>
       <c r="J11" t="s">
@@ -9500,38 +8990,32 @@
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A12" s="8"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
+      <c r="B12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="H12" s="1"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A13" s="24">
-        <v>1000</v>
-      </c>
-      <c r="B13" s="24"/>
-      <c r="C13" s="24"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="24" t="s">
+      <c r="A13" s="12" t="s">
+        <v>618</v>
+      </c>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="G13" s="24">
+      <c r="G13" s="12">
         <v>228</v>
       </c>
-      <c r="H13" s="24" t="s">
+      <c r="H13" s="12" t="s">
         <v>333</v>
       </c>
-      <c r="I13" s="25" t="s">
+      <c r="I13" s="14" t="s">
         <v>334</v>
       </c>
-      <c r="J13" s="24" t="s">
+      <c r="J13" s="12" t="s">
         <v>335</v>
       </c>
     </row>
@@ -9548,7 +9032,7 @@
       <c r="H15" t="s">
         <v>338</v>
       </c>
-      <c r="I15" s="11" t="s">
+      <c r="I15" s="5" t="s">
         <v>339</v>
       </c>
       <c r="J15" t="s">
@@ -9568,7 +9052,7 @@
       <c r="H17" t="s">
         <v>341</v>
       </c>
-      <c r="I17" s="12" t="s">
+      <c r="I17" s="5" t="s">
         <v>343</v>
       </c>
       <c r="J17" t="s">
@@ -9579,7 +9063,6 @@
       <c r="A19">
         <v>1000</v>
       </c>
-      <c r="E19" s="13"/>
       <c r="F19" t="s">
         <v>22</v>
       </c>
@@ -9589,7 +9072,7 @@
       <c r="H19" t="s">
         <v>342</v>
       </c>
-      <c r="I19" s="12" t="s">
+      <c r="I19" s="5" t="s">
         <v>345</v>
       </c>
       <c r="J19" t="s">
@@ -9597,61 +9080,61 @@
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A25" s="27" t="s">
+      <c r="A25" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="B25" s="27"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="27"/>
-      <c r="F25" s="28" t="s">
+      <c r="B25" s="15"/>
+      <c r="C25" s="15"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="G25" s="28"/>
-      <c r="H25" s="28"/>
-      <c r="I25" s="28"/>
-      <c r="J25" s="28"/>
+      <c r="G25" s="16"/>
+      <c r="H25" s="16"/>
+      <c r="I25" s="16"/>
+      <c r="J25" s="16"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A26" s="8" t="s">
+      <c r="A26" t="s">
         <v>181</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="B26" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" t="s">
         <v>183</v>
       </c>
-      <c r="D26" s="7" t="s">
+      <c r="D26" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E26" s="8" t="s">
+      <c r="E26" t="s">
         <v>11</v>
       </c>
-      <c r="F26" s="8" t="s">
+      <c r="F26" t="s">
         <v>181</v>
       </c>
-      <c r="G26" s="7" t="s">
+      <c r="G26" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="H26" s="8" t="s">
+      <c r="H26" t="s">
         <v>189</v>
       </c>
-      <c r="I26" s="7" t="s">
+      <c r="I26" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J26" s="8" t="s">
+      <c r="J26" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A27" s="8" t="s">
+      <c r="A27" t="s">
         <v>14</v>
       </c>
-      <c r="B27" s="7">
+      <c r="B27" s="1">
         <v>273</v>
       </c>
-      <c r="C27" s="8">
+      <c r="C27">
         <v>66</v>
       </c>
       <c r="D27" t="s">
@@ -9660,19 +9143,19 @@
       <c r="E27" t="s">
         <v>599</v>
       </c>
-      <c r="F27" s="7" t="s">
+      <c r="F27" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G27" s="8">
+      <c r="G27">
         <v>118</v>
       </c>
-      <c r="H27" s="7">
+      <c r="H27" s="1">
         <v>41</v>
       </c>
-      <c r="I27" s="6" t="s">
+      <c r="I27" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="J27" s="7" t="s">
+      <c r="J27" s="1" t="s">
         <v>600</v>
       </c>
     </row>
@@ -9686,7 +9169,7 @@
       <c r="C28">
         <v>285</v>
       </c>
-      <c r="D28" s="12" t="s">
+      <c r="D28" s="5" t="s">
         <v>334</v>
       </c>
       <c r="E28" t="s">
@@ -9701,7 +9184,7 @@
       <c r="H28">
         <v>79</v>
       </c>
-      <c r="I28" s="12" t="s">
+      <c r="I28" s="5" t="s">
         <v>336</v>
       </c>
       <c r="J28" t="s">
@@ -9718,7 +9201,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:L28"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -9736,81 +9219,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A1" s="7"/>
-      <c r="B1" s="8"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="9" t="s">
+      <c r="A1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="G1" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="H1" s="8"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
+      <c r="I1" s="1"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" s="7"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
+      <c r="A2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="I2" s="1"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3" s="7"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
+      <c r="A3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="I3" s="1"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" t="s">
         <v>1</v>
       </c>
-      <c r="G4" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="H4" s="8" t="s">
+      <c r="G4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H4" t="s">
         <v>3</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="I4" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="J4" t="s">
         <v>11</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="K4" t="s">
         <v>12</v>
       </c>
-      <c r="L4" s="8" t="s">
+      <c r="L4" t="s">
         <v>13</v>
       </c>
     </row>
@@ -9859,7 +9324,7 @@
       <c r="H7" t="s">
         <v>287</v>
       </c>
-      <c r="I7" s="11" t="s">
+      <c r="I7" s="5" t="s">
         <v>195</v>
       </c>
       <c r="J7" t="s">
@@ -9885,7 +9350,7 @@
       <c r="H9" t="s">
         <v>291</v>
       </c>
-      <c r="I9" s="12" t="s">
+      <c r="I9" s="5" t="s">
         <v>289</v>
       </c>
       <c r="J9" t="s">
@@ -9899,7 +9364,7 @@
       <c r="D11">
         <v>2</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="E11" t="s">
         <v>293</v>
       </c>
       <c r="F11" t="s">
@@ -9911,7 +9376,7 @@
       <c r="H11" t="s">
         <v>218</v>
       </c>
-      <c r="I11" s="12" t="s">
+      <c r="I11" s="5" t="s">
         <v>294</v>
       </c>
       <c r="J11" t="s">
@@ -9919,38 +9384,32 @@
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A12" s="8"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
+      <c r="B12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="H12" s="1"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A13" s="24">
-        <v>1000</v>
-      </c>
-      <c r="B13" s="24"/>
-      <c r="C13" s="24"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="24" t="s">
+      <c r="A13" s="12">
+        <v>1000</v>
+      </c>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="G13" s="24">
+      <c r="G13" s="12">
         <v>240</v>
       </c>
-      <c r="H13" s="24" t="s">
+      <c r="H13" s="12" t="s">
         <v>319</v>
       </c>
-      <c r="I13" s="25" t="s">
+      <c r="I13" s="14" t="s">
         <v>321</v>
       </c>
-      <c r="J13" s="26" t="s">
+      <c r="J13" s="13" t="s">
         <v>325</v>
       </c>
     </row>
@@ -9967,7 +9426,7 @@
       <c r="H15" t="s">
         <v>320</v>
       </c>
-      <c r="I15" s="11" t="s">
+      <c r="I15" s="5" t="s">
         <v>324</v>
       </c>
       <c r="J15" t="s">
@@ -9987,7 +9446,7 @@
       <c r="H17" t="s">
         <v>327</v>
       </c>
-      <c r="I17" s="12" t="s">
+      <c r="I17" s="5" t="s">
         <v>328</v>
       </c>
       <c r="J17" t="s">
@@ -9998,7 +9457,6 @@
       <c r="A19">
         <v>1000</v>
       </c>
-      <c r="E19" s="13"/>
       <c r="F19" t="s">
         <v>22</v>
       </c>
@@ -10008,7 +9466,7 @@
       <c r="H19" t="s">
         <v>330</v>
       </c>
-      <c r="I19" s="12" t="s">
+      <c r="I19" s="5" t="s">
         <v>331</v>
       </c>
       <c r="J19" t="s">
@@ -10016,61 +9474,61 @@
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A25" s="27" t="s">
+      <c r="A25" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="B25" s="27"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="27"/>
-      <c r="F25" s="28" t="s">
+      <c r="B25" s="15"/>
+      <c r="C25" s="15"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="G25" s="28"/>
-      <c r="H25" s="28"/>
-      <c r="I25" s="28"/>
-      <c r="J25" s="28"/>
+      <c r="G25" s="16"/>
+      <c r="H25" s="16"/>
+      <c r="I25" s="16"/>
+      <c r="J25" s="16"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A26" s="8" t="s">
+      <c r="A26" t="s">
         <v>181</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="B26" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" t="s">
         <v>183</v>
       </c>
-      <c r="D26" s="7" t="s">
+      <c r="D26" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E26" s="8" t="s">
+      <c r="E26" t="s">
         <v>11</v>
       </c>
-      <c r="F26" s="8" t="s">
+      <c r="F26" t="s">
         <v>181</v>
       </c>
-      <c r="G26" s="7" t="s">
+      <c r="G26" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="H26" s="8" t="s">
+      <c r="H26" t="s">
         <v>189</v>
       </c>
-      <c r="I26" s="7" t="s">
+      <c r="I26" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J26" s="8" t="s">
+      <c r="J26" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A27" s="8" t="s">
+      <c r="A27" t="s">
         <v>14</v>
       </c>
-      <c r="B27" s="7">
+      <c r="B27" s="1">
         <v>287</v>
       </c>
-      <c r="C27" s="8">
+      <c r="C27">
         <v>78</v>
       </c>
       <c r="D27" t="s">
@@ -10079,24 +9537,24 @@
       <c r="E27" t="s">
         <v>603</v>
       </c>
-      <c r="F27" s="7" t="s">
+      <c r="F27" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G27" s="8">
+      <c r="G27">
         <v>118</v>
       </c>
-      <c r="H27" s="7">
+      <c r="H27" s="1">
         <v>36</v>
       </c>
-      <c r="I27" s="6" t="s">
+      <c r="I27" s="5" t="s">
         <v>604</v>
       </c>
-      <c r="J27" s="7" t="s">
+      <c r="J27" s="1" t="s">
         <v>605</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A28" s="8" t="s">
+      <c r="A28" t="s">
         <v>14</v>
       </c>
       <c r="B28">
@@ -10105,22 +9563,22 @@
       <c r="C28">
         <v>252</v>
       </c>
-      <c r="D28" s="12" t="s">
+      <c r="D28" s="5" t="s">
         <v>321</v>
       </c>
-      <c r="E28" s="14">
+      <c r="E28" s="1">
         <v>246380</v>
       </c>
-      <c r="F28" s="8" t="s">
+      <c r="F28" t="s">
         <v>14</v>
       </c>
-      <c r="G28" s="8">
+      <c r="G28">
         <v>136</v>
       </c>
-      <c r="H28" s="8">
+      <c r="H28">
         <v>84</v>
       </c>
-      <c r="I28" s="12" t="s">
+      <c r="I28" s="5" t="s">
         <v>322</v>
       </c>
       <c r="J28" t="s">

--- a/Experiments/DBCV_Conclu.xlsx
+++ b/Experiments/DBCV_Conclu.xlsx
@@ -8,29 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\das-sb\Downloads\thesis_documentation\Experiments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A2D5C8C-9138-4E3A-BDC0-FBB8D1508B28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC3642A8-18F1-4EE1-94C4-02A228D635EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet10" sheetId="10" r:id="rId2"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
-    <sheet name="Sheet11" sheetId="11" r:id="rId4"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId5"/>
-    <sheet name="Sheet4" sheetId="4" r:id="rId6"/>
-    <sheet name="Sheet5" sheetId="5" r:id="rId7"/>
-    <sheet name="Sheet6" sheetId="6" r:id="rId8"/>
-    <sheet name="Sheet7" sheetId="7" r:id="rId9"/>
-    <sheet name="Sheet8" sheetId="8" r:id="rId10"/>
-    <sheet name="Sheet9" sheetId="9" r:id="rId11"/>
+    <sheet name="Sheet12" sheetId="12" r:id="rId4"/>
+    <sheet name="Sheet13" sheetId="13" r:id="rId5"/>
+    <sheet name="Sheet14" sheetId="14" r:id="rId6"/>
+    <sheet name="Sheet11" sheetId="11" r:id="rId7"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId8"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId9"/>
+    <sheet name="Sheet5" sheetId="5" r:id="rId10"/>
+    <sheet name="Sheet6" sheetId="6" r:id="rId11"/>
+    <sheet name="Sheet7" sheetId="7" r:id="rId12"/>
+    <sheet name="Sheet8" sheetId="8" r:id="rId13"/>
+    <sheet name="Sheet9" sheetId="9" r:id="rId14"/>
   </sheets>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1383" uniqueCount="619">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1700" uniqueCount="685">
   <si>
     <t>Datapoints</t>
   </si>
@@ -1896,6 +1899,204 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>(K=32)</t>
+  </si>
+  <si>
+    <t>6.731 secs</t>
+  </si>
+  <si>
+    <t>0.212 secs</t>
+  </si>
+  <si>
+    <t>0.173</t>
+  </si>
+  <si>
+    <t>3233.072 secs</t>
+  </si>
+  <si>
+    <t>598 clusters</t>
+  </si>
+  <si>
+    <t>217 outliers</t>
+  </si>
+  <si>
+    <t>-0.012</t>
+  </si>
+  <si>
+    <t>611.964 secs</t>
+  </si>
+  <si>
+    <t>12.671 secs</t>
+  </si>
+  <si>
+    <t>0.617 secs</t>
+  </si>
+  <si>
+    <t>0.214</t>
+  </si>
+  <si>
+    <t>119108.002 secs</t>
+  </si>
+  <si>
+    <t>1520 clusters</t>
+  </si>
+  <si>
+    <t>508 outliers</t>
+  </si>
+  <si>
+    <t>-0.249</t>
+  </si>
+  <si>
+    <t>3478.825 secs</t>
+  </si>
+  <si>
+    <t>6.729 secs</t>
+  </si>
+  <si>
+    <t>0.295</t>
+  </si>
+  <si>
+    <t>-0.211</t>
+  </si>
+  <si>
+    <t>6.589 secs</t>
+  </si>
+  <si>
+    <t>0.109</t>
+  </si>
+  <si>
+    <t>-0.159</t>
+  </si>
+  <si>
+    <t>Early stopping patience 3</t>
+  </si>
+  <si>
+    <t>(Dim=512)(K=32)</t>
+  </si>
+  <si>
+    <t>0.112 secs</t>
+  </si>
+  <si>
+    <t>0.132</t>
+  </si>
+  <si>
+    <t>Kmedoids</t>
+  </si>
+  <si>
+    <t>-0.054</t>
+  </si>
+  <si>
+    <t>3.535 secs</t>
+  </si>
+  <si>
+    <t>-0.008</t>
+  </si>
+  <si>
+    <t>3.614 secs</t>
+  </si>
+  <si>
+    <t>3.643 secs</t>
+  </si>
+  <si>
+    <t>3.765 secs</t>
+  </si>
+  <si>
+    <t>0.299</t>
+  </si>
+  <si>
+    <t>63.805 secs</t>
+  </si>
+  <si>
+    <t>Early stopping patience 7</t>
+  </si>
+  <si>
+    <t>0.126</t>
+  </si>
+  <si>
+    <t>0.199</t>
+  </si>
+  <si>
+    <t>0.011</t>
+  </si>
+  <si>
+    <t>0.032</t>
+  </si>
+  <si>
+    <t>-0.018</t>
+  </si>
+  <si>
+    <t>0.646</t>
+  </si>
+  <si>
+    <t>16.575 secs</t>
+  </si>
+  <si>
+    <t>-0.425</t>
+  </si>
+  <si>
+    <t>15.086 secs</t>
+  </si>
+  <si>
+    <t>-0.312</t>
+  </si>
+  <si>
+    <t>0.655</t>
+  </si>
+  <si>
+    <t>-0.352</t>
+  </si>
+  <si>
+    <t>Early stopping patience 10</t>
+  </si>
+  <si>
+    <t>0.190</t>
+  </si>
+  <si>
+    <t>-0.019</t>
+  </si>
+  <si>
+    <t>0.288</t>
+  </si>
+  <si>
+    <t>0.013</t>
+  </si>
+  <si>
+    <t>0.128</t>
+  </si>
+  <si>
+    <t>0.246</t>
+  </si>
+  <si>
+    <t>0.037</t>
+  </si>
+  <si>
+    <t>-0.083</t>
+  </si>
+  <si>
+    <t>0.273</t>
+  </si>
+  <si>
+    <t>0.113</t>
+  </si>
+  <si>
+    <t>0.212</t>
+  </si>
+  <si>
+    <t>0.009</t>
+  </si>
+  <si>
+    <t>lr=0.01, lr_decay=0.1</t>
+  </si>
+  <si>
+    <t>lr=0.001, lr_decay=0.5</t>
+  </si>
+  <si>
+    <t>0.043</t>
+  </si>
+  <si>
+    <t>-0.001</t>
   </si>
 </sst>
 </file>
@@ -2332,32 +2533,32 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:N75"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.90625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.6328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="29.90625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="80.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="80.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G1" s="6" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="4" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -2401,7 +2602,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>1000</v>
       </c>
@@ -2435,7 +2636,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
         <v>1000</v>
       </c>
@@ -2469,7 +2670,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>1000</v>
       </c>
@@ -2503,7 +2704,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>1000</v>
       </c>
@@ -2537,7 +2738,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>1000</v>
       </c>
@@ -2571,7 +2772,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>1000</v>
       </c>
@@ -2605,7 +2806,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>1000</v>
       </c>
@@ -2645,7 +2846,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>1000</v>
       </c>
@@ -2679,7 +2880,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="1"/>
       <c r="C13"/>
       <c r="D13" s="1"/>
@@ -2687,7 +2888,7 @@
       <c r="F13" s="1"/>
       <c r="G13"/>
     </row>
-    <row r="14" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="13">
         <v>1000</v>
       </c>
@@ -2717,7 +2918,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="1"/>
       <c r="C15"/>
       <c r="D15" s="1"/>
@@ -2725,7 +2926,7 @@
       <c r="F15" s="1"/>
       <c r="G15"/>
     </row>
-    <row r="16" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>1000</v>
       </c>
@@ -2755,7 +2956,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="1"/>
       <c r="C17"/>
       <c r="D17" s="1"/>
@@ -2764,7 +2965,7 @@
       <c r="G17"/>
       <c r="K17" s="5"/>
     </row>
-    <row r="18" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>1000</v>
       </c>
@@ -2794,7 +2995,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="1"/>
       <c r="C19"/>
       <c r="D19" s="1"/>
@@ -2803,7 +3004,7 @@
       <c r="G19"/>
       <c r="K19" s="5"/>
     </row>
-    <row r="20" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>1000</v>
       </c>
@@ -2833,7 +3034,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="1"/>
       <c r="C21"/>
       <c r="D21" s="1"/>
@@ -2841,7 +3042,7 @@
       <c r="F21" s="1"/>
       <c r="G21"/>
     </row>
-    <row r="22" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
         <v>180</v>
       </c>
@@ -2857,7 +3058,7 @@
       <c r="J22" s="16"/>
       <c r="K22" s="16"/>
     </row>
-    <row r="23" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>181</v>
       </c>
@@ -2889,7 +3090,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>1000</v>
       </c>
@@ -2924,7 +3125,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>1000</v>
       </c>
@@ -2935,7 +3136,7 @@
       <c r="J25" s="5"/>
       <c r="K25" s="1"/>
     </row>
-    <row r="26" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="1"/>
       <c r="C26"/>
       <c r="D26" s="1"/>
@@ -2943,7 +3144,7 @@
       <c r="F26" s="1"/>
       <c r="G26"/>
     </row>
-    <row r="27" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>2000</v>
       </c>
@@ -2976,8 +3177,11 @@
       <c r="L27" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="28" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M27" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>2000</v>
       </c>
@@ -3011,7 +3215,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>2000</v>
       </c>
@@ -3048,7 +3252,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>2000</v>
       </c>
@@ -3082,7 +3286,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>2000</v>
       </c>
@@ -3116,7 +3320,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>2000</v>
       </c>
@@ -3150,7 +3354,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="33" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>2000</v>
       </c>
@@ -3184,7 +3388,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="34" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>2000</v>
       </c>
@@ -3218,7 +3422,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="35" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="1"/>
       <c r="C35"/>
       <c r="D35" s="1"/>
@@ -3226,7 +3430,7 @@
       <c r="F35" s="1"/>
       <c r="G35"/>
     </row>
-    <row r="36" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="1"/>
       <c r="C36"/>
       <c r="D36" s="1"/>
@@ -3234,7 +3438,7 @@
       <c r="F36" s="1"/>
       <c r="G36"/>
     </row>
-    <row r="37" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>5000</v>
       </c>
@@ -3268,7 +3472,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="38" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>5000</v>
       </c>
@@ -3305,7 +3509,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="39" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>5000</v>
       </c>
@@ -3339,7 +3543,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="40" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>5000</v>
       </c>
@@ -3376,7 +3580,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="41" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>5000</v>
       </c>
@@ -3410,7 +3614,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="42" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>5000</v>
       </c>
@@ -3450,7 +3654,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="43" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>5000</v>
       </c>
@@ -3484,7 +3688,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="44" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>5000</v>
       </c>
@@ -3518,13 +3722,13 @@
         <v>148</v>
       </c>
     </row>
-    <row r="45" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B49" s="15" t="s">
         <v>180</v>
       </c>
@@ -3540,7 +3744,7 @@
       <c r="J49" s="16"/>
       <c r="K49" s="16"/>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
         <v>181</v>
       </c>
@@ -3572,7 +3776,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>1000</v>
       </c>
@@ -3607,12 +3811,12 @@
         <v>191</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="G66" s="6" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>0</v>
       </c>
@@ -3656,7 +3860,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>1000</v>
       </c>
@@ -3688,7 +3892,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>1000</v>
       </c>
@@ -3720,7 +3924,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>1000</v>
       </c>
@@ -3752,7 +3956,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>1000</v>
       </c>
@@ -3787,7 +3991,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>1000</v>
       </c>
@@ -3819,7 +4023,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>1000</v>
       </c>
@@ -3851,7 +4055,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>1000</v>
       </c>
@@ -3883,7 +4087,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>1000</v>
       </c>
@@ -3928,46 +4132,47 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:L33"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:L31"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="14.08984375" customWidth="1"/>
-    <col min="3" max="3" width="13.36328125" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" customWidth="1"/>
-    <col min="5" max="5" width="12.81640625" customWidth="1"/>
-    <col min="6" max="6" width="17.36328125" customWidth="1"/>
-    <col min="7" max="7" width="14.6328125" customWidth="1"/>
-    <col min="8" max="8" width="14.54296875" customWidth="1"/>
-    <col min="9" max="9" width="14.08984375" customWidth="1"/>
-    <col min="10" max="10" width="16.08984375" customWidth="1"/>
-    <col min="11" max="11" width="43.1796875" customWidth="1"/>
+    <col min="1" max="1" width="15.140625" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="5" width="14.140625" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" customWidth="1"/>
+    <col min="8" max="8" width="14.140625" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" customWidth="1"/>
+    <col min="10" max="10" width="15.85546875" customWidth="1"/>
+    <col min="11" max="11" width="30.85546875" customWidth="1"/>
+    <col min="12" max="12" width="75.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="C1" s="1"/>
       <c r="E1" s="1"/>
       <c r="G1" s="6" t="s">
-        <v>296</v>
+        <v>255</v>
       </c>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="C2" s="1"/>
       <c r="E2" s="1"/>
       <c r="G2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="C3" s="1"/>
       <c r="E3" s="1"/>
       <c r="G3" s="1"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -4005,7 +4210,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1000</v>
       </c>
@@ -4013,25 +4218,25 @@
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>297</v>
+        <v>259</v>
       </c>
       <c r="F5" t="s">
         <v>14</v>
       </c>
       <c r="G5">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="H5" t="s">
-        <v>170</v>
+        <v>593</v>
       </c>
       <c r="I5" t="s">
-        <v>606</v>
+        <v>594</v>
       </c>
       <c r="J5" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>1000</v>
       </c>
@@ -4039,7 +4244,7 @@
         <v>2</v>
       </c>
       <c r="E7" t="s">
-        <v>298</v>
+        <v>260</v>
       </c>
       <c r="F7" t="s">
         <v>33</v>
@@ -4048,16 +4253,16 @@
         <v>175</v>
       </c>
       <c r="H7" t="s">
-        <v>299</v>
+        <v>261</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>300</v>
+        <v>262</v>
       </c>
       <c r="J7" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>1000</v>
       </c>
@@ -4065,7 +4270,7 @@
         <v>2</v>
       </c>
       <c r="E9" t="s">
-        <v>302</v>
+        <v>264</v>
       </c>
       <c r="F9" t="s">
         <v>44</v>
@@ -4074,16 +4279,16 @@
         <v>175</v>
       </c>
       <c r="H9" t="s">
-        <v>303</v>
+        <v>265</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>304</v>
+        <v>219</v>
       </c>
       <c r="J9" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>1000</v>
       </c>
@@ -4091,7 +4296,7 @@
         <v>2</v>
       </c>
       <c r="E11" t="s">
-        <v>306</v>
+        <v>267</v>
       </c>
       <c r="F11" t="s">
         <v>22</v>
@@ -4100,22 +4305,22 @@
         <v>175</v>
       </c>
       <c r="H11" t="s">
-        <v>233</v>
+        <v>268</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>219</v>
+        <v>269</v>
       </c>
       <c r="J11" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B12" s="1"/>
       <c r="D12" s="1"/>
       <c r="F12" s="1"/>
       <c r="H12" s="1"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="12">
         <v>1000</v>
       </c>
@@ -4127,6 +4332,1189 @@
         <v>14</v>
       </c>
       <c r="G13" s="12">
+        <v>217</v>
+      </c>
+      <c r="H13" s="12" t="s">
+        <v>347</v>
+      </c>
+      <c r="I13" s="14" t="s">
+        <v>351</v>
+      </c>
+      <c r="J13" s="12" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>1000</v>
+      </c>
+      <c r="F15" t="s">
+        <v>33</v>
+      </c>
+      <c r="G15">
+        <v>175</v>
+      </c>
+      <c r="H15" t="s">
+        <v>348</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="J15" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>1000</v>
+      </c>
+      <c r="F17" t="s">
+        <v>44</v>
+      </c>
+      <c r="G17">
+        <v>175</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="J17" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>1000</v>
+      </c>
+      <c r="F19" t="s">
+        <v>22</v>
+      </c>
+      <c r="G19">
+        <v>175</v>
+      </c>
+      <c r="H19" t="s">
+        <v>358</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="J19" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="B28" s="15"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="G28" s="16"/>
+      <c r="H28" s="16"/>
+      <c r="I28" s="16"/>
+      <c r="J28" s="16"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>181</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C29" t="s">
+        <v>183</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E29" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" t="s">
+        <v>181</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="H29" t="s">
+        <v>189</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J29" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>14</v>
+      </c>
+      <c r="B30" s="1">
+        <v>286</v>
+      </c>
+      <c r="C30">
+        <v>88</v>
+      </c>
+      <c r="D30" t="s">
+        <v>257</v>
+      </c>
+      <c r="E30" t="s">
+        <v>258</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G30">
+        <v>104</v>
+      </c>
+      <c r="H30" s="1">
+        <v>28</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>596</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>14</v>
+      </c>
+      <c r="B31">
+        <v>217</v>
+      </c>
+      <c r="C31">
+        <v>266</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="E31" t="s">
+        <v>352</v>
+      </c>
+      <c r="F31" t="s">
+        <v>14</v>
+      </c>
+      <c r="G31">
+        <v>122</v>
+      </c>
+      <c r="H31">
+        <v>77</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="J31" t="s">
+        <v>354</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="F28:J28"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:L28"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.85546875" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" customWidth="1"/>
+    <col min="5" max="5" width="12.5703125" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" customWidth="1"/>
+    <col min="7" max="7" width="17.5703125" customWidth="1"/>
+    <col min="8" max="8" width="15.42578125" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" customWidth="1"/>
+    <col min="11" max="11" width="31.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="G1" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4" t="s">
+        <v>12</v>
+      </c>
+      <c r="L4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>1000</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5" t="s">
+        <v>272</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5">
+        <v>273</v>
+      </c>
+      <c r="H5" t="s">
+        <v>421</v>
+      </c>
+      <c r="I5" t="s">
+        <v>598</v>
+      </c>
+      <c r="J5" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>1000</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7" t="s">
+        <v>273</v>
+      </c>
+      <c r="F7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7">
+        <v>175</v>
+      </c>
+      <c r="H7" t="s">
+        <v>274</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="J7" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>1000</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9" t="s">
+        <v>277</v>
+      </c>
+      <c r="F9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G9">
+        <v>175</v>
+      </c>
+      <c r="H9" t="s">
+        <v>278</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="J9" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>1000</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+      <c r="E11" t="s">
+        <v>281</v>
+      </c>
+      <c r="F11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11">
+        <v>175</v>
+      </c>
+      <c r="H11" t="s">
+        <v>218</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="J11" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="H12" s="1"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="12" t="s">
+        <v>618</v>
+      </c>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" s="12">
+        <v>228</v>
+      </c>
+      <c r="H13" s="12" t="s">
+        <v>333</v>
+      </c>
+      <c r="I13" s="14" t="s">
+        <v>334</v>
+      </c>
+      <c r="J13" s="12" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>1000</v>
+      </c>
+      <c r="F15" t="s">
+        <v>33</v>
+      </c>
+      <c r="G15">
+        <v>175</v>
+      </c>
+      <c r="H15" t="s">
+        <v>338</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="J15" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>1000</v>
+      </c>
+      <c r="F17" t="s">
+        <v>44</v>
+      </c>
+      <c r="G17">
+        <v>175</v>
+      </c>
+      <c r="H17" t="s">
+        <v>341</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="J17" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>1000</v>
+      </c>
+      <c r="F19" t="s">
+        <v>22</v>
+      </c>
+      <c r="G19">
+        <v>175</v>
+      </c>
+      <c r="H19" t="s">
+        <v>342</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="J19" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="B25" s="15"/>
+      <c r="C25" s="15"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="G25" s="16"/>
+      <c r="H25" s="16"/>
+      <c r="I25" s="16"/>
+      <c r="J25" s="16"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>181</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C26" t="s">
+        <v>183</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E26" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" t="s">
+        <v>181</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="H26" t="s">
+        <v>189</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J26" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" s="1">
+        <v>273</v>
+      </c>
+      <c r="C27">
+        <v>66</v>
+      </c>
+      <c r="D27" t="s">
+        <v>598</v>
+      </c>
+      <c r="E27" t="s">
+        <v>599</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G27">
+        <v>118</v>
+      </c>
+      <c r="H27" s="1">
+        <v>41</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28">
+        <v>228</v>
+      </c>
+      <c r="C28">
+        <v>285</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="E28" t="s">
+        <v>335</v>
+      </c>
+      <c r="F28" t="s">
+        <v>14</v>
+      </c>
+      <c r="G28">
+        <v>124</v>
+      </c>
+      <c r="H28">
+        <v>79</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="J28" t="s">
+        <v>337</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="F25:J25"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:L28"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.85546875" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" customWidth="1"/>
+    <col min="5" max="5" width="16.140625" customWidth="1"/>
+    <col min="6" max="6" width="17.140625" customWidth="1"/>
+    <col min="7" max="7" width="17.5703125" customWidth="1"/>
+    <col min="8" max="8" width="16.5703125" customWidth="1"/>
+    <col min="9" max="9" width="16.85546875" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="27.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="G1" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4" t="s">
+        <v>12</v>
+      </c>
+      <c r="L4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>1000</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5" t="s">
+        <v>284</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5">
+        <v>287</v>
+      </c>
+      <c r="H5" t="s">
+        <v>601</v>
+      </c>
+      <c r="I5" t="s">
+        <v>602</v>
+      </c>
+      <c r="J5" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>1000</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7" t="s">
+        <v>286</v>
+      </c>
+      <c r="F7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7">
+        <v>175</v>
+      </c>
+      <c r="H7" t="s">
+        <v>287</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="J7" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>1000</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9" t="s">
+        <v>290</v>
+      </c>
+      <c r="F9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G9">
+        <v>175</v>
+      </c>
+      <c r="H9" t="s">
+        <v>291</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="J9" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>1000</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+      <c r="E11" t="s">
+        <v>293</v>
+      </c>
+      <c r="F11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11">
+        <v>175</v>
+      </c>
+      <c r="H11" t="s">
+        <v>218</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="J11" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="H12" s="1"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="12">
+        <v>1000</v>
+      </c>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" s="12">
+        <v>240</v>
+      </c>
+      <c r="H13" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="I13" s="14" t="s">
+        <v>321</v>
+      </c>
+      <c r="J13" s="13" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>1000</v>
+      </c>
+      <c r="F15" t="s">
+        <v>33</v>
+      </c>
+      <c r="G15">
+        <v>175</v>
+      </c>
+      <c r="H15" t="s">
+        <v>320</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="J15" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>1000</v>
+      </c>
+      <c r="F17" t="s">
+        <v>44</v>
+      </c>
+      <c r="G17">
+        <v>175</v>
+      </c>
+      <c r="H17" t="s">
+        <v>327</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="J17" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>1000</v>
+      </c>
+      <c r="F19" t="s">
+        <v>22</v>
+      </c>
+      <c r="G19">
+        <v>175</v>
+      </c>
+      <c r="H19" t="s">
+        <v>330</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="J19" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="B25" s="15"/>
+      <c r="C25" s="15"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="G25" s="16"/>
+      <c r="H25" s="16"/>
+      <c r="I25" s="16"/>
+      <c r="J25" s="16"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>181</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C26" t="s">
+        <v>183</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E26" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" t="s">
+        <v>181</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="H26" t="s">
+        <v>189</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J26" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" s="1">
+        <v>287</v>
+      </c>
+      <c r="C27">
+        <v>78</v>
+      </c>
+      <c r="D27" t="s">
+        <v>602</v>
+      </c>
+      <c r="E27" t="s">
+        <v>603</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G27">
+        <v>118</v>
+      </c>
+      <c r="H27" s="1">
+        <v>36</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>604</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28">
+        <v>240</v>
+      </c>
+      <c r="C28">
+        <v>252</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="E28" s="1">
+        <v>246380</v>
+      </c>
+      <c r="F28" t="s">
+        <v>14</v>
+      </c>
+      <c r="G28">
+        <v>136</v>
+      </c>
+      <c r="H28">
+        <v>84</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="J28" t="s">
+        <v>323</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="F25:J25"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <dimension ref="A1:L33"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="14.140625" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" customWidth="1"/>
+    <col min="5" max="5" width="12.85546875" customWidth="1"/>
+    <col min="6" max="6" width="17.42578125" customWidth="1"/>
+    <col min="7" max="8" width="14.5703125" customWidth="1"/>
+    <col min="9" max="9" width="14.140625" customWidth="1"/>
+    <col min="10" max="10" width="16.140625" customWidth="1"/>
+    <col min="11" max="11" width="43.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="G1" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4" t="s">
+        <v>12</v>
+      </c>
+      <c r="L4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>1000</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5" t="s">
+        <v>297</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5">
+        <v>290</v>
+      </c>
+      <c r="H5" t="s">
+        <v>170</v>
+      </c>
+      <c r="I5" t="s">
+        <v>606</v>
+      </c>
+      <c r="J5" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>1000</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7" t="s">
+        <v>298</v>
+      </c>
+      <c r="F7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7">
+        <v>175</v>
+      </c>
+      <c r="H7" t="s">
+        <v>299</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="J7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>1000</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9" t="s">
+        <v>302</v>
+      </c>
+      <c r="F9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G9">
+        <v>175</v>
+      </c>
+      <c r="H9" t="s">
+        <v>303</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="J9" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>1000</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+      <c r="E11" t="s">
+        <v>306</v>
+      </c>
+      <c r="F11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11">
+        <v>175</v>
+      </c>
+      <c r="H11" t="s">
+        <v>233</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="J11" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="H12" s="1"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="12">
+        <v>1000</v>
+      </c>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" s="12">
         <v>245</v>
       </c>
       <c r="H13" s="12" t="s">
@@ -4139,7 +5527,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>1000</v>
       </c>
@@ -4159,7 +5547,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>1000</v>
       </c>
@@ -4179,7 +5567,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>1000</v>
       </c>
@@ -4199,7 +5587,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="15" t="s">
         <v>180</v>
       </c>
@@ -4215,7 +5603,7 @@
       <c r="I30" s="16"/>
       <c r="J30" s="16"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>181</v>
       </c>
@@ -4247,7 +5635,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>14</v>
       </c>
@@ -4279,7 +5667,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>14</v>
       </c>
@@ -4321,25 +5709,23 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:L58"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.453125" customWidth="1"/>
-    <col min="2" max="2" width="16.36328125" customWidth="1"/>
-    <col min="3" max="3" width="13.08984375" customWidth="1"/>
-    <col min="4" max="4" width="13.1796875" customWidth="1"/>
-    <col min="5" max="5" width="13.36328125" customWidth="1"/>
-    <col min="6" max="6" width="15.81640625" customWidth="1"/>
-    <col min="7" max="7" width="13.1796875" customWidth="1"/>
-    <col min="8" max="8" width="13.81640625" customWidth="1"/>
-    <col min="9" max="9" width="13.90625" customWidth="1"/>
+    <col min="1" max="1" width="15.42578125" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" customWidth="1"/>
+    <col min="3" max="4" width="13.140625" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" customWidth="1"/>
+    <col min="6" max="6" width="15.85546875" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" customWidth="1"/>
+    <col min="8" max="9" width="13.85546875" customWidth="1"/>
     <col min="10" max="10" width="13" customWidth="1"/>
-    <col min="11" max="11" width="29.81640625" customWidth="1"/>
+    <col min="11" max="11" width="29.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="C1" s="1"/>
       <c r="E1" s="1"/>
@@ -4348,21 +5734,21 @@
       </c>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="C2" s="1"/>
       <c r="E2" s="1"/>
       <c r="G2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="C3" s="1"/>
       <c r="E3" s="1"/>
       <c r="G3" s="1"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -4400,7 +5786,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1000</v>
       </c>
@@ -4426,7 +5812,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>1000</v>
       </c>
@@ -4452,7 +5838,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>1000</v>
       </c>
@@ -4478,7 +5864,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>1000</v>
       </c>
@@ -4504,13 +5890,13 @@
         <v>408</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B12" s="1"/>
       <c r="D12" s="1"/>
       <c r="F12" s="1"/>
       <c r="H12" s="1"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="12">
         <v>1000</v>
       </c>
@@ -4534,7 +5920,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>1000</v>
       </c>
@@ -4554,7 +5940,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>1000</v>
       </c>
@@ -4574,7 +5960,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>1000</v>
       </c>
@@ -4594,7 +5980,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
         <v>180</v>
       </c>
@@ -4610,7 +5996,7 @@
       <c r="I24" s="16"/>
       <c r="J24" s="16"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>181</v>
       </c>
@@ -4642,7 +6028,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>14</v>
       </c>
@@ -4674,7 +6060,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>14</v>
       </c>
@@ -4706,7 +6092,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="C32" s="1"/>
       <c r="E32" s="1"/>
@@ -4715,21 +6101,21 @@
       </c>
       <c r="I32" s="1"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="C33" s="1"/>
       <c r="E33" s="1"/>
       <c r="G33" s="1"/>
       <c r="I33" s="1"/>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="C34" s="1"/>
       <c r="E34" s="1"/>
       <c r="G34" s="1"/>
       <c r="I34" s="1"/>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>0</v>
       </c>
@@ -4767,7 +6153,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>1000</v>
       </c>
@@ -4778,7 +6164,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>1000</v>
       </c>
@@ -4793,7 +6179,7 @@
       </c>
       <c r="I38" s="5"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>1000</v>
       </c>
@@ -4808,7 +6194,7 @@
       </c>
       <c r="I40" s="5"/>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>1000</v>
       </c>
@@ -4823,13 +6209,13 @@
       </c>
       <c r="I42" s="5"/>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B43" s="1"/>
       <c r="D43" s="1"/>
       <c r="F43" s="1"/>
       <c r="H43" s="1"/>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>1000</v>
       </c>
@@ -4849,7 +6235,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>1000</v>
       </c>
@@ -4869,7 +6255,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>1000</v>
       </c>
@@ -4889,7 +6275,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>1000</v>
       </c>
@@ -4909,7 +6295,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="15" t="s">
         <v>180</v>
       </c>
@@ -4925,7 +6311,7 @@
       <c r="I55" s="16"/>
       <c r="J55" s="16"/>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>181</v>
       </c>
@@ -4957,7 +6343,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>14</v>
       </c>
@@ -4969,7 +6355,7 @@
       <c r="I57" s="5"/>
       <c r="J57" s="1"/>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>14</v>
       </c>
@@ -5009,30 +6395,30 @@
     <mergeCell ref="F55:J55"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:N21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="2" max="2" width="12.90625" customWidth="1"/>
-    <col min="3" max="3" width="12.81640625" customWidth="1"/>
-    <col min="4" max="4" width="13.54296875" customWidth="1"/>
-    <col min="5" max="5" width="11.90625" customWidth="1"/>
-    <col min="6" max="6" width="9.6328125" customWidth="1"/>
-    <col min="7" max="7" width="11.36328125" customWidth="1"/>
-    <col min="8" max="8" width="16.81640625" customWidth="1"/>
-    <col min="9" max="9" width="14.08984375" customWidth="1"/>
-    <col min="10" max="10" width="15.1796875" customWidth="1"/>
-    <col min="11" max="11" width="13.90625" customWidth="1"/>
-    <col min="12" max="12" width="12.90625" customWidth="1"/>
-    <col min="13" max="13" width="27.90625" customWidth="1"/>
+    <col min="2" max="3" width="12.85546875" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" customWidth="1"/>
+    <col min="6" max="6" width="9.5703125" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" customWidth="1"/>
+    <col min="8" max="8" width="16.85546875" customWidth="1"/>
+    <col min="9" max="9" width="14.140625" customWidth="1"/>
+    <col min="10" max="10" width="15.140625" customWidth="1"/>
+    <col min="11" max="11" width="13.85546875" customWidth="1"/>
+    <col min="12" max="12" width="12.85546875" customWidth="1"/>
+    <col min="13" max="13" width="27.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="C1" s="1"/>
       <c r="E1" s="1"/>
@@ -5041,21 +6427,21 @@
       </c>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="C2" s="1"/>
       <c r="E2" s="1"/>
       <c r="G2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="C3" s="1"/>
       <c r="E3" s="1"/>
       <c r="G3" s="1"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -5099,7 +6485,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>1000</v>
       </c>
@@ -5132,14 +6518,14 @@
         <v>417</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="D6" s="2"/>
       <c r="F6" s="1"/>
       <c r="I6" s="2"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>1000</v>
       </c>
@@ -5172,7 +6558,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>1000</v>
       </c>
@@ -5205,14 +6591,14 @@
         <v>423</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="D10" s="2"/>
       <c r="F10" s="1"/>
       <c r="I10" s="2"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>1000</v>
       </c>
@@ -5245,28 +6631,28 @@
         <v>432</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="D13" s="1"/>
       <c r="F13" s="1"/>
       <c r="I13" s="1"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="D14" s="1"/>
       <c r="F14" s="1"/>
       <c r="I14" s="1"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="D15" s="1"/>
       <c r="F15" s="1"/>
       <c r="I15" s="1"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>99</v>
       </c>
@@ -5275,7 +6661,7 @@
       <c r="G16" s="1"/>
       <c r="I16" s="1"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="15" t="s">
         <v>180</v>
@@ -5292,7 +6678,7 @@
       <c r="J17" s="16"/>
       <c r="K17" s="16"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" t="s">
         <v>181</v>
@@ -5325,7 +6711,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>1000</v>
       </c>
@@ -5360,7 +6746,7 @@
         <v>65340</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="D20" s="1"/>
@@ -5368,7 +6754,7 @@
       <c r="I20" s="1"/>
       <c r="K20" s="5"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="D21" s="1"/>
@@ -5381,27 +6767,28 @@
     <mergeCell ref="G17:K17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L181"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
-    <col min="2" max="2" width="12.54296875" customWidth="1"/>
-    <col min="3" max="3" width="14.453125" customWidth="1"/>
-    <col min="4" max="4" width="15.90625" customWidth="1"/>
-    <col min="5" max="5" width="13.1796875" customWidth="1"/>
-    <col min="6" max="6" width="18.1796875" customWidth="1"/>
-    <col min="7" max="7" width="17.6328125" customWidth="1"/>
-    <col min="8" max="9" width="17.08984375" customWidth="1"/>
-    <col min="10" max="10" width="16.1796875" customWidth="1"/>
-    <col min="11" max="11" width="27.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" customWidth="1"/>
+    <col min="4" max="4" width="15.85546875" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" customWidth="1"/>
+    <col min="6" max="6" width="18.140625" customWidth="1"/>
+    <col min="7" max="7" width="17.5703125" customWidth="1"/>
+    <col min="8" max="9" width="17.140625" customWidth="1"/>
+    <col min="10" max="10" width="16.140625" customWidth="1"/>
+    <col min="11" max="11" width="27.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="C1" s="1"/>
       <c r="E1" s="1"/>
@@ -5413,21 +6800,21 @@
       </c>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="C2" s="1"/>
       <c r="E2" s="1"/>
       <c r="G2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="C3" s="1"/>
       <c r="E3" s="1"/>
       <c r="G3" s="1"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -5465,7 +6852,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1000</v>
       </c>
@@ -5491,7 +6878,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>1000</v>
       </c>
@@ -5517,7 +6904,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>1000</v>
       </c>
@@ -5543,7 +6930,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>1000</v>
       </c>
@@ -5569,7 +6956,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>99</v>
       </c>
@@ -5578,7 +6965,7 @@
       <c r="G14" s="1"/>
       <c r="I14" s="1"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="15" t="s">
         <v>180</v>
@@ -5595,7 +6982,7 @@
       <c r="J15" s="16"/>
       <c r="K15" s="16"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" t="s">
         <v>181</v>
@@ -5628,7 +7015,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>1000</v>
       </c>
@@ -5663,7 +7050,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G20" s="6" t="s">
         <v>201</v>
       </c>
@@ -5671,7 +7058,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>0</v>
       </c>
@@ -5709,7 +7096,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>1000</v>
       </c>
@@ -5735,7 +7122,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>1000</v>
       </c>
@@ -5761,7 +7148,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>1000</v>
       </c>
@@ -5787,7 +7174,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>1000</v>
       </c>
@@ -5813,7 +7200,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>99</v>
       </c>
@@ -5822,7 +7209,7 @@
       <c r="G32" s="1"/>
       <c r="I32" s="1"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="B33" s="15" t="s">
         <v>180</v>
@@ -5839,7 +7226,7 @@
       <c r="J33" s="16"/>
       <c r="K33" s="16"/>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="B34" t="s">
         <v>181</v>
@@ -5872,7 +7259,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>1000</v>
       </c>
@@ -5907,7 +7294,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G38" s="6" t="s">
         <v>201</v>
       </c>
@@ -5915,7 +7302,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>0</v>
       </c>
@@ -5953,7 +7340,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>1000</v>
       </c>
@@ -5979,7 +7366,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>1000</v>
       </c>
@@ -6005,7 +7392,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>1000</v>
       </c>
@@ -6031,7 +7418,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>1000</v>
       </c>
@@ -6057,7 +7444,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>99</v>
       </c>
@@ -6066,7 +7453,7 @@
       <c r="G50" s="1"/>
       <c r="I50" s="1"/>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
       <c r="B51" s="15" t="s">
         <v>180</v>
@@ -6083,7 +7470,7 @@
       <c r="J51" s="16"/>
       <c r="K51" s="16"/>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
       <c r="B52" t="s">
         <v>181</v>
@@ -6116,7 +7503,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>1000</v>
       </c>
@@ -6151,7 +7538,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G56" s="6" t="s">
         <v>201</v>
       </c>
@@ -6159,7 +7546,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>0</v>
       </c>
@@ -6197,7 +7584,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>1000</v>
       </c>
@@ -6223,7 +7610,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>1000</v>
       </c>
@@ -6249,7 +7636,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>1000</v>
       </c>
@@ -6275,7 +7662,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>1000</v>
       </c>
@@ -6301,7 +7688,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>99</v>
       </c>
@@ -6310,7 +7697,7 @@
       <c r="G68" s="1"/>
       <c r="I68" s="1"/>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="1"/>
       <c r="B69" s="15" t="s">
         <v>180</v>
@@ -6327,7 +7714,7 @@
       <c r="J69" s="16"/>
       <c r="K69" s="16"/>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
       <c r="B70" t="s">
         <v>181</v>
@@ -6360,7 +7747,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>1000</v>
       </c>
@@ -6395,7 +7782,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G94" s="6" t="s">
         <v>201</v>
       </c>
@@ -6403,7 +7790,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>0</v>
       </c>
@@ -6441,7 +7828,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>1000</v>
       </c>
@@ -6467,7 +7854,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>1000</v>
       </c>
@@ -6493,7 +7880,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>1000</v>
       </c>
@@ -6519,7 +7906,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>1000</v>
       </c>
@@ -6545,7 +7932,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>99</v>
       </c>
@@ -6554,7 +7941,7 @@
       <c r="G106" s="1"/>
       <c r="I106" s="1"/>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="B107" s="9" t="s">
         <v>180</v>
@@ -6571,7 +7958,7 @@
       <c r="J107" s="10"/>
       <c r="K107" s="10"/>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" s="1"/>
       <c r="B108" t="s">
         <v>181</v>
@@ -6604,7 +7991,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>1000</v>
       </c>
@@ -6639,7 +8026,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="G112" s="6" t="s">
         <v>201</v>
       </c>
@@ -6647,7 +8034,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>0</v>
       </c>
@@ -6685,7 +8072,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>1000</v>
       </c>
@@ -6711,7 +8098,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>1000</v>
       </c>
@@ -6737,7 +8124,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>1000</v>
       </c>
@@ -6763,7 +8150,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>1000</v>
       </c>
@@ -6789,7 +8176,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>99</v>
       </c>
@@ -6798,7 +8185,7 @@
       <c r="G124" s="1"/>
       <c r="I124" s="1"/>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
       <c r="B125" s="9" t="s">
         <v>180</v>
@@ -6815,7 +8202,7 @@
       <c r="J125" s="10"/>
       <c r="K125" s="10"/>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="B126" t="s">
         <v>181</v>
@@ -6848,7 +8235,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>1000</v>
       </c>
@@ -6883,7 +8270,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G130" s="6" t="s">
         <v>201</v>
       </c>
@@ -6891,7 +8278,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>0</v>
       </c>
@@ -6929,7 +8316,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>1000</v>
       </c>
@@ -6955,7 +8342,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>1000</v>
       </c>
@@ -6981,7 +8368,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>1000</v>
       </c>
@@ -7007,7 +8394,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>1000</v>
       </c>
@@ -7033,7 +8420,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>99</v>
       </c>
@@ -7042,7 +8429,7 @@
       <c r="G142" s="1"/>
       <c r="I142" s="1"/>
     </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A143" s="1"/>
       <c r="B143" s="9" t="s">
         <v>180</v>
@@ -7059,7 +8446,7 @@
       <c r="J143" s="10"/>
       <c r="K143" s="10"/>
     </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A144" s="1"/>
       <c r="B144" t="s">
         <v>181</v>
@@ -7092,7 +8479,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
         <v>1000</v>
       </c>
@@ -7127,7 +8514,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G148" s="6" t="s">
         <v>201</v>
       </c>
@@ -7135,7 +8522,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>0</v>
       </c>
@@ -7173,7 +8560,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>1000</v>
       </c>
@@ -7199,7 +8586,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>1000</v>
       </c>
@@ -7225,7 +8612,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>1000</v>
       </c>
@@ -7251,7 +8638,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>1000</v>
       </c>
@@ -7277,7 +8664,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
         <v>99</v>
       </c>
@@ -7286,7 +8673,7 @@
       <c r="G160" s="1"/>
       <c r="I160" s="1"/>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A161" s="1"/>
       <c r="B161" s="9" t="s">
         <v>180</v>
@@ -7303,7 +8690,7 @@
       <c r="J161" s="10"/>
       <c r="K161" s="10"/>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A162" s="1"/>
       <c r="B162" t="s">
         <v>181</v>
@@ -7336,7 +8723,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
         <v>1000</v>
       </c>
@@ -7371,7 +8758,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G166" s="6" t="s">
         <v>201</v>
       </c>
@@ -7379,7 +8766,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
         <v>0</v>
       </c>
@@ -7417,7 +8804,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>1000</v>
       </c>
@@ -7443,7 +8830,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>1000</v>
       </c>
@@ -7469,7 +8856,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>1000</v>
       </c>
@@ -7495,7 +8882,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>1000</v>
       </c>
@@ -7521,7 +8908,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
         <v>99</v>
       </c>
@@ -7530,7 +8917,7 @@
       <c r="G178" s="1"/>
       <c r="I178" s="1"/>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A179" s="1"/>
       <c r="B179" s="9" t="s">
         <v>180</v>
@@ -7547,7 +8934,7 @@
       <c r="J179" s="10"/>
       <c r="K179" s="10"/>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A180" s="1"/>
       <c r="B180" t="s">
         <v>181</v>
@@ -7580,7 +8967,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
         <v>1000</v>
       </c>
@@ -7632,22 +9019,1945 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC51EADD-ED9D-426A-9B66-438F915E2068}">
+  <dimension ref="A1:L34"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="14.140625" customWidth="1"/>
+    <col min="3" max="3" width="16.28515625" customWidth="1"/>
+    <col min="4" max="4" width="18.5703125" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" customWidth="1"/>
+    <col min="6" max="6" width="18.85546875" customWidth="1"/>
+    <col min="7" max="7" width="19.42578125" customWidth="1"/>
+    <col min="8" max="8" width="22.5703125" customWidth="1"/>
+    <col min="9" max="9" width="17.85546875" customWidth="1"/>
+    <col min="10" max="10" width="19.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="G1" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>619</v>
+      </c>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4" t="s">
+        <v>12</v>
+      </c>
+      <c r="L4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>2000</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5" t="s">
+        <v>620</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5">
+        <v>598</v>
+      </c>
+      <c r="H5" t="s">
+        <v>621</v>
+      </c>
+      <c r="I5" t="s">
+        <v>622</v>
+      </c>
+      <c r="J5" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>2000</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7" t="s">
+        <v>636</v>
+      </c>
+      <c r="F7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7">
+        <v>175</v>
+      </c>
+      <c r="H7" t="s">
+        <v>637</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>638</v>
+      </c>
+      <c r="J7" s="1">
+        <v>474365</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>2000</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9" t="s">
+        <v>636</v>
+      </c>
+      <c r="F9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G9">
+        <v>175</v>
+      </c>
+      <c r="H9" s="1">
+        <v>23992</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>504</v>
+      </c>
+      <c r="J9" s="1">
+        <v>477260</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>2000</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+      <c r="E11" t="s">
+        <v>639</v>
+      </c>
+      <c r="F11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11">
+        <v>175</v>
+      </c>
+      <c r="H11" t="s">
+        <v>640</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="J11" s="1">
+        <v>455365</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="I13" s="1"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="16"/>
+      <c r="K14" s="16"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="1"/>
+      <c r="B15" t="s">
+        <v>181</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D15" t="s">
+        <v>183</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15" t="s">
+        <v>181</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="I15" t="s">
+        <v>189</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K15" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>1000</v>
+      </c>
+      <c r="B16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="D16" t="s">
+        <v>625</v>
+      </c>
+      <c r="E16" t="s">
+        <v>622</v>
+      </c>
+      <c r="F16" t="s">
+        <v>623</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H16">
+        <v>238</v>
+      </c>
+      <c r="I16" s="1">
+        <v>74</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>626</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="G19" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>619</v>
+      </c>
+      <c r="I19" s="1"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="I20" s="1"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="I21" s="1"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" t="s">
+        <v>1</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H22" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" t="s">
+        <v>10</v>
+      </c>
+      <c r="J22" t="s">
+        <v>11</v>
+      </c>
+      <c r="K22" t="s">
+        <v>12</v>
+      </c>
+      <c r="L22" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>5000</v>
+      </c>
+      <c r="D23">
+        <v>2</v>
+      </c>
+      <c r="E23" t="s">
+        <v>628</v>
+      </c>
+      <c r="F23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G23">
+        <v>1520</v>
+      </c>
+      <c r="H23" t="s">
+        <v>629</v>
+      </c>
+      <c r="I23" t="s">
+        <v>630</v>
+      </c>
+      <c r="J23" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>5000</v>
+      </c>
+      <c r="D25">
+        <v>2</v>
+      </c>
+      <c r="E25" t="s">
+        <v>662</v>
+      </c>
+      <c r="F25" t="s">
+        <v>33</v>
+      </c>
+      <c r="G25">
+        <v>175</v>
+      </c>
+      <c r="H25" t="s">
+        <v>661</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>663</v>
+      </c>
+      <c r="J25" s="1">
+        <v>4027242</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>5000</v>
+      </c>
+      <c r="D27">
+        <v>2</v>
+      </c>
+      <c r="E27" t="s">
+        <v>664</v>
+      </c>
+      <c r="F27" t="s">
+        <v>44</v>
+      </c>
+      <c r="G27">
+        <v>175</v>
+      </c>
+      <c r="H27" s="1">
+        <v>368698</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>665</v>
+      </c>
+      <c r="J27" s="1">
+        <v>3945783</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>5000</v>
+      </c>
+      <c r="D29">
+        <v>2</v>
+      </c>
+      <c r="E29" s="1">
+        <v>12797</v>
+      </c>
+      <c r="F29" t="s">
+        <v>22</v>
+      </c>
+      <c r="G29">
+        <v>175</v>
+      </c>
+      <c r="H29" t="s">
+        <v>666</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>667</v>
+      </c>
+      <c r="J29" s="1">
+        <v>2272504</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="I31" s="1"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" s="1"/>
+      <c r="B32" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="H32" s="16"/>
+      <c r="I32" s="16"/>
+      <c r="J32" s="16"/>
+      <c r="K32" s="16"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" s="1"/>
+      <c r="B33" t="s">
+        <v>181</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D33" t="s">
+        <v>183</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F33" t="s">
+        <v>11</v>
+      </c>
+      <c r="G33" t="s">
+        <v>181</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="I33" t="s">
+        <v>189</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K33" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>1000</v>
+      </c>
+      <c r="B34" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="D34" t="s">
+        <v>633</v>
+      </c>
+      <c r="E34" t="s">
+        <v>630</v>
+      </c>
+      <c r="F34" t="s">
+        <v>631</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H34">
+        <v>228</v>
+      </c>
+      <c r="I34" s="1">
+        <v>87</v>
+      </c>
+      <c r="J34" s="5" t="s">
+        <v>634</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>635</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="G14:K14"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="G32:K32"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6173260-4FF4-456C-873A-56DC08848DD8}">
+  <dimension ref="A1:L53"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.85546875" customWidth="1"/>
+    <col min="2" max="2" width="17.28515625" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" customWidth="1"/>
+    <col min="4" max="4" width="17.140625" customWidth="1"/>
+    <col min="5" max="5" width="17.85546875" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" customWidth="1"/>
+    <col min="7" max="7" width="28.28515625" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" customWidth="1"/>
+    <col min="9" max="9" width="16.5703125" customWidth="1"/>
+    <col min="10" max="10" width="16.140625" customWidth="1"/>
+    <col min="11" max="11" width="29.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="G1" s="6" t="s">
+        <v>642</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>643</v>
+      </c>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4" t="s">
+        <v>12</v>
+      </c>
+      <c r="L4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>1000</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5" t="s">
+        <v>651</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5">
+        <v>289</v>
+      </c>
+      <c r="H5" t="s">
+        <v>644</v>
+      </c>
+      <c r="I5" t="s">
+        <v>645</v>
+      </c>
+      <c r="J5" s="1">
+        <v>260046</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>1000</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7" t="s">
+        <v>650</v>
+      </c>
+      <c r="F7" t="s">
+        <v>646</v>
+      </c>
+      <c r="G7">
+        <v>175</v>
+      </c>
+      <c r="H7" t="s">
+        <v>611</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>647</v>
+      </c>
+      <c r="J7" s="1">
+        <v>115333</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>1000</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9" t="s">
+        <v>648</v>
+      </c>
+      <c r="F9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G9">
+        <v>175</v>
+      </c>
+      <c r="H9" s="1">
+        <v>5567</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>649</v>
+      </c>
+      <c r="J9" s="1">
+        <v>114561</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>1000</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+      <c r="E11" t="s">
+        <v>652</v>
+      </c>
+      <c r="F11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11">
+        <v>175</v>
+      </c>
+      <c r="H11" t="s">
+        <v>653</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="J11" s="1">
+        <v>106243</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="I13" s="1"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="16"/>
+      <c r="K14" s="16"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="1"/>
+      <c r="B15" t="s">
+        <v>181</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D15" t="s">
+        <v>183</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15" t="s">
+        <v>181</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="I15" t="s">
+        <v>189</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K15" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>1000</v>
+      </c>
+      <c r="B16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="1">
+        <v>289</v>
+      </c>
+      <c r="D16">
+        <v>98</v>
+      </c>
+      <c r="E16" t="s">
+        <v>645</v>
+      </c>
+      <c r="F16" s="1">
+        <v>260046</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H16">
+        <v>119</v>
+      </c>
+      <c r="I16" s="1">
+        <v>41</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="G19" s="6" t="s">
+        <v>655</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>643</v>
+      </c>
+      <c r="I19" s="1"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="I20" s="1"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="I21" s="1"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" t="s">
+        <v>1</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H22" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" t="s">
+        <v>10</v>
+      </c>
+      <c r="J22" t="s">
+        <v>11</v>
+      </c>
+      <c r="K22" t="s">
+        <v>12</v>
+      </c>
+      <c r="L22" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>1000</v>
+      </c>
+      <c r="D23">
+        <v>2</v>
+      </c>
+      <c r="E23" s="1">
+        <v>3731</v>
+      </c>
+      <c r="F23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G23">
+        <v>298</v>
+      </c>
+      <c r="H23" t="s">
+        <v>656</v>
+      </c>
+      <c r="I23" t="s">
+        <v>657</v>
+      </c>
+      <c r="J23" s="1">
+        <v>293794</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>1000</v>
+      </c>
+      <c r="D25">
+        <v>2</v>
+      </c>
+      <c r="E25" s="1">
+        <v>3257</v>
+      </c>
+      <c r="F25" t="s">
+        <v>646</v>
+      </c>
+      <c r="G25">
+        <v>175</v>
+      </c>
+      <c r="H25" t="s">
+        <v>615</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="J25" s="1">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>1000</v>
+      </c>
+      <c r="D27">
+        <v>2</v>
+      </c>
+      <c r="E27" s="1">
+        <v>3340</v>
+      </c>
+      <c r="F27" t="s">
+        <v>44</v>
+      </c>
+      <c r="G27">
+        <v>175</v>
+      </c>
+      <c r="H27" s="1">
+        <v>9391</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>658</v>
+      </c>
+      <c r="J27" s="1">
+        <v>94393</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>1000</v>
+      </c>
+      <c r="D29">
+        <v>2</v>
+      </c>
+      <c r="E29" s="1">
+        <v>2788</v>
+      </c>
+      <c r="F29" t="s">
+        <v>22</v>
+      </c>
+      <c r="G29">
+        <v>175</v>
+      </c>
+      <c r="H29" t="s">
+        <v>659</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>660</v>
+      </c>
+      <c r="J29" s="1">
+        <v>93149</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="I31" s="1"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" s="1"/>
+      <c r="B32" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="H32" s="16"/>
+      <c r="I32" s="16"/>
+      <c r="J32" s="16"/>
+      <c r="K32" s="16"/>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" s="1"/>
+      <c r="B33" t="s">
+        <v>181</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D33" t="s">
+        <v>183</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F33" t="s">
+        <v>11</v>
+      </c>
+      <c r="G33" t="s">
+        <v>181</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="I33" t="s">
+        <v>189</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K33" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>1000</v>
+      </c>
+      <c r="B34" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34" s="1">
+        <v>298</v>
+      </c>
+      <c r="D34">
+        <v>99</v>
+      </c>
+      <c r="E34" t="s">
+        <v>657</v>
+      </c>
+      <c r="F34" s="1">
+        <v>293794</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H34" s="1">
+        <v>117</v>
+      </c>
+      <c r="I34" s="1">
+        <v>40</v>
+      </c>
+      <c r="J34" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="K34" s="1">
+        <v>64412</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="G38" s="6" t="s">
+        <v>668</v>
+      </c>
+      <c r="H38" s="8" t="s">
+        <v>643</v>
+      </c>
+      <c r="I38" s="1"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="I39" s="1"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="I40" s="1"/>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" t="s">
+        <v>7</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" t="s">
+        <v>9</v>
+      </c>
+      <c r="F41" t="s">
+        <v>1</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H41" t="s">
+        <v>3</v>
+      </c>
+      <c r="I41" t="s">
+        <v>10</v>
+      </c>
+      <c r="J41" t="s">
+        <v>11</v>
+      </c>
+      <c r="K41" t="s">
+        <v>12</v>
+      </c>
+      <c r="L41" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>1000</v>
+      </c>
+      <c r="D42">
+        <v>2</v>
+      </c>
+      <c r="E42" s="1">
+        <v>3338</v>
+      </c>
+      <c r="F42" t="s">
+        <v>14</v>
+      </c>
+      <c r="G42">
+        <v>308</v>
+      </c>
+      <c r="H42" t="s">
+        <v>656</v>
+      </c>
+      <c r="I42" t="s">
+        <v>669</v>
+      </c>
+      <c r="J42" s="1">
+        <v>330257</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>1000</v>
+      </c>
+      <c r="D44">
+        <v>2</v>
+      </c>
+      <c r="E44" s="1">
+        <v>3191</v>
+      </c>
+      <c r="F44" t="s">
+        <v>646</v>
+      </c>
+      <c r="G44">
+        <v>175</v>
+      </c>
+      <c r="H44" t="s">
+        <v>671</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="J44" s="1">
+        <v>166315</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>1000</v>
+      </c>
+      <c r="D46">
+        <v>2</v>
+      </c>
+      <c r="E46" s="1">
+        <v>3072</v>
+      </c>
+      <c r="F46" t="s">
+        <v>44</v>
+      </c>
+      <c r="G46">
+        <v>175</v>
+      </c>
+      <c r="H46" s="1">
+        <v>7785</v>
+      </c>
+      <c r="I46" s="5" t="s">
+        <v>672</v>
+      </c>
+      <c r="J46" s="1">
+        <v>156930</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>1000</v>
+      </c>
+      <c r="D48">
+        <v>2</v>
+      </c>
+      <c r="E48" s="1">
+        <v>3441</v>
+      </c>
+      <c r="F48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G48">
+        <v>175</v>
+      </c>
+      <c r="H48" t="s">
+        <v>659</v>
+      </c>
+      <c r="I48" s="5" t="s">
+        <v>481</v>
+      </c>
+      <c r="J48" s="1">
+        <v>159887</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="I50" s="1"/>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A51" s="1"/>
+      <c r="B51" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="C51" s="15"/>
+      <c r="D51" s="15"/>
+      <c r="E51" s="15"/>
+      <c r="F51" s="15"/>
+      <c r="G51" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="H51" s="16"/>
+      <c r="I51" s="16"/>
+      <c r="J51" s="16"/>
+      <c r="K51" s="16"/>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A52" s="1"/>
+      <c r="B52" t="s">
+        <v>181</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D52" t="s">
+        <v>183</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F52" t="s">
+        <v>11</v>
+      </c>
+      <c r="G52" t="s">
+        <v>181</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="I52" t="s">
+        <v>189</v>
+      </c>
+      <c r="J52" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K52" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
+        <v>1000</v>
+      </c>
+      <c r="B53" t="s">
+        <v>14</v>
+      </c>
+      <c r="C53" s="1">
+        <v>308</v>
+      </c>
+      <c r="D53">
+        <v>82</v>
+      </c>
+      <c r="E53" t="s">
+        <v>669</v>
+      </c>
+      <c r="F53" s="1">
+        <v>330257</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H53" s="1">
+        <v>118</v>
+      </c>
+      <c r="I53" s="1">
+        <v>34</v>
+      </c>
+      <c r="J53" s="5" t="s">
+        <v>670</v>
+      </c>
+      <c r="K53" s="1">
+        <v>70164</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="G14:K14"/>
+    <mergeCell ref="G32:K32"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B51:F51"/>
+    <mergeCell ref="G51:K51"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A52165C-8103-45CF-858B-152B066FCF0E}">
+  <dimension ref="A1:L34"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.7109375" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" customWidth="1"/>
+    <col min="3" max="3" width="15.28515625" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" customWidth="1"/>
+    <col min="6" max="6" width="16.85546875" customWidth="1"/>
+    <col min="7" max="7" width="27" customWidth="1"/>
+    <col min="8" max="8" width="18.28515625" customWidth="1"/>
+    <col min="9" max="9" width="16.85546875" customWidth="1"/>
+    <col min="10" max="10" width="15.5703125" customWidth="1"/>
+    <col min="11" max="11" width="28.42578125" customWidth="1"/>
+    <col min="12" max="12" width="55" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="G1" s="6" t="s">
+        <v>681</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>643</v>
+      </c>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4" t="s">
+        <v>12</v>
+      </c>
+      <c r="L4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>1000</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5" s="1">
+        <v>3417</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5">
+        <v>285</v>
+      </c>
+      <c r="H5" t="s">
+        <v>640</v>
+      </c>
+      <c r="I5" t="s">
+        <v>673</v>
+      </c>
+      <c r="J5" s="1">
+        <v>315829</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>1000</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7" s="1">
+        <v>3455</v>
+      </c>
+      <c r="F7" t="s">
+        <v>646</v>
+      </c>
+      <c r="G7">
+        <v>175</v>
+      </c>
+      <c r="H7" t="s">
+        <v>674</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>529</v>
+      </c>
+      <c r="J7" s="1">
+        <v>147585</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>1000</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9" s="1">
+        <v>3270</v>
+      </c>
+      <c r="F9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G9">
+        <v>175</v>
+      </c>
+      <c r="H9" s="1">
+        <v>6347</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J9" s="1">
+        <v>156651</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>1000</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+      <c r="E11" s="1">
+        <v>3844</v>
+      </c>
+      <c r="F11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11">
+        <v>175</v>
+      </c>
+      <c r="H11" t="s">
+        <v>675</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>676</v>
+      </c>
+      <c r="J11" s="1">
+        <v>162778</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="I13" s="1"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="16"/>
+      <c r="K14" s="16"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="1"/>
+      <c r="B15" t="s">
+        <v>181</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D15" t="s">
+        <v>183</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15" t="s">
+        <v>181</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="I15" t="s">
+        <v>189</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K15" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>1000</v>
+      </c>
+      <c r="B16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="1">
+        <v>285</v>
+      </c>
+      <c r="D16">
+        <v>107</v>
+      </c>
+      <c r="E16" t="s">
+        <v>673</v>
+      </c>
+      <c r="F16" s="1">
+        <v>315829</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H16" s="1">
+        <v>121</v>
+      </c>
+      <c r="I16" s="1">
+        <v>42</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>517</v>
+      </c>
+      <c r="K16" s="1">
+        <v>62360</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="G19" s="6" t="s">
+        <v>682</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>643</v>
+      </c>
+      <c r="I19" s="1"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="I20" s="1"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="I21" s="1"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" t="s">
+        <v>1</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H22" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" t="s">
+        <v>10</v>
+      </c>
+      <c r="J22" t="s">
+        <v>11</v>
+      </c>
+      <c r="K22" t="s">
+        <v>12</v>
+      </c>
+      <c r="L22" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>1000</v>
+      </c>
+      <c r="D23">
+        <v>2</v>
+      </c>
+      <c r="E23" s="1">
+        <v>3351</v>
+      </c>
+      <c r="F23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G23">
+        <v>303</v>
+      </c>
+      <c r="H23" t="s">
+        <v>678</v>
+      </c>
+      <c r="I23" t="s">
+        <v>679</v>
+      </c>
+      <c r="J23" s="1">
+        <v>334613</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>1000</v>
+      </c>
+      <c r="D25">
+        <v>2</v>
+      </c>
+      <c r="E25" s="1">
+        <v>3734</v>
+      </c>
+      <c r="F25" t="s">
+        <v>646</v>
+      </c>
+      <c r="G25">
+        <v>175</v>
+      </c>
+      <c r="H25" t="s">
+        <v>677</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="J25" s="1">
+        <v>164001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>1000</v>
+      </c>
+      <c r="D27">
+        <v>2</v>
+      </c>
+      <c r="E27" s="1">
+        <v>3192</v>
+      </c>
+      <c r="F27" t="s">
+        <v>44</v>
+      </c>
+      <c r="G27">
+        <v>175</v>
+      </c>
+      <c r="H27" s="1">
+        <v>6865</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>457</v>
+      </c>
+      <c r="J27" s="1">
+        <v>109385</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>1000</v>
+      </c>
+      <c r="D29">
+        <v>2</v>
+      </c>
+      <c r="E29" s="1">
+        <v>3722</v>
+      </c>
+      <c r="F29" t="s">
+        <v>22</v>
+      </c>
+      <c r="G29">
+        <v>175</v>
+      </c>
+      <c r="H29" t="s">
+        <v>683</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>684</v>
+      </c>
+      <c r="J29" s="1">
+        <v>92632</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="I31" s="1"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" s="1"/>
+      <c r="B32" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="H32" s="16"/>
+      <c r="I32" s="16"/>
+      <c r="J32" s="16"/>
+      <c r="K32" s="16"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" s="1"/>
+      <c r="B33" t="s">
+        <v>181</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D33" t="s">
+        <v>183</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F33" t="s">
+        <v>11</v>
+      </c>
+      <c r="G33" t="s">
+        <v>181</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="I33" t="s">
+        <v>189</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K33" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>1000</v>
+      </c>
+      <c r="B34" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34" s="1">
+        <v>303</v>
+      </c>
+      <c r="D34">
+        <v>71</v>
+      </c>
+      <c r="E34" t="s">
+        <v>679</v>
+      </c>
+      <c r="F34" s="1">
+        <v>334613</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H34" s="1">
+        <v>118</v>
+      </c>
+      <c r="I34" s="1">
+        <v>34</v>
+      </c>
+      <c r="J34" s="5" t="s">
+        <v>680</v>
+      </c>
+      <c r="K34" s="1">
+        <v>62142</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="G14:K14"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="G32:K32"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="20.81640625" customWidth="1"/>
-    <col min="4" max="4" width="15.1796875" customWidth="1"/>
-    <col min="5" max="5" width="14.08984375" customWidth="1"/>
-    <col min="6" max="6" width="12.1796875" customWidth="1"/>
+    <col min="1" max="3" width="20.85546875" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" customWidth="1"/>
+    <col min="6" max="6" width="12.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>556</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>561</v>
       </c>
@@ -7667,7 +10977,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>949647</v>
       </c>
@@ -7687,7 +10997,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>949647</v>
       </c>
@@ -7707,7 +11017,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>949647</v>
       </c>
@@ -7727,7 +11037,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>949647</v>
       </c>
@@ -7753,24 +11063,24 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:L15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.36328125" customWidth="1"/>
-    <col min="2" max="2" width="15.6328125" customWidth="1"/>
+    <col min="1" max="1" width="10.42578125" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="11.54296875" customWidth="1"/>
-    <col min="5" max="5" width="14.453125" customWidth="1"/>
-    <col min="6" max="6" width="16.08984375" customWidth="1"/>
-    <col min="7" max="8" width="17.08984375" customWidth="1"/>
-    <col min="9" max="9" width="13.1796875" customWidth="1"/>
-    <col min="10" max="10" width="15.90625" customWidth="1"/>
-    <col min="11" max="11" width="27.453125" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" customWidth="1"/>
+    <col min="7" max="8" width="17.140625" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" customWidth="1"/>
+    <col min="10" max="10" width="15.85546875" customWidth="1"/>
+    <col min="11" max="11" width="27.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="C1" s="1"/>
       <c r="E1" s="1"/>
@@ -7779,21 +11089,21 @@
       </c>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="C2" s="1"/>
       <c r="E2" s="1"/>
       <c r="G2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="C3" s="1"/>
       <c r="E3" s="1"/>
       <c r="G3" s="1"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -7831,7 +11141,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1000</v>
       </c>
@@ -7857,7 +11167,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>1000</v>
       </c>
@@ -7883,7 +11193,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>1000</v>
       </c>
@@ -7909,7 +11219,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>1000</v>
       </c>
@@ -7935,13 +11245,13 @@
         <v>220</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B12" s="1"/>
       <c r="D12" s="1"/>
       <c r="F12" s="1"/>
       <c r="H12" s="1"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
         <v>180</v>
       </c>
@@ -7957,7 +11267,7 @@
       <c r="I13" s="16"/>
       <c r="J13" s="16"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>181</v>
       </c>
@@ -7989,7 +11299,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -8027,29 +11337,30 @@
     <mergeCell ref="F13:J13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:L26"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.453125" customWidth="1"/>
+    <col min="1" max="1" width="13.42578125" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="12.453125" customWidth="1"/>
-    <col min="4" max="4" width="12.81640625" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="6" max="6" width="15.6328125" customWidth="1"/>
-    <col min="7" max="7" width="15.08984375" customWidth="1"/>
-    <col min="8" max="8" width="17.36328125" customWidth="1"/>
-    <col min="9" max="9" width="16.81640625" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" customWidth="1"/>
+    <col min="9" max="9" width="16.85546875" customWidth="1"/>
     <col min="10" max="10" width="15" customWidth="1"/>
-    <col min="11" max="11" width="29.1796875" customWidth="1"/>
+    <col min="11" max="11" width="29.140625" customWidth="1"/>
     <col min="12" max="12" width="79" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="C1" s="1"/>
       <c r="E1" s="1"/>
@@ -8058,21 +11369,21 @@
       </c>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="C2" s="1"/>
       <c r="E2" s="1"/>
       <c r="G2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="C3" s="1"/>
       <c r="E3" s="1"/>
       <c r="G3" s="1"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -8110,7 +11421,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1000</v>
       </c>
@@ -8136,7 +11447,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>1000</v>
       </c>
@@ -8162,7 +11473,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>1000</v>
       </c>
@@ -8188,7 +11499,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>1000</v>
       </c>
@@ -8214,13 +11525,13 @@
         <v>254</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B12" s="1"/>
       <c r="D12" s="1"/>
       <c r="F12" s="1"/>
       <c r="H12" s="1"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="7">
         <v>1000</v>
       </c>
@@ -8244,7 +11555,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>1000</v>
       </c>
@@ -8264,7 +11575,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>1000</v>
       </c>
@@ -8284,7 +11595,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>1000</v>
       </c>
@@ -8304,7 +11615,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="15" t="s">
         <v>180</v>
       </c>
@@ -8320,7 +11631,7 @@
       <c r="I23" s="16"/>
       <c r="J23" s="16"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>181</v>
       </c>
@@ -8352,7 +11663,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>14</v>
       </c>
@@ -8384,7 +11695,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>14</v>
       </c>
@@ -8409,1187 +11720,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:L31"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="15.1796875" customWidth="1"/>
-    <col min="2" max="2" width="13.90625" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="5" width="14.1796875" customWidth="1"/>
-    <col min="6" max="6" width="14.453125" customWidth="1"/>
-    <col min="7" max="7" width="13.6328125" customWidth="1"/>
-    <col min="8" max="8" width="14.1796875" customWidth="1"/>
-    <col min="9" max="9" width="13.453125" customWidth="1"/>
-    <col min="10" max="10" width="15.81640625" customWidth="1"/>
-    <col min="11" max="11" width="30.90625" customWidth="1"/>
-    <col min="12" max="12" width="75.54296875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="G1" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="I1" s="1"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="I2" s="1"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="I3" s="1"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>1</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H4" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4" t="s">
-        <v>10</v>
-      </c>
-      <c r="J4" t="s">
-        <v>11</v>
-      </c>
-      <c r="K4" t="s">
-        <v>12</v>
-      </c>
-      <c r="L4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A5">
-        <v>1000</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5" t="s">
-        <v>259</v>
-      </c>
-      <c r="F5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5">
-        <v>286</v>
-      </c>
-      <c r="H5" t="s">
-        <v>593</v>
-      </c>
-      <c r="I5" t="s">
-        <v>594</v>
-      </c>
-      <c r="J5" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A7">
-        <v>1000</v>
-      </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-      <c r="E7" t="s">
-        <v>260</v>
-      </c>
-      <c r="F7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G7">
-        <v>175</v>
-      </c>
-      <c r="H7" t="s">
-        <v>261</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="J7" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A9">
-        <v>1000</v>
-      </c>
-      <c r="D9">
-        <v>2</v>
-      </c>
-      <c r="E9" t="s">
-        <v>264</v>
-      </c>
-      <c r="F9" t="s">
-        <v>44</v>
-      </c>
-      <c r="G9">
-        <v>175</v>
-      </c>
-      <c r="H9" t="s">
-        <v>265</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="J9" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A11">
-        <v>1000</v>
-      </c>
-      <c r="D11">
-        <v>2</v>
-      </c>
-      <c r="E11" t="s">
-        <v>267</v>
-      </c>
-      <c r="F11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G11">
-        <v>175</v>
-      </c>
-      <c r="H11" t="s">
-        <v>268</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="J11" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="B12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="H12" s="1"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A13" s="12">
-        <v>1000</v>
-      </c>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G13" s="12">
-        <v>217</v>
-      </c>
-      <c r="H13" s="12" t="s">
-        <v>347</v>
-      </c>
-      <c r="I13" s="14" t="s">
-        <v>351</v>
-      </c>
-      <c r="J13" s="12" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A15">
-        <v>1000</v>
-      </c>
-      <c r="F15" t="s">
-        <v>33</v>
-      </c>
-      <c r="G15">
-        <v>175</v>
-      </c>
-      <c r="H15" t="s">
-        <v>348</v>
-      </c>
-      <c r="I15" s="5" t="s">
-        <v>349</v>
-      </c>
-      <c r="J15" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A17">
-        <v>1000</v>
-      </c>
-      <c r="F17" t="s">
-        <v>44</v>
-      </c>
-      <c r="G17">
-        <v>175</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="I17" s="5" t="s">
-        <v>355</v>
-      </c>
-      <c r="J17" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A19">
-        <v>1000</v>
-      </c>
-      <c r="F19" t="s">
-        <v>22</v>
-      </c>
-      <c r="G19">
-        <v>175</v>
-      </c>
-      <c r="H19" t="s">
-        <v>358</v>
-      </c>
-      <c r="I19" s="5" t="s">
-        <v>359</v>
-      </c>
-      <c r="J19" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A28" s="15" t="s">
-        <v>180</v>
-      </c>
-      <c r="B28" s="15"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="16" t="s">
-        <v>184</v>
-      </c>
-      <c r="G28" s="16"/>
-      <c r="H28" s="16"/>
-      <c r="I28" s="16"/>
-      <c r="J28" s="16"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>181</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="C29" t="s">
-        <v>183</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E29" t="s">
-        <v>11</v>
-      </c>
-      <c r="F29" t="s">
-        <v>181</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="H29" t="s">
-        <v>189</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="J29" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>14</v>
-      </c>
-      <c r="B30" s="1">
-        <v>286</v>
-      </c>
-      <c r="C30">
-        <v>88</v>
-      </c>
-      <c r="D30" t="s">
-        <v>257</v>
-      </c>
-      <c r="E30" t="s">
-        <v>258</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G30">
-        <v>104</v>
-      </c>
-      <c r="H30" s="1">
-        <v>28</v>
-      </c>
-      <c r="I30" s="5" t="s">
-        <v>596</v>
-      </c>
-      <c r="J30" s="1" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>14</v>
-      </c>
-      <c r="B31">
-        <v>217</v>
-      </c>
-      <c r="C31">
-        <v>266</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>351</v>
-      </c>
-      <c r="E31" t="s">
-        <v>352</v>
-      </c>
-      <c r="F31" t="s">
-        <v>14</v>
-      </c>
-      <c r="G31">
-        <v>122</v>
-      </c>
-      <c r="H31">
-        <v>77</v>
-      </c>
-      <c r="I31" s="5" t="s">
-        <v>353</v>
-      </c>
-      <c r="J31" t="s">
-        <v>354</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="F28:J28"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:L28"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="12.90625" customWidth="1"/>
-    <col min="2" max="2" width="13.81640625" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="13.54296875" customWidth="1"/>
-    <col min="5" max="5" width="12.54296875" customWidth="1"/>
-    <col min="6" max="6" width="14.36328125" customWidth="1"/>
-    <col min="7" max="7" width="17.54296875" customWidth="1"/>
-    <col min="8" max="8" width="15.36328125" customWidth="1"/>
-    <col min="9" max="9" width="14.54296875" customWidth="1"/>
-    <col min="10" max="10" width="14.453125" customWidth="1"/>
-    <col min="11" max="11" width="31.08984375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="G1" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="I1" s="1"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="I2" s="1"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="I3" s="1"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>1</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H4" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4" t="s">
-        <v>10</v>
-      </c>
-      <c r="J4" t="s">
-        <v>11</v>
-      </c>
-      <c r="K4" t="s">
-        <v>12</v>
-      </c>
-      <c r="L4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A5">
-        <v>1000</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5" t="s">
-        <v>272</v>
-      </c>
-      <c r="F5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5">
-        <v>273</v>
-      </c>
-      <c r="H5" t="s">
-        <v>421</v>
-      </c>
-      <c r="I5" t="s">
-        <v>598</v>
-      </c>
-      <c r="J5" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A7">
-        <v>1000</v>
-      </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-      <c r="E7" t="s">
-        <v>273</v>
-      </c>
-      <c r="F7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G7">
-        <v>175</v>
-      </c>
-      <c r="H7" t="s">
-        <v>274</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="J7" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A9">
-        <v>1000</v>
-      </c>
-      <c r="D9">
-        <v>2</v>
-      </c>
-      <c r="E9" t="s">
-        <v>277</v>
-      </c>
-      <c r="F9" t="s">
-        <v>44</v>
-      </c>
-      <c r="G9">
-        <v>175</v>
-      </c>
-      <c r="H9" t="s">
-        <v>278</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="J9" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A11">
-        <v>1000</v>
-      </c>
-      <c r="D11">
-        <v>2</v>
-      </c>
-      <c r="E11" t="s">
-        <v>281</v>
-      </c>
-      <c r="F11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G11">
-        <v>175</v>
-      </c>
-      <c r="H11" t="s">
-        <v>218</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="J11" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="B12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="H12" s="1"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A13" s="12" t="s">
-        <v>618</v>
-      </c>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G13" s="12">
-        <v>228</v>
-      </c>
-      <c r="H13" s="12" t="s">
-        <v>333</v>
-      </c>
-      <c r="I13" s="14" t="s">
-        <v>334</v>
-      </c>
-      <c r="J13" s="12" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A15">
-        <v>1000</v>
-      </c>
-      <c r="F15" t="s">
-        <v>33</v>
-      </c>
-      <c r="G15">
-        <v>175</v>
-      </c>
-      <c r="H15" t="s">
-        <v>338</v>
-      </c>
-      <c r="I15" s="5" t="s">
-        <v>339</v>
-      </c>
-      <c r="J15" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A17">
-        <v>1000</v>
-      </c>
-      <c r="F17" t="s">
-        <v>44</v>
-      </c>
-      <c r="G17">
-        <v>175</v>
-      </c>
-      <c r="H17" t="s">
-        <v>341</v>
-      </c>
-      <c r="I17" s="5" t="s">
-        <v>343</v>
-      </c>
-      <c r="J17" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A19">
-        <v>1000</v>
-      </c>
-      <c r="F19" t="s">
-        <v>22</v>
-      </c>
-      <c r="G19">
-        <v>175</v>
-      </c>
-      <c r="H19" t="s">
-        <v>342</v>
-      </c>
-      <c r="I19" s="5" t="s">
-        <v>345</v>
-      </c>
-      <c r="J19" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A25" s="15" t="s">
-        <v>180</v>
-      </c>
-      <c r="B25" s="15"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="16" t="s">
-        <v>184</v>
-      </c>
-      <c r="G25" s="16"/>
-      <c r="H25" s="16"/>
-      <c r="I25" s="16"/>
-      <c r="J25" s="16"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>181</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="C26" t="s">
-        <v>183</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E26" t="s">
-        <v>11</v>
-      </c>
-      <c r="F26" t="s">
-        <v>181</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="H26" t="s">
-        <v>189</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="J26" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>14</v>
-      </c>
-      <c r="B27" s="1">
-        <v>273</v>
-      </c>
-      <c r="C27">
-        <v>66</v>
-      </c>
-      <c r="D27" t="s">
-        <v>598</v>
-      </c>
-      <c r="E27" t="s">
-        <v>599</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G27">
-        <v>118</v>
-      </c>
-      <c r="H27" s="1">
-        <v>41</v>
-      </c>
-      <c r="I27" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>14</v>
-      </c>
-      <c r="B28">
-        <v>228</v>
-      </c>
-      <c r="C28">
-        <v>285</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>334</v>
-      </c>
-      <c r="E28" t="s">
-        <v>335</v>
-      </c>
-      <c r="F28" t="s">
-        <v>14</v>
-      </c>
-      <c r="G28">
-        <v>124</v>
-      </c>
-      <c r="H28">
-        <v>79</v>
-      </c>
-      <c r="I28" s="5" t="s">
-        <v>336</v>
-      </c>
-      <c r="J28" t="s">
-        <v>337</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="F25:J25"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:L28"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="14.90625" customWidth="1"/>
-    <col min="2" max="2" width="14.453125" customWidth="1"/>
-    <col min="3" max="3" width="13.453125" customWidth="1"/>
-    <col min="4" max="4" width="13.1796875" customWidth="1"/>
-    <col min="5" max="5" width="16.08984375" customWidth="1"/>
-    <col min="6" max="6" width="17.08984375" customWidth="1"/>
-    <col min="7" max="7" width="17.54296875" customWidth="1"/>
-    <col min="8" max="8" width="16.54296875" customWidth="1"/>
-    <col min="9" max="9" width="16.81640625" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="27.6328125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="G1" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="I1" s="1"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="I2" s="1"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="I3" s="1"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>1</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H4" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4" t="s">
-        <v>10</v>
-      </c>
-      <c r="J4" t="s">
-        <v>11</v>
-      </c>
-      <c r="K4" t="s">
-        <v>12</v>
-      </c>
-      <c r="L4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A5">
-        <v>1000</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5" t="s">
-        <v>284</v>
-      </c>
-      <c r="F5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5">
-        <v>287</v>
-      </c>
-      <c r="H5" t="s">
-        <v>601</v>
-      </c>
-      <c r="I5" t="s">
-        <v>602</v>
-      </c>
-      <c r="J5" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A7">
-        <v>1000</v>
-      </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-      <c r="E7" t="s">
-        <v>286</v>
-      </c>
-      <c r="F7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G7">
-        <v>175</v>
-      </c>
-      <c r="H7" t="s">
-        <v>287</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="J7" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A9">
-        <v>1000</v>
-      </c>
-      <c r="D9">
-        <v>2</v>
-      </c>
-      <c r="E9" t="s">
-        <v>290</v>
-      </c>
-      <c r="F9" t="s">
-        <v>44</v>
-      </c>
-      <c r="G9">
-        <v>175</v>
-      </c>
-      <c r="H9" t="s">
-        <v>291</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="J9" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A11">
-        <v>1000</v>
-      </c>
-      <c r="D11">
-        <v>2</v>
-      </c>
-      <c r="E11" t="s">
-        <v>293</v>
-      </c>
-      <c r="F11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G11">
-        <v>175</v>
-      </c>
-      <c r="H11" t="s">
-        <v>218</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="J11" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="B12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="H12" s="1"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A13" s="12">
-        <v>1000</v>
-      </c>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G13" s="12">
-        <v>240</v>
-      </c>
-      <c r="H13" s="12" t="s">
-        <v>319</v>
-      </c>
-      <c r="I13" s="14" t="s">
-        <v>321</v>
-      </c>
-      <c r="J13" s="13" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A15">
-        <v>1000</v>
-      </c>
-      <c r="F15" t="s">
-        <v>33</v>
-      </c>
-      <c r="G15">
-        <v>175</v>
-      </c>
-      <c r="H15" t="s">
-        <v>320</v>
-      </c>
-      <c r="I15" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="J15" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A17">
-        <v>1000</v>
-      </c>
-      <c r="F17" t="s">
-        <v>44</v>
-      </c>
-      <c r="G17">
-        <v>175</v>
-      </c>
-      <c r="H17" t="s">
-        <v>327</v>
-      </c>
-      <c r="I17" s="5" t="s">
-        <v>328</v>
-      </c>
-      <c r="J17" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A19">
-        <v>1000</v>
-      </c>
-      <c r="F19" t="s">
-        <v>22</v>
-      </c>
-      <c r="G19">
-        <v>175</v>
-      </c>
-      <c r="H19" t="s">
-        <v>330</v>
-      </c>
-      <c r="I19" s="5" t="s">
-        <v>331</v>
-      </c>
-      <c r="J19" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A25" s="15" t="s">
-        <v>180</v>
-      </c>
-      <c r="B25" s="15"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="16" t="s">
-        <v>184</v>
-      </c>
-      <c r="G25" s="16"/>
-      <c r="H25" s="16"/>
-      <c r="I25" s="16"/>
-      <c r="J25" s="16"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>181</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="C26" t="s">
-        <v>183</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E26" t="s">
-        <v>11</v>
-      </c>
-      <c r="F26" t="s">
-        <v>181</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="H26" t="s">
-        <v>189</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="J26" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>14</v>
-      </c>
-      <c r="B27" s="1">
-        <v>287</v>
-      </c>
-      <c r="C27">
-        <v>78</v>
-      </c>
-      <c r="D27" t="s">
-        <v>602</v>
-      </c>
-      <c r="E27" t="s">
-        <v>603</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G27">
-        <v>118</v>
-      </c>
-      <c r="H27" s="1">
-        <v>36</v>
-      </c>
-      <c r="I27" s="5" t="s">
-        <v>604</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>14</v>
-      </c>
-      <c r="B28">
-        <v>240</v>
-      </c>
-      <c r="C28">
-        <v>252</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>321</v>
-      </c>
-      <c r="E28" s="1">
-        <v>246380</v>
-      </c>
-      <c r="F28" t="s">
-        <v>14</v>
-      </c>
-      <c r="G28">
-        <v>136</v>
-      </c>
-      <c r="H28">
-        <v>84</v>
-      </c>
-      <c r="I28" s="5" t="s">
-        <v>322</v>
-      </c>
-      <c r="J28" t="s">
-        <v>323</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="F25:J25"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Experiments/DBCV_Conclu.xlsx
+++ b/Experiments/DBCV_Conclu.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\das-sb\Downloads\thesis_documentation\Experiments\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\das-sb\Documents\GIT\thesis_documentation\Experiments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC3642A8-18F1-4EE1-94C4-02A228D635EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E3F1DEE-2E00-49F3-BE39-289374B59F83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1700" uniqueCount="685">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1742" uniqueCount="692">
   <si>
     <t>Datapoints</t>
   </si>
@@ -2097,6 +2097,27 @@
   </si>
   <si>
     <t>-0.001</t>
+  </si>
+  <si>
+    <t>lr=0.001, lr_decay=0.9</t>
+  </si>
+  <si>
+    <t>0.114</t>
+  </si>
+  <si>
+    <t>0.184</t>
+  </si>
+  <si>
+    <t>0.144</t>
+  </si>
+  <si>
+    <t>0.010</t>
+  </si>
+  <si>
+    <t>0.033</t>
+  </si>
+  <si>
+    <t>0.017</t>
   </si>
 </sst>
 </file>
@@ -10389,7 +10410,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A52165C-8103-45CF-858B-152B066FCF0E}">
-  <dimension ref="A1:L34"/>
+  <dimension ref="A1:L53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.7109375" customWidth="1"/>
@@ -10862,7 +10883,7 @@
       <c r="J32" s="16"/>
       <c r="K32" s="16"/>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="B33" t="s">
         <v>181</v>
@@ -10895,7 +10916,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>1000</v>
       </c>
@@ -10930,14 +10951,279 @@
         <v>62142</v>
       </c>
     </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="G38" s="6" t="s">
+        <v>685</v>
+      </c>
+      <c r="H38" s="8" t="s">
+        <v>643</v>
+      </c>
+      <c r="I38" s="1"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="I39" s="1"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="I40" s="1"/>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" t="s">
+        <v>7</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" t="s">
+        <v>9</v>
+      </c>
+      <c r="F41" t="s">
+        <v>1</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H41" t="s">
+        <v>3</v>
+      </c>
+      <c r="I41" t="s">
+        <v>10</v>
+      </c>
+      <c r="J41" t="s">
+        <v>11</v>
+      </c>
+      <c r="K41" t="s">
+        <v>12</v>
+      </c>
+      <c r="L41" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>1000</v>
+      </c>
+      <c r="D42">
+        <v>2</v>
+      </c>
+      <c r="E42" s="1">
+        <v>3265</v>
+      </c>
+      <c r="F42" t="s">
+        <v>14</v>
+      </c>
+      <c r="G42">
+        <v>287</v>
+      </c>
+      <c r="H42" t="s">
+        <v>686</v>
+      </c>
+      <c r="I42" t="s">
+        <v>687</v>
+      </c>
+      <c r="J42" s="1">
+        <v>225236</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>1000</v>
+      </c>
+      <c r="D44">
+        <v>2</v>
+      </c>
+      <c r="E44" s="1">
+        <v>3298</v>
+      </c>
+      <c r="F44" t="s">
+        <v>646</v>
+      </c>
+      <c r="G44">
+        <v>175</v>
+      </c>
+      <c r="H44" t="s">
+        <v>688</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>689</v>
+      </c>
+      <c r="J44" s="1">
+        <v>95764</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>1000</v>
+      </c>
+      <c r="D46">
+        <v>2</v>
+      </c>
+      <c r="E46" s="1">
+        <v>4107</v>
+      </c>
+      <c r="F46" t="s">
+        <v>44</v>
+      </c>
+      <c r="G46">
+        <v>175</v>
+      </c>
+      <c r="H46" s="1">
+        <v>14298</v>
+      </c>
+      <c r="I46" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="J46" s="1">
+        <v>116901</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>1000</v>
+      </c>
+      <c r="D48">
+        <v>2</v>
+      </c>
+      <c r="E48" s="1">
+        <v>3297</v>
+      </c>
+      <c r="F48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G48">
+        <v>175</v>
+      </c>
+      <c r="H48" t="s">
+        <v>690</v>
+      </c>
+      <c r="I48" s="5" t="s">
+        <v>691</v>
+      </c>
+      <c r="J48" s="1">
+        <v>96614</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="I50" s="1"/>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A51" s="1"/>
+      <c r="B51" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="C51" s="15"/>
+      <c r="D51" s="15"/>
+      <c r="E51" s="15"/>
+      <c r="F51" s="15"/>
+      <c r="G51" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="H51" s="16"/>
+      <c r="I51" s="16"/>
+      <c r="J51" s="16"/>
+      <c r="K51" s="16"/>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A52" s="1"/>
+      <c r="B52" t="s">
+        <v>181</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D52" t="s">
+        <v>183</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F52" t="s">
+        <v>11</v>
+      </c>
+      <c r="G52" t="s">
+        <v>181</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="I52" t="s">
+        <v>189</v>
+      </c>
+      <c r="J52" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K52" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
+        <v>1000</v>
+      </c>
+      <c r="B53" t="s">
+        <v>14</v>
+      </c>
+      <c r="C53">
+        <v>287</v>
+      </c>
+      <c r="D53">
+        <v>80</v>
+      </c>
+      <c r="E53" t="s">
+        <v>687</v>
+      </c>
+      <c r="F53" s="1">
+        <v>225236</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H53" s="1">
+        <v>120</v>
+      </c>
+      <c r="I53" s="1">
+        <v>46</v>
+      </c>
+      <c r="J53" s="5" t="s">
+        <v>596</v>
+      </c>
+      <c r="K53" s="1">
+        <v>56283</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="6">
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="G14:K14"/>
     <mergeCell ref="B32:F32"/>
     <mergeCell ref="G32:K32"/>
+    <mergeCell ref="B51:F51"/>
+    <mergeCell ref="G51:K51"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
